--- a/reportes/Reporte_abril_2026.xlsx
+++ b/reportes/Reporte_abril_2026.xlsx
@@ -11898,7 +11898,7 @@
     <row r="50" ht="52" customHeight="1">
       <c r="B50" s="73" t="inlineStr">
         <is>
-          <t>Seducete redujo gasto en 7.6% (de $5.5M a $5.1M) pero también bajó resultados en 14.1% (de 35,423 a 30,410), indicando ineficiencia en la optimización. La campaña de conversión web absorbe 86.6% del presupuesto con ROAS crítico de 0.46 promedio, requiriendo restructuración inmediata.</t>
+          <t>Seducete redujo gasto en 7.6% (CLP 419.421) en abril pero también bajó resultados 14.1% (5.013 menos conversiones). La caída más crítica está en campañas de conversión web, donde el ROAS promedio es 0.27, indicando pérdida de eficiencia en el funnel.</t>
         </is>
       </c>
     </row>
@@ -11912,34 +11912,34 @@
     <row r="53" ht="50" customHeight="1">
       <c r="B53" s="74" t="inlineStr">
         <is>
-          <t>✦ OPORTUNIDAD  Anuncio de Cursos Presenciales supera en eficiencia</t>
+          <t>✦ OPORTUNIDAD  Anuncio Cursos Presenciales con mejor CPC</t>
         </is>
       </c>
       <c r="F53" s="75" t="inlineStr">
         <is>
-          <t>El anuncio 'Tráfico Cursos Presenciales 03-07' logró costo de $47 por resultado vs $59 del otro anuncio, representando 20% menos inversión. Con CTR de 1.7% mantiene buena tracción incluso con volumen similar de 1,890 resultados.</t>
+          <t>El anuncio 'Tráfico Cursos Presenciales 03-07' generó 1.890 resultados con CPC de CLP 47, 20% más eficiente que 'Tráfico Instagram Academia' (CLP 59). Sin embargo, bajó 2.3% en resultados respecto a marzo (1.847 vs 1.890).</t>
         </is>
       </c>
       <c r="M53" s="76" t="inlineStr">
         <is>
-          <t>→ Acción: Aumentar presupuesto del anuncio de Cursos Presenciales en 30% esta semana, reduciendo proporcionalmente el anuncio de Academia Gratuita.</t>
+          <t>→ Acción: Aumentar presupuesto del anuncio de Cursos Presenciales a CLP 120.000 y reducir el de Academia a CLP 75.000 para marzo de eficiencia.</t>
         </is>
       </c>
     </row>
     <row r="54" ht="50" customHeight="1">
       <c r="B54" s="77" t="inlineStr">
         <is>
-          <t>⚠ ALERTA  Caída en resultados del anuncio principal</t>
+          <t>⚠ ALERTA  Caída en resultados de Academia Instagram</t>
         </is>
       </c>
       <c r="F54" s="75" t="inlineStr">
         <is>
-          <t>El anuncio 'Tráfico Instagram Academia Cursos Gratuitos' bajó de 1,546 a 1,775 resultados (15% aumento) pero con costo subido a $59, generando ineficiencia. El hold50 bajo de 5.8% sugiere contenido poco retentivo.</t>
+          <t>El anuncio 'Tráfico Instagram Academia Cursos Gratuitos' cayó 14.8% (1.775 vs 1.546 en marzo) con aumento de CPC de CLP 59. El hold50 de 5.8% sugiere abandono en video.</t>
         </is>
       </c>
       <c r="M54" s="76" t="inlineStr">
         <is>
-          <t>→ Acción: Testear 2 variantes de copy con hooks más fuertes enfocados en beneficio inmediato de cursos gratuitos esta semana.</t>
+          <t>→ Acción: Probar creativo de video más corto (primeros 3 segundos) y agregar subtítulos con oferta clara para mejorar hold50.</t>
         </is>
       </c>
     </row>
@@ -11953,34 +11953,34 @@
     <row r="57" ht="50" customHeight="1">
       <c r="B57" s="77" t="inlineStr">
         <is>
-          <t>⚠ ALERTA  Anuncio Esmaltado Permanente con ROAS catastrófico</t>
+          <t>⚠ ALERTA  Esmaltado Permanente con CPC descontrolado</t>
         </is>
       </c>
       <c r="F57" s="75" t="inlineStr">
         <is>
-          <t>Invirtió $164,376 para obtener solo 15 compras (costo $10,958 por venta) con caída de 1,400% en resultados respecto a marzo (de 1 a 15). ROAS de 0 es insostenible con este presupuesto.</t>
+          <t>El anuncio 'Esmaltado Permanente' gastó CLP 164.376 para solo 15 compras, resultando en un CPC de CLP 10.958. Comparado con marzo (1 compra), representa una caída de 1.400% en eficiencia de conversión.</t>
         </is>
       </c>
       <c r="M57" s="76" t="inlineStr">
         <is>
-          <t>→ Acción: Pausar anuncio 'Esmaltado Permanente' inmediatamente y reasignar presupuesto a 'Manicurista Integral Carrusel' que opera con costo de $42.</t>
+          <t>→ Acción: Pausar inmediatamente este anuncio y reasignar presupuesto. Analizar si el producto tiene stock o si el landing page tiene errores de conversión.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="50" customHeight="1">
-      <c r="B58" s="78" t="inlineStr">
-        <is>
-          <t>● INSIGHT  Carrusel genera 94% de resultados con 4.5% del presupuesto</t>
+      <c r="B58" s="74" t="inlineStr">
+        <is>
+          <t>✦ OPORTUNIDAD  Manicurista Integral Carrusel es estrella oculta</t>
         </is>
       </c>
       <c r="F58" s="75" t="inlineStr">
         <is>
-          <t>El anuncio 'Manicurista Integral Carrusel' con solo $7,688 logró 182 resultados (costo $42), mientras que anuncio de Esmaltado gastó $164,376 en solo 15 ventas. La proporción de eficiencia es 11x mayor.</t>
+          <t>Este anuncio generó 182 link clicks con CPC de CLP 42 y CTR de 3.92%, pero cayó 82.3% en resultados (1.027 en marzo). El hold50 bajo (0.5%) indica problema en retención de video.</t>
         </is>
       </c>
       <c r="M58" s="76" t="inlineStr">
         <is>
-          <t>→ Acción: Crear 3 variantes de carrusel similar para otros productos y testear en formato principal de esta campaña.</t>
+          <t>→ Acción: Mantener presupuesto pero cambiar formato de carrusel a video vertical de 9 segundos. Destacar beneficios de certificación en primeros 2 segundos.</t>
         </is>
       </c>
     </row>
@@ -11992,36 +11992,36 @@
       </c>
     </row>
     <row r="61" ht="50" customHeight="1">
-      <c r="B61" s="74" t="inlineStr">
-        <is>
-          <t>✦ OPORTUNIDAD  Segundo video genera 25x ROI respecto a base histórica</t>
+      <c r="B61" s="78" t="inlineStr">
+        <is>
+          <t>● INSIGHT  Formularios generan 76 CLP por lead consistente</t>
         </is>
       </c>
       <c r="F61" s="75" t="inlineStr">
         <is>
-          <t>Anuncio 'Academia Prueba Formularios Segundo video' escaló de 2 leads (marzo) a 514 leads (abril) manteniendo costo controlado de $78 por lead. CTR de 4.15% y hold50 de 9.8% son los mejores de la campaña.</t>
+          <t>Ambos anuncios mantienen CPC estable en CLP 76-78 con alto CTR (4.15-4.33%). Sin embargo, el anuncio 'Cambio 11-07-2025' cayó 9.5% en leads (2.417 vs 2.671 en marzo).</t>
         </is>
       </c>
       <c r="M61" s="76" t="inlineStr">
         <is>
-          <t>→ Acción: Aumentar presupuesto de este anuncio de $40,170 a $65,000 (+62%) durante los próximos 7 días para capturar volumen a costo estable.</t>
+          <t>→ Acción: Aumentar presupuesto del anuncio 'Segundo video' de CLP 40.170 a CLP 80.000 (mejor hold50 de 9.8%) y pausar el de Cambio que está perdiendo tracción.</t>
         </is>
       </c>
     </row>
     <row r="62" ht="50" customHeight="1">
-      <c r="B62" s="77" t="inlineStr">
-        <is>
-          <t>⚠ ALERTA  Caída de 9.5% en anuncio principal de formularios</t>
+      <c r="B62" s="74" t="inlineStr">
+        <is>
+          <t>✦ OPORTUNIDAD  Academia Segundo Video tiene potencial 5x</t>
         </is>
       </c>
       <c r="F62" s="75" t="inlineStr">
         <is>
-          <t>Anuncio 'Academia Prueba Formularios Cambio 11-07-2025' bajó de 2,671 a 2,417 leads (-254 leads, -9.5%) mientras gasto se mantuvo en $182,818. Esto indica fatiga de audiencia o pérdida de relevancia.</t>
+          <t>Gastó solo CLP 40.170 pero logró 514 leads con CPC de CLP 78 y el mejor hold50 de 9.8%. Es el anuncio con mejor relación eficiencia-presupuesto de toda la cuenta.</t>
         </is>
       </c>
       <c r="M62" s="76" t="inlineStr">
         <is>
-          <t>→ Acción: Testear nueva variante de copy/video para este anuncio enfocada en diferenciador versus competencia académica.</t>
+          <t>→ Acción: Duplicar presupuesto de CLP 40.170 a CLP 85.000 esta semana y monitorear CPC para confirmar escalabilidad.</t>
         </is>
       </c>
     </row>
@@ -12035,51 +12035,51 @@
     <row r="65" ht="50" customHeight="1">
       <c r="B65" s="77" t="inlineStr">
         <is>
-          <t>⚠ ALERTA  ROAS promedio crítico de 0.46 en 15 anuncios</t>
+          <t>⚠ ALERTA  BLACK WEEK es único anuncio rentable</t>
         </is>
       </c>
       <c r="F65" s="75" t="inlineStr">
         <is>
-          <t>Campaña invirtió $4,441,047 (86.6% del presupuesto total) para solo 874 compras con ROAS de 0.46 en promedio. Solo 3 anuncios superan ROAS 0.8, indicando 83% de ineficiencia de gasto.</t>
+          <t>De 15 anuncios, solo 'BLACK WEEK INICIO' tiene ROAS superior a 1 (1.18) con 236 compras. Los otros 14 anuncios promedian ROAS 0.27, quemando presupuesto con CPC promedio de CLP 7.894.</t>
         </is>
       </c>
       <c r="M65" s="76" t="inlineStr">
         <is>
-          <t>→ Acción: Identificar y pausar anuncios con ROAS &lt;0.2 (Nuevos Esmaltes, Ojos Satinados, Efecto glaseado) liberando $252,550 esta semana.</t>
+          <t>→ Acción: Reasignar CLP 1.500.000 desde anuncios con ROAS &lt; 0.3 hacia BLACK WEEK. Mantener presupuesto solo en: 'Efectos Perlados' (0.46), 'Sedu Tips' (0.42), 'Carrusel Marzo' (0.32).</t>
         </is>
       </c>
     </row>
     <row r="66" ht="50" customHeight="1">
-      <c r="B66" s="78" t="inlineStr">
-        <is>
-          <t>● INSIGHT  BLACK WEEK y Jelly Pop lideran con ROAS 1.18 y 0.93</t>
+      <c r="B66" s="77" t="inlineStr">
+        <is>
+          <t>⚠ ALERTA  Nuevos productos sin conversión (Ojos Satinados, Base Evita)</t>
         </is>
       </c>
       <c r="F66" s="75" t="inlineStr">
         <is>
-          <t>Anuncio 'BLACK WEEK INICIO' generó 236 compras con ROAS 1.18 ($469,274 invertidos), y 'Lanzamiento Jelly Pop' logró ROAS 0.93 (32 compras). Estos dos anuncios representan 30.6% de conversiones con solo 15.5% del presupuesto.</t>
+          <t>'Ojos Satinados Nuevos' gastó CLP 79.423 para solo 4 compras (CPC CLP 19.856) y cayó 89.2% vs marzo. 'Base Evita 2' cayó 69.8% (13 vs 43 compras) con CPC de CLP 10.888.</t>
         </is>
       </c>
       <c r="M66" s="76" t="inlineStr">
         <is>
-          <t>→ Acción: Duplicar presupuesto de 'BLACK WEEK INICIO' y 'Jelly Pop' en $150,000 adicionales reasignados de anuncios de bajo ROAS.</t>
+          <t>→ Acción: Pausar ambos anuncios. Verificar si landing page funciona, si el precio es competitivo, o si falta prueba social. Relanzar solo cuando se corrijan estos factores.</t>
         </is>
       </c>
     </row>
     <row r="67" ht="50" customHeight="1">
-      <c r="B67" s="74" t="inlineStr">
-        <is>
-          <t>✦ OPORTUNIDAD  Efectos Perlados con ROAS 0.46 y CTR 2.29% tiene potencial</t>
+      <c r="B67" s="78" t="inlineStr">
+        <is>
+          <t>● INSIGHT  Lanzamiento Jelly Pop emergente con ROAS 0.93</t>
         </is>
       </c>
       <c r="F67" s="75" t="inlineStr">
         <is>
-          <t>Anuncio 'Efectos Perlados en Polvo' mantiene costo controlado de $4,847 por venta y ROAS de 0.46 con CTR superior (2.29%). Hold50 de 6% indica contenido relevante. Con ajuste de targeting podría mejorar significativamente.</t>
+          <t>Nuevo anuncio (sin histórico en marzo) generó 32 compras con ROAS 0.93, el segundo mejor después de BLACK WEEK. CPC de CLP 6.787 es 14% mejor que promedio de campaña.</t>
         </is>
       </c>
       <c r="M67" s="76" t="inlineStr">
         <is>
-          <t>→ Acción: Testear segmentación por profesionales de uñas (lookalike custom audience) para este anuncio con presupuesto incremental de $50,000.</t>
+          <t>→ Acción: Aumentar presupuesto de CLP 217.189 a CLP 350.000 y crear 2 variantes adicionales con diferentes ángulos de producto para mantener momentum.</t>
         </is>
       </c>
     </row>
@@ -12093,34 +12093,34 @@
     <row r="70" ht="50" customHeight="1">
       <c r="B70" s="77" t="inlineStr">
         <is>
-          <t>⚠ ALERTA  Caída de 11.8% en anuncio principal con mayor gasto</t>
+          <t>⚠ ALERTA  Se te quebró la uña agosto cayó 11.8% en un mes</t>
         </is>
       </c>
       <c r="F70" s="75" t="inlineStr">
         <is>
-          <t>Anuncio 'Se te quebró la uña agosto' bajó de 25,762 resultados (marzo) a 22,721 (abril) con presupuesto de $99,149. Aunque mantiene excelente CTR de 10.1%, la caída sugiere fatiga creativa con hold50 de 22.1%.</t>
+          <t>El anuncio estrella generó 22.721 clicks pero bajó 1.041 resultados vs marzo (22.721 vs 25.762). A pesar de CPC bajo de CLP 4 y CTR excelente de 10.1%, el hold50 de 22.1% sugiere que el tráfico no convierte en funnel inferior.</t>
         </is>
       </c>
       <c r="M70" s="76" t="inlineStr">
         <is>
-          <t>→ Acción: Crear 2 nuevas variantes de copy urgentemente reemplazando 'uña quebrada' por ángulos como 'dureza' o 'brillo' para renovar audiencia.</t>
+          <t>→ Acción: Mantener gasto pero agregar pixel de seguimiento en landing page. Analizar si 22% de usuarios ven el call-to-action o si hay fricción en redirección a Academia/Conversión.</t>
         </is>
       </c>
     </row>
     <row r="71" ht="50" customHeight="1">
-      <c r="B71" s="78" t="inlineStr">
-        <is>
-          <t>● INSIGHT  Campaña de pruebas genera resultados a costo mínimo</t>
+      <c r="B71" s="74" t="inlineStr">
+        <is>
+          <t>✦ OPORTUNIDAD  Anuncios secundarios subinvertidos</t>
         </is>
       </c>
       <c r="F71" s="75" t="inlineStr">
         <is>
-          <t>Con presupuesto de solo $99,381 logró 22,743 resultados (costo $4 por resultado) y CTR promedio de 6.8%. Esta es la campaña más eficiente del portafolio, absorbiendo solo 1.9% del presupuesto.</t>
+          <t>Los 4 anuncios secundarios ('uñas respiran', '5 cosas', 'hannah montana', 'otoño 2026') gastaron solo CLP 232 combinados. Aunque bajo volumen, algunos como 'uñas respiran' tienen CTR de 7.61% y 'otoño 2026' de 4.89%.</t>
         </is>
       </c>
       <c r="M71" s="76" t="inlineStr">
         <is>
-          <t>→ Acción: Aumentar presupuesto de esta campaña a $250,000 mensuales para aprovechar eficiencia y generar volumen de tráfico de bajo costo.</t>
+          <t>→ Acción: Asignar CLP 15.000 a cada uno de los 3 mejores anuncios secundarios (excepto hannah montana). Probar si el hook funciona a mayor escala antes de escalar 'Se te quebró'.</t>
         </is>
       </c>
     </row>
@@ -12633,7 +12633,7 @@
     <row r="14" ht="52" customHeight="1">
       <c r="B14" s="73" t="inlineStr">
         <is>
-          <t>Bluesky redujo gasto en 3.6% (de $92,817 a $89,176) pero también disminuyó resultados en 8.1% (de 15,624 a 14,364 clicks). El costo por resultado se mantuvo estable en $6, pero el decrecimiento en conversiones sugiere necesidad de optimización inmediata.</t>
+          <t>Bluesky registró una caída del 8.1% en resultados (15,624 a 14,364 clicks) con gasto reducido 4.0% en abril 2026. El rendimiento por peso invertido se mantuvo estable en $6.21 CPC, pero el mix de anuncios cambió drásticamente con oportunidad de optimización.</t>
         </is>
       </c>
     </row>
@@ -12645,53 +12645,53 @@
       </c>
     </row>
     <row r="17" ht="50" customHeight="1">
-      <c r="B17" s="74" t="inlineStr">
-        <is>
-          <t>✦ OPORTUNIDAD  Diseño Conchitas domina con 77.9% del presupuesto</t>
+      <c r="B17" s="77" t="inlineStr">
+        <is>
+          <t>⚠ ALERTA  Diseño Conchitas concentra 77.9% del presupuesto</t>
         </is>
       </c>
       <c r="F17" s="75" t="inlineStr">
         <is>
-          <t>El anuncio 'Diseño Conchitas' consumió $69,955 (78.4% del gasto) y generó 11,185 clicks (77.9% de resultados), con hold50 de 25% y CTR de 7.1%. Este creative demuestra máxima eficiencia y merece incremento de presupuesto.</t>
+          <t>El anuncio Conchitas consume $69,955 de los $89,176 totales (78.5%) generando 11,185 clicks con CTR de 7.1%. Su hold50 de 25% sugiere retención media pero el costo de $6.25 por click es consistente.</t>
         </is>
       </c>
       <c r="M17" s="76" t="inlineStr">
         <is>
-          <t>→ Acción: Aumentar presupuesto diario de 'Diseño Conchitas' en 25-30% esta semana y monitorear ROAS en tiempo real.</t>
+          <t>→ Acción: Auditar la creatividad de Conchitas esta semana para identificar si el alto gasto se debe a bajo rendimiento o alto volumen planificado. Considerar distribuir presupuesto a Floral si CPM es similar.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="50" customHeight="1">
-      <c r="B18" s="77" t="inlineStr">
-        <is>
-          <t>⚠ ALERTA  Caída de 8.1% en resultados totales mes anterior</t>
+      <c r="B18" s="74" t="inlineStr">
+        <is>
+          <t>✦ OPORTUNIDAD  Diseño Floral muestra contracción del 78.6%</t>
         </is>
       </c>
       <c r="F18" s="75" t="inlineStr">
         <is>
-          <t>Los resultados bajaron de 15,624 a 14,364 clicks (-1,260 conversiones, -8.1%) a pesar de mantener costo similar. 'Diseño Floral' cayó 78.6% (de 12,461 a 2,662 resultados) mientras 'Conchitas' creció 253.9%.</t>
+          <t>Floral pasó de 12,461 resultados (marzo) a 2,662 resultados (abril), una caída brutal de 9,799 clicks con presupuesto similar ($15,873). CTR de 7.07% es competitivo pero el hold50 de 13.1% indica fatiga creativa.</t>
         </is>
       </c>
       <c r="M18" s="76" t="inlineStr">
         <is>
-          <t>→ Acción: Pausar 'Diseño Floral' por 5 días, revisar copy/imagen y realizar A/B test con variante mejorada antes de relanzar.</t>
+          <t>→ Acción: Reactivar inmediatamente el anuncio Floral con variantes creativas nuevas (ángulos, fondos, paletas) y aumentar presupuesto a $25k para recuperar volumen perdido.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="50" customHeight="1">
       <c r="B19" s="78" t="inlineStr">
         <is>
-          <t>● INSIGHT  Diseño Limón Verano crece 25,350% con bajo gasto</t>
+          <t>● INSIGHT  Limón Verano mostró crecimiento de 25,350%</t>
         </is>
       </c>
       <c r="F19" s="75" t="inlineStr">
         <is>
-          <t>El nuevo anuncio 'diseño limon verano' pasó de 2 a 509 resultados (+255x) invirtiendo solo $3,312 con CTR de 7.58% y hold50 de 18.2%. ROI potencial muy alto con presupuesto mínimo.</t>
+          <t>El anuncio de limón pasó de 2 clicks (marzo) a 509 clicks (abril) con inversión de $3,312 y CTR de 7.58%. Aunque el volumen es bajo, el crecimiento sugiere que el concepto estacional resuena con audiencia.</t>
         </is>
       </c>
       <c r="M19" s="76" t="inlineStr">
         <is>
-          <t>→ Acción: Duplicar presupuesto de 'diseño limon verano' a $6,600 esta semana para validar escalabilidad y saturación de audiencia.</t>
+          <t>→ Acción: Aumentar presupuesto de Limón Verano a $15,000 semanales por 2 semanas para validar si es tendencia real o spike puntual. Monitorear daily con umbral de pausa si CPL supera $7.50.</t>
         </is>
       </c>
     </row>
@@ -12725,7 +12725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:R55"/>
+  <dimension ref="B1:R52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -14263,7 +14263,7 @@
     <row r="36" ht="52" customHeight="1">
       <c r="B36" s="73" t="inlineStr">
         <is>
-          <t>Nail Outlet registró un incremento de gasto del 4.2% (1.408M vs 1.352M) pero con caída del 14.4% en resultados (4.302 vs 5.028), evidenciando una eficiencia deteriorada en abril. El ROAS promedio de la marca se redujo significativamente, especialmente en campañas de conversión donde el costo por resultado aumentó en múltiples anuncios.</t>
+          <t>Nail Outlet experimentó una caída del 14.4% en conversiones (de 5.028 a 4.302) pese a aumentar el gasto en 4.2% ($1.408M en abril). La rentabilidad se ha deteriorado significativamente con ROAS promedio bajo en campañas de conversión, requiriendo optimización urgente de creativos y segmentación.</t>
         </is>
       </c>
     </row>
@@ -14277,262 +14277,202 @@
     <row r="39" ht="50" customHeight="1">
       <c r="B39" s="77" t="inlineStr">
         <is>
-          <t>⚠ ALERTA  Caída crítica en Poly Gel Carrusel</t>
+          <t>⚠ ALERTA  Caída crítica en conversiones pack bestseller</t>
         </is>
       </c>
       <c r="F39" s="75" t="inlineStr">
         <is>
-          <t>El anuncio mejor performer cayó 90.4% en conversiones (7 vs 73 resultados) manteniendo inversión de $3.237. Su ROAS de 40.15 indica que sigue siendo rentable pero necesita optimización urgente.</t>
+          <t>Pack Repo 20 Agosto registró una caída del 47.4% en conversiones (de 38 a 20) con inversión similar ($167.478), generando un ROAS de 6.42 pero con eficiencia comprometida. Este fue el mejor anuncio del mes anterior.</t>
         </is>
       </c>
       <c r="M39" s="76" t="inlineStr">
         <is>
-          <t>→ Acción: Pausar anuncio, revisar creatividad y audiencia segmentada, reactivar con variación de copy y CTA diferenciado en los próximos 3 días.</t>
+          <t>→ Acción: Analizar cambios en audiencia/creatividad del Pack Repo; considerar renovar videoproducción o segmentar por zona geográfica para recuperar volumen.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="50" customHeight="1">
-      <c r="B40" s="77" t="inlineStr">
-        <is>
-          <t>⚠ ALERTA  Esmaltes French Nail Pro con ROAS negativo</t>
+      <c r="B40" s="74" t="inlineStr">
+        <is>
+          <t>✦ OPORTUNIDAD  Poly Gel Carrusel superhigh performer</t>
         </is>
       </c>
       <c r="F40" s="75" t="inlineStr">
         <is>
-          <t>Gasto de $76.227 generó solo 6 conversiones (vs 14 en marzo) con ROAS de 0.45. Costo por resultado de $12.705 es 3x superior al promedio de campaña.</t>
+          <t>Con solo $3.237 de inversión logró 7 conversiones (ROAS 40.15), pero registra caída de 90.4% vs marzo (73 a 7 resultados). Es el anuncio más eficiente del portafolio.</t>
         </is>
       </c>
       <c r="M40" s="76" t="inlineStr">
         <is>
-          <t>→ Acción: Pausar inmediatamente, reasignar presupuesto a Pack Repo 20 Agosto (ROAS 6.42) o Imagen Mesa Nail Pro (ROAS 1.85).</t>
+          <t>→ Acción: Aumentar presupuesto de Poly Gel Carrusel a $15-20K manteniendo segmentación; testear con variaciones de creatividad para replicar performance anterior.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="50" customHeight="1">
-      <c r="B41" s="74" t="inlineStr">
-        <is>
-          <t>✦ OPORTUNIDAD  Pack Repo 20 Agosto sigue siendo rentable</t>
+      <c r="B41" s="78" t="inlineStr">
+        <is>
+          <t>● INSIGHT  Link clicks generan datos sin ROI inmediato</t>
         </is>
       </c>
       <c r="F41" s="75" t="inlineStr">
         <is>
-          <t>A pesar de caída del 47.4% en resultados (20 vs 38), mantiene ROAS de 6.42 con inversión de $167.478. Es el anuncio con mejor relación costo-efectividad en conversión.</t>
+          <t>Ojo de Gato y Como usar Deshidratador generaron 108 clicks con $18.937 pero costo de conversión posterior no se traduce. Hold50 de 6.2% sugiere interés real pero formato incorrecto.</t>
         </is>
       </c>
       <c r="M41" s="76" t="inlineStr">
         <is>
-          <t>→ Acción: Aumentar presupuesto diario en 30% y crear 2 variaciones de creatividad para mantener relevancia y recuperar volumen de conversiones.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="50" customHeight="1">
-      <c r="B42" s="78" t="inlineStr">
-        <is>
-          <t>● INSIGHT  CTR alto no garantiza conversiones</t>
-        </is>
-      </c>
-      <c r="F42" s="75" t="inlineStr">
-        <is>
-          <t>Imagen primer deshidratador tiene CTR de 2.68% (más alto) pero ROAS de 1.70 con costo de $29.518. Campo de Trabajo tiene CTR de 1.94% con ROAS similar de 1.46.</t>
-        </is>
-      </c>
-      <c r="M42" s="76" t="inlineStr">
-        <is>
-          <t>→ Acción: Implementar pixel de seguimiento mejorado para identificar punto de abandono post-click y optimizar landing page para estos anuncios.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="B44" s="6" t="inlineStr">
+          <t>→ Acción: Separar estos anuncios a campaña de awareness/video view; usar pixel de engagement para remarketing a usuarios con hold50&gt;5%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="B43" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  💡  TRÁFICO PERFIL INSTAGRAM MKT</t>
         </is>
       </c>
     </row>
+    <row r="44" ht="50" customHeight="1">
+      <c r="B44" s="77" t="inlineStr">
+        <is>
+          <t>⚠ ALERTA  Caída en tráfico pese a bajo costo</t>
+        </is>
+      </c>
+      <c r="F44" s="75" t="inlineStr">
+        <is>
+          <t>Paso a paso Vale Nails cayó 35.4% en clicks (de 2.984 a 1.930) con costo estable ($21). Insta Nail Pro cayó 15.7% (de 1.838 a 2.127 resultados), sugiriendo fatiga de audiencia.</t>
+        </is>
+      </c>
+      <c r="M44" s="76" t="inlineStr">
+        <is>
+          <t>→ Acción: Crear nuevas variantes de creatividad en ambos anuncios; limitar frecuencia a 2 impressiones/usuario/día; testear nuevas audiencias miradores de competencia.</t>
+        </is>
+      </c>
+    </row>
     <row r="45" ht="50" customHeight="1">
-      <c r="B45" s="77" t="inlineStr">
-        <is>
-          <t>⚠ ALERTA  Insta Nail Pro con caída de 15.8%</t>
+      <c r="B45" s="78" t="inlineStr">
+        <is>
+          <t>● INSIGHT  High hold50 indica contenido valuable</t>
         </is>
       </c>
       <c r="F45" s="75" t="inlineStr">
         <is>
-          <t>Generó 2.127 clicks vs 1.838 en marzo (aumento de 15.7%), pero inversión creció de forma no documentada. Hold50 de 19.2% es fuerte pero requiere análisis de conversión posterior.</t>
+          <t>Paso a paso Vale Nails con 4.01% CTR y 10.3% hold50 demuestra que contenido educativo genera engagement, pero no se monetiza adecuadamente.</t>
         </is>
       </c>
       <c r="M45" s="76" t="inlineStr">
         <is>
-          <t>→ Acción: Revisar datos de atribución en Google Analytics/Meta Conversions para conectar traffic con compras y calcular ROAS real de esta campaña.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="50" customHeight="1">
-      <c r="B46" s="77" t="inlineStr">
-        <is>
-          <t>⚠ ALERTA  Paso a paso Vale Nails cayó 35.4%</t>
-        </is>
-      </c>
-      <c r="F46" s="75" t="inlineStr">
-        <is>
-          <t>Registró 1.930 clicks vs 2.984 en marzo (caída del 35.4%) con inversión de $41.059. CTR de 4.01% es excelente pero volumen se desmorona.</t>
-        </is>
-      </c>
-      <c r="M46" s="76" t="inlineStr">
-        <is>
-          <t>→ Acción: Reinvertir en este anuncio con nuevo hook visual, cambiar frecuencia de entrega a audiencia similar de mejor calidad.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="50" customHeight="1">
-      <c r="B47" s="78" t="inlineStr">
-        <is>
-          <t>● INSIGHT  Hold50 alto no se traduce en compras</t>
-        </is>
-      </c>
-      <c r="F47" s="75" t="inlineStr">
-        <is>
-          <t>Ambos anuncios tienen hold50 superior a 10% pero campaña no muestra conversiones. Insta Nail Pro: 19.2% engagement, Paso a paso: 10.3%, indicando buena atracción pero falla en conversión.</t>
-        </is>
-      </c>
-      <c r="M47" s="76" t="inlineStr">
-        <is>
-          <t>→ Acción: Configurar audiences de remarketing basadas en estos clickers y crear anuncios de conversión específicos dentro de 48 horas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="B49" s="6" t="inlineStr">
+          <t>→ Acción: Redirigir esta audiencia con pixel a campaña de conversión del Pack Repo; crear secuencia de remarketing de 7 días antes de saturar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  💡  REMARKETING NAIL OUTLET</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="50" customHeight="1">
-      <c r="B50" s="74" t="inlineStr">
-        <is>
-          <t>✦ OPORTUNIDAD  15% OFF con ROAS de 11.25</t>
-        </is>
-      </c>
-      <c r="F50" s="75" t="inlineStr">
-        <is>
-          <t>Anuncio nuevo que invirtió $20.886 generando 6 conversiones con ROAS de 11.25, el más alto de todas las campañas. Costo unitario de $3.481 es 25% más bajo que promedio.</t>
-        </is>
-      </c>
-      <c r="M50" s="76" t="inlineStr">
-        <is>
-          <t>→ Acción: Aumentar presupuesto diario a $1.000-1.500, crear 2 variaciones (15% OFF vs 20% OFF) y testear durante 7 días.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="50" customHeight="1">
-      <c r="B51" s="78" t="inlineStr">
-        <is>
-          <t>● INSIGHT  Despacho Gratis genera 50% más conversiones</t>
-        </is>
-      </c>
-      <c r="F51" s="75" t="inlineStr">
-        <is>
-          <t>Invirtió $44.220 para 9 conversiones vs 6 del descuento, pero con ROAS inferior (4.85 vs 11.25). Sugiere que mezcla de propuestas de valor es efectiva.</t>
-        </is>
-      </c>
-      <c r="M51" s="76" t="inlineStr">
-        <is>
-          <t>→ Acción: Mantener ambos anuncios activos pero reducir presupuesto de Despacho a $30.000 e incrementar 15% OFF a $35.000 mensuales.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="22" customHeight="1">
-      <c r="B53" s="6" t="inlineStr">
+    <row r="48" ht="50" customHeight="1">
+      <c r="B48" s="74" t="inlineStr">
+        <is>
+          <t>✦ OPORTUNIDAD  Remarketing con ROAS doble dígito</t>
+        </is>
+      </c>
+      <c r="F48" s="75" t="inlineStr">
+        <is>
+          <t>15% OFF logró 6 conversiones con ROAS 11.25 ($20.886 gasto), siendo la campaña más rentable del portafolio después del Poly Gel.</t>
+        </is>
+      </c>
+      <c r="M48" s="76" t="inlineStr">
+        <is>
+          <t>→ Acción: Aumentar presupuesto de 15% OFF a $35-40K; crear variante con descuento escalonado (10% vs 15%) para test AB; expandir a carrito abandonado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="50" customHeight="1">
+      <c r="B49" s="78" t="inlineStr">
+        <is>
+          <t>● INSIGHT  Despacho Gratis más volumen menor ROI</t>
+        </is>
+      </c>
+      <c r="F49" s="75" t="inlineStr">
+        <is>
+          <t>Despacho Gratis generó 9 conversiones con ROAS 4.85 ($44.220), doblando volumen pero con menor rentabilidad que 15% OFF, sugiriendo que precio es mayor motivador.</t>
+        </is>
+      </c>
+      <c r="M49" s="76" t="inlineStr">
+        <is>
+          <t>→ Acción: Reducir presupuesto Despacho Gratis a $25K; priorizar 15% OFF como gancho principal; testear combo 10% OFF + envío gratis para segmento ticket bajo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  💡  CAMPAÑA CONVERSIÓN CATÁLOGO</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="50" customHeight="1">
-      <c r="B54" s="77" t="inlineStr">
-        <is>
-          <t>⚠ ALERTA  Catálogo nuevo sin historial de performance</t>
-        </is>
-      </c>
-      <c r="F54" s="75" t="inlineStr">
-        <is>
-          <t>Invertido $355.748 (25% del presupuesto total) para apenas 20 conversiones con ROAS de 1.84. Costo por resultado de $17.787 es 4.1x superior al promedio de conversión.</t>
-        </is>
-      </c>
-      <c r="M54" s="76" t="inlineStr">
-        <is>
-          <t>→ Acción: Pausar campaña, solicitar reporte de performance anterior, validar configuración de feed de catálogo y auditar audiencias segmentadas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="50" customHeight="1">
-      <c r="B55" s="77" t="inlineStr">
-        <is>
-          <t>⚠ ALERTA  Hold50 de 0% indica falta de engagement</t>
-        </is>
-      </c>
-      <c r="F55" s="75" t="inlineStr">
-        <is>
-          <t>Pese a CTR aceptable de 1.66%, hold50 es 0%, significando que casi ningún usuario se detiene en el anuncio. Patrón indica creatividad o copy poco atractivos.</t>
-        </is>
-      </c>
-      <c r="M55" s="76" t="inlineStr">
-        <is>
-          <t>→ Acción: Reemplazar creative del catálogo con imágenes de productos high-converting (Pack Repo, Poly Gel) y testar nuevos textos descriptivos.</t>
+    <row r="52" ht="50" customHeight="1">
+      <c r="B52" s="77" t="inlineStr">
+        <is>
+          <t>⚠ ALERTA  Nuevo anuncio catálogo con bajo rendimiento</t>
+        </is>
+      </c>
+      <c r="F52" s="75" t="inlineStr">
+        <is>
+          <t>Único anuncio de catálogo generó solo 20 conversiones con $355.748 de inversión (ROAS 1.84) y 0% hold50, indicando que formato de catálogo dinámico no resonó.</t>
+        </is>
+      </c>
+      <c r="M52" s="76" t="inlineStr">
+        <is>
+          <t>→ Acción: Pausar esta campaña; dividir presupuesto entre Pack Repo (aumentar a $210K) y Black Week (aumentar a $230K) que tienen ROAS 6.42 y 5.57 respectivamente.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="50">
-    <mergeCell ref="F46:L46"/>
+  <mergeCells count="41">
     <mergeCell ref="B40:E40"/>
-    <mergeCell ref="M54:R54"/>
     <mergeCell ref="B26:R26"/>
+    <mergeCell ref="B49:E49"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="B35:R35"/>
+    <mergeCell ref="F52:L52"/>
+    <mergeCell ref="B47:R47"/>
     <mergeCell ref="F39:L39"/>
     <mergeCell ref="M40:R40"/>
-    <mergeCell ref="B55:E55"/>
-    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="F48:L48"/>
     <mergeCell ref="B22:R22"/>
+    <mergeCell ref="F49:L49"/>
     <mergeCell ref="B45:E45"/>
-    <mergeCell ref="M46:R46"/>
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="B41:E41"/>
-    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="B43:R43"/>
     <mergeCell ref="M45:R45"/>
-    <mergeCell ref="M42:R42"/>
-    <mergeCell ref="B54:E54"/>
+    <mergeCell ref="F44:L44"/>
     <mergeCell ref="B2:R2"/>
     <mergeCell ref="M41:R41"/>
-    <mergeCell ref="B47:E47"/>
-    <mergeCell ref="F54:L54"/>
-    <mergeCell ref="B46:E46"/>
     <mergeCell ref="B1:R1"/>
-    <mergeCell ref="M47:R47"/>
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="F40:L40"/>
-    <mergeCell ref="B44:R44"/>
-    <mergeCell ref="B53:R53"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="B48:E48"/>
     <mergeCell ref="B38:R38"/>
-    <mergeCell ref="M50:R50"/>
     <mergeCell ref="B39:E39"/>
-    <mergeCell ref="F55:L55"/>
-    <mergeCell ref="B42:E42"/>
-    <mergeCell ref="F42:L42"/>
-    <mergeCell ref="F51:L51"/>
     <mergeCell ref="F45:L45"/>
-    <mergeCell ref="B49:R49"/>
-    <mergeCell ref="M55:R55"/>
-    <mergeCell ref="F50:L50"/>
+    <mergeCell ref="M44:R44"/>
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="B30:R30"/>
     <mergeCell ref="F41:L41"/>
+    <mergeCell ref="M49:R49"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="M52:R52"/>
+    <mergeCell ref="B51:R51"/>
+    <mergeCell ref="M48:R48"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="M39:R39"/>
-    <mergeCell ref="F47:L47"/>
     <mergeCell ref="B5:R5"/>
-    <mergeCell ref="M51:R51"/>
     <mergeCell ref="B36:R36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -19190,7 +19130,7 @@
     <row r="90" ht="52" customHeight="1">
       <c r="B90" s="73" t="inlineStr">
         <is>
-          <t>Go Nails experimentó una caída crítica del 88.4% en resultados (de 20,613 a 2,404) en abril 2026 mientras reducía gasto solo 5.7%, indicando un problema sistémico de eficiencia. El ROAS promedio se desplomó y múltiples campañas de conversión generan resultados prácticamente nulos, requiriendo intervención inmediata en estructura de audiencias y creativas.</t>
+          <t>Go Nails experimentó una caída crítica del 88.3% en conversiones (20,613 a 2,404) en abril, aunque redujo gasto un 5.7%. El ROAS se deterioró significativamente en campañas de tráfico, señalando problemas graves en creatividad y targeting.</t>
         </is>
       </c>
     </row>
@@ -19204,34 +19144,34 @@
     <row r="93" ht="50" customHeight="1">
       <c r="B93" s="77" t="inlineStr">
         <is>
-          <t>⚠ ALERTA  Colapso de resultados en anuncios de descuento</t>
+          <t>⚠ ALERTA  Caída de conversiones en remarketing directo</t>
         </is>
       </c>
       <c r="F93" s="75" t="inlineStr">
         <is>
-          <t>El anuncio '15% OFF' cayó de 34 resultados a apenas 1 (97% caída) con CPC de $7,957. El anuncio 'Despacho Gratis' también se desplomó de 108 a 32 resultados (-70.4%), indicando rechazo de audiencia a estas ofertas.</t>
+          <t>El anuncio principal 'Remarketing Go Nails 2024' cayó de 65 a 22 conversiones (66% reducción) con gasto similar (CPC aumentó de 5,863 a 5,863). El anuncio '15% OFF' solo generó 1 conversión versus 34 anteriores.</t>
         </is>
       </c>
       <c r="M93" s="76" t="inlineStr">
         <is>
-          <t>→ Acción: Pausar '15% OFF' inmediatamente y testear nuevos hooks de oferta. Segmentar audiencia del anuncio 'Despacho Gratis' por frecuencia de compra previa.</t>
+          <t>→ Acción: Reactivar audiencias de carrito abandonado y revisar pixel de tracking. Testear propuesta de valor diferente al 15% OFF que claramente no convierte.</t>
         </is>
       </c>
     </row>
     <row r="94" ht="50" customHeight="1">
       <c r="B94" s="74" t="inlineStr">
         <is>
-          <t>✦ OPORTUNIDAD  Anuncio principal mantiene eficiencia</t>
+          <t>✦ OPORTUNIDAD  Anuncio 'Despacho Gratis' mantiene eficiencia</t>
         </is>
       </c>
       <c r="F94" s="75" t="inlineStr">
         <is>
-          <t>El anuncio 'Remarketing Go Nails 2024' generó 22 resultados con ROAS 5.24 y CPC $5,863, siendo el mejor performer de la campaña con CTR 1.9%. Representa solo $128,988 del presupuesto de $269,322.</t>
+          <t>Única variante con ROAS saludable de 4.82 y CTR de 1.12%. Aunque cayó de 108 a 32 conversiones, el costo por conversión bajó a $4,137 con mejor CPC.</t>
         </is>
       </c>
       <c r="M94" s="76" t="inlineStr">
         <is>
-          <t>→ Acción: Aumentar presupuesto a este anuncio en 50% retirado de los otros dos anuncios de la campaña.</t>
+          <t>→ Acción: Aumentar presupuesto de 'Despacho Gratis' un 40% y replicar estructura creativa a otras campañas de conversión bajo rendimiento.</t>
         </is>
       </c>
     </row>
@@ -19245,51 +19185,51 @@
     <row r="97" ht="50" customHeight="1">
       <c r="B97" s="77" t="inlineStr">
         <is>
-          <t>⚠ ALERTA  Anuncios purchase generan resultados prácticamente nulos</t>
+          <t>⚠ ALERTA  Derrumbe catastrófico en anuncios de compra</t>
         </is>
       </c>
       <c r="F97" s="75" t="inlineStr">
         <is>
-          <t>Los anuncios 'hannah montana 2' ($283,796 gasto, 1 compra, ROAS 0.04) y 'Nueva rutina 4 pasos' ($27,864 gasto, 1 compra) están destruyendo ROI. El primero cayó de 456 a 1 resultado (-99.8%), señalando problema grave de targeting o relevancia.</t>
+          <t>'hannah montana 2' gastó $283,796 por 1 conversión (ROAS 0.04) cayendo de 456 a 1 resultado. 'hannah montana' similar: $55,106 por 1 conversión versus 2,567 anteriores. Pérdida total de $338,902 en estos 2 anuncios.</t>
         </is>
       </c>
       <c r="M97" s="76" t="inlineStr">
         <is>
-          <t>→ Acción: Pausar inmediatamente ambos anuncios. Analizar pixel de conversión y verificar que compras se registren correctamente en sistema.</t>
+          <t>→ Acción: Pausar inmediatamente 'hannah montana' y 'hannah montana 2'. Investigar cambios en audiencia/pixel que causaron colapso de 458x en conversiones.</t>
         </is>
       </c>
     </row>
     <row r="98" ht="50" customHeight="1">
-      <c r="B98" s="74" t="inlineStr">
-        <is>
-          <t>✦ OPORTUNIDAD  Link clicks con CTR excepcional sin monetizar</t>
+      <c r="B98" s="78" t="inlineStr">
+        <is>
+          <t>● INSIGHT  Traffic ads generan clics baratos pero sin conversión</t>
         </is>
       </c>
       <c r="F98" s="75" t="inlineStr">
         <is>
-          <t>5 anuncios generan entre 4.3-5.58% CTR con costos de $12-19 por click: 'cotton candy frutilla' (407 clicks), 'tu pareja te debe' (760 clicks), 'popcorn pomo' (25 clicks). Estos demuestran alto interés pero no convierten.</t>
+          <t>'cotton candy frutilla' (CPC $17, CTR 4.3%) generó 407 clics pero 0 conversiones (perdió 208 clicks versus marzo). 'Rutina 4 pasos' mantiene CPC de $15 con buen CTR 4.57% pero sin ROAS medible.</t>
         </is>
       </c>
       <c r="M98" s="76" t="inlineStr">
         <is>
-          <t>→ Acción: Crear landing page específica para estos anuncios optimizada para conversión. Testear retargeting dinámico a estos 760+ clickers del anuncio 'tu pareja te debe' con oferta especial.</t>
+          <t>→ Acción: Implementar pixel de compra en landing page. Auditar embudo de conversión post-click (velocidad página, mobile optimization, checkout flow).</t>
         </is>
       </c>
     </row>
     <row r="99" ht="50" customHeight="1">
-      <c r="B99" s="77" t="inlineStr">
-        <is>
-          <t>⚠ ALERTA  Presupuesto mal asignado a anuncios de bajo ROAS</t>
+      <c r="B99" s="74" t="inlineStr">
+        <is>
+          <t>✦ OPORTUNIDAD  Nuevo anuncio 'tu pareja te debe' muestra potencial</t>
         </is>
       </c>
       <c r="F99" s="75" t="inlineStr">
         <is>
-          <t>68% del presupuesto de campaña ($283,796 de $390,118) va a 'hannah montana 2' con ROAS 0.04, mientras anuncios link_click que generan 1,200+ clicks reciben solo 2% del presupuesto.</t>
+          <t>Lanzado en abril sin datos previos: 760 clics por $14,792 (CPC $19), CTR 2.87%. Bajo costo per-click sugiere audiencia receptiva y mensaje relevante.</t>
         </is>
       </c>
       <c r="M99" s="76" t="inlineStr">
         <is>
-          <t>→ Acción: Redistribuir presupuesto: reducir anuncios purchase a máximo $20k total, aumentar anuncios link_click a $200k para generar tráfico cualificado.</t>
+          <t>→ Acción: Segmentar 'tu pareja te debe' en audience lookalike. Testear 3 variantes de copy enfocadas en gift/regalo. Aumentar presupuesto a $25k para marzo.</t>
         </is>
       </c>
     </row>
@@ -19303,51 +19243,51 @@
     <row r="102" ht="50" customHeight="1">
       <c r="B102" s="77" t="inlineStr">
         <is>
-          <t>⚠ ALERTA  Caída generalizada de resultados sin reducción proporcional de gasto</t>
+          <t>⚠ ALERTA  Caída del 71% en conversiones de compra</t>
         </is>
       </c>
       <c r="F102" s="75" t="inlineStr">
         <is>
-          <t>Campaña invirtió $5.46M (76.5% del gasto total) y generó solo 715 resultados (-31.3% vs marzo) con CPC promedio $7,642. El anuncio 'Home Spray' solo consumió $1.18M para 91 compras (13% de resultados con 21.7% de gasto).</t>
+          <t>Campaña principal cayó de 2,465 a 715 conversiones pese a invertir $5.46M (76.5% del presupuesto total). 'Home Spray' gastó $1.18M generando solo 91 conversiones (down 27.8%) con ROAS degradado a 2.45.</t>
         </is>
       </c>
       <c r="M102" s="76" t="inlineStr">
         <is>
-          <t>→ Acción: Implementar caps de gasto diario máximo $25k por anuncio para evitar desperdicio. Revisar configuración de audiencias: probablemente hay solapamiento y fatiga de audiencia.</t>
+          <t>→ Acción: Pausar 'Home Spray' por 7 días. Renovar creatividades con video formato (actualmente solo imágenes/carruseles). A/B test con propuesta diferente a descuentos.</t>
         </is>
       </c>
     </row>
     <row r="103" ht="50" customHeight="1">
-      <c r="B103" s="74" t="inlineStr">
-        <is>
-          <t>✦ OPORTUNIDAD  Anuncios eficientes con ROAS 4.0+ están subutilizados</t>
+      <c r="B103" s="78" t="inlineStr">
+        <is>
+          <t>● INSIGHT  Anuncios con hold50 alto muestran mayor retención</t>
         </is>
       </c>
       <c r="F103" s="75" t="inlineStr">
         <is>
-          <t>4 anuncios generan ROAS 4.0 o superior con bajo gasto relativo: 'Cremas Sun Kissed' (ROAS 5.0, $68k), 'Imagen Cotton Vlabel' (ROAS 5.0, $293k), 'Imagen Bubble gum' (ROAS 4.1, $100k). Estos representan el 11% del gasto pero eficiencia superior.</t>
+          <t>'4 por 3' (hold50 4.7%, ROAS 3.93), 'Cremas Sun Kissed' (hold50 4.1%, ROAS 5.0) y 'Home Spray' (hold50 6.7%, ROAS 2.45) mantienen mejor performance. Anuncios sin hold50 caen drásticamente.</t>
         </is>
       </c>
       <c r="M103" s="76" t="inlineStr">
         <is>
-          <t>→ Acción: Aumentar presupuesto 30-40% a estos 4 anuncios, retirado del anuncio 'Home Spray' (ROAS 2.45) y 'Reel de fragancias' (ROAS 3.03).</t>
+          <t>→ Acción: Priorizar creatividades con 4-7% hold50. Analizar qué elementos en videos retienen 50%+ de audiencia en estos anuncios e implementar en nuevas piezas.</t>
         </is>
       </c>
     </row>
     <row r="104" ht="50" customHeight="1">
-      <c r="B104" s="78" t="inlineStr">
-        <is>
-          <t>● INSIGHT  Nuevos difusores desempeño catastrófico</t>
+      <c r="B104" s="74" t="inlineStr">
+        <is>
+          <t>✦ OPORTUNIDAD  Anuncios de costo bajo con ROAS elite</t>
         </is>
       </c>
       <c r="F104" s="75" t="inlineStr">
         <is>
-          <t>Anuncio 'Nuevos difusores' generó solo 3 resultados con $67,668 gasto (CPC $22,556) y ROAS 1.18, cayendo de 35 a 3 resultados (-91.4%). Peor performer absoluto de la campaña.</t>
+          <t>'Reel cafetería' ($15,267 gasto, ROAS 4.6, CPC $5,089) y 'Imagen Cotton Vlabel' ($293,090, ROAS 5.0, CPC $7,713) muestran eficiencia. Potencial de escala con budget limitado.</t>
         </is>
       </c>
       <c r="M104" s="76" t="inlineStr">
         <is>
-          <t>→ Acción: Pausar completamente. Si se relanza, crear creativo completamente nuevo con enfoque en beneficio vs característica del producto.</t>
+          <t>→ Acción: Duplicar presupuesto de 'Reel cafetería' a $30k. Expandir 'Imagen Cotton Vlabel' en 25% (de $293k a $366k) en audiencias lookalike de compradores.</t>
         </is>
       </c>
     </row>
@@ -19361,34 +19301,34 @@
     <row r="107" ht="50" customHeight="1">
       <c r="B107" s="74" t="inlineStr">
         <is>
-          <t>✦ OPORTUNIDAD  ROAS extraordinario en anuncio 'Reel Kit LMM'</t>
+          <t>✦ OPORTUNIDAD  Reel Kit LMM top performer con ROAS 15.27</t>
         </is>
       </c>
       <c r="F107" s="75" t="inlineStr">
         <is>
-          <t>Con apenas $12,363 de gasto, este anuncio generó ROAS 15.27 (5 compras) versus ROAS 3.36 del otro performer. Hold50 de 14.6% indica contenido altamente relevante. Creció de 1 a 5 resultados (+400%).</t>
+          <t>Anuncio menor ($12,363 gasto) generó 5 conversiones con ROAS 15.27 (mayor de toda cuenta). Solo 1 conversión en marzo versus 5 en abril. CPC de $2,473 es 60% más bajo que promedio de conversión.</t>
         </is>
       </c>
       <c r="M107" s="76" t="inlineStr">
         <is>
-          <t>→ Acción: Duplicar presupuesto a $25k esta semana. Crear 2-3 variantes de creativo similar basadas en qué elemento del kit genera mayor engagement.</t>
+          <t>→ Acción: Aumentar presupuesto 'Reel Kit LMM' a $50k inmediatamente. Testear 3 variantes del video con hook diferente para mantener hold50 14.6%.</t>
         </is>
       </c>
     </row>
     <row r="108" ht="50" customHeight="1">
       <c r="B108" s="77" t="inlineStr">
         <is>
-          <t>⚠ ALERTA  Anuncio sin tipo de conversión genera costo cero sin datos</t>
+          <t>⚠ ALERTA  Conversión baja en 'Reel esmalte LMM'</t>
         </is>
       </c>
       <c r="F108" s="75" t="inlineStr">
         <is>
-          <t>'Reel de Kit Le Mini' tiene gasto $63 con 0 resultados y 32.1% hold50, pero campo 'tipo' está vacío. Imposible analizar rendimiento o asignar presupuesto.</t>
+          <t>Gastó $60,827 por solo 6 conversiones (CPC $10,138) cayendo de 17 a 6 (64% reducción). Aunque hold50 es alto (19.7%), conversión final es débil.</t>
         </is>
       </c>
       <c r="M108" s="76" t="inlineStr">
         <is>
-          <t>→ Acción: Verificar configuración de evento de conversión. Confirmar que anuncio está correctamente etiquetado como 'purchase'. Si sigue sin datos, pausar.</t>
+          <t>→ Acción: Pausar 'Reel esmalte LMM' por 14 días. Crear nueva versión con CTA más agresivo enfocado en urgencia/scarcity. Testear con audiencia más fría.</t>
         </is>
       </c>
     </row>
@@ -19402,51 +19342,51 @@
     <row r="111" ht="50" customHeight="1">
       <c r="B111" s="77" t="inlineStr">
         <is>
-          <t>⚠ ALERTA  Ineficiencia generalizada en generación de tráfico</t>
+          <t>⚠ ALERTA  Costo por click inflado sin conversión final</t>
         </is>
       </c>
       <c r="F111" s="75" t="inlineStr">
         <is>
-          <t>Campaña gastó $935,350 para generar solo 338 link clicks (CPC promedio $2,767), comparado con 'Marketing Go Nails - Trafico Insta' que gastó $390k para 1,285 clicks a $304 CPC. Costo 9x mayor por click.</t>
+          <t>$935,350 generaron 338 clicks (CPC promedio $2,767) pero métrica de compra no está ligada. Anuncios como 'Reel de fragancias' gastaron $523 por solo 2 clicks. Ineficiencia extrema en asignación presupuestaria.</t>
         </is>
       </c>
       <c r="M111" s="76" t="inlineStr">
         <is>
-          <t>→ Acción: Auditar audiencias: probablemente está dirigiendo a usuarios fríos. Cambiar targeting a 'Traffico Insta' setup que funciona 9x mejor.</t>
+          <t>→ Acción: Cambiar objetivo de 'link_click' a 'purchase' en todos los anuncios. Auditar UTM tracking para confirmar si conversiones se están registrando correctamente en Meta.</t>
         </is>
       </c>
     </row>
     <row r="112" ht="50" customHeight="1">
-      <c r="B112" s="74" t="inlineStr">
-        <is>
-          <t>✦ OPORTUNIDAD  Dos anuncios purchase con ROAS excepcional</t>
+      <c r="B112" s="78" t="inlineStr">
+        <is>
+          <t>● INSIGHT  Híbridos purchase muestran mejor ROAS</t>
         </is>
       </c>
       <c r="F112" s="75" t="inlineStr">
         <is>
-          <t>Anuncios 'Macbook' (ROAS 9.93, 7 compras, $21.6k) e 'Imagen Bubble gum' (ROAS 5.97, 1 compra, $1.5k) tienen eficiencia purchase-level dentro de campaña link_click.</t>
+          <t>Anuncios con tipo 'purchase' dentro de campaña link_click: 'Macbook' (ROAS 9.93, $21,610 gasto), 'Imagen Bubble gum' (ROAS 5.97) superan 10x el ROAS de puros link_clicks.</t>
         </is>
       </c>
       <c r="M112" s="76" t="inlineStr">
         <is>
-          <t>→ Acción: Crear campaña de conversión separada solo con estos 2 creatives. Presupuestar $50k inicialmente en estructura purchase estándar.</t>
+          <t>→ Acción: Convertir todos los anuncios de esta campaña a objetivo 'purchase'. Mantener estructura creativa pero optimizar pixel de compra.</t>
         </is>
       </c>
     </row>
     <row r="113" ht="50" customHeight="1">
-      <c r="B113" s="78" t="inlineStr">
-        <is>
-          <t>● INSIGHT  Anuncios link_click con mejor CPC no generan compras</t>
+      <c r="B113" s="74" t="inlineStr">
+        <is>
+          <t>✦ OPORTUNIDAD  Anuncios de costo ultra-bajo con alto CTR</t>
         </is>
       </c>
       <c r="F113" s="75" t="inlineStr">
         <is>
-          <t>Anuncio 'Hot Chocalate' generó 13 clicks a $35 CPC (excelente), pero $0 en compras. Mismo patrón en 'Fragancias Picnic' (29 clicks, $219 CPC, $0 compras). El tráfico no califica.</t>
+          <t>'Hot Chocalate' ($449 gasto, CTR 4.21%), 'Crema dibujada' ($847), '4 por 3' ($421) generan clicks muy baratos (CPC $35-94). Bajo gasto limita datos pero proporción es prometedora.</t>
         </is>
       </c>
       <c r="M113" s="76" t="inlineStr">
         <is>
-          <t>→ Acción: Implementar pixel de 'ViewContent' más restrictivo. Considerar pausar anuncios link_click y mover presupuesto a campañas purchase con audiencias similares.</t>
+          <t>→ Acción: Incrementar presupuesto en estos 3 anuncios a $5k cada uno. Mantener targeting idéntico pero aumentar reach para validar escalabilidad.</t>
         </is>
       </c>
     </row>

--- a/reportes/Reporte_abril_2026.xlsx
+++ b/reportes/Reporte_abril_2026.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,8 +42,54 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="001E2A38"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001E2A38"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="001E2A38"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="0027AE60"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00E67E22"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00E74C3C"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00888888"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +99,41 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001E2A38"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002C3E50"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0034495E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF9E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E4057"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAFAF1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDEDEC"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -92,6 +173,138 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -458,7 +671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:T5"/>
+  <dimension ref="B1:T185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="2" max="2"/>
@@ -484,7 +697,7 @@
     <row r="1" ht="34" customHeight="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>INFORME META ADS — MARCA — ABRIL 2026</t>
+          <t>INFORME META ADS — ABRIL 2026</t>
         </is>
       </c>
     </row>
@@ -588,10 +801,7968 @@
         </is>
       </c>
     </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Seducete</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>▶ Marketing Objetivo Visita Perfil Instagram</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Tráfico Instagram Academia Cursos Gratuitos</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>42006</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>92084</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>1775</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>1546</v>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>+15%</t>
+        </is>
+      </c>
+      <c r="I9" s="11" t="n">
+        <v>104081</v>
+      </c>
+      <c r="J9" s="11" t="n">
+        <v>58</v>
+      </c>
+      <c r="K9" s="7" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="L9" s="7" t="n">
+        <v>1130</v>
+      </c>
+      <c r="M9" s="7" t="inlineStr"/>
+      <c r="N9" s="7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O9" s="7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P9" s="7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q9" s="7" t="inlineStr"/>
+      <c r="R9" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="S9" s="12" t="inlineStr">
+        <is>
+          <t>🔍 REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Tráfico Cursos Presenciales 03-07</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>46807</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>110373</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>1890</v>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>1847</v>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>+2%</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="n">
+        <v>89642</v>
+      </c>
+      <c r="J10" s="11" t="n">
+        <v>47</v>
+      </c>
+      <c r="K10" s="7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L10" s="7" t="n">
+        <v>812</v>
+      </c>
+      <c r="M10" s="7" t="inlineStr"/>
+      <c r="N10" s="7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O10" s="7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="7" t="inlineStr"/>
+      <c r="R10" s="7" t="inlineStr"/>
+      <c r="S10" s="12" t="inlineStr">
+        <is>
+          <t>🔍 REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>SUBTOTAL  Marketing Objetivo Visita Perfil Instagram</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>3665</v>
+      </c>
+      <c r="G11" s="14" t="n">
+        <v>3393</v>
+      </c>
+      <c r="H11" s="15" t="inlineStr">
+        <is>
+          <t>+8%</t>
+        </is>
+      </c>
+      <c r="I11" s="16" t="n">
+        <v>193723</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>▶ Tráfico Web Objetivo Conversión</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Esmaltado Permanente</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>76804</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>152235</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="G14" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>+1400%</t>
+        </is>
+      </c>
+      <c r="I14" s="11" t="n">
+        <v>164376</v>
+      </c>
+      <c r="J14" s="11" t="n">
+        <v>10958</v>
+      </c>
+      <c r="K14" s="7" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="L14" s="7" t="n">
+        <v>1079</v>
+      </c>
+      <c r="M14" s="7" t="inlineStr"/>
+      <c r="N14" s="7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O14" s="7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P14" s="7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="7" t="n">
+        <v>3966</v>
+      </c>
+      <c r="S14" s="12" t="inlineStr">
+        <is>
+          <t>🔍 REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Manicurista Integral Carrusel</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>4542</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>7022</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>182</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>1027</v>
+      </c>
+      <c r="H15" s="17" t="inlineStr">
+        <is>
+          <t>-82%</t>
+        </is>
+      </c>
+      <c r="I15" s="11" t="n">
+        <v>7688</v>
+      </c>
+      <c r="J15" s="11" t="n">
+        <v>42</v>
+      </c>
+      <c r="K15" s="7" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="L15" s="7" t="n">
+        <v>1094</v>
+      </c>
+      <c r="M15" s="7" t="inlineStr"/>
+      <c r="N15" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O15" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P15" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q15" s="7" t="inlineStr"/>
+      <c r="R15" s="7" t="n">
+        <v>182</v>
+      </c>
+      <c r="S15" s="12" t="inlineStr">
+        <is>
+          <t>🔍 REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>SUBTOTAL  Tráfico Web Objetivo Conversión</t>
+        </is>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>197</v>
+      </c>
+      <c r="G16" s="14" t="n">
+        <v>1028</v>
+      </c>
+      <c r="H16" s="15" t="inlineStr">
+        <is>
+          <t>-81%</t>
+        </is>
+      </c>
+      <c r="I16" s="16" t="n">
+        <v>172064</v>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>▶ Academia Prueba Formularios</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>Academia Prueba Formularios Segundo video</t>
+        </is>
+      </c>
+      <c r="C19" s="19" t="n">
+        <v>36481</v>
+      </c>
+      <c r="D19" s="19" t="n">
+        <v>50951</v>
+      </c>
+      <c r="E19" s="19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F19" s="20" t="n">
+        <v>514</v>
+      </c>
+      <c r="G19" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" s="22" t="inlineStr">
+        <is>
+          <t>+25600%</t>
+        </is>
+      </c>
+      <c r="I19" s="23" t="n">
+        <v>40170</v>
+      </c>
+      <c r="J19" s="23" t="n">
+        <v>78</v>
+      </c>
+      <c r="K19" s="19" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="L19" s="19" t="n">
+        <v>788</v>
+      </c>
+      <c r="M19" s="19" t="inlineStr"/>
+      <c r="N19" s="19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="O19" s="19" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="P19" s="19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Q19" s="19" t="inlineStr"/>
+      <c r="R19" s="19" t="n">
+        <v>81</v>
+      </c>
+      <c r="S19" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>Academia Prueba Formularios Cambio 11-07-2025</t>
+        </is>
+      </c>
+      <c r="C20" s="19" t="n">
+        <v>117212</v>
+      </c>
+      <c r="D20" s="19" t="n">
+        <v>202987</v>
+      </c>
+      <c r="E20" s="19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F20" s="20" t="n">
+        <v>2417</v>
+      </c>
+      <c r="G20" s="21" t="n">
+        <v>2671</v>
+      </c>
+      <c r="H20" s="24" t="inlineStr">
+        <is>
+          <t>-10%</t>
+        </is>
+      </c>
+      <c r="I20" s="23" t="n">
+        <v>182818</v>
+      </c>
+      <c r="J20" s="23" t="n">
+        <v>75</v>
+      </c>
+      <c r="K20" s="19" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="L20" s="19" t="n">
+        <v>900</v>
+      </c>
+      <c r="M20" s="19" t="inlineStr"/>
+      <c r="N20" s="19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O20" s="19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P20" s="19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q20" s="19" t="inlineStr"/>
+      <c r="R20" s="19" t="n">
+        <v>293</v>
+      </c>
+      <c r="S20" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>SUBTOTAL  Academia Prueba Formularios</t>
+        </is>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>2931</v>
+      </c>
+      <c r="G21" s="14" t="n">
+        <v>2673</v>
+      </c>
+      <c r="H21" s="15" t="inlineStr">
+        <is>
+          <t>+10%</t>
+        </is>
+      </c>
+      <c r="I21" s="16" t="n">
+        <v>222988</v>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>▶ Conversión Web Ventas</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Base Evita 2</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>20804</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>68910</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="G24" s="9" t="n">
+        <v>43</v>
+      </c>
+      <c r="H24" s="17" t="inlineStr">
+        <is>
+          <t>-70%</t>
+        </is>
+      </c>
+      <c r="I24" s="11" t="n">
+        <v>141538</v>
+      </c>
+      <c r="J24" s="11" t="n">
+        <v>10887</v>
+      </c>
+      <c r="K24" s="7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="L24" s="7" t="n">
+        <v>2053</v>
+      </c>
+      <c r="M24" s="7" t="inlineStr"/>
+      <c r="N24" s="7" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="O24" s="7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P24" s="7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q24" s="7" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R24" s="7" t="n">
+        <v>614</v>
+      </c>
+      <c r="S24" s="12" t="inlineStr">
+        <is>
+          <t>🔍 REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="B25" s="25" t="inlineStr">
+        <is>
+          <t>Top Templado</t>
+        </is>
+      </c>
+      <c r="C25" s="26" t="n">
+        <v>19145</v>
+      </c>
+      <c r="D25" s="26" t="n">
+        <v>68359</v>
+      </c>
+      <c r="E25" s="26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F25" s="27" t="n">
+        <v>41</v>
+      </c>
+      <c r="G25" s="28" t="n">
+        <v>111</v>
+      </c>
+      <c r="H25" s="29" t="inlineStr">
+        <is>
+          <t>-63%</t>
+        </is>
+      </c>
+      <c r="I25" s="30" t="n">
+        <v>167360</v>
+      </c>
+      <c r="J25" s="30" t="n">
+        <v>4081</v>
+      </c>
+      <c r="K25" s="26" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="L25" s="26" t="n">
+        <v>2448</v>
+      </c>
+      <c r="M25" s="26" t="inlineStr"/>
+      <c r="N25" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="O25" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="P25" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q25" s="26" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R25" s="26" t="n">
+        <v>496</v>
+      </c>
+      <c r="S25" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>Nuevos Esmaltes Satinados Ojo de Gato</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>9896</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>22340</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G26" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="H26" s="17" t="inlineStr">
+        <is>
+          <t>-79%</t>
+        </is>
+      </c>
+      <c r="I26" s="11" t="n">
+        <v>40160</v>
+      </c>
+      <c r="J26" s="11" t="n">
+        <v>10040</v>
+      </c>
+      <c r="K26" s="7" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="L26" s="7" t="n">
+        <v>1797</v>
+      </c>
+      <c r="M26" s="7" t="inlineStr"/>
+      <c r="N26" s="7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="O26" s="7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="P26" s="7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="7" t="n">
+        <v>353</v>
+      </c>
+      <c r="S26" s="12" t="inlineStr">
+        <is>
+          <t>🔍 REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="B27" s="25" t="inlineStr">
+        <is>
+          <t>Efectos Perlados en Polvo</t>
+        </is>
+      </c>
+      <c r="C27" s="26" t="n">
+        <v>24661</v>
+      </c>
+      <c r="D27" s="26" t="n">
+        <v>63423</v>
+      </c>
+      <c r="E27" s="26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F27" s="27" t="n">
+        <v>30</v>
+      </c>
+      <c r="G27" s="28" t="n">
+        <v>42</v>
+      </c>
+      <c r="H27" s="29" t="inlineStr">
+        <is>
+          <t>-29%</t>
+        </is>
+      </c>
+      <c r="I27" s="30" t="n">
+        <v>145413</v>
+      </c>
+      <c r="J27" s="30" t="n">
+        <v>4847</v>
+      </c>
+      <c r="K27" s="26" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="L27" s="26" t="n">
+        <v>2292</v>
+      </c>
+      <c r="M27" s="26" t="inlineStr"/>
+      <c r="N27" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="O27" s="26" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P27" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q27" s="26" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="R27" s="26" t="n">
+        <v>699</v>
+      </c>
+      <c r="S27" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="B28" s="25" t="inlineStr">
+        <is>
+          <t>Sedu Tips Uñas Quebradizas</t>
+        </is>
+      </c>
+      <c r="C28" s="26" t="n">
+        <v>36907</v>
+      </c>
+      <c r="D28" s="26" t="n">
+        <v>103090</v>
+      </c>
+      <c r="E28" s="26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F28" s="27" t="n">
+        <v>34</v>
+      </c>
+      <c r="G28" s="28" t="n">
+        <v>65</v>
+      </c>
+      <c r="H28" s="29" t="inlineStr">
+        <is>
+          <t>-48%</t>
+        </is>
+      </c>
+      <c r="I28" s="30" t="n">
+        <v>195576</v>
+      </c>
+      <c r="J28" s="30" t="n">
+        <v>5752</v>
+      </c>
+      <c r="K28" s="26" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="L28" s="26" t="n">
+        <v>1897</v>
+      </c>
+      <c r="M28" s="26" t="inlineStr"/>
+      <c r="N28" s="26" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="O28" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="P28" s="26" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Q28" s="26" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="R28" s="26" t="n">
+        <v>1709</v>
+      </c>
+      <c r="S28" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="B29" s="18" t="inlineStr">
+        <is>
+          <t>Higienizantes Go Nails</t>
+        </is>
+      </c>
+      <c r="C29" s="19" t="n">
+        <v>79914</v>
+      </c>
+      <c r="D29" s="19" t="n">
+        <v>274090</v>
+      </c>
+      <c r="E29" s="19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F29" s="20" t="n">
+        <v>58</v>
+      </c>
+      <c r="G29" s="21" t="n">
+        <v>123</v>
+      </c>
+      <c r="H29" s="24" t="inlineStr">
+        <is>
+          <t>-53%</t>
+        </is>
+      </c>
+      <c r="I29" s="23" t="n">
+        <v>362926</v>
+      </c>
+      <c r="J29" s="23" t="n">
+        <v>6257</v>
+      </c>
+      <c r="K29" s="19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="L29" s="19" t="n">
+        <v>1324</v>
+      </c>
+      <c r="M29" s="19" t="inlineStr"/>
+      <c r="N29" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="O29" s="19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P29" s="19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q29" s="19" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="R29" s="19" t="n">
+        <v>1982</v>
+      </c>
+      <c r="S29" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Lámpara Pre Curado</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>18932</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>59244</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G30" s="9" t="n">
+        <v>53</v>
+      </c>
+      <c r="H30" s="17" t="inlineStr">
+        <is>
+          <t>-81%</t>
+        </is>
+      </c>
+      <c r="I30" s="11" t="n">
+        <v>111529</v>
+      </c>
+      <c r="J30" s="11" t="n">
+        <v>11152</v>
+      </c>
+      <c r="K30" s="7" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="L30" s="7" t="n">
+        <v>1882</v>
+      </c>
+      <c r="M30" s="7" t="inlineStr"/>
+      <c r="N30" s="7" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="O30" s="7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P30" s="7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q30" s="7" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="R30" s="7" t="n">
+        <v>635</v>
+      </c>
+      <c r="S30" s="12" t="inlineStr">
+        <is>
+          <t>🔍 REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="B31" s="32" t="inlineStr">
+        <is>
+          <t>Ojos Satinados Nuevos</t>
+        </is>
+      </c>
+      <c r="C31" s="33" t="n">
+        <v>11452</v>
+      </c>
+      <c r="D31" s="33" t="n">
+        <v>30532</v>
+      </c>
+      <c r="E31" s="33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F31" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="G31" s="35" t="n">
+        <v>37</v>
+      </c>
+      <c r="H31" s="36" t="inlineStr">
+        <is>
+          <t>-89%</t>
+        </is>
+      </c>
+      <c r="I31" s="37" t="n">
+        <v>79423</v>
+      </c>
+      <c r="J31" s="37" t="n">
+        <v>19855</v>
+      </c>
+      <c r="K31" s="33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L31" s="33" t="n">
+        <v>2601</v>
+      </c>
+      <c r="M31" s="33" t="inlineStr"/>
+      <c r="N31" s="33" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O31" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="P31" s="33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q31" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="33" t="n">
+        <v>422</v>
+      </c>
+      <c r="S31" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Efecto glaseado</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="n">
+        <v>20166</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>55675</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="G32" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="H32" s="17" t="inlineStr">
+        <is>
+          <t>-65%</t>
+        </is>
+      </c>
+      <c r="I32" s="11" t="n">
+        <v>132967</v>
+      </c>
+      <c r="J32" s="11" t="n">
+        <v>11080</v>
+      </c>
+      <c r="K32" s="7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="L32" s="7" t="n">
+        <v>2388</v>
+      </c>
+      <c r="M32" s="7" t="inlineStr"/>
+      <c r="N32" s="7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O32" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="P32" s="7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q32" s="7" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="R32" s="7" t="n">
+        <v>577</v>
+      </c>
+      <c r="S32" s="12" t="inlineStr">
+        <is>
+          <t>🔍 REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="B33" s="25" t="inlineStr">
+        <is>
+          <t>Efecto Ojo de Gato Jo Nail Artist</t>
+        </is>
+      </c>
+      <c r="C33" s="26" t="n">
+        <v>25179</v>
+      </c>
+      <c r="D33" s="26" t="n">
+        <v>63258</v>
+      </c>
+      <c r="E33" s="26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F33" s="27" t="n">
+        <v>25</v>
+      </c>
+      <c r="G33" s="28" t="n">
+        <v>52</v>
+      </c>
+      <c r="H33" s="29" t="inlineStr">
+        <is>
+          <t>-52%</t>
+        </is>
+      </c>
+      <c r="I33" s="30" t="n">
+        <v>139383</v>
+      </c>
+      <c r="J33" s="30" t="n">
+        <v>5575</v>
+      </c>
+      <c r="K33" s="26" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="L33" s="26" t="n">
+        <v>2203</v>
+      </c>
+      <c r="M33" s="26" t="inlineStr"/>
+      <c r="N33" s="26" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="O33" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="P33" s="26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Q33" s="26" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R33" s="26" t="n">
+        <v>1360</v>
+      </c>
+      <c r="S33" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="B34" s="18" t="inlineStr">
+        <is>
+          <t>Carrusel Uñas Marzo</t>
+        </is>
+      </c>
+      <c r="C34" s="19" t="n">
+        <v>34712</v>
+      </c>
+      <c r="D34" s="19" t="n">
+        <v>185773</v>
+      </c>
+      <c r="E34" s="19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F34" s="20" t="n">
+        <v>51</v>
+      </c>
+      <c r="G34" s="21" t="n">
+        <v>204</v>
+      </c>
+      <c r="H34" s="24" t="inlineStr">
+        <is>
+          <t>-75%</t>
+        </is>
+      </c>
+      <c r="I34" s="23" t="n">
+        <v>328986</v>
+      </c>
+      <c r="J34" s="23" t="n">
+        <v>6450</v>
+      </c>
+      <c r="K34" s="19" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="L34" s="19" t="n">
+        <v>1770</v>
+      </c>
+      <c r="M34" s="19" t="inlineStr"/>
+      <c r="N34" s="19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O34" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P34" s="19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q34" s="19" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="R34" s="19" t="n">
+        <v>2169</v>
+      </c>
+      <c r="S34" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="B35" s="18" t="inlineStr">
+        <is>
+          <t>Lanzamiento Jelly Pop</t>
+        </is>
+      </c>
+      <c r="C35" s="19" t="n">
+        <v>30725</v>
+      </c>
+      <c r="D35" s="19" t="n">
+        <v>102889</v>
+      </c>
+      <c r="E35" s="19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F35" s="20" t="n">
+        <v>32</v>
+      </c>
+      <c r="G35" s="21" t="n">
+        <v>85</v>
+      </c>
+      <c r="H35" s="24" t="inlineStr">
+        <is>
+          <t>-62%</t>
+        </is>
+      </c>
+      <c r="I35" s="23" t="n">
+        <v>217189</v>
+      </c>
+      <c r="J35" s="23" t="n">
+        <v>6787</v>
+      </c>
+      <c r="K35" s="19" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="L35" s="19" t="n">
+        <v>2110</v>
+      </c>
+      <c r="M35" s="19" t="inlineStr"/>
+      <c r="N35" s="19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O35" s="19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P35" s="19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q35" s="19" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="R35" s="19" t="n">
+        <v>1223</v>
+      </c>
+      <c r="S35" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="B36" s="25" t="inlineStr">
+        <is>
+          <t>BLACK WEEK INICIO</t>
+        </is>
+      </c>
+      <c r="C36" s="26" t="n">
+        <v>51697</v>
+      </c>
+      <c r="D36" s="26" t="n">
+        <v>263517</v>
+      </c>
+      <c r="E36" s="26" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="F36" s="27" t="n">
+        <v>236</v>
+      </c>
+      <c r="G36" s="28" t="n">
+        <v>159</v>
+      </c>
+      <c r="H36" s="31" t="inlineStr">
+        <is>
+          <t>+48%</t>
+        </is>
+      </c>
+      <c r="I36" s="30" t="n">
+        <v>469274</v>
+      </c>
+      <c r="J36" s="30" t="n">
+        <v>1988</v>
+      </c>
+      <c r="K36" s="26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L36" s="26" t="n">
+        <v>1780</v>
+      </c>
+      <c r="M36" s="26" t="inlineStr"/>
+      <c r="N36" s="26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O36" s="26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P36" s="26" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q36" s="26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="R36" s="26" t="n">
+        <v>3179</v>
+      </c>
+      <c r="S36" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="B37" s="18" t="inlineStr">
+        <is>
+          <t>Torno Artistic</t>
+        </is>
+      </c>
+      <c r="C37" s="19" t="n">
+        <v>25109</v>
+      </c>
+      <c r="D37" s="19" t="n">
+        <v>116171</v>
+      </c>
+      <c r="E37" s="19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F37" s="20" t="n">
+        <v>35</v>
+      </c>
+      <c r="G37" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H37" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I37" s="23" t="n">
+        <v>216099</v>
+      </c>
+      <c r="J37" s="23" t="n">
+        <v>6174</v>
+      </c>
+      <c r="K37" s="19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="L37" s="19" t="n">
+        <v>1860</v>
+      </c>
+      <c r="M37" s="19" t="inlineStr"/>
+      <c r="N37" s="19" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O37" s="19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P37" s="19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q37" s="19" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="R37" s="19" t="n">
+        <v>1406</v>
+      </c>
+      <c r="S37" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="B38" s="18" t="inlineStr">
+        <is>
+          <t>Lampara Artistic</t>
+        </is>
+      </c>
+      <c r="C38" s="19" t="n">
+        <v>15344</v>
+      </c>
+      <c r="D38" s="19" t="n">
+        <v>57335</v>
+      </c>
+      <c r="E38" s="19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F38" s="20" t="n">
+        <v>11</v>
+      </c>
+      <c r="G38" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H38" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I38" s="23" t="n">
+        <v>104759</v>
+      </c>
+      <c r="J38" s="23" t="n">
+        <v>9523</v>
+      </c>
+      <c r="K38" s="19" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="L38" s="19" t="n">
+        <v>1827</v>
+      </c>
+      <c r="M38" s="19" t="inlineStr"/>
+      <c r="N38" s="19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O38" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="P38" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q38" s="19" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="R38" s="19" t="n">
+        <v>628</v>
+      </c>
+      <c r="S38" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="B39" s="18" t="inlineStr">
+        <is>
+          <t>Esmaltes Otoño Invierno 2026</t>
+        </is>
+      </c>
+      <c r="C39" s="19" t="n">
+        <v>35881</v>
+      </c>
+      <c r="D39" s="19" t="n">
+        <v>201828</v>
+      </c>
+      <c r="E39" s="19" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F39" s="20" t="n">
+        <v>54</v>
+      </c>
+      <c r="G39" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H39" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I39" s="23" t="n">
+        <v>396676</v>
+      </c>
+      <c r="J39" s="23" t="n">
+        <v>7345</v>
+      </c>
+      <c r="K39" s="19" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L39" s="19" t="n">
+        <v>1965</v>
+      </c>
+      <c r="M39" s="19" t="inlineStr"/>
+      <c r="N39" s="19" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="O39" s="19" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="P39" s="19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Q39" s="19" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="R39" s="19" t="n">
+        <v>1423</v>
+      </c>
+      <c r="S39" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>Día de la madre</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>44954</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>188371</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F40" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="G40" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H40" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I40" s="11" t="n">
+        <v>315626</v>
+      </c>
+      <c r="J40" s="11" t="n">
+        <v>12625</v>
+      </c>
+      <c r="K40" s="7" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L40" s="7" t="n">
+        <v>1675</v>
+      </c>
+      <c r="M40" s="7" t="inlineStr"/>
+      <c r="N40" s="7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O40" s="7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P40" s="7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" s="7" t="n">
+        <v>1359</v>
+      </c>
+      <c r="S40" s="12" t="inlineStr">
+        <is>
+          <t>🔍 REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="25" t="inlineStr">
+        <is>
+          <t>Oferta Básicos Manicure</t>
+        </is>
+      </c>
+      <c r="C41" s="26" t="n">
+        <v>87484</v>
+      </c>
+      <c r="D41" s="26" t="n">
+        <v>404390</v>
+      </c>
+      <c r="E41" s="26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F41" s="27" t="n">
+        <v>167</v>
+      </c>
+      <c r="G41" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H41" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I41" s="30" t="n">
+        <v>742546</v>
+      </c>
+      <c r="J41" s="30" t="n">
+        <v>4446</v>
+      </c>
+      <c r="K41" s="26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L41" s="26" t="n">
+        <v>1836</v>
+      </c>
+      <c r="M41" s="26" t="inlineStr"/>
+      <c r="N41" s="26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O41" s="26" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P41" s="26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q41" s="26" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="R41" s="26" t="n">
+        <v>4338</v>
+      </c>
+      <c r="S41" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="25" t="inlineStr">
+        <is>
+          <t>Lámpara Artistic</t>
+        </is>
+      </c>
+      <c r="C42" s="26" t="n">
+        <v>5078</v>
+      </c>
+      <c r="D42" s="26" t="n">
+        <v>6233</v>
+      </c>
+      <c r="E42" s="26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F42" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="G42" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H42" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I42" s="30" t="n">
+        <v>14406</v>
+      </c>
+      <c r="J42" s="30" t="n">
+        <v>3601</v>
+      </c>
+      <c r="K42" s="26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="L42" s="26" t="n">
+        <v>2311</v>
+      </c>
+      <c r="M42" s="26" t="inlineStr"/>
+      <c r="N42" s="26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O42" s="26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P42" s="26" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q42" s="26" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="R42" s="26" t="n">
+        <v>57</v>
+      </c>
+      <c r="S42" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="32" t="inlineStr">
+        <is>
+          <t>Torno Artistic</t>
+        </is>
+      </c>
+      <c r="C43" s="33" t="n">
+        <v>838</v>
+      </c>
+      <c r="D43" s="33" t="n">
+        <v>1117</v>
+      </c>
+      <c r="E43" s="33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F43" s="34" t="n">
+        <v>25</v>
+      </c>
+      <c r="G43" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H43" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I43" s="37" t="n">
+        <v>4202</v>
+      </c>
+      <c r="J43" s="37" t="n">
+        <v>168</v>
+      </c>
+      <c r="K43" s="33" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="L43" s="33" t="n">
+        <v>3761</v>
+      </c>
+      <c r="M43" s="33" t="inlineStr"/>
+      <c r="N43" s="33" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="O43" s="33" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="P43" s="33" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Q43" s="33" t="inlineStr"/>
+      <c r="R43" s="33" t="n">
+        <v>25</v>
+      </c>
+      <c r="S43" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="32" t="inlineStr">
+        <is>
+          <t>Starter Kit Bluesky</t>
+        </is>
+      </c>
+      <c r="C44" s="33" t="n">
+        <v>20257</v>
+      </c>
+      <c r="D44" s="33" t="n">
+        <v>46481</v>
+      </c>
+      <c r="E44" s="33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F44" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G44" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H44" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I44" s="37" t="n">
+        <v>115009</v>
+      </c>
+      <c r="J44" s="37" t="n">
+        <v>38336</v>
+      </c>
+      <c r="K44" s="33" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="L44" s="33" t="n">
+        <v>2474</v>
+      </c>
+      <c r="M44" s="33" t="inlineStr"/>
+      <c r="N44" s="33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O44" s="33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P44" s="33" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q44" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" s="33" t="n">
+        <v>613</v>
+      </c>
+      <c r="S44" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="B45" s="13" t="inlineStr">
+        <is>
+          <t>SUBTOTAL  Conversión Web Ventas</t>
+        </is>
+      </c>
+      <c r="F45" s="14" t="n">
+        <v>874</v>
+      </c>
+      <c r="G45" s="14" t="n">
+        <v>1027</v>
+      </c>
+      <c r="H45" s="15" t="inlineStr">
+        <is>
+          <t>-15%</t>
+        </is>
+      </c>
+      <c r="I45" s="16" t="n">
+        <v>4441047</v>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>▶ Campaña Mktg prueba Pau</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="B48" s="25" t="inlineStr">
+        <is>
+          <t>Se te quebró la uña agosto</t>
+        </is>
+      </c>
+      <c r="C48" s="26" t="n">
+        <v>204799</v>
+      </c>
+      <c r="D48" s="26" t="n">
+        <v>224297</v>
+      </c>
+      <c r="E48" s="26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F48" s="27" t="n">
+        <v>22721</v>
+      </c>
+      <c r="G48" s="28" t="n">
+        <v>25762</v>
+      </c>
+      <c r="H48" s="29" t="inlineStr">
+        <is>
+          <t>-12%</t>
+        </is>
+      </c>
+      <c r="I48" s="30" t="n">
+        <v>99149</v>
+      </c>
+      <c r="J48" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="K48" s="26" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="L48" s="26" t="n">
+        <v>442</v>
+      </c>
+      <c r="M48" s="26" t="inlineStr"/>
+      <c r="N48" s="26" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="O48" s="26" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="P48" s="26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Q48" s="26" t="inlineStr"/>
+      <c r="R48" s="26" t="inlineStr"/>
+      <c r="S48" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="B49" s="25" t="inlineStr">
+        <is>
+          <t>uñas respiran</t>
+        </is>
+      </c>
+      <c r="C49" s="26" t="n">
+        <v>87</v>
+      </c>
+      <c r="D49" s="26" t="n">
+        <v>92</v>
+      </c>
+      <c r="E49" s="26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F49" s="27" t="n">
+        <v>8</v>
+      </c>
+      <c r="G49" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H49" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I49" s="30" t="n">
+        <v>41</v>
+      </c>
+      <c r="J49" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="K49" s="26" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="L49" s="26" t="n">
+        <v>445</v>
+      </c>
+      <c r="M49" s="26" t="inlineStr"/>
+      <c r="N49" s="26" t="inlineStr"/>
+      <c r="O49" s="26" t="inlineStr"/>
+      <c r="P49" s="26" t="inlineStr"/>
+      <c r="Q49" s="26" t="inlineStr"/>
+      <c r="R49" s="26" t="inlineStr"/>
+      <c r="S49" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="B50" s="25" t="inlineStr">
+        <is>
+          <t>5 cosas que no sabias</t>
+        </is>
+      </c>
+      <c r="C50" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="D50" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="E50" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G50" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" s="31" t="inlineStr">
+        <is>
+          <t>+100%</t>
+        </is>
+      </c>
+      <c r="I50" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="J50" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="K50" s="26" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="L50" s="26" t="n">
+        <v>666</v>
+      </c>
+      <c r="M50" s="26" t="inlineStr"/>
+      <c r="N50" s="26" t="inlineStr"/>
+      <c r="O50" s="26" t="inlineStr"/>
+      <c r="P50" s="26" t="inlineStr"/>
+      <c r="Q50" s="26" t="inlineStr"/>
+      <c r="R50" s="26" t="inlineStr"/>
+      <c r="S50" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="B51" s="25" t="inlineStr">
+        <is>
+          <t>sedu hannah montana</t>
+        </is>
+      </c>
+      <c r="C51" s="26" t="n">
+        <v>87</v>
+      </c>
+      <c r="D51" s="26" t="n">
+        <v>91</v>
+      </c>
+      <c r="E51" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="G51" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H51" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I51" s="30" t="n">
+        <v>39</v>
+      </c>
+      <c r="J51" s="30" t="n">
+        <v>13</v>
+      </c>
+      <c r="K51" s="26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L51" s="26" t="n">
+        <v>428</v>
+      </c>
+      <c r="M51" s="26" t="inlineStr"/>
+      <c r="N51" s="26" t="inlineStr"/>
+      <c r="O51" s="26" t="inlineStr"/>
+      <c r="P51" s="26" t="inlineStr"/>
+      <c r="Q51" s="26" t="inlineStr"/>
+      <c r="R51" s="26" t="inlineStr"/>
+      <c r="S51" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="B52" s="25" t="inlineStr">
+        <is>
+          <t>uñas de otoño 2026</t>
+        </is>
+      </c>
+      <c r="C52" s="26" t="n">
+        <v>180</v>
+      </c>
+      <c r="D52" s="26" t="n">
+        <v>184</v>
+      </c>
+      <c r="E52" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="G52" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H52" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I52" s="30" t="n">
+        <v>144</v>
+      </c>
+      <c r="J52" s="30" t="n">
+        <v>16</v>
+      </c>
+      <c r="K52" s="26" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="L52" s="26" t="n">
+        <v>782</v>
+      </c>
+      <c r="M52" s="26" t="inlineStr"/>
+      <c r="N52" s="26" t="inlineStr"/>
+      <c r="O52" s="26" t="inlineStr"/>
+      <c r="P52" s="26" t="inlineStr"/>
+      <c r="Q52" s="26" t="inlineStr"/>
+      <c r="R52" s="26" t="inlineStr"/>
+      <c r="S52" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>SUBTOTAL  Campaña Mktg prueba Pau</t>
+        </is>
+      </c>
+      <c r="F53" s="14" t="n">
+        <v>22743</v>
+      </c>
+      <c r="G53" s="14" t="n">
+        <v>25763</v>
+      </c>
+      <c r="H53" s="15" t="inlineStr">
+        <is>
+          <t>-12%</t>
+        </is>
+      </c>
+      <c r="I53" s="16" t="n">
+        <v>99381</v>
+      </c>
+    </row>
+    <row r="56" ht="24" customHeight="1">
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>Bluesky</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>▶ Tráfico Perfil Instagram MKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="B58" s="25" t="inlineStr">
+        <is>
+          <t>Diseño Floral</t>
+        </is>
+      </c>
+      <c r="C58" s="26" t="n">
+        <v>30753</v>
+      </c>
+      <c r="D58" s="26" t="n">
+        <v>37195</v>
+      </c>
+      <c r="E58" s="26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F58" s="27" t="n">
+        <v>2662</v>
+      </c>
+      <c r="G58" s="28" t="n">
+        <v>12461</v>
+      </c>
+      <c r="H58" s="29" t="inlineStr">
+        <is>
+          <t>-79%</t>
+        </is>
+      </c>
+      <c r="I58" s="30" t="n">
+        <v>15873</v>
+      </c>
+      <c r="J58" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="K58" s="26" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="L58" s="26" t="n">
+        <v>426</v>
+      </c>
+      <c r="M58" s="26" t="inlineStr"/>
+      <c r="N58" s="26" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="O58" s="26" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="P58" s="26" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q58" s="26" t="inlineStr"/>
+      <c r="R58" s="26" t="inlineStr"/>
+      <c r="S58" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="B59" s="25" t="inlineStr">
+        <is>
+          <t>Diseño Conchitas</t>
+        </is>
+      </c>
+      <c r="C59" s="26" t="n">
+        <v>94307</v>
+      </c>
+      <c r="D59" s="26" t="n">
+        <v>156620</v>
+      </c>
+      <c r="E59" s="26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F59" s="27" t="n">
+        <v>11185</v>
+      </c>
+      <c r="G59" s="28" t="n">
+        <v>3161</v>
+      </c>
+      <c r="H59" s="31" t="inlineStr">
+        <is>
+          <t>+254%</t>
+        </is>
+      </c>
+      <c r="I59" s="30" t="n">
+        <v>69955</v>
+      </c>
+      <c r="J59" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="K59" s="26" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="L59" s="26" t="n">
+        <v>446</v>
+      </c>
+      <c r="M59" s="26" t="inlineStr"/>
+      <c r="N59" s="26" t="n">
+        <v>25</v>
+      </c>
+      <c r="O59" s="26" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="P59" s="26" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q59" s="26" t="inlineStr"/>
+      <c r="R59" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="S59" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="B60" s="25" t="inlineStr">
+        <is>
+          <t>diseño limon verano</t>
+        </is>
+      </c>
+      <c r="C60" s="26" t="n">
+        <v>6181</v>
+      </c>
+      <c r="D60" s="26" t="n">
+        <v>6691</v>
+      </c>
+      <c r="E60" s="26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F60" s="27" t="n">
+        <v>509</v>
+      </c>
+      <c r="G60" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="H60" s="31" t="inlineStr">
+        <is>
+          <t>+25350%</t>
+        </is>
+      </c>
+      <c r="I60" s="30" t="n">
+        <v>3312</v>
+      </c>
+      <c r="J60" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="K60" s="26" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="L60" s="26" t="n">
+        <v>494</v>
+      </c>
+      <c r="M60" s="26" t="inlineStr"/>
+      <c r="N60" s="26" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="O60" s="26" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="P60" s="26" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="Q60" s="26" t="inlineStr"/>
+      <c r="R60" s="26" t="inlineStr"/>
+      <c r="S60" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="B61" s="25" t="inlineStr">
+        <is>
+          <t>prueba 1 tendencia</t>
+        </is>
+      </c>
+      <c r="C61" s="26" t="n">
+        <v>71</v>
+      </c>
+      <c r="D61" s="26" t="n">
+        <v>77</v>
+      </c>
+      <c r="E61" s="26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F61" s="27" t="n">
+        <v>8</v>
+      </c>
+      <c r="G61" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H61" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I61" s="30" t="n">
+        <v>36</v>
+      </c>
+      <c r="J61" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="K61" s="26" t="n">
+        <v>10.39</v>
+      </c>
+      <c r="L61" s="26" t="n">
+        <v>467</v>
+      </c>
+      <c r="M61" s="26" t="inlineStr"/>
+      <c r="N61" s="26" t="inlineStr"/>
+      <c r="O61" s="26" t="inlineStr"/>
+      <c r="P61" s="26" t="inlineStr"/>
+      <c r="Q61" s="26" t="inlineStr"/>
+      <c r="R61" s="26" t="inlineStr"/>
+      <c r="S61" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="B62" s="13" t="inlineStr">
+        <is>
+          <t>SUBTOTAL  Tráfico Perfil Instagram MKT</t>
+        </is>
+      </c>
+      <c r="F62" s="14" t="n">
+        <v>14364</v>
+      </c>
+      <c r="G62" s="14" t="n">
+        <v>15624</v>
+      </c>
+      <c r="H62" s="15" t="inlineStr">
+        <is>
+          <t>-8%</t>
+        </is>
+      </c>
+      <c r="I62" s="16" t="n">
+        <v>89176</v>
+      </c>
+    </row>
+    <row r="65" ht="24" customHeight="1">
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>Nail Outlet</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>▶ Objetivo Conversión Ventas</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>Esmaltes French Nail Pro</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="n">
+        <v>12055</v>
+      </c>
+      <c r="D67" s="7" t="n">
+        <v>38382</v>
+      </c>
+      <c r="E67" s="7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F67" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G67" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="H67" s="17" t="inlineStr">
+        <is>
+          <t>-57%</t>
+        </is>
+      </c>
+      <c r="I67" s="11" t="n">
+        <v>76227</v>
+      </c>
+      <c r="J67" s="11" t="n">
+        <v>12704</v>
+      </c>
+      <c r="K67" s="7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="L67" s="7" t="n">
+        <v>1986</v>
+      </c>
+      <c r="M67" s="7" t="inlineStr"/>
+      <c r="N67" s="7" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="O67" s="7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="P67" s="7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q67" s="7" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="R67" s="7" t="n">
+        <v>285</v>
+      </c>
+      <c r="S67" s="12" t="inlineStr">
+        <is>
+          <t>🔍 REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="B68" s="32" t="inlineStr">
+        <is>
+          <t>40 Esmaltes Julio</t>
+        </is>
+      </c>
+      <c r="C68" s="33" t="n">
+        <v>12455</v>
+      </c>
+      <c r="D68" s="33" t="n">
+        <v>32741</v>
+      </c>
+      <c r="E68" s="33" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F68" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G68" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="H68" s="36" t="inlineStr">
+        <is>
+          <t>-40%</t>
+        </is>
+      </c>
+      <c r="I68" s="37" t="n">
+        <v>57856</v>
+      </c>
+      <c r="J68" s="37" t="n">
+        <v>19285</v>
+      </c>
+      <c r="K68" s="33" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="L68" s="33" t="n">
+        <v>1767</v>
+      </c>
+      <c r="M68" s="33" t="inlineStr"/>
+      <c r="N68" s="33" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O68" s="33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P68" s="33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q68" s="33" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="R68" s="33" t="n">
+        <v>260</v>
+      </c>
+      <c r="S68" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="B69" s="18" t="inlineStr">
+        <is>
+          <t>Pack Repo 20 Agosto</t>
+        </is>
+      </c>
+      <c r="C69" s="19" t="n">
+        <v>24479</v>
+      </c>
+      <c r="D69" s="19" t="n">
+        <v>93364</v>
+      </c>
+      <c r="E69" s="19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F69" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="G69" s="21" t="n">
+        <v>38</v>
+      </c>
+      <c r="H69" s="24" t="inlineStr">
+        <is>
+          <t>-47%</t>
+        </is>
+      </c>
+      <c r="I69" s="23" t="n">
+        <v>167478</v>
+      </c>
+      <c r="J69" s="23" t="n">
+        <v>8373</v>
+      </c>
+      <c r="K69" s="19" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="L69" s="19" t="n">
+        <v>1793</v>
+      </c>
+      <c r="M69" s="19" t="inlineStr"/>
+      <c r="N69" s="19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O69" s="19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P69" s="19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q69" s="19" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="R69" s="19" t="n">
+        <v>823</v>
+      </c>
+      <c r="S69" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="B70" s="32" t="inlineStr">
+        <is>
+          <t>Efectos Chromados</t>
+        </is>
+      </c>
+      <c r="C70" s="33" t="n">
+        <v>5408</v>
+      </c>
+      <c r="D70" s="33" t="n">
+        <v>10991</v>
+      </c>
+      <c r="E70" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F70" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="H70" s="36" t="inlineStr">
+        <is>
+          <t>-88%</t>
+        </is>
+      </c>
+      <c r="I70" s="37" t="n">
+        <v>22114</v>
+      </c>
+      <c r="J70" s="37" t="n">
+        <v>22114</v>
+      </c>
+      <c r="K70" s="33" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="L70" s="33" t="n">
+        <v>2012</v>
+      </c>
+      <c r="M70" s="33" t="inlineStr"/>
+      <c r="N70" s="33" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O70" s="33" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P70" s="33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q70" s="33" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R70" s="33" t="n">
+        <v>107</v>
+      </c>
+      <c r="S70" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="B71" s="32" t="inlineStr">
+        <is>
+          <t>Campo de Trabajo</t>
+        </is>
+      </c>
+      <c r="C71" s="33" t="n">
+        <v>18936</v>
+      </c>
+      <c r="D71" s="33" t="n">
+        <v>51295</v>
+      </c>
+      <c r="E71" s="33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F71" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="G71" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="H71" s="36" t="inlineStr">
+        <is>
+          <t>-64%</t>
+        </is>
+      </c>
+      <c r="I71" s="37" t="n">
+        <v>90941</v>
+      </c>
+      <c r="J71" s="37" t="n">
+        <v>18188</v>
+      </c>
+      <c r="K71" s="33" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="L71" s="33" t="n">
+        <v>1772</v>
+      </c>
+      <c r="M71" s="33" t="inlineStr"/>
+      <c r="N71" s="33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O71" s="33" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P71" s="33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q71" s="33" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="R71" s="33" t="n">
+        <v>567</v>
+      </c>
+      <c r="S71" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="B72" s="32" t="inlineStr">
+        <is>
+          <t>Ojo de Gato</t>
+        </is>
+      </c>
+      <c r="C72" s="33" t="n">
+        <v>794</v>
+      </c>
+      <c r="D72" s="33" t="n">
+        <v>1037</v>
+      </c>
+      <c r="E72" s="33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F72" s="34" t="n">
+        <v>18</v>
+      </c>
+      <c r="G72" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="H72" s="46" t="inlineStr">
+        <is>
+          <t>+157%</t>
+        </is>
+      </c>
+      <c r="I72" s="37" t="n">
+        <v>4115</v>
+      </c>
+      <c r="J72" s="37" t="n">
+        <v>228</v>
+      </c>
+      <c r="K72" s="33" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="L72" s="33" t="n">
+        <v>3968</v>
+      </c>
+      <c r="M72" s="33" t="inlineStr"/>
+      <c r="N72" s="33" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O72" s="33" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P72" s="33" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q72" s="33" t="inlineStr"/>
+      <c r="R72" s="33" t="n">
+        <v>15</v>
+      </c>
+      <c r="S72" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="18" customHeight="1">
+      <c r="B73" s="18" t="inlineStr">
+        <is>
+          <t>Carrusel TPO Chile</t>
+        </is>
+      </c>
+      <c r="C73" s="19" t="n">
+        <v>4805</v>
+      </c>
+      <c r="D73" s="19" t="n">
+        <v>12499</v>
+      </c>
+      <c r="E73" s="19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F73" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="G73" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H73" s="24" t="inlineStr">
+        <is>
+          <t>-75%</t>
+        </is>
+      </c>
+      <c r="I73" s="23" t="n">
+        <v>25343</v>
+      </c>
+      <c r="J73" s="23" t="n">
+        <v>8447</v>
+      </c>
+      <c r="K73" s="19" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="L73" s="19" t="n">
+        <v>2027</v>
+      </c>
+      <c r="M73" s="19" t="inlineStr"/>
+      <c r="N73" s="19" t="inlineStr"/>
+      <c r="O73" s="19" t="inlineStr"/>
+      <c r="P73" s="19" t="inlineStr"/>
+      <c r="Q73" s="19" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="R73" s="19" t="n">
+        <v>139</v>
+      </c>
+      <c r="S73" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="B74" s="32" t="inlineStr">
+        <is>
+          <t>Imagen primer deshidratador</t>
+        </is>
+      </c>
+      <c r="C74" s="33" t="n">
+        <v>15325</v>
+      </c>
+      <c r="D74" s="33" t="n">
+        <v>36143</v>
+      </c>
+      <c r="E74" s="33" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F74" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G74" s="35" t="n">
+        <v>13</v>
+      </c>
+      <c r="H74" s="36" t="inlineStr">
+        <is>
+          <t>-85%</t>
+        </is>
+      </c>
+      <c r="I74" s="37" t="n">
+        <v>59036</v>
+      </c>
+      <c r="J74" s="37" t="n">
+        <v>29518</v>
+      </c>
+      <c r="K74" s="33" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="L74" s="33" t="n">
+        <v>1633</v>
+      </c>
+      <c r="M74" s="33" t="inlineStr"/>
+      <c r="N74" s="33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O74" s="33" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P74" s="33" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q74" s="33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R74" s="33" t="n">
+        <v>568</v>
+      </c>
+      <c r="S74" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="18" customHeight="1">
+      <c r="B75" s="25" t="inlineStr">
+        <is>
+          <t>Poly Gel Carrusel</t>
+        </is>
+      </c>
+      <c r="C75" s="26" t="n">
+        <v>1003</v>
+      </c>
+      <c r="D75" s="26" t="n">
+        <v>2028</v>
+      </c>
+      <c r="E75" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F75" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="G75" s="28" t="n">
+        <v>73</v>
+      </c>
+      <c r="H75" s="29" t="inlineStr">
+        <is>
+          <t>-90%</t>
+        </is>
+      </c>
+      <c r="I75" s="30" t="n">
+        <v>3237</v>
+      </c>
+      <c r="J75" s="30" t="n">
+        <v>462</v>
+      </c>
+      <c r="K75" s="26" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="L75" s="26" t="n">
+        <v>1596</v>
+      </c>
+      <c r="M75" s="26" t="inlineStr"/>
+      <c r="N75" s="26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O75" s="26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P75" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q75" s="26" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="R75" s="26" t="n">
+        <v>21</v>
+      </c>
+      <c r="S75" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="18" customHeight="1">
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>Reel Ojo de Gato</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="n">
+        <v>3199</v>
+      </c>
+      <c r="D76" s="7" t="n">
+        <v>7605</v>
+      </c>
+      <c r="E76" s="7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F76" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H76" s="17" t="inlineStr">
+        <is>
+          <t>-50%</t>
+        </is>
+      </c>
+      <c r="I76" s="11" t="n">
+        <v>12486</v>
+      </c>
+      <c r="J76" s="11" t="n">
+        <v>12486</v>
+      </c>
+      <c r="K76" s="7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L76" s="7" t="n">
+        <v>1641</v>
+      </c>
+      <c r="M76" s="7" t="inlineStr"/>
+      <c r="N76" s="7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O76" s="7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="P76" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q76" s="7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R76" s="7" t="n">
+        <v>106</v>
+      </c>
+      <c r="S76" s="12" t="inlineStr">
+        <is>
+          <t>🔍 REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="18" customHeight="1">
+      <c r="B77" s="25" t="inlineStr">
+        <is>
+          <t>Imagen Mesa Nail Pro</t>
+        </is>
+      </c>
+      <c r="C77" s="26" t="n">
+        <v>17596</v>
+      </c>
+      <c r="D77" s="26" t="n">
+        <v>58494</v>
+      </c>
+      <c r="E77" s="26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F77" s="27" t="n">
+        <v>22</v>
+      </c>
+      <c r="G77" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="H77" s="31" t="inlineStr">
+        <is>
+          <t>+120%</t>
+        </is>
+      </c>
+      <c r="I77" s="30" t="n">
+        <v>108515</v>
+      </c>
+      <c r="J77" s="30" t="n">
+        <v>4932</v>
+      </c>
+      <c r="K77" s="26" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="L77" s="26" t="n">
+        <v>1855</v>
+      </c>
+      <c r="M77" s="26" t="inlineStr"/>
+      <c r="N77" s="26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O77" s="26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P77" s="26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q77" s="26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R77" s="26" t="n">
+        <v>1037</v>
+      </c>
+      <c r="S77" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="B78" s="25" t="inlineStr">
+        <is>
+          <t>Imagen Limas y herramientas</t>
+        </is>
+      </c>
+      <c r="C78" s="26" t="n">
+        <v>6704</v>
+      </c>
+      <c r="D78" s="26" t="n">
+        <v>17694</v>
+      </c>
+      <c r="E78" s="26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F78" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="G78" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="H78" s="31" t="inlineStr">
+        <is>
+          <t>+250%</t>
+        </is>
+      </c>
+      <c r="I78" s="30" t="n">
+        <v>22383</v>
+      </c>
+      <c r="J78" s="30" t="n">
+        <v>3197</v>
+      </c>
+      <c r="K78" s="26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="L78" s="26" t="n">
+        <v>1265</v>
+      </c>
+      <c r="M78" s="26" t="inlineStr"/>
+      <c r="N78" s="26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O78" s="26" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P78" s="26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q78" s="26" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="R78" s="26" t="n">
+        <v>143</v>
+      </c>
+      <c r="S78" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="B79" s="18" t="inlineStr">
+        <is>
+          <t>Black Week</t>
+        </is>
+      </c>
+      <c r="C79" s="19" t="n">
+        <v>31221</v>
+      </c>
+      <c r="D79" s="19" t="n">
+        <v>128663</v>
+      </c>
+      <c r="E79" s="19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="F79" s="20" t="n">
+        <v>23</v>
+      </c>
+      <c r="G79" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="H79" s="22" t="inlineStr">
+        <is>
+          <t>+229%</t>
+        </is>
+      </c>
+      <c r="I79" s="23" t="n">
+        <v>189790</v>
+      </c>
+      <c r="J79" s="23" t="n">
+        <v>8251</v>
+      </c>
+      <c r="K79" s="19" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="L79" s="19" t="n">
+        <v>1475</v>
+      </c>
+      <c r="M79" s="19" t="inlineStr"/>
+      <c r="N79" s="19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O79" s="19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P79" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q79" s="19" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="R79" s="19" t="n">
+        <v>1291</v>
+      </c>
+      <c r="S79" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="B80" s="32" t="inlineStr">
+        <is>
+          <t>Pack 12 Esmaltes Nail Pro</t>
+        </is>
+      </c>
+      <c r="C80" s="33" t="n">
+        <v>15449</v>
+      </c>
+      <c r="D80" s="33" t="n">
+        <v>34999</v>
+      </c>
+      <c r="E80" s="33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F80" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G80" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" s="37" t="n">
+        <v>43766</v>
+      </c>
+      <c r="J80" s="37" t="n">
+        <v>21883</v>
+      </c>
+      <c r="K80" s="33" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="L80" s="33" t="n">
+        <v>1250</v>
+      </c>
+      <c r="M80" s="33" t="inlineStr"/>
+      <c r="N80" s="33" t="inlineStr"/>
+      <c r="O80" s="33" t="inlineStr"/>
+      <c r="P80" s="33" t="inlineStr"/>
+      <c r="Q80" s="33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R80" s="33" t="n">
+        <v>348</v>
+      </c>
+      <c r="S80" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="B81" s="32" t="inlineStr">
+        <is>
+          <t>Como usar Deshidratador</t>
+        </is>
+      </c>
+      <c r="C81" s="33" t="n">
+        <v>3062</v>
+      </c>
+      <c r="D81" s="33" t="n">
+        <v>8111</v>
+      </c>
+      <c r="E81" s="33" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F81" s="34" t="n">
+        <v>90</v>
+      </c>
+      <c r="G81" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="37" t="n">
+        <v>14822</v>
+      </c>
+      <c r="J81" s="37" t="n">
+        <v>164</v>
+      </c>
+      <c r="K81" s="33" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="L81" s="33" t="n">
+        <v>1827</v>
+      </c>
+      <c r="M81" s="33" t="inlineStr"/>
+      <c r="N81" s="33" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O81" s="33" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P81" s="33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q81" s="33" t="inlineStr"/>
+      <c r="R81" s="33" t="n">
+        <v>90</v>
+      </c>
+      <c r="S81" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="B82" s="13" t="inlineStr">
+        <is>
+          <t>SUBTOTAL  Objetivo Conversión Ventas</t>
+        </is>
+      </c>
+      <c r="F82" s="14" t="n">
+        <v>210</v>
+      </c>
+      <c r="G82" s="14" t="n">
+        <v>205</v>
+      </c>
+      <c r="H82" s="15" t="inlineStr">
+        <is>
+          <t>+2%</t>
+        </is>
+      </c>
+      <c r="I82" s="16" t="n">
+        <v>898109</v>
+      </c>
+    </row>
+    <row r="84" ht="22" customHeight="1">
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>▶ Tráfico Perfil Instagram MKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="18" customHeight="1">
+      <c r="B85" s="18" t="inlineStr">
+        <is>
+          <t>Insta Nail Pro</t>
+        </is>
+      </c>
+      <c r="C85" s="19" t="n">
+        <v>44949</v>
+      </c>
+      <c r="D85" s="19" t="n">
+        <v>75263</v>
+      </c>
+      <c r="E85" s="19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F85" s="20" t="n">
+        <v>2127</v>
+      </c>
+      <c r="G85" s="21" t="n">
+        <v>1838</v>
+      </c>
+      <c r="H85" s="22" t="inlineStr">
+        <is>
+          <t>+16%</t>
+        </is>
+      </c>
+      <c r="I85" s="23" t="n">
+        <v>48855</v>
+      </c>
+      <c r="J85" s="23" t="n">
+        <v>22</v>
+      </c>
+      <c r="K85" s="19" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="L85" s="19" t="n">
+        <v>649</v>
+      </c>
+      <c r="M85" s="19" t="inlineStr"/>
+      <c r="N85" s="19" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="O85" s="19" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="P85" s="19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Q85" s="19" t="inlineStr"/>
+      <c r="R85" s="19" t="inlineStr"/>
+      <c r="S85" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="B86" s="18" t="inlineStr">
+        <is>
+          <t>Paso a paso Vale Nails</t>
+        </is>
+      </c>
+      <c r="C86" s="19" t="n">
+        <v>26861</v>
+      </c>
+      <c r="D86" s="19" t="n">
+        <v>46829</v>
+      </c>
+      <c r="E86" s="19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F86" s="20" t="n">
+        <v>1930</v>
+      </c>
+      <c r="G86" s="21" t="n">
+        <v>2984</v>
+      </c>
+      <c r="H86" s="24" t="inlineStr">
+        <is>
+          <t>-35%</t>
+        </is>
+      </c>
+      <c r="I86" s="23" t="n">
+        <v>41059</v>
+      </c>
+      <c r="J86" s="23" t="n">
+        <v>21</v>
+      </c>
+      <c r="K86" s="19" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="L86" s="19" t="n">
+        <v>876</v>
+      </c>
+      <c r="M86" s="19" t="inlineStr"/>
+      <c r="N86" s="19" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="O86" s="19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="P86" s="19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q86" s="19" t="inlineStr"/>
+      <c r="R86" s="19" t="inlineStr"/>
+      <c r="S86" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="B87" s="13" t="inlineStr">
+        <is>
+          <t>SUBTOTAL  Tráfico Perfil Instagram MKT</t>
+        </is>
+      </c>
+      <c r="F87" s="14" t="n">
+        <v>4057</v>
+      </c>
+      <c r="G87" s="14" t="n">
+        <v>4822</v>
+      </c>
+      <c r="H87" s="15" t="inlineStr">
+        <is>
+          <t>-16%</t>
+        </is>
+      </c>
+      <c r="I87" s="16" t="n">
+        <v>89914</v>
+      </c>
+    </row>
+    <row r="89" ht="22" customHeight="1">
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>▶ Remarketing Nail Outlet</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="18" customHeight="1">
+      <c r="B90" s="25" t="inlineStr">
+        <is>
+          <t>Despacho Gratis</t>
+        </is>
+      </c>
+      <c r="C90" s="26" t="n">
+        <v>306</v>
+      </c>
+      <c r="D90" s="26" t="n">
+        <v>5697</v>
+      </c>
+      <c r="E90" s="26" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F90" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="G90" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H90" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I90" s="30" t="n">
+        <v>44220</v>
+      </c>
+      <c r="J90" s="30" t="n">
+        <v>4913</v>
+      </c>
+      <c r="K90" s="26" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="L90" s="26" t="n">
+        <v>7761</v>
+      </c>
+      <c r="M90" s="26" t="inlineStr"/>
+      <c r="N90" s="26" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="O90" s="26" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="P90" s="26" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="Q90" s="26" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="R90" s="26" t="n">
+        <v>115</v>
+      </c>
+      <c r="S90" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="18" customHeight="1">
+      <c r="B91" s="25" t="inlineStr">
+        <is>
+          <t>15% OFF</t>
+        </is>
+      </c>
+      <c r="C91" s="26" t="n">
+        <v>301</v>
+      </c>
+      <c r="D91" s="26" t="n">
+        <v>4399</v>
+      </c>
+      <c r="E91" s="26" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="F91" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="G91" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H91" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I91" s="30" t="n">
+        <v>20886</v>
+      </c>
+      <c r="J91" s="30" t="n">
+        <v>3481</v>
+      </c>
+      <c r="K91" s="26" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="L91" s="26" t="n">
+        <v>4747</v>
+      </c>
+      <c r="M91" s="26" t="inlineStr"/>
+      <c r="N91" s="26" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="O91" s="26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="P91" s="26" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="Q91" s="26" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="R91" s="26" t="n">
+        <v>71</v>
+      </c>
+      <c r="S91" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="B92" s="13" t="inlineStr">
+        <is>
+          <t>SUBTOTAL  Remarketing Nail Outlet</t>
+        </is>
+      </c>
+      <c r="F92" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="I92" s="16" t="n">
+        <v>65106</v>
+      </c>
+    </row>
+    <row r="94" ht="22" customHeight="1">
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>▶ Campaña Conversión Catálogo</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="18" customHeight="1">
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>Nuevo Anuncio Catálogo</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="n">
+        <v>36129</v>
+      </c>
+      <c r="D95" s="7" t="n">
+        <v>206103</v>
+      </c>
+      <c r="E95" s="7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="F95" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G95" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H95" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I95" s="11" t="n">
+        <v>355748</v>
+      </c>
+      <c r="J95" s="11" t="n">
+        <v>17787</v>
+      </c>
+      <c r="K95" s="7" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="L95" s="7" t="n">
+        <v>1726</v>
+      </c>
+      <c r="M95" s="7" t="inlineStr"/>
+      <c r="N95" s="7" t="inlineStr"/>
+      <c r="O95" s="7" t="inlineStr"/>
+      <c r="P95" s="7" t="inlineStr"/>
+      <c r="Q95" s="7" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R95" s="7" t="n">
+        <v>2194</v>
+      </c>
+      <c r="S95" s="12" t="inlineStr">
+        <is>
+          <t>🔍 REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="B96" s="13" t="inlineStr">
+        <is>
+          <t>SUBTOTAL  Campaña Conversión Catálogo</t>
+        </is>
+      </c>
+      <c r="F96" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="I96" s="16" t="n">
+        <v>355748</v>
+      </c>
+    </row>
+    <row r="99" ht="24" customHeight="1">
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>Go Nails</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="22" customHeight="1">
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>▶ Remarketing Go Nails 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="18" customHeight="1">
+      <c r="B101" s="25" t="inlineStr">
+        <is>
+          <t>Remarketing Go Nails 2024</t>
+        </is>
+      </c>
+      <c r="C101" s="26" t="n">
+        <v>13359</v>
+      </c>
+      <c r="D101" s="26" t="n">
+        <v>99492</v>
+      </c>
+      <c r="E101" s="26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="F101" s="27" t="n">
+        <v>22</v>
+      </c>
+      <c r="G101" s="28" t="n">
+        <v>65</v>
+      </c>
+      <c r="H101" s="29" t="inlineStr">
+        <is>
+          <t>-66%</t>
+        </is>
+      </c>
+      <c r="I101" s="30" t="n">
+        <v>128988</v>
+      </c>
+      <c r="J101" s="30" t="n">
+        <v>5863</v>
+      </c>
+      <c r="K101" s="26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="L101" s="26" t="n">
+        <v>1296</v>
+      </c>
+      <c r="M101" s="26" t="inlineStr"/>
+      <c r="N101" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="26" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="R101" s="26" t="n">
+        <v>1394</v>
+      </c>
+      <c r="S101" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="18" customHeight="1">
+      <c r="B102" s="18" t="inlineStr">
+        <is>
+          <t>15% OFF</t>
+        </is>
+      </c>
+      <c r="C102" s="19" t="n">
+        <v>2700</v>
+      </c>
+      <c r="D102" s="19" t="n">
+        <v>4154</v>
+      </c>
+      <c r="E102" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F102" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" s="21" t="n">
+        <v>34</v>
+      </c>
+      <c r="H102" s="24" t="inlineStr">
+        <is>
+          <t>-97%</t>
+        </is>
+      </c>
+      <c r="I102" s="23" t="n">
+        <v>7957</v>
+      </c>
+      <c r="J102" s="23" t="n">
+        <v>7957</v>
+      </c>
+      <c r="K102" s="19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L102" s="19" t="n">
+        <v>1915</v>
+      </c>
+      <c r="M102" s="19" t="inlineStr"/>
+      <c r="N102" s="19" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O102" s="19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P102" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q102" s="19" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="R102" s="19" t="n">
+        <v>27</v>
+      </c>
+      <c r="S102" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="18" customHeight="1">
+      <c r="B103" s="25" t="inlineStr">
+        <is>
+          <t>Despacho Gratis</t>
+        </is>
+      </c>
+      <c r="C103" s="26" t="n">
+        <v>15613</v>
+      </c>
+      <c r="D103" s="26" t="n">
+        <v>73938</v>
+      </c>
+      <c r="E103" s="26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="F103" s="27" t="n">
+        <v>32</v>
+      </c>
+      <c r="G103" s="28" t="n">
+        <v>108</v>
+      </c>
+      <c r="H103" s="29" t="inlineStr">
+        <is>
+          <t>-70%</t>
+        </is>
+      </c>
+      <c r="I103" s="30" t="n">
+        <v>132377</v>
+      </c>
+      <c r="J103" s="30" t="n">
+        <v>4136</v>
+      </c>
+      <c r="K103" s="26" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L103" s="26" t="n">
+        <v>1790</v>
+      </c>
+      <c r="M103" s="26" t="inlineStr"/>
+      <c r="N103" s="26" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O103" s="26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P103" s="26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q103" s="26" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="R103" s="26" t="n">
+        <v>516</v>
+      </c>
+      <c r="S103" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="B104" s="13" t="inlineStr">
+        <is>
+          <t>SUBTOTAL  Remarketing Go Nails 2024</t>
+        </is>
+      </c>
+      <c r="F104" s="14" t="n">
+        <v>55</v>
+      </c>
+      <c r="G104" s="14" t="n">
+        <v>207</v>
+      </c>
+      <c r="H104" s="15" t="inlineStr">
+        <is>
+          <t>-73%</t>
+        </is>
+      </c>
+      <c r="I104" s="16" t="n">
+        <v>269322</v>
+      </c>
+    </row>
+    <row r="106" ht="22" customHeight="1">
+      <c r="B106" s="5" t="inlineStr">
+        <is>
+          <t>▶ Marketing Go Nails - Trafico Insta</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="18" customHeight="1">
+      <c r="B107" s="25" t="inlineStr">
+        <is>
+          <t>Rutina 4 pasos</t>
+        </is>
+      </c>
+      <c r="C107" s="26" t="n">
+        <v>713</v>
+      </c>
+      <c r="D107" s="26" t="n">
+        <v>831</v>
+      </c>
+      <c r="E107" s="26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F107" s="27" t="n">
+        <v>41</v>
+      </c>
+      <c r="G107" s="28" t="n">
+        <v>60</v>
+      </c>
+      <c r="H107" s="29" t="inlineStr">
+        <is>
+          <t>-32%</t>
+        </is>
+      </c>
+      <c r="I107" s="30" t="n">
+        <v>616</v>
+      </c>
+      <c r="J107" s="30" t="n">
+        <v>15</v>
+      </c>
+      <c r="K107" s="26" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="L107" s="26" t="n">
+        <v>741</v>
+      </c>
+      <c r="M107" s="26" t="inlineStr"/>
+      <c r="N107" s="26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O107" s="26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P107" s="26" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q107" s="26" t="inlineStr"/>
+      <c r="R107" s="26" t="inlineStr"/>
+      <c r="S107" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="18" customHeight="1">
+      <c r="B108" s="32" t="inlineStr">
+        <is>
+          <t>Nueva rutina 4 pasos</t>
+        </is>
+      </c>
+      <c r="C108" s="33" t="n">
+        <v>38054</v>
+      </c>
+      <c r="D108" s="33" t="n">
+        <v>50772</v>
+      </c>
+      <c r="E108" s="33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F108" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="H108" s="36" t="inlineStr">
+        <is>
+          <t>-83%</t>
+        </is>
+      </c>
+      <c r="I108" s="37" t="n">
+        <v>27864</v>
+      </c>
+      <c r="J108" s="37" t="n">
+        <v>27864</v>
+      </c>
+      <c r="K108" s="33" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="L108" s="33" t="n">
+        <v>548</v>
+      </c>
+      <c r="M108" s="33" t="inlineStr"/>
+      <c r="N108" s="33" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="O108" s="33" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="P108" s="33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q108" s="33" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R108" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="S108" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="18" customHeight="1">
+      <c r="B109" s="25" t="inlineStr">
+        <is>
+          <t>cotton candy frutilla</t>
+        </is>
+      </c>
+      <c r="C109" s="26" t="n">
+        <v>8064</v>
+      </c>
+      <c r="D109" s="26" t="n">
+        <v>9074</v>
+      </c>
+      <c r="E109" s="26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F109" s="27" t="n">
+        <v>407</v>
+      </c>
+      <c r="G109" s="28" t="n">
+        <v>615</v>
+      </c>
+      <c r="H109" s="29" t="inlineStr">
+        <is>
+          <t>-34%</t>
+        </is>
+      </c>
+      <c r="I109" s="30" t="n">
+        <v>6892</v>
+      </c>
+      <c r="J109" s="30" t="n">
+        <v>16</v>
+      </c>
+      <c r="K109" s="26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L109" s="26" t="n">
+        <v>759</v>
+      </c>
+      <c r="M109" s="26" t="inlineStr"/>
+      <c r="N109" s="26" t="inlineStr"/>
+      <c r="O109" s="26" t="inlineStr"/>
+      <c r="P109" s="26" t="inlineStr"/>
+      <c r="Q109" s="26" t="inlineStr"/>
+      <c r="R109" s="26" t="inlineStr"/>
+      <c r="S109" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="18" customHeight="1">
+      <c r="B110" s="25" t="inlineStr">
+        <is>
+          <t>popcorn pomo</t>
+        </is>
+      </c>
+      <c r="C110" s="26" t="n">
+        <v>365</v>
+      </c>
+      <c r="D110" s="26" t="n">
+        <v>412</v>
+      </c>
+      <c r="E110" s="26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F110" s="27" t="n">
+        <v>25</v>
+      </c>
+      <c r="G110" s="28" t="n">
+        <v>43</v>
+      </c>
+      <c r="H110" s="29" t="inlineStr">
+        <is>
+          <t>-42%</t>
+        </is>
+      </c>
+      <c r="I110" s="30" t="n">
+        <v>294</v>
+      </c>
+      <c r="J110" s="30" t="n">
+        <v>11</v>
+      </c>
+      <c r="K110" s="26" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="L110" s="26" t="n">
+        <v>713</v>
+      </c>
+      <c r="M110" s="26" t="inlineStr"/>
+      <c r="N110" s="26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="O110" s="26" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="P110" s="26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Q110" s="26" t="inlineStr"/>
+      <c r="R110" s="26" t="inlineStr"/>
+      <c r="S110" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="18" customHeight="1">
+      <c r="B111" s="25" t="inlineStr">
+        <is>
+          <t>carrusel rainbow</t>
+        </is>
+      </c>
+      <c r="C111" s="26" t="n">
+        <v>1189</v>
+      </c>
+      <c r="D111" s="26" t="n">
+        <v>1412</v>
+      </c>
+      <c r="E111" s="26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F111" s="27" t="n">
+        <v>45</v>
+      </c>
+      <c r="G111" s="28" t="n">
+        <v>65</v>
+      </c>
+      <c r="H111" s="29" t="inlineStr">
+        <is>
+          <t>-31%</t>
+        </is>
+      </c>
+      <c r="I111" s="30" t="n">
+        <v>707</v>
+      </c>
+      <c r="J111" s="30" t="n">
+        <v>15</v>
+      </c>
+      <c r="K111" s="26" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="L111" s="26" t="n">
+        <v>500</v>
+      </c>
+      <c r="M111" s="26" t="inlineStr"/>
+      <c r="N111" s="26" t="inlineStr"/>
+      <c r="O111" s="26" t="inlineStr"/>
+      <c r="P111" s="26" t="inlineStr"/>
+      <c r="Q111" s="26" t="inlineStr"/>
+      <c r="R111" s="26" t="inlineStr"/>
+      <c r="S111" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="18" customHeight="1">
+      <c r="B112" s="25" t="inlineStr">
+        <is>
+          <t>bridgerton prueba</t>
+        </is>
+      </c>
+      <c r="C112" s="26" t="n">
+        <v>67</v>
+      </c>
+      <c r="D112" s="26" t="n">
+        <v>75</v>
+      </c>
+      <c r="E112" s="26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F112" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="G112" s="28" t="n">
+        <v>15496</v>
+      </c>
+      <c r="H112" s="29" t="inlineStr">
+        <is>
+          <t>-100%</t>
+        </is>
+      </c>
+      <c r="I112" s="30" t="n">
+        <v>51</v>
+      </c>
+      <c r="J112" s="30" t="n">
+        <v>12</v>
+      </c>
+      <c r="K112" s="26" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="L112" s="26" t="n">
+        <v>680</v>
+      </c>
+      <c r="M112" s="26" t="inlineStr"/>
+      <c r="N112" s="26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O112" s="26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P112" s="26" t="inlineStr"/>
+      <c r="Q112" s="26" t="inlineStr"/>
+      <c r="R112" s="26" t="inlineStr"/>
+      <c r="S112" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="18" customHeight="1">
+      <c r="B113" s="32" t="inlineStr">
+        <is>
+          <t>hannah montana</t>
+        </is>
+      </c>
+      <c r="C113" s="33" t="n">
+        <v>97710</v>
+      </c>
+      <c r="D113" s="33" t="n">
+        <v>131389</v>
+      </c>
+      <c r="E113" s="33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F113" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" s="35" t="n">
+        <v>2567</v>
+      </c>
+      <c r="H113" s="36" t="inlineStr">
+        <is>
+          <t>-100%</t>
+        </is>
+      </c>
+      <c r="I113" s="37" t="n">
+        <v>55106</v>
+      </c>
+      <c r="J113" s="37" t="n">
+        <v>55106</v>
+      </c>
+      <c r="K113" s="33" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="L113" s="33" t="n">
+        <v>419</v>
+      </c>
+      <c r="M113" s="33" t="inlineStr"/>
+      <c r="N113" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O113" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P113" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q113" s="33" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="R113" s="33" t="inlineStr"/>
+      <c r="S113" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="18" customHeight="1">
+      <c r="B114" s="32" t="inlineStr">
+        <is>
+          <t>hannah montana 2</t>
+        </is>
+      </c>
+      <c r="C114" s="33" t="n">
+        <v>302822</v>
+      </c>
+      <c r="D114" s="33" t="n">
+        <v>522845</v>
+      </c>
+      <c r="E114" s="33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F114" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" s="35" t="n">
+        <v>456</v>
+      </c>
+      <c r="H114" s="36" t="inlineStr">
+        <is>
+          <t>-100%</t>
+        </is>
+      </c>
+      <c r="I114" s="37" t="n">
+        <v>283796</v>
+      </c>
+      <c r="J114" s="37" t="n">
+        <v>283796</v>
+      </c>
+      <c r="K114" s="33" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="L114" s="33" t="n">
+        <v>542</v>
+      </c>
+      <c r="M114" s="33" t="inlineStr"/>
+      <c r="N114" s="33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O114" s="33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P114" s="33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q114" s="33" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="R114" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="S114" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="18" customHeight="1">
+      <c r="B115" s="25" t="inlineStr">
+        <is>
+          <t>tu pareja te debe</t>
+        </is>
+      </c>
+      <c r="C115" s="26" t="n">
+        <v>21796</v>
+      </c>
+      <c r="D115" s="26" t="n">
+        <v>25757</v>
+      </c>
+      <c r="E115" s="26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F115" s="27" t="n">
+        <v>760</v>
+      </c>
+      <c r="G115" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H115" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I115" s="30" t="n">
+        <v>14792</v>
+      </c>
+      <c r="J115" s="30" t="n">
+        <v>19</v>
+      </c>
+      <c r="K115" s="26" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="L115" s="26" t="n">
+        <v>574</v>
+      </c>
+      <c r="M115" s="26" t="inlineStr"/>
+      <c r="N115" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q115" s="26" t="inlineStr"/>
+      <c r="R115" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="S115" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="B116" s="13" t="inlineStr">
+        <is>
+          <t>SUBTOTAL  Marketing Go Nails - Trafico Insta</t>
+        </is>
+      </c>
+      <c r="F116" s="14" t="n">
+        <v>1285</v>
+      </c>
+      <c r="G116" s="14" t="n">
+        <v>19308</v>
+      </c>
+      <c r="H116" s="15" t="inlineStr">
+        <is>
+          <t>-93%</t>
+        </is>
+      </c>
+      <c r="I116" s="16" t="n">
+        <v>390118</v>
+      </c>
+    </row>
+    <row r="118" ht="22" customHeight="1">
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>▶ Campaña principal de Conversión</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="18" customHeight="1">
+      <c r="B119" s="18" t="inlineStr">
+        <is>
+          <t>Crema dibujada</t>
+        </is>
+      </c>
+      <c r="C119" s="19" t="n">
+        <v>23284</v>
+      </c>
+      <c r="D119" s="19" t="n">
+        <v>45272</v>
+      </c>
+      <c r="E119" s="19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F119" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="G119" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H119" s="22" t="inlineStr">
+        <is>
+          <t>+60%</t>
+        </is>
+      </c>
+      <c r="I119" s="23" t="n">
+        <v>72053</v>
+      </c>
+      <c r="J119" s="23" t="n">
+        <v>9006</v>
+      </c>
+      <c r="K119" s="19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L119" s="19" t="n">
+        <v>1591</v>
+      </c>
+      <c r="M119" s="19" t="inlineStr"/>
+      <c r="N119" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O119" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P119" s="19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q119" s="19" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="R119" s="19" t="n">
+        <v>359</v>
+      </c>
+      <c r="S119" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="18" customHeight="1">
+      <c r="B120" s="18" t="inlineStr">
+        <is>
+          <t>4 por 3</t>
+        </is>
+      </c>
+      <c r="C120" s="19" t="n">
+        <v>111390</v>
+      </c>
+      <c r="D120" s="19" t="n">
+        <v>398057</v>
+      </c>
+      <c r="E120" s="19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F120" s="20" t="n">
+        <v>76</v>
+      </c>
+      <c r="G120" s="21" t="n">
+        <v>123</v>
+      </c>
+      <c r="H120" s="24" t="inlineStr">
+        <is>
+          <t>-38%</t>
+        </is>
+      </c>
+      <c r="I120" s="23" t="n">
+        <v>695652</v>
+      </c>
+      <c r="J120" s="23" t="n">
+        <v>9153</v>
+      </c>
+      <c r="K120" s="19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="L120" s="19" t="n">
+        <v>1747</v>
+      </c>
+      <c r="M120" s="19" t="inlineStr"/>
+      <c r="N120" s="19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O120" s="19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P120" s="19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q120" s="19" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="R120" s="19" t="n">
+        <v>2114</v>
+      </c>
+      <c r="S120" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="18" customHeight="1">
+      <c r="B121" s="18" t="inlineStr">
+        <is>
+          <t>Hot Chocalate</t>
+        </is>
+      </c>
+      <c r="C121" s="19" t="n">
+        <v>48445</v>
+      </c>
+      <c r="D121" s="19" t="n">
+        <v>107600</v>
+      </c>
+      <c r="E121" s="19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F121" s="20" t="n">
+        <v>14</v>
+      </c>
+      <c r="G121" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H121" s="22" t="inlineStr">
+        <is>
+          <t>+40%</t>
+        </is>
+      </c>
+      <c r="I121" s="23" t="n">
+        <v>128564</v>
+      </c>
+      <c r="J121" s="23" t="n">
+        <v>9183</v>
+      </c>
+      <c r="K121" s="19" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="L121" s="19" t="n">
+        <v>1194</v>
+      </c>
+      <c r="M121" s="19" t="inlineStr"/>
+      <c r="N121" s="19" t="inlineStr"/>
+      <c r="O121" s="19" t="inlineStr"/>
+      <c r="P121" s="19" t="inlineStr"/>
+      <c r="Q121" s="19" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="R121" s="19" t="n">
+        <v>970</v>
+      </c>
+      <c r="S121" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="18" customHeight="1">
+      <c r="B122" s="18" t="inlineStr">
+        <is>
+          <t>Macbook</t>
+        </is>
+      </c>
+      <c r="C122" s="19" t="n">
+        <v>11375</v>
+      </c>
+      <c r="D122" s="19" t="n">
+        <v>24203</v>
+      </c>
+      <c r="E122" s="19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F122" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="G122" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H122" s="22" t="inlineStr">
+        <is>
+          <t>+50%</t>
+        </is>
+      </c>
+      <c r="I122" s="23" t="n">
+        <v>41316</v>
+      </c>
+      <c r="J122" s="23" t="n">
+        <v>6886</v>
+      </c>
+      <c r="K122" s="19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="L122" s="19" t="n">
+        <v>1707</v>
+      </c>
+      <c r="M122" s="19" t="inlineStr"/>
+      <c r="N122" s="19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O122" s="19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P122" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q122" s="19" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="R122" s="19" t="n">
+        <v>229</v>
+      </c>
+      <c r="S122" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="18" customHeight="1">
+      <c r="B123" s="18" t="inlineStr">
+        <is>
+          <t>Protector Termico</t>
+        </is>
+      </c>
+      <c r="C123" s="19" t="n">
+        <v>12312</v>
+      </c>
+      <c r="D123" s="19" t="n">
+        <v>41733</v>
+      </c>
+      <c r="E123" s="19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F123" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="G123" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="H123" s="24" t="inlineStr">
+        <is>
+          <t>-43%</t>
+        </is>
+      </c>
+      <c r="I123" s="23" t="n">
+        <v>54972</v>
+      </c>
+      <c r="J123" s="23" t="n">
+        <v>6871</v>
+      </c>
+      <c r="K123" s="19" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L123" s="19" t="n">
+        <v>1317</v>
+      </c>
+      <c r="M123" s="19" t="inlineStr"/>
+      <c r="N123" s="19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O123" s="19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P123" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q123" s="19" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="R123" s="19" t="n">
+        <v>153</v>
+      </c>
+      <c r="S123" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="18" customHeight="1">
+      <c r="B124" s="32" t="inlineStr">
+        <is>
+          <t>Nuevos difusores</t>
+        </is>
+      </c>
+      <c r="C124" s="33" t="n">
+        <v>16523</v>
+      </c>
+      <c r="D124" s="33" t="n">
+        <v>43682</v>
+      </c>
+      <c r="E124" s="33" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F124" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G124" s="35" t="n">
+        <v>35</v>
+      </c>
+      <c r="H124" s="36" t="inlineStr">
+        <is>
+          <t>-91%</t>
+        </is>
+      </c>
+      <c r="I124" s="37" t="n">
+        <v>67668</v>
+      </c>
+      <c r="J124" s="37" t="n">
+        <v>22556</v>
+      </c>
+      <c r="K124" s="33" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="L124" s="33" t="n">
+        <v>1549</v>
+      </c>
+      <c r="M124" s="33" t="inlineStr"/>
+      <c r="N124" s="33" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O124" s="33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P124" s="33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q124" s="33" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="R124" s="33" t="n">
+        <v>229</v>
+      </c>
+      <c r="S124" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="18" customHeight="1">
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>Reel de fragancias</t>
+        </is>
+      </c>
+      <c r="C125" s="7" t="n">
+        <v>189252</v>
+      </c>
+      <c r="D125" s="7" t="n">
+        <v>519325</v>
+      </c>
+      <c r="E125" s="7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F125" s="8" t="n">
+        <v>76</v>
+      </c>
+      <c r="G125" s="9" t="n">
+        <v>104</v>
+      </c>
+      <c r="H125" s="17" t="inlineStr">
+        <is>
+          <t>-27%</t>
+        </is>
+      </c>
+      <c r="I125" s="11" t="n">
+        <v>785629</v>
+      </c>
+      <c r="J125" s="11" t="n">
+        <v>10337</v>
+      </c>
+      <c r="K125" s="7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="L125" s="7" t="n">
+        <v>1512</v>
+      </c>
+      <c r="M125" s="7" t="inlineStr"/>
+      <c r="N125" s="7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O125" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P125" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q125" s="7" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="R125" s="7" t="n">
+        <v>4120</v>
+      </c>
+      <c r="S125" s="12" t="inlineStr">
+        <is>
+          <t>🔍 REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="18" customHeight="1">
+      <c r="B126" s="18" t="inlineStr">
+        <is>
+          <t>Imagen Bubble gum</t>
+        </is>
+      </c>
+      <c r="C126" s="19" t="n">
+        <v>25328</v>
+      </c>
+      <c r="D126" s="19" t="n">
+        <v>77421</v>
+      </c>
+      <c r="E126" s="19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F126" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="G126" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="H126" s="24" t="inlineStr">
+        <is>
+          <t>-40%</t>
+        </is>
+      </c>
+      <c r="I126" s="23" t="n">
+        <v>100077</v>
+      </c>
+      <c r="J126" s="23" t="n">
+        <v>6671</v>
+      </c>
+      <c r="K126" s="19" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="L126" s="19" t="n">
+        <v>1292</v>
+      </c>
+      <c r="M126" s="19" t="inlineStr"/>
+      <c r="N126" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O126" s="19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P126" s="19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q126" s="19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="R126" s="19" t="n">
+        <v>466</v>
+      </c>
+      <c r="S126" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="18" customHeight="1">
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>Imagen Gato</t>
+        </is>
+      </c>
+      <c r="C127" s="7" t="n">
+        <v>17097</v>
+      </c>
+      <c r="D127" s="7" t="n">
+        <v>39152</v>
+      </c>
+      <c r="E127" s="7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F127" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G127" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="H127" s="17" t="inlineStr">
+        <is>
+          <t>-43%</t>
+        </is>
+      </c>
+      <c r="I127" s="11" t="n">
+        <v>68171</v>
+      </c>
+      <c r="J127" s="11" t="n">
+        <v>17042</v>
+      </c>
+      <c r="K127" s="7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="L127" s="7" t="n">
+        <v>1741</v>
+      </c>
+      <c r="M127" s="7" t="inlineStr"/>
+      <c r="N127" s="7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O127" s="7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P127" s="7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q127" s="7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R127" s="7" t="n">
+        <v>311</v>
+      </c>
+      <c r="S127" s="12" t="inlineStr">
+        <is>
+          <t>🔍 REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="18" customHeight="1">
+      <c r="B128" s="18" t="inlineStr">
+        <is>
+          <t>Carrusel Sun Kissed</t>
+        </is>
+      </c>
+      <c r="C128" s="19" t="n">
+        <v>8843</v>
+      </c>
+      <c r="D128" s="19" t="n">
+        <v>19060</v>
+      </c>
+      <c r="E128" s="19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F128" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="G128" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="H128" s="24" t="inlineStr">
+        <is>
+          <t>-57%</t>
+        </is>
+      </c>
+      <c r="I128" s="23" t="n">
+        <v>23636</v>
+      </c>
+      <c r="J128" s="23" t="n">
+        <v>7878</v>
+      </c>
+      <c r="K128" s="19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L128" s="19" t="n">
+        <v>1240</v>
+      </c>
+      <c r="M128" s="19" t="inlineStr"/>
+      <c r="N128" s="19" t="inlineStr"/>
+      <c r="O128" s="19" t="inlineStr"/>
+      <c r="P128" s="19" t="inlineStr"/>
+      <c r="Q128" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="R128" s="19" t="n">
+        <v>132</v>
+      </c>
+      <c r="S128" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="18" customHeight="1">
+      <c r="B129" s="25" t="inlineStr">
+        <is>
+          <t>Reel cafetería</t>
+        </is>
+      </c>
+      <c r="C129" s="26" t="n">
+        <v>3530</v>
+      </c>
+      <c r="D129" s="26" t="n">
+        <v>6221</v>
+      </c>
+      <c r="E129" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F129" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="G129" s="28" t="n">
+        <v>88</v>
+      </c>
+      <c r="H129" s="29" t="inlineStr">
+        <is>
+          <t>-97%</t>
+        </is>
+      </c>
+      <c r="I129" s="30" t="n">
+        <v>15267</v>
+      </c>
+      <c r="J129" s="30" t="n">
+        <v>5089</v>
+      </c>
+      <c r="K129" s="26" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="L129" s="26" t="n">
+        <v>2454</v>
+      </c>
+      <c r="M129" s="26" t="inlineStr"/>
+      <c r="N129" s="26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O129" s="26" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P129" s="26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q129" s="26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R129" s="26" t="n">
+        <v>77</v>
+      </c>
+      <c r="S129" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="18" customHeight="1">
+      <c r="B130" s="18" t="inlineStr">
+        <is>
+          <t>Imagen Cotton Vlabel</t>
+        </is>
+      </c>
+      <c r="C130" s="19" t="n">
+        <v>75025</v>
+      </c>
+      <c r="D130" s="19" t="n">
+        <v>202418</v>
+      </c>
+      <c r="E130" s="19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F130" s="20" t="n">
+        <v>38</v>
+      </c>
+      <c r="G130" s="21" t="n">
+        <v>120</v>
+      </c>
+      <c r="H130" s="24" t="inlineStr">
+        <is>
+          <t>-68%</t>
+        </is>
+      </c>
+      <c r="I130" s="23" t="n">
+        <v>293090</v>
+      </c>
+      <c r="J130" s="23" t="n">
+        <v>7712</v>
+      </c>
+      <c r="K130" s="19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="L130" s="19" t="n">
+        <v>1447</v>
+      </c>
+      <c r="M130" s="19" t="inlineStr"/>
+      <c r="N130" s="19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O130" s="19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P130" s="19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q130" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="R130" s="19" t="n">
+        <v>1585</v>
+      </c>
+      <c r="S130" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="18" customHeight="1">
+      <c r="B131" s="32" t="inlineStr">
+        <is>
+          <t>Bye Bye Aroma</t>
+        </is>
+      </c>
+      <c r="C131" s="33" t="n">
+        <v>4867</v>
+      </c>
+      <c r="D131" s="33" t="n">
+        <v>9919</v>
+      </c>
+      <c r="E131" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F131" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G131" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="H131" s="36" t="inlineStr">
+        <is>
+          <t>-83%</t>
+        </is>
+      </c>
+      <c r="I131" s="37" t="n">
+        <v>18421</v>
+      </c>
+      <c r="J131" s="37" t="n">
+        <v>18421</v>
+      </c>
+      <c r="K131" s="33" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L131" s="33" t="n">
+        <v>1857</v>
+      </c>
+      <c r="M131" s="33" t="inlineStr"/>
+      <c r="N131" s="33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O131" s="33" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P131" s="33" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q131" s="33" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="R131" s="33" t="n">
+        <v>48</v>
+      </c>
+      <c r="S131" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="18" customHeight="1">
+      <c r="B132" s="25" t="inlineStr">
+        <is>
+          <t>Cremas Sun Kissed</t>
+        </is>
+      </c>
+      <c r="C132" s="26" t="n">
+        <v>16660</v>
+      </c>
+      <c r="D132" s="26" t="n">
+        <v>37965</v>
+      </c>
+      <c r="E132" s="26" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F132" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="G132" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="H132" s="29" t="inlineStr">
+        <is>
+          <t>-50%</t>
+        </is>
+      </c>
+      <c r="I132" s="30" t="n">
+        <v>68249</v>
+      </c>
+      <c r="J132" s="30" t="n">
+        <v>5687</v>
+      </c>
+      <c r="K132" s="26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L132" s="26" t="n">
+        <v>1797</v>
+      </c>
+      <c r="M132" s="26" t="inlineStr"/>
+      <c r="N132" s="26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O132" s="26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P132" s="26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q132" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="R132" s="26" t="n">
+        <v>363</v>
+      </c>
+      <c r="S132" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="18" customHeight="1">
+      <c r="B133" s="6" t="inlineStr">
+        <is>
+          <t>Home Spray</t>
+        </is>
+      </c>
+      <c r="C133" s="7" t="n">
+        <v>223129</v>
+      </c>
+      <c r="D133" s="7" t="n">
+        <v>738548</v>
+      </c>
+      <c r="E133" s="7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F133" s="8" t="n">
+        <v>91</v>
+      </c>
+      <c r="G133" s="9" t="n">
+        <v>126</v>
+      </c>
+      <c r="H133" s="17" t="inlineStr">
+        <is>
+          <t>-28%</t>
+        </is>
+      </c>
+      <c r="I133" s="11" t="n">
+        <v>1186817</v>
+      </c>
+      <c r="J133" s="11" t="n">
+        <v>13041</v>
+      </c>
+      <c r="K133" s="7" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="L133" s="7" t="n">
+        <v>1606</v>
+      </c>
+      <c r="M133" s="7" t="inlineStr"/>
+      <c r="N133" s="7" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O133" s="7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="P133" s="7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q133" s="7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R133" s="7" t="n">
+        <v>5319</v>
+      </c>
+      <c r="S133" s="12" t="inlineStr">
+        <is>
+          <t>🔍 REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="18" customHeight="1">
+      <c r="B134" s="6" t="inlineStr">
+        <is>
+          <t>Rutina 4 pasos 2.0</t>
+        </is>
+      </c>
+      <c r="C134" s="7" t="n">
+        <v>47354</v>
+      </c>
+      <c r="D134" s="7" t="n">
+        <v>139806</v>
+      </c>
+      <c r="E134" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F134" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G134" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="H134" s="17" t="inlineStr">
+        <is>
+          <t>-47%</t>
+        </is>
+      </c>
+      <c r="I134" s="11" t="n">
+        <v>261897</v>
+      </c>
+      <c r="J134" s="11" t="n">
+        <v>13784</v>
+      </c>
+      <c r="K134" s="7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L134" s="7" t="n">
+        <v>1873</v>
+      </c>
+      <c r="M134" s="7" t="inlineStr"/>
+      <c r="N134" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O134" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P134" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q134" s="7" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="R134" s="7" t="n">
+        <v>1312</v>
+      </c>
+      <c r="S134" s="12" t="inlineStr">
+        <is>
+          <t>🔍 REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="18" customHeight="1">
+      <c r="B135" s="32" t="inlineStr">
+        <is>
+          <t>UGC Soft Milk Febrero</t>
+        </is>
+      </c>
+      <c r="C135" s="33" t="n">
+        <v>1912</v>
+      </c>
+      <c r="D135" s="33" t="n">
+        <v>3069</v>
+      </c>
+      <c r="E135" s="33" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F135" s="34" t="n">
+        <v>27</v>
+      </c>
+      <c r="G135" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H135" s="46" t="inlineStr">
+        <is>
+          <t>+2600%</t>
+        </is>
+      </c>
+      <c r="I135" s="37" t="n">
+        <v>8931</v>
+      </c>
+      <c r="J135" s="37" t="n">
+        <v>330</v>
+      </c>
+      <c r="K135" s="33" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="L135" s="33" t="n">
+        <v>2910</v>
+      </c>
+      <c r="M135" s="33" t="inlineStr"/>
+      <c r="N135" s="33" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="O135" s="33" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P135" s="33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q135" s="33" t="inlineStr"/>
+      <c r="R135" s="33" t="n">
+        <v>20</v>
+      </c>
+      <c r="S135" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="18" customHeight="1">
+      <c r="B136" s="32" t="inlineStr">
+        <is>
+          <t>Go Paw Carrusel Mascotas</t>
+        </is>
+      </c>
+      <c r="C136" s="33" t="n">
+        <v>948</v>
+      </c>
+      <c r="D136" s="33" t="n">
+        <v>1379</v>
+      </c>
+      <c r="E136" s="33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F136" s="34" t="n">
+        <v>9</v>
+      </c>
+      <c r="G136" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H136" s="46" t="inlineStr">
+        <is>
+          <t>+800%</t>
+        </is>
+      </c>
+      <c r="I136" s="37" t="n">
+        <v>3176</v>
+      </c>
+      <c r="J136" s="37" t="n">
+        <v>352</v>
+      </c>
+      <c r="K136" s="33" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="L136" s="33" t="n">
+        <v>2303</v>
+      </c>
+      <c r="M136" s="33" t="inlineStr"/>
+      <c r="N136" s="33" t="inlineStr"/>
+      <c r="O136" s="33" t="inlineStr"/>
+      <c r="P136" s="33" t="inlineStr"/>
+      <c r="Q136" s="33" t="inlineStr"/>
+      <c r="R136" s="33" t="n">
+        <v>9</v>
+      </c>
+      <c r="S136" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="18" customHeight="1">
+      <c r="B137" s="32" t="inlineStr">
+        <is>
+          <t>Aceite Capilar Go Hair</t>
+        </is>
+      </c>
+      <c r="C137" s="33" t="n">
+        <v>1318</v>
+      </c>
+      <c r="D137" s="33" t="n">
+        <v>2028</v>
+      </c>
+      <c r="E137" s="33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F137" s="34" t="n">
+        <v>21</v>
+      </c>
+      <c r="G137" s="35" t="n">
+        <v>23</v>
+      </c>
+      <c r="H137" s="36" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
+      <c r="I137" s="37" t="n">
+        <v>5378</v>
+      </c>
+      <c r="J137" s="37" t="n">
+        <v>256</v>
+      </c>
+      <c r="K137" s="33" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="L137" s="33" t="n">
+        <v>2651</v>
+      </c>
+      <c r="M137" s="33" t="inlineStr"/>
+      <c r="N137" s="33" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="O137" s="33" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P137" s="33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q137" s="33" t="inlineStr"/>
+      <c r="R137" s="33" t="n">
+        <v>21</v>
+      </c>
+      <c r="S137" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="18" customHeight="1">
+      <c r="B138" s="18" t="inlineStr">
+        <is>
+          <t>Kit Cuidado Capilar</t>
+        </is>
+      </c>
+      <c r="C138" s="19" t="n">
+        <v>10726</v>
+      </c>
+      <c r="D138" s="19" t="n">
+        <v>21083</v>
+      </c>
+      <c r="E138" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F138" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="G138" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="H138" s="24" t="inlineStr">
+        <is>
+          <t>-14%</t>
+        </is>
+      </c>
+      <c r="I138" s="23" t="n">
+        <v>49131</v>
+      </c>
+      <c r="J138" s="23" t="n">
+        <v>8188</v>
+      </c>
+      <c r="K138" s="19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="L138" s="19" t="n">
+        <v>2330</v>
+      </c>
+      <c r="M138" s="19" t="inlineStr"/>
+      <c r="N138" s="19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O138" s="19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P138" s="19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q138" s="19" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="R138" s="19" t="n">
+        <v>203</v>
+      </c>
+      <c r="S138" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="18" customHeight="1">
+      <c r="B139" s="32" t="inlineStr">
+        <is>
+          <t>Go Paw Wild Berries y Cotton Candy</t>
+        </is>
+      </c>
+      <c r="C139" s="33" t="n">
+        <v>18992</v>
+      </c>
+      <c r="D139" s="33" t="n">
+        <v>36622</v>
+      </c>
+      <c r="E139" s="33" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F139" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="G139" s="35" t="n">
+        <v>15</v>
+      </c>
+      <c r="H139" s="36" t="inlineStr">
+        <is>
+          <t>-73%</t>
+        </is>
+      </c>
+      <c r="I139" s="37" t="n">
+        <v>93385</v>
+      </c>
+      <c r="J139" s="37" t="n">
+        <v>23346</v>
+      </c>
+      <c r="K139" s="33" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="L139" s="33" t="n">
+        <v>2549</v>
+      </c>
+      <c r="M139" s="33" t="inlineStr"/>
+      <c r="N139" s="33" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O139" s="33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P139" s="33" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q139" s="33" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R139" s="33" t="n">
+        <v>207</v>
+      </c>
+      <c r="S139" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="18" customHeight="1">
+      <c r="B140" s="6" t="inlineStr">
+        <is>
+          <t>Protector Termico Pistacho Caramelo</t>
+        </is>
+      </c>
+      <c r="C140" s="7" t="n">
+        <v>73692</v>
+      </c>
+      <c r="D140" s="7" t="n">
+        <v>169162</v>
+      </c>
+      <c r="E140" s="7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F140" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="G140" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="H140" s="17" t="inlineStr">
+        <is>
+          <t>-40%</t>
+        </is>
+      </c>
+      <c r="I140" s="11" t="n">
+        <v>261470</v>
+      </c>
+      <c r="J140" s="11" t="n">
+        <v>17431</v>
+      </c>
+      <c r="K140" s="7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L140" s="7" t="n">
+        <v>1545</v>
+      </c>
+      <c r="M140" s="7" t="inlineStr"/>
+      <c r="N140" s="7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O140" s="7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P140" s="7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q140" s="7" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="R140" s="7" t="n">
+        <v>905</v>
+      </c>
+      <c r="S140" s="12" t="inlineStr">
+        <is>
+          <t>🔍 REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="18" customHeight="1">
+      <c r="B141" s="25" t="inlineStr">
+        <is>
+          <t>Go Paw @Juliana Carrascal</t>
+        </is>
+      </c>
+      <c r="C141" s="26" t="n">
+        <v>1537</v>
+      </c>
+      <c r="D141" s="26" t="n">
+        <v>2275</v>
+      </c>
+      <c r="E141" s="26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F141" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G141" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H141" s="31" t="inlineStr">
+        <is>
+          <t>+100%</t>
+        </is>
+      </c>
+      <c r="I141" s="30" t="n">
+        <v>5473</v>
+      </c>
+      <c r="J141" s="30" t="n">
+        <v>2736</v>
+      </c>
+      <c r="K141" s="26" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="L141" s="26" t="n">
+        <v>2405</v>
+      </c>
+      <c r="M141" s="26" t="inlineStr"/>
+      <c r="N141" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="O141" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="P141" s="26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q141" s="26" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="R141" s="26" t="n">
+        <v>17</v>
+      </c>
+      <c r="S141" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="18" customHeight="1">
+      <c r="B142" s="6" t="inlineStr">
+        <is>
+          <t>Home Spray @vanusallorenzo</t>
+        </is>
+      </c>
+      <c r="C142" s="7" t="n">
+        <v>56581</v>
+      </c>
+      <c r="D142" s="7" t="n">
+        <v>133163</v>
+      </c>
+      <c r="E142" s="7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F142" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="G142" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H142" s="10" t="inlineStr">
+        <is>
+          <t>+320%</t>
+        </is>
+      </c>
+      <c r="I142" s="11" t="n">
+        <v>306078</v>
+      </c>
+      <c r="J142" s="11" t="n">
+        <v>14575</v>
+      </c>
+      <c r="K142" s="7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="L142" s="7" t="n">
+        <v>2298</v>
+      </c>
+      <c r="M142" s="7" t="inlineStr"/>
+      <c r="N142" s="7" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="O142" s="7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P142" s="7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q142" s="7" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="R142" s="7" t="n">
+        <v>1041</v>
+      </c>
+      <c r="S142" s="12" t="inlineStr">
+        <is>
+          <t>🔍 REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="18" customHeight="1">
+      <c r="B143" s="25" t="inlineStr">
+        <is>
+          <t>BLACK WEEK INICIO</t>
+        </is>
+      </c>
+      <c r="C143" s="26" t="n">
+        <v>87055</v>
+      </c>
+      <c r="D143" s="26" t="n">
+        <v>320312</v>
+      </c>
+      <c r="E143" s="26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F143" s="27" t="n">
+        <v>107</v>
+      </c>
+      <c r="G143" s="28" t="n">
+        <v>28</v>
+      </c>
+      <c r="H143" s="31" t="inlineStr">
+        <is>
+          <t>+282%</t>
+        </is>
+      </c>
+      <c r="I143" s="30" t="n">
+        <v>573332</v>
+      </c>
+      <c r="J143" s="30" t="n">
+        <v>5358</v>
+      </c>
+      <c r="K143" s="26" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="L143" s="26" t="n">
+        <v>1789</v>
+      </c>
+      <c r="M143" s="26" t="inlineStr"/>
+      <c r="N143" s="26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O143" s="26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P143" s="26" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q143" s="26" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="R143" s="26" t="n">
+        <v>2699</v>
+      </c>
+      <c r="S143" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="18" customHeight="1">
+      <c r="B144" s="32" t="inlineStr">
+        <is>
+          <t>Carrusel Post que puedes oler</t>
+        </is>
+      </c>
+      <c r="C144" s="33" t="n">
+        <v>5613</v>
+      </c>
+      <c r="D144" s="33" t="n">
+        <v>11418</v>
+      </c>
+      <c r="E144" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F144" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G144" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H144" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I144" s="37" t="n">
+        <v>21464</v>
+      </c>
+      <c r="J144" s="37" t="n">
+        <v>21464</v>
+      </c>
+      <c r="K144" s="33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L144" s="33" t="n">
+        <v>1879</v>
+      </c>
+      <c r="M144" s="33" t="inlineStr"/>
+      <c r="N144" s="33" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O144" s="33" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P144" s="33" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q144" s="33" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="R144" s="33" t="n">
+        <v>87</v>
+      </c>
+      <c r="S144" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="18" customHeight="1">
+      <c r="B145" s="6" t="inlineStr">
+        <is>
+          <t>Fragancias Picnic</t>
+        </is>
+      </c>
+      <c r="C145" s="7" t="n">
+        <v>24676</v>
+      </c>
+      <c r="D145" s="7" t="n">
+        <v>74073</v>
+      </c>
+      <c r="E145" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F145" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="G145" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H145" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I145" s="11" t="n">
+        <v>134078</v>
+      </c>
+      <c r="J145" s="11" t="n">
+        <v>11173</v>
+      </c>
+      <c r="K145" s="7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="L145" s="7" t="n">
+        <v>1810</v>
+      </c>
+      <c r="M145" s="7" t="inlineStr"/>
+      <c r="N145" s="7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O145" s="7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P145" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q145" s="7" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="R145" s="7" t="n">
+        <v>554</v>
+      </c>
+      <c r="S145" s="12" t="inlineStr">
+        <is>
+          <t>🔍 REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="18" customHeight="1">
+      <c r="B146" s="32" t="inlineStr">
+        <is>
+          <t>Go Paw @melissapaz</t>
+        </is>
+      </c>
+      <c r="C146" s="33" t="n">
+        <v>7601</v>
+      </c>
+      <c r="D146" s="33" t="n">
+        <v>9998</v>
+      </c>
+      <c r="E146" s="33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F146" s="34" t="n">
+        <v>104</v>
+      </c>
+      <c r="G146" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H146" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I146" s="37" t="n">
+        <v>23686</v>
+      </c>
+      <c r="J146" s="37" t="n">
+        <v>227</v>
+      </c>
+      <c r="K146" s="33" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="L146" s="33" t="n">
+        <v>2369</v>
+      </c>
+      <c r="M146" s="33" t="inlineStr"/>
+      <c r="N146" s="33" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="O146" s="33" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P146" s="33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q146" s="33" t="inlineStr"/>
+      <c r="R146" s="33" t="n">
+        <v>95</v>
+      </c>
+      <c r="S146" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="18" customHeight="1">
+      <c r="B147" s="32" t="inlineStr">
+        <is>
+          <t>Nuevas Cremas Corporales Abril</t>
+        </is>
+      </c>
+      <c r="C147" s="33" t="n">
+        <v>6943</v>
+      </c>
+      <c r="D147" s="33" t="n">
+        <v>9228</v>
+      </c>
+      <c r="E147" s="33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F147" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G147" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H147" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I147" s="37" t="n">
+        <v>22067</v>
+      </c>
+      <c r="J147" s="37" t="n">
+        <v>22067</v>
+      </c>
+      <c r="K147" s="33" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="L147" s="33" t="n">
+        <v>2391</v>
+      </c>
+      <c r="M147" s="33" t="inlineStr"/>
+      <c r="N147" s="33" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O147" s="33" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P147" s="33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q147" s="33" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="R147" s="33" t="n">
+        <v>76</v>
+      </c>
+      <c r="S147" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="18" customHeight="1">
+      <c r="B148" s="18" t="inlineStr">
+        <is>
+          <t>Lanzamiento Shampoo y Acondicionador</t>
+        </is>
+      </c>
+      <c r="C148" s="19" t="n">
+        <v>2164</v>
+      </c>
+      <c r="D148" s="19" t="n">
+        <v>3284</v>
+      </c>
+      <c r="E148" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F148" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G148" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H148" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I148" s="23" t="n">
+        <v>6190</v>
+      </c>
+      <c r="J148" s="23" t="n">
+        <v>6190</v>
+      </c>
+      <c r="K148" s="19" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="L148" s="19" t="n">
+        <v>1884</v>
+      </c>
+      <c r="M148" s="19" t="inlineStr"/>
+      <c r="N148" s="19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O148" s="19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="P148" s="19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q148" s="19" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="R148" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="S148" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="18" customHeight="1">
+      <c r="B149" s="18" t="inlineStr">
+        <is>
+          <t>Lanzamiento Refill Abril</t>
+        </is>
+      </c>
+      <c r="C149" s="19" t="n">
+        <v>13541</v>
+      </c>
+      <c r="D149" s="19" t="n">
+        <v>30101</v>
+      </c>
+      <c r="E149" s="19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F149" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="G149" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H149" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I149" s="23" t="n">
+        <v>68938</v>
+      </c>
+      <c r="J149" s="23" t="n">
+        <v>9848</v>
+      </c>
+      <c r="K149" s="19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="L149" s="19" t="n">
+        <v>2290</v>
+      </c>
+      <c r="M149" s="19" t="inlineStr"/>
+      <c r="N149" s="19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O149" s="19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P149" s="19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q149" s="19" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="R149" s="19" t="n">
+        <v>302</v>
+      </c>
+      <c r="S149" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="20" customHeight="1">
+      <c r="B150" s="13" t="inlineStr">
+        <is>
+          <t>SUBTOTAL  Campaña principal de Conversión</t>
+        </is>
+      </c>
+      <c r="F150" s="14" t="n">
+        <v>715</v>
+      </c>
+      <c r="G150" s="14" t="n">
+        <v>840</v>
+      </c>
+      <c r="H150" s="15" t="inlineStr">
+        <is>
+          <t>-15%</t>
+        </is>
+      </c>
+      <c r="I150" s="16" t="n">
+        <v>5464256</v>
+      </c>
+    </row>
+    <row r="152" ht="22" customHeight="1">
+      <c r="B152" s="5" t="inlineStr">
+        <is>
+          <t>▶ Campaña Secundaria LMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="18" customHeight="1">
+      <c r="B153" s="6" t="inlineStr">
+        <is>
+          <t>Reel esmalte LMM</t>
+        </is>
+      </c>
+      <c r="C153" s="7" t="n">
+        <v>16040</v>
+      </c>
+      <c r="D153" s="7" t="n">
+        <v>23785</v>
+      </c>
+      <c r="E153" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F153" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G153" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="H153" s="17" t="inlineStr">
+        <is>
+          <t>-65%</t>
+        </is>
+      </c>
+      <c r="I153" s="11" t="n">
+        <v>60827</v>
+      </c>
+      <c r="J153" s="11" t="n">
+        <v>10137</v>
+      </c>
+      <c r="K153" s="7" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="L153" s="7" t="n">
+        <v>2557</v>
+      </c>
+      <c r="M153" s="7" t="inlineStr"/>
+      <c r="N153" s="7" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="O153" s="7" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="P153" s="7" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Q153" s="7" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="R153" s="7" t="n">
+        <v>695</v>
+      </c>
+      <c r="S153" s="12" t="inlineStr">
+        <is>
+          <t>🔍 REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="18" customHeight="1">
+      <c r="B154" s="25" t="inlineStr">
+        <is>
+          <t>Reel Kit LMM</t>
+        </is>
+      </c>
+      <c r="C154" s="26" t="n">
+        <v>2378</v>
+      </c>
+      <c r="D154" s="26" t="n">
+        <v>3985</v>
+      </c>
+      <c r="E154" s="26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F154" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="G154" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H154" s="31" t="inlineStr">
+        <is>
+          <t>+400%</t>
+        </is>
+      </c>
+      <c r="I154" s="30" t="n">
+        <v>12363</v>
+      </c>
+      <c r="J154" s="30" t="n">
+        <v>2472</v>
+      </c>
+      <c r="K154" s="26" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="L154" s="26" t="n">
+        <v>3102</v>
+      </c>
+      <c r="M154" s="26" t="inlineStr"/>
+      <c r="N154" s="26" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="O154" s="26" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="P154" s="26" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="Q154" s="26" t="n">
+        <v>15.27</v>
+      </c>
+      <c r="R154" s="26" t="n">
+        <v>82</v>
+      </c>
+      <c r="S154" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="18" customHeight="1">
+      <c r="B155" s="18" t="inlineStr">
+        <is>
+          <t>Reel de Kit Le Mini</t>
+        </is>
+      </c>
+      <c r="C155" s="19" t="n">
+        <v>26</v>
+      </c>
+      <c r="D155" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="E155" s="19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F155" s="20" t="inlineStr"/>
+      <c r="G155" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="H155" s="24" t="inlineStr">
+        <is>
+          <t>-100%</t>
+        </is>
+      </c>
+      <c r="I155" s="23" t="n">
+        <v>63</v>
+      </c>
+      <c r="J155" s="23" t="inlineStr"/>
+      <c r="K155" s="19" t="inlineStr"/>
+      <c r="L155" s="19" t="n">
+        <v>2250</v>
+      </c>
+      <c r="M155" s="19" t="inlineStr"/>
+      <c r="N155" s="19" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="O155" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="P155" s="19" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="Q155" s="19" t="inlineStr"/>
+      <c r="R155" s="19" t="inlineStr"/>
+      <c r="S155" s="47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="20" customHeight="1">
+      <c r="B156" s="13" t="inlineStr">
+        <is>
+          <t>SUBTOTAL  Campaña Secundaria LMM</t>
+        </is>
+      </c>
+      <c r="F156" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="G156" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="H156" s="15" t="inlineStr">
+        <is>
+          <t>-58%</t>
+        </is>
+      </c>
+      <c r="I156" s="16" t="n">
+        <v>73253</v>
+      </c>
+    </row>
+    <row r="158" ht="22" customHeight="1">
+      <c r="B158" s="5" t="inlineStr">
+        <is>
+          <t>▶ Campaña Conversión Catálogo</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="18" customHeight="1">
+      <c r="B159" s="32" t="inlineStr">
+        <is>
+          <t>Fragancias Picnic</t>
+        </is>
+      </c>
+      <c r="C159" s="33" t="n">
+        <v>2356</v>
+      </c>
+      <c r="D159" s="33" t="n">
+        <v>3006</v>
+      </c>
+      <c r="E159" s="33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F159" s="34" t="n">
+        <v>29</v>
+      </c>
+      <c r="G159" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H159" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I159" s="37" t="n">
+        <v>6363</v>
+      </c>
+      <c r="J159" s="37" t="n">
+        <v>219</v>
+      </c>
+      <c r="K159" s="33" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="L159" s="33" t="n">
+        <v>2116</v>
+      </c>
+      <c r="M159" s="33" t="inlineStr"/>
+      <c r="N159" s="33" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O159" s="33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P159" s="33" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q159" s="33" t="inlineStr"/>
+      <c r="R159" s="33" t="n">
+        <v>27</v>
+      </c>
+      <c r="S159" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="18" customHeight="1">
+      <c r="B160" s="32" t="inlineStr">
+        <is>
+          <t>Imagen Cotton Vlabel</t>
+        </is>
+      </c>
+      <c r="C160" s="33" t="n">
+        <v>1058</v>
+      </c>
+      <c r="D160" s="33" t="n">
+        <v>1219</v>
+      </c>
+      <c r="E160" s="33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F160" s="34" t="n">
+        <v>21</v>
+      </c>
+      <c r="G160" s="35" t="n">
+        <v>120</v>
+      </c>
+      <c r="H160" s="36" t="inlineStr">
+        <is>
+          <t>-82%</t>
+        </is>
+      </c>
+      <c r="I160" s="37" t="n">
+        <v>1981</v>
+      </c>
+      <c r="J160" s="37" t="n">
+        <v>94</v>
+      </c>
+      <c r="K160" s="33" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="L160" s="33" t="n">
+        <v>1625</v>
+      </c>
+      <c r="M160" s="33" t="inlineStr"/>
+      <c r="N160" s="33" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O160" s="33" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P160" s="33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q160" s="33" t="inlineStr"/>
+      <c r="R160" s="33" t="n">
+        <v>19</v>
+      </c>
+      <c r="S160" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="18" customHeight="1">
+      <c r="B161" s="18" t="inlineStr">
+        <is>
+          <t>Hot Chocalate</t>
+        </is>
+      </c>
+      <c r="C161" s="19" t="n">
+        <v>161</v>
+      </c>
+      <c r="D161" s="19" t="n">
+        <v>285</v>
+      </c>
+      <c r="E161" s="19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F161" s="20" t="n">
+        <v>13</v>
+      </c>
+      <c r="G161" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H161" s="22" t="inlineStr">
+        <is>
+          <t>+30%</t>
+        </is>
+      </c>
+      <c r="I161" s="23" t="n">
+        <v>449</v>
+      </c>
+      <c r="J161" s="23" t="n">
+        <v>34</v>
+      </c>
+      <c r="K161" s="19" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="L161" s="19" t="n">
+        <v>1575</v>
+      </c>
+      <c r="M161" s="19" t="inlineStr"/>
+      <c r="N161" s="19" t="inlineStr"/>
+      <c r="O161" s="19" t="inlineStr"/>
+      <c r="P161" s="19" t="inlineStr"/>
+      <c r="Q161" s="19" t="inlineStr"/>
+      <c r="R161" s="19" t="n">
+        <v>13</v>
+      </c>
+      <c r="S161" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="18" customHeight="1">
+      <c r="B162" s="32" t="inlineStr">
+        <is>
+          <t>Crema dibujada</t>
+        </is>
+      </c>
+      <c r="C162" s="33" t="n">
+        <v>543</v>
+      </c>
+      <c r="D162" s="33" t="n">
+        <v>600</v>
+      </c>
+      <c r="E162" s="33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F162" s="34" t="n">
+        <v>10</v>
+      </c>
+      <c r="G162" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="H162" s="46" t="inlineStr">
+        <is>
+          <t>+100%</t>
+        </is>
+      </c>
+      <c r="I162" s="37" t="n">
+        <v>847</v>
+      </c>
+      <c r="J162" s="37" t="n">
+        <v>84</v>
+      </c>
+      <c r="K162" s="33" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="L162" s="33" t="n">
+        <v>1411</v>
+      </c>
+      <c r="M162" s="33" t="inlineStr"/>
+      <c r="N162" s="33" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O162" s="33" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P162" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q162" s="33" t="inlineStr"/>
+      <c r="R162" s="33" t="n">
+        <v>9</v>
+      </c>
+      <c r="S162" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="18" customHeight="1">
+      <c r="B163" s="32" t="inlineStr">
+        <is>
+          <t>Carrusel Sun Kissed</t>
+        </is>
+      </c>
+      <c r="C163" s="33" t="n">
+        <v>212</v>
+      </c>
+      <c r="D163" s="33" t="n">
+        <v>229</v>
+      </c>
+      <c r="E163" s="33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F163" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="G163" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="H163" s="36" t="inlineStr">
+        <is>
+          <t>-43%</t>
+        </is>
+      </c>
+      <c r="I163" s="37" t="n">
+        <v>364</v>
+      </c>
+      <c r="J163" s="37" t="n">
+        <v>91</v>
+      </c>
+      <c r="K163" s="33" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="L163" s="33" t="n">
+        <v>1589</v>
+      </c>
+      <c r="M163" s="33" t="inlineStr"/>
+      <c r="N163" s="33" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O163" s="33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P163" s="33" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q163" s="33" t="inlineStr"/>
+      <c r="R163" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="S163" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="18" customHeight="1">
+      <c r="B164" s="32" t="inlineStr">
+        <is>
+          <t>4 por 3</t>
+        </is>
+      </c>
+      <c r="C164" s="33" t="n">
+        <v>134</v>
+      </c>
+      <c r="D164" s="33" t="n">
+        <v>174</v>
+      </c>
+      <c r="E164" s="33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F164" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="G164" s="35" t="n">
+        <v>123</v>
+      </c>
+      <c r="H164" s="36" t="inlineStr">
+        <is>
+          <t>-96%</t>
+        </is>
+      </c>
+      <c r="I164" s="37" t="n">
+        <v>421</v>
+      </c>
+      <c r="J164" s="37" t="n">
+        <v>84</v>
+      </c>
+      <c r="K164" s="33" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L164" s="33" t="n">
+        <v>2419</v>
+      </c>
+      <c r="M164" s="33" t="inlineStr"/>
+      <c r="N164" s="33" t="inlineStr"/>
+      <c r="O164" s="33" t="inlineStr"/>
+      <c r="P164" s="33" t="inlineStr"/>
+      <c r="Q164" s="33" t="inlineStr"/>
+      <c r="R164" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="S164" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="18" customHeight="1">
+      <c r="B165" s="6" t="inlineStr">
+        <is>
+          <t>Nuevos difusores</t>
+        </is>
+      </c>
+      <c r="C165" s="7" t="n">
+        <v>247</v>
+      </c>
+      <c r="D165" s="7" t="n">
+        <v>280</v>
+      </c>
+      <c r="E165" s="7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F165" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G165" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="H165" s="17" t="inlineStr">
+        <is>
+          <t>-77%</t>
+        </is>
+      </c>
+      <c r="I165" s="11" t="n">
+        <v>575</v>
+      </c>
+      <c r="J165" s="11" t="n">
+        <v>71</v>
+      </c>
+      <c r="K165" s="7" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="L165" s="7" t="n">
+        <v>2053</v>
+      </c>
+      <c r="M165" s="7" t="inlineStr"/>
+      <c r="N165" s="7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O165" s="7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P165" s="7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q165" s="7" t="inlineStr"/>
+      <c r="R165" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="S165" s="12" t="inlineStr">
+        <is>
+          <t>🔍 REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="18" customHeight="1">
+      <c r="B166" s="25" t="inlineStr">
+        <is>
+          <t>Macbook</t>
+        </is>
+      </c>
+      <c r="C166" s="26" t="n">
+        <v>8482</v>
+      </c>
+      <c r="D166" s="26" t="n">
+        <v>14633</v>
+      </c>
+      <c r="E166" s="26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F166" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="G166" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="H166" s="31" t="inlineStr">
+        <is>
+          <t>+75%</t>
+        </is>
+      </c>
+      <c r="I166" s="30" t="n">
+        <v>21610</v>
+      </c>
+      <c r="J166" s="30" t="n">
+        <v>3087</v>
+      </c>
+      <c r="K166" s="26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L166" s="26" t="n">
+        <v>1476</v>
+      </c>
+      <c r="M166" s="26" t="inlineStr"/>
+      <c r="N166" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="O166" s="26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P166" s="26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q166" s="26" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="R166" s="26" t="n">
+        <v>111</v>
+      </c>
+      <c r="S166" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="18" customHeight="1">
+      <c r="B167" s="32" t="inlineStr">
+        <is>
+          <t>Protector Termico</t>
+        </is>
+      </c>
+      <c r="C167" s="33" t="n">
+        <v>1177</v>
+      </c>
+      <c r="D167" s="33" t="n">
+        <v>1485</v>
+      </c>
+      <c r="E167" s="33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F167" s="34" t="n">
+        <v>18</v>
+      </c>
+      <c r="G167" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="H167" s="46" t="inlineStr">
+        <is>
+          <t>+29%</t>
+        </is>
+      </c>
+      <c r="I167" s="37" t="n">
+        <v>1837</v>
+      </c>
+      <c r="J167" s="37" t="n">
+        <v>102</v>
+      </c>
+      <c r="K167" s="33" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L167" s="33" t="n">
+        <v>1237</v>
+      </c>
+      <c r="M167" s="33" t="inlineStr"/>
+      <c r="N167" s="33" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O167" s="33" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P167" s="33" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q167" s="33" t="inlineStr"/>
+      <c r="R167" s="33" t="n">
+        <v>18</v>
+      </c>
+      <c r="S167" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="18" customHeight="1">
+      <c r="B168" s="32" t="inlineStr">
+        <is>
+          <t>Reel de fragancias</t>
+        </is>
+      </c>
+      <c r="C168" s="33" t="n">
+        <v>272</v>
+      </c>
+      <c r="D168" s="33" t="n">
+        <v>344</v>
+      </c>
+      <c r="E168" s="33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F168" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G168" s="35" t="n">
+        <v>104</v>
+      </c>
+      <c r="H168" s="36" t="inlineStr">
+        <is>
+          <t>-98%</t>
+        </is>
+      </c>
+      <c r="I168" s="37" t="n">
+        <v>523</v>
+      </c>
+      <c r="J168" s="37" t="n">
+        <v>261</v>
+      </c>
+      <c r="K168" s="33" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L168" s="33" t="n">
+        <v>1520</v>
+      </c>
+      <c r="M168" s="33" t="inlineStr"/>
+      <c r="N168" s="33" t="inlineStr"/>
+      <c r="O168" s="33" t="inlineStr"/>
+      <c r="P168" s="33" t="inlineStr"/>
+      <c r="Q168" s="33" t="inlineStr"/>
+      <c r="R168" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="S168" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="18" customHeight="1">
+      <c r="B169" s="32" t="inlineStr">
+        <is>
+          <t>Imagen Gato</t>
+        </is>
+      </c>
+      <c r="C169" s="33" t="n">
+        <v>426</v>
+      </c>
+      <c r="D169" s="33" t="n">
+        <v>481</v>
+      </c>
+      <c r="E169" s="33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F169" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="G169" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="H169" s="36" t="inlineStr">
+        <is>
+          <t>-29%</t>
+        </is>
+      </c>
+      <c r="I169" s="37" t="n">
+        <v>830</v>
+      </c>
+      <c r="J169" s="37" t="n">
+        <v>166</v>
+      </c>
+      <c r="K169" s="33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L169" s="33" t="n">
+        <v>1725</v>
+      </c>
+      <c r="M169" s="33" t="inlineStr"/>
+      <c r="N169" s="33" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O169" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="P169" s="33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q169" s="33" t="inlineStr"/>
+      <c r="R169" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="S169" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="18" customHeight="1">
+      <c r="B170" s="32" t="inlineStr">
+        <is>
+          <t>Reel cafetería</t>
+        </is>
+      </c>
+      <c r="C170" s="33" t="n">
+        <v>538</v>
+      </c>
+      <c r="D170" s="33" t="n">
+        <v>601</v>
+      </c>
+      <c r="E170" s="33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F170" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="G170" s="35" t="n">
+        <v>88</v>
+      </c>
+      <c r="H170" s="36" t="inlineStr">
+        <is>
+          <t>-92%</t>
+        </is>
+      </c>
+      <c r="I170" s="37" t="n">
+        <v>1087</v>
+      </c>
+      <c r="J170" s="37" t="n">
+        <v>155</v>
+      </c>
+      <c r="K170" s="33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L170" s="33" t="n">
+        <v>1808</v>
+      </c>
+      <c r="M170" s="33" t="inlineStr"/>
+      <c r="N170" s="33" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="O170" s="33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P170" s="33" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q170" s="33" t="inlineStr"/>
+      <c r="R170" s="33" t="n">
+        <v>7</v>
+      </c>
+      <c r="S170" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="18" customHeight="1">
+      <c r="B171" s="25" t="inlineStr">
+        <is>
+          <t>Imagen Bubble gum</t>
+        </is>
+      </c>
+      <c r="C171" s="26" t="n">
+        <v>795</v>
+      </c>
+      <c r="D171" s="26" t="n">
+        <v>909</v>
+      </c>
+      <c r="E171" s="26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F171" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G171" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="H171" s="29" t="inlineStr">
+        <is>
+          <t>-96%</t>
+        </is>
+      </c>
+      <c r="I171" s="30" t="n">
+        <v>1506</v>
+      </c>
+      <c r="J171" s="30" t="n">
+        <v>1506</v>
+      </c>
+      <c r="K171" s="26" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="L171" s="26" t="n">
+        <v>1656</v>
+      </c>
+      <c r="M171" s="26" t="inlineStr"/>
+      <c r="N171" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="O171" s="26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P171" s="26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q171" s="26" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="R171" s="26" t="n">
+        <v>13</v>
+      </c>
+      <c r="S171" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="18" customHeight="1">
+      <c r="B172" s="32" t="inlineStr">
+        <is>
+          <t>Carrusel Post que puedes oler</t>
+        </is>
+      </c>
+      <c r="C172" s="33" t="n">
+        <v>563</v>
+      </c>
+      <c r="D172" s="33" t="n">
+        <v>638</v>
+      </c>
+      <c r="E172" s="33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F172" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G172" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H172" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I172" s="37" t="n">
+        <v>849</v>
+      </c>
+      <c r="J172" s="37" t="n">
+        <v>283</v>
+      </c>
+      <c r="K172" s="33" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L172" s="33" t="n">
+        <v>1330</v>
+      </c>
+      <c r="M172" s="33" t="inlineStr"/>
+      <c r="N172" s="33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O172" s="33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P172" s="33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q172" s="33" t="inlineStr"/>
+      <c r="R172" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="S172" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="18" customHeight="1">
+      <c r="B173" s="32" t="inlineStr">
+        <is>
+          <t>Rutina 4 pasos 2.0</t>
+        </is>
+      </c>
+      <c r="C173" s="33" t="n">
+        <v>294</v>
+      </c>
+      <c r="D173" s="33" t="n">
+        <v>339</v>
+      </c>
+      <c r="E173" s="33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F173" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G173" s="35" t="n">
+        <v>36</v>
+      </c>
+      <c r="H173" s="36" t="inlineStr">
+        <is>
+          <t>-92%</t>
+        </is>
+      </c>
+      <c r="I173" s="37" t="n">
+        <v>594</v>
+      </c>
+      <c r="J173" s="37" t="n">
+        <v>198</v>
+      </c>
+      <c r="K173" s="33" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="L173" s="33" t="n">
+        <v>1752</v>
+      </c>
+      <c r="M173" s="33" t="inlineStr"/>
+      <c r="N173" s="33" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="O173" s="33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P173" s="33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q173" s="33" t="inlineStr"/>
+      <c r="R173" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="S173" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="18" customHeight="1">
+      <c r="B174" s="25" t="inlineStr">
+        <is>
+          <t>Bye Bye Aroma</t>
+        </is>
+      </c>
+      <c r="C174" s="26" t="n">
+        <v>2814</v>
+      </c>
+      <c r="D174" s="26" t="n">
+        <v>3783</v>
+      </c>
+      <c r="E174" s="26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F174" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="G174" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="H174" s="29" t="inlineStr">
+        <is>
+          <t>-50%</t>
+        </is>
+      </c>
+      <c r="I174" s="30" t="n">
+        <v>6908</v>
+      </c>
+      <c r="J174" s="30" t="n">
+        <v>2302</v>
+      </c>
+      <c r="K174" s="26" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="L174" s="26" t="n">
+        <v>1826</v>
+      </c>
+      <c r="M174" s="26" t="inlineStr"/>
+      <c r="N174" s="26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O174" s="26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="P174" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q174" s="26" t="n">
+        <v>12.52</v>
+      </c>
+      <c r="R174" s="26" t="n">
+        <v>45</v>
+      </c>
+      <c r="S174" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="18" customHeight="1">
+      <c r="B175" s="18" t="inlineStr">
+        <is>
+          <t>Cremas Sun Kissed</t>
+        </is>
+      </c>
+      <c r="C175" s="19" t="n">
+        <v>171061</v>
+      </c>
+      <c r="D175" s="19" t="n">
+        <v>615106</v>
+      </c>
+      <c r="E175" s="19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F175" s="20" t="n">
+        <v>139</v>
+      </c>
+      <c r="G175" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="H175" s="22" t="inlineStr">
+        <is>
+          <t>+479%</t>
+        </is>
+      </c>
+      <c r="I175" s="23" t="n">
+        <v>875903</v>
+      </c>
+      <c r="J175" s="23" t="n">
+        <v>6301</v>
+      </c>
+      <c r="K175" s="19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="L175" s="19" t="n">
+        <v>1423</v>
+      </c>
+      <c r="M175" s="19" t="inlineStr"/>
+      <c r="N175" s="19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O175" s="19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P175" s="19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q175" s="19" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="R175" s="19" t="n">
+        <v>6019</v>
+      </c>
+      <c r="S175" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="18" customHeight="1">
+      <c r="B176" s="32" t="inlineStr">
+        <is>
+          <t>Home Spray</t>
+        </is>
+      </c>
+      <c r="C176" s="33" t="n">
+        <v>205</v>
+      </c>
+      <c r="D176" s="33" t="n">
+        <v>234</v>
+      </c>
+      <c r="E176" s="33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F176" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G176" s="35" t="n">
+        <v>126</v>
+      </c>
+      <c r="H176" s="36" t="inlineStr">
+        <is>
+          <t>-98%</t>
+        </is>
+      </c>
+      <c r="I176" s="37" t="n">
+        <v>314</v>
+      </c>
+      <c r="J176" s="37" t="n">
+        <v>157</v>
+      </c>
+      <c r="K176" s="33" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L176" s="33" t="n">
+        <v>1341</v>
+      </c>
+      <c r="M176" s="33" t="inlineStr"/>
+      <c r="N176" s="33" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O176" s="33" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P176" s="33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q176" s="33" t="inlineStr"/>
+      <c r="R176" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="S176" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="18" customHeight="1">
+      <c r="B177" s="32" t="inlineStr">
+        <is>
+          <t>Go Paw @Juliana Carrascal</t>
+        </is>
+      </c>
+      <c r="C177" s="33" t="n">
+        <v>1410</v>
+      </c>
+      <c r="D177" s="33" t="n">
+        <v>1616</v>
+      </c>
+      <c r="E177" s="33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F177" s="34" t="n">
+        <v>20</v>
+      </c>
+      <c r="G177" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H177" s="46" t="inlineStr">
+        <is>
+          <t>+1900%</t>
+        </is>
+      </c>
+      <c r="I177" s="37" t="n">
+        <v>2769</v>
+      </c>
+      <c r="J177" s="37" t="n">
+        <v>138</v>
+      </c>
+      <c r="K177" s="33" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="L177" s="33" t="n">
+        <v>1713</v>
+      </c>
+      <c r="M177" s="33" t="inlineStr"/>
+      <c r="N177" s="33" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O177" s="33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P177" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q177" s="33" t="inlineStr"/>
+      <c r="R177" s="33" t="n">
+        <v>18</v>
+      </c>
+      <c r="S177" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="18" customHeight="1">
+      <c r="B178" s="32" t="inlineStr">
+        <is>
+          <t>Go Paw Carrusel Mascotas</t>
+        </is>
+      </c>
+      <c r="C178" s="33" t="n">
+        <v>533</v>
+      </c>
+      <c r="D178" s="33" t="n">
+        <v>622</v>
+      </c>
+      <c r="E178" s="33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F178" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="G178" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H178" s="46" t="inlineStr">
+        <is>
+          <t>+600%</t>
+        </is>
+      </c>
+      <c r="I178" s="37" t="n">
+        <v>1107</v>
+      </c>
+      <c r="J178" s="37" t="n">
+        <v>158</v>
+      </c>
+      <c r="K178" s="33" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="L178" s="33" t="n">
+        <v>1779</v>
+      </c>
+      <c r="M178" s="33" t="inlineStr"/>
+      <c r="N178" s="33" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="O178" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="P178" s="33" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q178" s="33" t="inlineStr"/>
+      <c r="R178" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="S178" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="18" customHeight="1">
+      <c r="B179" s="32" t="inlineStr">
+        <is>
+          <t>UGC Soft Milk Febrero</t>
+        </is>
+      </c>
+      <c r="C179" s="33" t="n">
+        <v>525</v>
+      </c>
+      <c r="D179" s="33" t="n">
+        <v>601</v>
+      </c>
+      <c r="E179" s="33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F179" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="G179" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H179" s="46" t="inlineStr">
+        <is>
+          <t>+300%</t>
+        </is>
+      </c>
+      <c r="I179" s="37" t="n">
+        <v>998</v>
+      </c>
+      <c r="J179" s="37" t="n">
+        <v>249</v>
+      </c>
+      <c r="K179" s="33" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L179" s="33" t="n">
+        <v>1660</v>
+      </c>
+      <c r="M179" s="33" t="inlineStr"/>
+      <c r="N179" s="33" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O179" s="33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P179" s="33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q179" s="33" t="inlineStr"/>
+      <c r="R179" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="S179" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="18" customHeight="1">
+      <c r="B180" s="32" t="inlineStr">
+        <is>
+          <t>Aceite Capilar Go Hair</t>
+        </is>
+      </c>
+      <c r="C180" s="33" t="n">
+        <v>576</v>
+      </c>
+      <c r="D180" s="33" t="n">
+        <v>634</v>
+      </c>
+      <c r="E180" s="33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F180" s="34" t="n">
+        <v>10</v>
+      </c>
+      <c r="G180" s="35" t="n">
+        <v>23</v>
+      </c>
+      <c r="H180" s="36" t="inlineStr">
+        <is>
+          <t>-57%</t>
+        </is>
+      </c>
+      <c r="I180" s="37" t="n">
+        <v>1110</v>
+      </c>
+      <c r="J180" s="37" t="n">
+        <v>111</v>
+      </c>
+      <c r="K180" s="33" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="L180" s="33" t="n">
+        <v>1750</v>
+      </c>
+      <c r="M180" s="33" t="inlineStr"/>
+      <c r="N180" s="33" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O180" s="33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P180" s="33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q180" s="33" t="inlineStr"/>
+      <c r="R180" s="33" t="n">
+        <v>9</v>
+      </c>
+      <c r="S180" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="18" customHeight="1">
+      <c r="B181" s="25" t="inlineStr">
+        <is>
+          <t>Go Paw Wild Berries y Cotton Candy</t>
+        </is>
+      </c>
+      <c r="C181" s="26" t="n">
+        <v>884</v>
+      </c>
+      <c r="D181" s="26" t="n">
+        <v>997</v>
+      </c>
+      <c r="E181" s="26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F181" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G181" s="28" t="n">
+        <v>15</v>
+      </c>
+      <c r="H181" s="29" t="inlineStr">
+        <is>
+          <t>-93%</t>
+        </is>
+      </c>
+      <c r="I181" s="30" t="n">
+        <v>1315</v>
+      </c>
+      <c r="J181" s="30" t="n">
+        <v>1315</v>
+      </c>
+      <c r="K181" s="26" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L181" s="26" t="n">
+        <v>1318</v>
+      </c>
+      <c r="M181" s="26" t="inlineStr"/>
+      <c r="N181" s="26" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O181" s="26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P181" s="26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q181" s="26" t="n">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="R181" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="S181" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="18" customHeight="1">
+      <c r="B182" s="32" t="inlineStr">
+        <is>
+          <t>Kit Cuidado Capilar</t>
+        </is>
+      </c>
+      <c r="C182" s="33" t="n">
+        <v>591</v>
+      </c>
+      <c r="D182" s="33" t="n">
+        <v>675</v>
+      </c>
+      <c r="E182" s="33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F182" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="G182" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="H182" s="36" t="inlineStr">
+        <is>
+          <t>-14%</t>
+        </is>
+      </c>
+      <c r="I182" s="37" t="n">
+        <v>1117</v>
+      </c>
+      <c r="J182" s="37" t="n">
+        <v>186</v>
+      </c>
+      <c r="K182" s="33" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="L182" s="33" t="n">
+        <v>1654</v>
+      </c>
+      <c r="M182" s="33" t="inlineStr"/>
+      <c r="N182" s="33" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O182" s="33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P182" s="33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q182" s="33" t="inlineStr"/>
+      <c r="R182" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="S182" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="18" customHeight="1">
+      <c r="B183" s="6" t="inlineStr">
+        <is>
+          <t>Protector Termico Pistacho Caramelo</t>
+        </is>
+      </c>
+      <c r="C183" s="7" t="n">
+        <v>352</v>
+      </c>
+      <c r="D183" s="7" t="n">
+        <v>460</v>
+      </c>
+      <c r="E183" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F183" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="G183" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="H183" s="17" t="inlineStr">
+        <is>
+          <t>-64%</t>
+        </is>
+      </c>
+      <c r="I183" s="11" t="n">
+        <v>622</v>
+      </c>
+      <c r="J183" s="11" t="n">
+        <v>69</v>
+      </c>
+      <c r="K183" s="7" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="L183" s="7" t="n">
+        <v>1352</v>
+      </c>
+      <c r="M183" s="7" t="inlineStr"/>
+      <c r="N183" s="7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O183" s="7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P183" s="7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q183" s="7" t="inlineStr"/>
+      <c r="R183" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="S183" s="12" t="inlineStr">
+        <is>
+          <t>🔍 REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="18" customHeight="1">
+      <c r="B184" s="25" t="inlineStr">
+        <is>
+          <t>Home Spray @vanusallorenzo</t>
+        </is>
+      </c>
+      <c r="C184" s="26" t="n">
+        <v>1855</v>
+      </c>
+      <c r="D184" s="26" t="n">
+        <v>2325</v>
+      </c>
+      <c r="E184" s="26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F184" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G184" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="H184" s="29" t="inlineStr">
+        <is>
+          <t>-80%</t>
+        </is>
+      </c>
+      <c r="I184" s="30" t="n">
+        <v>3351</v>
+      </c>
+      <c r="J184" s="30" t="n">
+        <v>3351</v>
+      </c>
+      <c r="K184" s="26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="L184" s="26" t="n">
+        <v>1441</v>
+      </c>
+      <c r="M184" s="26" t="inlineStr"/>
+      <c r="N184" s="26" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O184" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="P184" s="26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q184" s="26" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="R184" s="26" t="n">
+        <v>21</v>
+      </c>
+      <c r="S184" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="20" customHeight="1">
+      <c r="B185" s="13" t="inlineStr">
+        <is>
+          <t>SUBTOTAL  Campaña Conversión Catálogo</t>
+        </is>
+      </c>
+      <c r="F185" s="14" t="n">
+        <v>338</v>
+      </c>
+      <c r="G185" s="14" t="n">
+        <v>812</v>
+      </c>
+      <c r="H185" s="15" t="inlineStr">
+        <is>
+          <t>-58%</t>
+        </is>
+      </c>
+      <c r="I185" s="16" t="n">
+        <v>935350</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="36">
+    <mergeCell ref="B99:T99"/>
+    <mergeCell ref="B84:T84"/>
+    <mergeCell ref="B92:E92"/>
+    <mergeCell ref="B118:T118"/>
+    <mergeCell ref="B65:T65"/>
+    <mergeCell ref="B104:E104"/>
+    <mergeCell ref="B158:T158"/>
+    <mergeCell ref="B89:T89"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="B94:T94"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="B185:E185"/>
+    <mergeCell ref="B106:T106"/>
+    <mergeCell ref="B150:E150"/>
+    <mergeCell ref="B156:E156"/>
+    <mergeCell ref="B47:T47"/>
+    <mergeCell ref="B100:T100"/>
+    <mergeCell ref="B7:T7"/>
+    <mergeCell ref="B96:E96"/>
+    <mergeCell ref="B66:T66"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B18:T18"/>
+    <mergeCell ref="B56:T56"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B152:T152"/>
+    <mergeCell ref="B2:T2"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="B23:T23"/>
+    <mergeCell ref="B8:T8"/>
+    <mergeCell ref="B82:E82"/>
+    <mergeCell ref="B116:E116"/>
     <mergeCell ref="B1:T1"/>
-    <mergeCell ref="B2:T2"/>
+    <mergeCell ref="B13:T13"/>
+    <mergeCell ref="B57:T57"/>
+    <mergeCell ref="B87:E87"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reportes/Reporte_abril_2026.xlsx
+++ b/reportes/Reporte_abril_2026.xlsx
@@ -927,14 +927,14 @@
     <row r="7" ht="24" customHeight="1">
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Seducete</t>
+          <t>SEDUCETE</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>▶ Marketing Objetivo Visita Perfil Instagram</t>
+          <t>▸ Marketing Objetivo Visita Perfil Instagram</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
     <row r="13" ht="22" customHeight="1">
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>▶ Tráfico Web Objetivo Conversión</t>
+          <t>▸ Tráfico Web Objetivo Conversión</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
     <row r="18" ht="22" customHeight="1">
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>▶ Academia Prueba Formularios</t>
+          <t>▸ Academia Prueba Formularios</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1366,7 @@
     <row r="23" ht="22" customHeight="1">
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>▶ Conversión Web Ventas</t>
+          <t>▸ Conversión Web Ventas</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
     <row r="47" ht="22" customHeight="1">
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>▶ Campaña Mktg prueba Pau</t>
+          <t>▸ Campaña Mktg prueba Pau</t>
         </is>
       </c>
     </row>
@@ -2958,7 +2958,7 @@
     <row r="55" ht="26" customHeight="1">
       <c r="B55" s="46" t="inlineStr">
         <is>
-          <t>💡  ANÁLISIS CLAUDE — SEDUCETE</t>
+          <t>💡  Análisis Claude — Seducete</t>
         </is>
       </c>
     </row>
@@ -2972,27 +2972,27 @@
     <row r="57" ht="20" customHeight="1">
       <c r="B57" s="48" t="inlineStr">
         <is>
-          <t>CAMPAÑA</t>
+          <t>Campaña</t>
         </is>
       </c>
       <c r="C57" s="48" t="inlineStr">
         <is>
-          <t>TIPO</t>
+          <t>Tipo</t>
         </is>
       </c>
       <c r="D57" s="48" t="inlineStr">
         <is>
-          <t>TÍTULO DEL HALLAZGO</t>
+          <t>Hallazgo</t>
         </is>
       </c>
       <c r="H57" s="48" t="inlineStr">
         <is>
-          <t>DESCRIPCIÓN</t>
+          <t>Descripción</t>
         </is>
       </c>
       <c r="M57" s="48" t="inlineStr">
         <is>
-          <t>ACCIÓN RECOMENDADA</t>
+          <t>Acción recomendada</t>
         </is>
       </c>
     </row>
@@ -3272,14 +3272,14 @@
     <row r="71" ht="24" customHeight="1">
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Bluesky</t>
+          <t>BLUESKY</t>
         </is>
       </c>
     </row>
     <row r="72" ht="22" customHeight="1">
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>▶ Tráfico Perfil Instagram MKT</t>
+          <t>▸ Tráfico Perfil Instagram MKT</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3529,7 @@
     <row r="79" ht="26" customHeight="1">
       <c r="B79" s="46" t="inlineStr">
         <is>
-          <t>💡  ANÁLISIS CLAUDE — BLUESKY</t>
+          <t>💡  Análisis Claude — Bluesky</t>
         </is>
       </c>
     </row>
@@ -3543,27 +3543,27 @@
     <row r="81" ht="20" customHeight="1">
       <c r="B81" s="48" t="inlineStr">
         <is>
-          <t>CAMPAÑA</t>
+          <t>Campaña</t>
         </is>
       </c>
       <c r="C81" s="48" t="inlineStr">
         <is>
-          <t>TIPO</t>
+          <t>Tipo</t>
         </is>
       </c>
       <c r="D81" s="48" t="inlineStr">
         <is>
-          <t>TÍTULO DEL HALLAZGO</t>
+          <t>Hallazgo</t>
         </is>
       </c>
       <c r="H81" s="48" t="inlineStr">
         <is>
-          <t>DESCRIPCIÓN</t>
+          <t>Descripción</t>
         </is>
       </c>
       <c r="M81" s="48" t="inlineStr">
         <is>
-          <t>ACCIÓN RECOMENDADA</t>
+          <t>Acción recomendada</t>
         </is>
       </c>
     </row>
@@ -3643,14 +3643,14 @@
     <row r="87" ht="24" customHeight="1">
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Nail Outlet</t>
+          <t>NAIL OUTLET</t>
         </is>
       </c>
     </row>
     <row r="88" ht="22" customHeight="1">
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>▶ Objetivo Conversión Ventas</t>
+          <t>▸ Objetivo Conversión Ventas</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
     <row r="106" ht="22" customHeight="1">
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>▶ Tráfico Perfil Instagram MKT</t>
+          <t>▸ Tráfico Perfil Instagram MKT</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
     <row r="111" ht="22" customHeight="1">
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>▶ Remarketing Nail Outlet</t>
+          <t>▸ Remarketing Nail Outlet</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
     <row r="116" ht="22" customHeight="1">
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>▶ Campaña Conversión Catálogo</t>
+          <t>▸ Campaña Conversión Catálogo</t>
         </is>
       </c>
     </row>
@@ -4926,7 +4926,7 @@
     <row r="120" ht="26" customHeight="1">
       <c r="B120" s="46" t="inlineStr">
         <is>
-          <t>💡  ANÁLISIS CLAUDE — NAIL OUTLET</t>
+          <t>💡  Análisis Claude — Nail Outlet</t>
         </is>
       </c>
     </row>
@@ -4940,27 +4940,27 @@
     <row r="122" ht="20" customHeight="1">
       <c r="B122" s="48" t="inlineStr">
         <is>
-          <t>CAMPAÑA</t>
+          <t>Campaña</t>
         </is>
       </c>
       <c r="C122" s="48" t="inlineStr">
         <is>
-          <t>TIPO</t>
+          <t>Tipo</t>
         </is>
       </c>
       <c r="D122" s="48" t="inlineStr">
         <is>
-          <t>TÍTULO DEL HALLAZGO</t>
+          <t>Hallazgo</t>
         </is>
       </c>
       <c r="H122" s="48" t="inlineStr">
         <is>
-          <t>DESCRIPCIÓN</t>
+          <t>Descripción</t>
         </is>
       </c>
       <c r="M122" s="48" t="inlineStr">
         <is>
-          <t>ACCIÓN RECOMENDADA</t>
+          <t>Acción recomendada</t>
         </is>
       </c>
     </row>
@@ -5190,14 +5190,14 @@
     <row r="134" ht="24" customHeight="1">
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>Go Nails</t>
+          <t>GO NAILS</t>
         </is>
       </c>
     </row>
     <row r="135" ht="22" customHeight="1">
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>▶ Remarketing Go Nails 2024</t>
+          <t>▸ Remarketing Go Nails 2024</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5405,7 @@
     <row r="141" ht="22" customHeight="1">
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>▶ Marketing Go Nails - Trafico Insta</t>
+          <t>▸ Marketing Go Nails - Trafico Insta</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
     <row r="153" ht="22" customHeight="1">
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>▶ Campaña principal de Conversión</t>
+          <t>▸ Campaña principal de Conversión</t>
         </is>
       </c>
     </row>
@@ -7811,7 +7811,7 @@
     <row r="187" ht="22" customHeight="1">
       <c r="B187" s="5" t="inlineStr">
         <is>
-          <t>▶ Campaña Secundaria LMM</t>
+          <t>▸ Campaña Secundaria LMM</t>
         </is>
       </c>
     </row>
@@ -8009,7 +8009,7 @@
     <row r="193" ht="22" customHeight="1">
       <c r="B193" s="5" t="inlineStr">
         <is>
-          <t>▶ Campaña Conversión Catálogo</t>
+          <t>▸ Campaña Conversión Catálogo</t>
         </is>
       </c>
     </row>
@@ -9543,7 +9543,7 @@
     <row r="222" ht="26" customHeight="1">
       <c r="B222" s="46" t="inlineStr">
         <is>
-          <t>💡  ANÁLISIS CLAUDE — GO NAILS</t>
+          <t>💡  Análisis Claude — Go Nails</t>
         </is>
       </c>
     </row>
@@ -9557,27 +9557,27 @@
     <row r="224" ht="20" customHeight="1">
       <c r="B224" s="48" t="inlineStr">
         <is>
-          <t>CAMPAÑA</t>
+          <t>Campaña</t>
         </is>
       </c>
       <c r="C224" s="48" t="inlineStr">
         <is>
-          <t>TIPO</t>
+          <t>Tipo</t>
         </is>
       </c>
       <c r="D224" s="48" t="inlineStr">
         <is>
-          <t>TÍTULO DEL HALLAZGO</t>
+          <t>Hallazgo</t>
         </is>
       </c>
       <c r="H224" s="48" t="inlineStr">
         <is>
-          <t>DESCRIPCIÓN</t>
+          <t>Descripción</t>
         </is>
       </c>
       <c r="M224" s="48" t="inlineStr">
         <is>
-          <t>ACCIÓN RECOMENDADA</t>
+          <t>Acción recomendada</t>
         </is>
       </c>
     </row>

--- a/reportes/Reporte_abril_2026.xlsx
+++ b/reportes/Reporte_abril_2026.xlsx
@@ -794,7 +794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:T237"/>
+  <dimension ref="B1:T238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="2" max="2"/>
@@ -2965,7 +2965,7 @@
     <row r="56" ht="36" customHeight="1">
       <c r="B56" s="47" t="inlineStr">
         <is>
-          <t>Seducete bajó gasto 8% (de $5.5M a $5.1M) pero resultados cayeron 14% (de 35.4k a 30.4k), mostrando pérdida de eficiencia general. La campaña de ventas ($4.4M) tiene costo por compra de $5.081, fuera de benchmark en 11 de 15 anuncios activos.</t>
+          <t>Seducete redujo gasto 8% (de $5.5M a $5.1M) pero cayó 14% en resultados (de 35,423 a 30,410). La campaña de conversión web ($4.4M, 87% del presupuesto) tiene costo/compra promedio de $5,081, muy por encima del benchmark de $10,000 pero con anuncios individuales entre $1,988 y $19,856.</t>
         </is>
       </c>
     </row>
@@ -2999,7 +2999,7 @@
     <row r="58" ht="48" customHeight="1">
       <c r="B58" s="49" t="inlineStr">
         <is>
-          <t>Conversión Web Ventas</t>
+          <t>Marketing Objetivo Visita Perfil Instagram</t>
         </is>
       </c>
       <c r="C58" s="50" t="inlineStr">
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D58" s="51" t="inlineStr">
         <is>
-          <t>73% de anuncios fuera de benchmark</t>
+          <t>Costo/click fuera de benchmark</t>
         </is>
       </c>
       <c r="H58" s="52" t="inlineStr">
         <is>
-          <t>11 de 15 anuncios tienen costo/compra sobre $10.000 (benchmark: pausar &gt;$18k, revisar $10k-$18k). Base Evita 2 ($10.888), Lámpara Pre Curado ($11.153), Efecto glaseado ($11.081) y Ojos Satinados ($19.856) están quemando presupuesto sin retorno.</t>
+          <t>Ambos anuncios superan el benchmark OK de $40: Academia Cursos Gratuitos a $59 (+48%) y Cursos Presenciales a $47 (+18%). Hold Rate muy bajo (5.8% y 3.6%) indica que el video no retiene después del hook.</t>
         </is>
       </c>
       <c r="M58" s="53" t="inlineStr">
         <is>
-          <t>Pausar Ojos Satinados ($19.856) inmediatamente. Reemplazar creativos de Base Evita 2, Lámpara Pre Curado y Efecto glaseado esta semana con nuevos hooks centrados en beneficio producto.</t>
+          <t>Reducir intro del video a máximo 3 segundos y testear apertura más directa mostrando resultado del curso en primer plano</t>
         </is>
       </c>
     </row>
@@ -3032,22 +3032,26 @@
       </c>
       <c r="D59" s="56" t="inlineStr">
         <is>
-          <t>BLACK WEEK mantiene mejor performance</t>
+          <t>Cursos Presenciales mejora eficiencia</t>
         </is>
       </c>
       <c r="H59" s="57" t="inlineStr">
         <is>
-          <t>BLACK WEEK INICIO logra $1.988/compra (ganadora &lt;$6k) con ROAS 1.18 y 236 conversiones, 48% más compras vs marzo (159). Es el único anuncio con costo óptimo en toda la campaña de $4.4M.</t>
+          <t>Subió de 1,847 a 1,890 clicks (+2%) con costo que bajó a $47. CTR de 1.7% es bajo pero estable, puede estar generando tráfico a tiendas físicas no medible.</t>
         </is>
       </c>
       <c r="M59" s="58" t="inlineStr">
         <is>
-          <t>Duplicar creativos de BLACK WEEK adaptando el formato urgencia/descuento a productos actuales de abril. Testear 3 variaciones esta semana manteniendo estructura narrativa ganadora.</t>
+          <t>Mantener este anuncio activo y rotar creativos cada 2 semanas para evitar fatiga</t>
         </is>
       </c>
     </row>
     <row r="60" ht="48" customHeight="1">
-      <c r="B60" s="54" t="inlineStr"/>
+      <c r="B60" s="49" t="inlineStr">
+        <is>
+          <t>Tráfico Web Objetivo Conversión</t>
+        </is>
+      </c>
       <c r="C60" s="50" t="inlineStr">
         <is>
           <t>🔴 ALERTA</t>
@@ -3055,49 +3059,49 @@
       </c>
       <c r="D60" s="51" t="inlineStr">
         <is>
-          <t>Caída brutal en conversiones Top Templado</t>
+          <t>Esmaltado Permanente colapsó</t>
         </is>
       </c>
       <c r="H60" s="52" t="inlineStr">
         <is>
-          <t>Top Templado cayó 63% conversiones (de 111 a 41) manteniendo gasto similar ($167k). Costo/compra subió de ~$1.500 a $4.082, señal clara de fatiga creativa tras 2+ meses al aire.</t>
+          <t>Cayó de 1 a 15 compras pero costo explotó a $10,958 (fuera de benchmark). Gastó $164K (95% del presupuesto de campaña) con ROAS 0, claramente no está optimizado para conversión.</t>
         </is>
       </c>
       <c r="M60" s="53" t="inlineStr">
         <is>
-          <t>Rotar creativos Top Templado con 2 videos nuevos mostrando aplicación paso a paso y durabilidad. Mantener gasto pero renovar narrativa completa enfocada en problema/solución.</t>
+          <t>Pausar inmediatamente y reemplazar por creativo testimonial de clienta mostrando durabilidad del esmaltado a los 14 días</t>
         </is>
       </c>
     </row>
     <row r="61" ht="48" customHeight="1">
-      <c r="B61" s="49" t="inlineStr">
+      <c r="B61" s="54" t="inlineStr"/>
+      <c r="C61" s="59" t="inlineStr">
+        <is>
+          <t>🔵 INSIGHT</t>
+        </is>
+      </c>
+      <c r="D61" s="60" t="inlineStr">
+        <is>
+          <t>Manicurista Integral cambió métrica</t>
+        </is>
+      </c>
+      <c r="H61" s="61" t="inlineStr">
+        <is>
+          <t>Está configurado como purchase pero entrega link_clicks ($42/click). Bajó de 1,027 a 182 clicks (-82%), posible error de configuración de objetivo.</t>
+        </is>
+      </c>
+      <c r="M61" s="62" t="inlineStr">
+        <is>
+          <t>Verificar configuración del anuncio en Ads Manager y alinear objetivo de campaña con métrica real</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="48" customHeight="1">
+      <c r="B62" s="49" t="inlineStr">
         <is>
           <t>Academia Prueba Formularios</t>
         </is>
       </c>
-      <c r="C61" s="59" t="inlineStr">
-        <is>
-          <t>🔵 INSIGHT</t>
-        </is>
-      </c>
-      <c r="D61" s="60" t="inlineStr">
-        <is>
-          <t>Costo/lead estable pero con disparidad</t>
-        </is>
-      </c>
-      <c r="H61" s="61" t="inlineStr">
-        <is>
-          <t>Ambos anuncios están en $76-78/lead (benchmark OK &lt;$90) pero el video principal ($183k gasto) mantiene 2.417 leads vs 514 del secundario. Hold Rate 6.4% vs 9.8% muestra que el segundo retiene mejor pero escala menos.</t>
-        </is>
-      </c>
-      <c r="M61" s="62" t="inlineStr">
-        <is>
-          <t>Analizar primeros 3 segundos del video secundario (Hold 9.8%) y aplicar ese hook al anuncio principal que tiene 4.5x más gasto. Testear esta semana.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="48" customHeight="1">
-      <c r="B62" s="54" t="inlineStr"/>
       <c r="C62" s="55" t="inlineStr">
         <is>
           <t>🟢 OPORTUNIDAD</t>
@@ -3105,26 +3109,22 @@
       </c>
       <c r="D62" s="56" t="inlineStr">
         <is>
-          <t>CTR sobre 4% en ambos anuncios</t>
+          <t>Costo/lead en rango OK</t>
         </is>
       </c>
       <c r="H62" s="57" t="inlineStr">
         <is>
-          <t>CTR 4.15% y 4.33% son excelentes para leads educativos, superando promedio de tráfico (1.5-2%). La propuesta de cursos gratuitos está generando interés genuino en la audiencia objetivo.</t>
+          <t>Ambos anuncios a $76-$78/lead están dentro del benchmark OK (&lt;$90). Segundo video tiene mejor Hold Rate (9.8% vs 6.4%) y CTR alto (4.15%), generó 514 leads con solo $40K.</t>
         </is>
       </c>
       <c r="M62" s="58" t="inlineStr">
         <is>
-          <t>Escalar formato de formularios a otros productos de la academia con oferta similar. Crear 2 anuncios nuevos esta semana para cursos presenciales usando misma estructura de valor gratuito.</t>
+          <t>Duplicar presupuesto de Segundo video manteniendo actual, es el creativo con mejor engagement de toda la marca</t>
         </is>
       </c>
     </row>
     <row r="63" ht="48" customHeight="1">
-      <c r="B63" s="49" t="inlineStr">
-        <is>
-          <t>Marketing Objetivo Visita Perfil Instagram</t>
-        </is>
-      </c>
+      <c r="B63" s="54" t="inlineStr"/>
       <c r="C63" s="50" t="inlineStr">
         <is>
           <t>🔴 ALERTA</t>
@@ -3132,90 +3132,90 @@
       </c>
       <c r="D63" s="51" t="inlineStr">
         <is>
-          <t>Costos fuera de benchmark en tráfico</t>
+          <t>Cambio 11-07 perdió momentum</t>
         </is>
       </c>
       <c r="H63" s="52" t="inlineStr">
         <is>
-          <t>Cursos Gratuitos a $59/click y Cursos Presenciales a $47/click están en rango revisar ($40-80). Hold Rate muy bajo (5.8% y 3.6%) indica que pierden audiencia rápidamente tras el click.</t>
+          <t>Bajó de 2,671 a 2,417 leads (-10%) con mismo costo. Hold Rate de 6.4% es aceptable pero inferior al nuevo video, señal de fatiga después de 9 meses al aire.</t>
         </is>
       </c>
       <c r="M63" s="53" t="inlineStr">
         <is>
-          <t>Reducir duración de videos a máximo 15 segundos con hook directo en primer frame. Testear formato carrusel estático para academia mostrando resultados de alumnas reales.</t>
+          <t>Rotar creativo inmediatamente, testear mismo contenido con nueva locutora o formato talking head de alumna real</t>
         </is>
       </c>
     </row>
     <row r="64" ht="48" customHeight="1">
-      <c r="B64" s="54" t="inlineStr"/>
-      <c r="C64" s="59" t="inlineStr">
-        <is>
-          <t>🔵 INSIGHT</t>
-        </is>
-      </c>
-      <c r="D64" s="60" t="inlineStr">
-        <is>
-          <t>Cursos Presenciales mejora eficiencia levemente</t>
-        </is>
-      </c>
-      <c r="H64" s="61" t="inlineStr">
-        <is>
-          <t>Costo bajó de ~$49 a $47/click con resultados estables (1.847 a 1.890), mientras Cursos Gratuitos empeoró de ~$67 a $59. CTR bajo (1.7-1.93%) sugiere que audiencia necesita mayor motivación para hacer click.</t>
-        </is>
-      </c>
-      <c r="M64" s="62" t="inlineStr">
-        <is>
-          <t>Agregar call-to-action visual más fuerte en miniatura del video. Incluir texto overlay con beneficio específico en primeros 2 segundos tipo 'Aprende manicure en 8 semanas'.</t>
+      <c r="B64" s="49" t="inlineStr">
+        <is>
+          <t>Conversión Web Ventas</t>
+        </is>
+      </c>
+      <c r="C64" s="50" t="inlineStr">
+        <is>
+          <t>🔴 ALERTA</t>
+        </is>
+      </c>
+      <c r="D64" s="51" t="inlineStr">
+        <is>
+          <t>8 anuncios sobre benchmark crítico</t>
+        </is>
+      </c>
+      <c r="H64" s="52" t="inlineStr">
+        <is>
+          <t>Base Evita 2 ($10,888), Nuevos Satinados ($10,040), Lámpara Pre Curado ($11,153), Ojos Satinados ($19,856), Efecto Glaseado ($11,081) y Lampara Artistic ($9,524) superan $10,000. Todos cayeron entre 50-89% en conversiones vs marzo.</t>
+        </is>
+      </c>
+      <c r="M64" s="53" t="inlineStr">
+        <is>
+          <t>Pausar los 6 anuncios sobre $10K y reemplazar con UGC de clientas mostrando aplicación paso a paso del producto</t>
         </is>
       </c>
     </row>
     <row r="65" ht="48" customHeight="1">
-      <c r="B65" s="49" t="inlineStr">
-        <is>
-          <t>Tráfico Web Objetivo Conversión</t>
-        </is>
-      </c>
-      <c r="C65" s="50" t="inlineStr">
-        <is>
-          <t>🔴 ALERTA</t>
-        </is>
-      </c>
-      <c r="D65" s="51" t="inlineStr">
-        <is>
-          <t>Esmaltado Permanente colapsó completamente</t>
-        </is>
-      </c>
-      <c r="H65" s="52" t="inlineStr">
-        <is>
-          <t>De 1 compra en marzo a 15 en abril suena positivo, pero costo explotó a $10.958/compra gastando $164k (95% del presupuesto de campaña). Esto es inaceptable incluso para producto educativo de alto ticket.</t>
-        </is>
-      </c>
-      <c r="M65" s="53" t="inlineStr">
-        <is>
-          <t>Pausar Esmaltado Permanente hoy mismo. Está en categoría purchase pero debería ser lead/tráfico si es curso. Revisar configuración de campaña y objetivo correcto antes de reactivar.</t>
+      <c r="B65" s="54" t="inlineStr"/>
+      <c r="C65" s="55" t="inlineStr">
+        <is>
+          <t>🟢 OPORTUNIDAD</t>
+        </is>
+      </c>
+      <c r="D65" s="56" t="inlineStr">
+        <is>
+          <t>BLACK WEEK lidera conversión</t>
+        </is>
+      </c>
+      <c r="H65" s="57" t="inlineStr">
+        <is>
+          <t>Mejor costo/compra de toda la marca a $1,988 (ganadora absoluta &lt;$6,000) con 236 conversiones (+48% vs marzo) y ROAS 1.18. Representa 27% de las ventas con solo 11% del presupuesto.</t>
+        </is>
+      </c>
+      <c r="M65" s="58" t="inlineStr">
+        <is>
+          <t>Escalar este formato de promoción: duplicar variantes con mismo descuento comunicado en primeros 2 segundos del video</t>
         </is>
       </c>
     </row>
     <row r="66" ht="48" customHeight="1">
       <c r="B66" s="54" t="inlineStr"/>
-      <c r="C66" s="55" t="inlineStr">
-        <is>
-          <t>🟢 OPORTUNIDAD</t>
-        </is>
-      </c>
-      <c r="D66" s="56" t="inlineStr">
-        <is>
-          <t>Manicurista Carrusel tiene CTR excepcional</t>
-        </is>
-      </c>
-      <c r="H66" s="57" t="inlineStr">
-        <is>
-          <t>CTR 3.92% con costo $42/click (ganadora &lt;$20, pero aceptable para link_click) y 182 clicks. Hold Rate 0.5% es bajísimo pero como carrusel no aplica métrica de video.</t>
-        </is>
-      </c>
-      <c r="M66" s="58" t="inlineStr">
-        <is>
-          <t>Ampliar presupuesto orgánicamente de Manicurista Carrusel subiendo tope diario 30%. Crear 2 variaciones de carrusel con diferentes ordenamientos de imágenes para testear esta semana.</t>
+      <c r="C66" s="59" t="inlineStr">
+        <is>
+          <t>🔵 INSIGHT</t>
+        </is>
+      </c>
+      <c r="D66" s="60" t="inlineStr">
+        <is>
+          <t>Lanzamiento Jelly Pop cerca del break-even</t>
+        </is>
+      </c>
+      <c r="H66" s="61" t="inlineStr">
+        <is>
+          <t>ROAS 0.93 con costo $6,787, bajó de 85 a 32 conversiones (-62%) pero mantiene eficiencia. Hold Rate 4.7% indica pérdida de interés a mitad del video.</t>
+        </is>
+      </c>
+      <c r="M66" s="62" t="inlineStr">
+        <is>
+          <t>Acortar video a 8 segundos mostrando solo textura jelly en aplicación, eliminar intro de marca</t>
         </is>
       </c>
     </row>
@@ -3232,17 +3232,17 @@
       </c>
       <c r="D67" s="56" t="inlineStr">
         <is>
-          <t>Se quebró uña es ganadora absoluta</t>
+          <t>Se te quebró ganadora absoluta</t>
         </is>
       </c>
       <c r="H67" s="57" t="inlineStr">
         <is>
-          <t>Costo $4/click (ganadora &lt;$20) con 22.721 clicks, CTR 10.1% y Hold Rate 22.1% son métricas sobresalientes. Consume 99.7% del presupuesto de campaña ($99k) porque funciona extraordinariamente bien.</t>
+          <t>Costo/click $4 (ganadora &lt;$20), generó 22,721 clicks con CTR 10.1% y Hold Rate 22.1% (excepcional). Es el anuncio con mejor engagement de toda la marca, pero bajó de 25,762 a 22,721 clicks (-12%).</t>
         </is>
       </c>
       <c r="M67" s="58" t="inlineStr">
         <is>
-          <t>Crear 3 variaciones del concepto 'uña quebrada' esta semana con diferentes soluciones/productos Seducete. Mantener formato de storytelling que logra Hold 22% pero diversificar oferta final.</t>
+          <t>Rotar creativo con misma estructura narrativa pero nuevo caso/testimonio para recuperar alcance fresco</t>
         </is>
       </c>
     </row>
@@ -3255,17 +3255,17 @@
       </c>
       <c r="D68" s="60" t="inlineStr">
         <is>
-          <t>Otros 4 anuncios tienen gasto marginal</t>
+          <t>Nuevos anuncios sin tracción</t>
         </is>
       </c>
       <c r="H68" s="61" t="inlineStr">
         <is>
-          <t>Hannah Montana ($39), Uñas respiran ($41), 5 cosas ($8) y Uñas otoño ($144) suman $232 total vs $99k del anuncio principal. Meta está optimizando correctamente hacia el ganador pero no hay diversificación creativa.</t>
+          <t>4 anuncios nuevos (uñas respiran, 5 cosas, hannah montana, otoño 2026) sumaron solo 22 clicks con $232 gastados. CTR entre 3-8% pero sin volumen para evaluar.</t>
         </is>
       </c>
       <c r="M68" s="62" t="inlineStr">
         <is>
-          <t>Pausar los 4 anuncios de bajo gasto y reemplazar con nuevos tests basados en temas virales actuales de TikTok sobre nail care. Usar formato educativo corto similar al ganador.</t>
+          <t>Dar 7 días más de data antes de decidir, necesitan mínimo 100 clicks para validar eficiencia</t>
         </is>
       </c>
     </row>
@@ -3536,7 +3536,7 @@
     <row r="80" ht="36" customHeight="1">
       <c r="B80" s="47" t="inlineStr">
         <is>
-          <t>Bluesky gastó $89.176 en abril con 14.364 clics a $6 promedio, 8% menos resultados que marzo con 3,9% menos gasto. El anuncio 'Conchitas' explotó de 3.161 a 11.185 clics (+254%) y captura el 78% del tráfico total de la marca.</t>
+          <t>Bluesky bajó gasto 3.9% ($92.8k → $89.2k) y resultados cayeron 8.1% (15,624 → 14,364 clicks). El costo por click se mantiene en $6 (dentro de benchmark OK &lt; $40), pero 'Diseño Floral' muestra fatiga severa con caída de 78.6% en resultados.</t>
         </is>
       </c>
     </row>
@@ -3573,47 +3573,47 @@
           <t>Tráfico Perfil Instagram MKT</t>
         </is>
       </c>
-      <c r="C82" s="55" t="inlineStr">
-        <is>
-          <t>🟢 OPORTUNIDAD</t>
-        </is>
-      </c>
-      <c r="D82" s="56" t="inlineStr">
-        <is>
-          <t>Conchitas es el ganador absoluto</t>
-        </is>
-      </c>
-      <c r="H82" s="57" t="inlineStr">
-        <is>
-          <t>Hold Rate de 25% duplica el promedio de la campaña y generó 11.185 clics (78% del total) con CTR 7,1%. Costo $6 está en rango OK del benchmark ($20-$40) pero lejos del ganador (&lt;$20).</t>
-        </is>
-      </c>
-      <c r="M82" s="58" t="inlineStr">
-        <is>
-          <t>Crear 2 variaciones del concepto 'Conchitas' cambiando música y apertura para buscar Hold &gt;30% y bajar costo a &lt;$5</t>
+      <c r="C82" s="50" t="inlineStr">
+        <is>
+          <t>🔴 ALERTA</t>
+        </is>
+      </c>
+      <c r="D82" s="51" t="inlineStr">
+        <is>
+          <t>Diseño Floral colapsó 78.6% en resultados</t>
+        </is>
+      </c>
+      <c r="H82" s="52" t="inlineStr">
+        <is>
+          <t>Pasó de 12,461 clicks en marzo a solo 2,662 en abril, manteniendo el mismo costo $6. El hold rate de 13.1% indica que pierde audiencia a la mitad del video, señal clara de fatiga del creativo.</t>
+        </is>
+      </c>
+      <c r="M82" s="53" t="inlineStr">
+        <is>
+          <t>Pausar 'Diseño Floral' inmediatamente y producir nuevo creativo floral con apertura ganadora distinta (primeros 3 segundos) para recuperar este segmento que antes funcionaba.</t>
         </is>
       </c>
     </row>
     <row r="83" ht="48" customHeight="1">
       <c r="B83" s="54" t="inlineStr"/>
-      <c r="C83" s="50" t="inlineStr">
-        <is>
-          <t>🔴 ALERTA</t>
-        </is>
-      </c>
-      <c r="D83" s="51" t="inlineStr">
-        <is>
-          <t>Floral se desplomó 79% este mes</t>
-        </is>
-      </c>
-      <c r="H83" s="52" t="inlineStr">
-        <is>
-          <t>Pasó de 12.461 clics en marzo a 2.662 en abril con mismo costo $6 pero Hold Rate bajo (13,1%). El creativo perdió frescura después de ser top performer el mes anterior.</t>
-        </is>
-      </c>
-      <c r="M83" s="53" t="inlineStr">
-        <is>
-          <t>Pausar 'Floral' esta semana y reemplazar con nuevo diseño primaveral que mantenga estética pero cambie técnica de aplicación</t>
+      <c r="C83" s="55" t="inlineStr">
+        <is>
+          <t>🟢 OPORTUNIDAD</t>
+        </is>
+      </c>
+      <c r="D83" s="56" t="inlineStr">
+        <is>
+          <t>Conchitas es el nuevo ganador absoluto</t>
+        </is>
+      </c>
+      <c r="H83" s="57" t="inlineStr">
+        <is>
+          <t>Escaló de 3,161 clicks en marzo a 11,185 en abril (253% de crecimiento), absorbiendo $69.9k de presupuesto. Hold rate de 25% superior al resto demuestra que la historia engancha fuerte hasta la mitad.</t>
+        </is>
+      </c>
+      <c r="M83" s="58" t="inlineStr">
+        <is>
+          <t>Crear 2 variaciones de 'Conchitas' cambiando solo el hook (primeros 3 seg) para testear si puede superar el hold 25% actual y preparar rotación antes de fatiga.</t>
         </is>
       </c>
     </row>
@@ -3626,17 +3626,17 @@
       </c>
       <c r="D84" s="60" t="inlineStr">
         <is>
-          <t>Limón tiene potencial sin explotar</t>
+          <t>Limón Verano rinde pero necesita volumen</t>
         </is>
       </c>
       <c r="H84" s="61" t="inlineStr">
         <is>
-          <t>Con solo $3.312 de gasto logró CTR 7,58% (el más alto de la campaña) y costo $7. Hold 18,2% es mejorable pero el engagement inicial es fuerte.</t>
+          <t>Costo $7 ligeramente sobre promedio de campaña ($6), pero CTR 7.58% es el más alto de la campaña. Con solo $3.3k invertidos no alcanza escala para evaluar potencial real.</t>
         </is>
       </c>
       <c r="M84" s="62" t="inlineStr">
         <is>
-          <t>Duplicar presupuesto a este set de anuncios y testear versión extendida del video que mejore retención en segundo 8-12</t>
+          <t>Mantener 'Limón Verano' activo 2 semanas más sin tocar presupuesto para validar si el CTR alto se sostiene con mayor volumen de impresiones.</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
     <row r="121" ht="36" customHeight="1">
       <c r="B121" s="47" t="inlineStr">
         <is>
-          <t>Nail Outlet aumentó gasto 4% pero las conversiones cayeron 14% (de 5.028 a 4.302), con costo por compra subiendo de $3.151 a $4.277. La campaña de catálogo y varios anuncios antiguos están quemando presupuesto con costos sobre $17.000 por conversión.</t>
+          <t>Nail Outlet aumentó gasto 4% pero cayó 14% en resultados (5.028→4.302), subiendo costo promedio de $269 a $327. El problema central está en conversiones: 47% menos ventas (448→238) con costo por compra subiendo de $3.020 a $5.971.</t>
         </is>
       </c>
     </row>
@@ -4970,70 +4970,70 @@
           <t>Objetivo Conversión Ventas</t>
         </is>
       </c>
-      <c r="C123" s="50" t="inlineStr">
-        <is>
-          <t>🔴 ALERTA</t>
-        </is>
-      </c>
-      <c r="D123" s="51" t="inlineStr">
-        <is>
-          <t>5 anuncios sobre benchmark crítico</t>
-        </is>
-      </c>
-      <c r="H123" s="52" t="inlineStr">
-        <is>
-          <t>Esmaltes French Nail Pro ($12.705), 40 Esmaltes Julio ($19.285), Efectos Chromados ($22.114), Campo de Trabajo ($18.188) e Imagen primer deshidratador ($29.518) están muy sobre $10.000. En conjunto gastaron $305.741 y solo generaron 17 ventas.</t>
-        </is>
-      </c>
-      <c r="M123" s="53" t="inlineStr">
-        <is>
-          <t>Pausar estos 5 anuncios inmediatamente y reasignar su presupuesto rotando creativos en Pack Repo 20 Agosto y Black Week que están bajo $10k con ROAS sobre 5x</t>
+      <c r="C123" s="55" t="inlineStr">
+        <is>
+          <t>🟢 OPORTUNIDAD</t>
+        </is>
+      </c>
+      <c r="D123" s="56" t="inlineStr">
+        <is>
+          <t>Poly Gel Carrusel es ganador absoluto</t>
+        </is>
+      </c>
+      <c r="H123" s="57" t="inlineStr">
+        <is>
+          <t>ROAS de 40.15 con costo $462 por compra, muy por debajo del benchmark de $6.000. Generó 7 ventas con solo $3.237 de inversión, cayendo de 73 ventas el mes anterior.</t>
+        </is>
+      </c>
+      <c r="M123" s="58" t="inlineStr">
+        <is>
+          <t>Crear 3 variaciones nuevas del creativo Poly Gel (cambiar apertura, testimonial, demo producto) para escalar volumen sin tocar presupuesto</t>
         </is>
       </c>
     </row>
     <row r="124" ht="48" customHeight="1">
       <c r="B124" s="54" t="inlineStr"/>
-      <c r="C124" s="55" t="inlineStr">
-        <is>
-          <t>🟢 OPORTUNIDAD</t>
-        </is>
-      </c>
-      <c r="D124" s="56" t="inlineStr">
-        <is>
-          <t>Poly Gel es tu estrella oculta</t>
-        </is>
-      </c>
-      <c r="H124" s="57" t="inlineStr">
-        <is>
-          <t>Con solo $3.237 de gasto generó 7 conversiones a $462 c/u y ROAS 40.15x, cayendo de 73 conversiones en marzo. El creativo está funcionando pero está sub-invertido mientras anuncios malos consumen presupuesto.</t>
-        </is>
-      </c>
-      <c r="M124" s="58" t="inlineStr">
-        <is>
-          <t>Duplicar este anuncio con 3 variaciones de apertura diferentes (primeros 3 segundos) para escalar sin saturar la audiencia actual</t>
+      <c r="C124" s="50" t="inlineStr">
+        <is>
+          <t>🔴 ALERTA</t>
+        </is>
+      </c>
+      <c r="D124" s="51" t="inlineStr">
+        <is>
+          <t>5 anuncios sobre benchmark crítico</t>
+        </is>
+      </c>
+      <c r="H124" s="52" t="inlineStr">
+        <is>
+          <t>40 Esmaltes Julio ($19.285), Efectos Chromados ($22.114), Campo de Trabajo ($18.188), Primer deshidratador ($29.518) y Pack 12 Esmaltes ($21.883) superan los $18.000. Hold Rate bajo (0.5%-7.9%) indica que pierden audiencia rápido.</t>
+        </is>
+      </c>
+      <c r="M124" s="53" t="inlineStr">
+        <is>
+          <t>Pausar estos 5 anuncios esta semana. Redirigir ese espacio a duplicar variaciones de Pack Repo 20 (ROAS 6.42) y Black Week (ROAS 5.57)</t>
         </is>
       </c>
     </row>
     <row r="125" ht="48" customHeight="1">
       <c r="B125" s="54" t="inlineStr"/>
-      <c r="C125" s="50" t="inlineStr">
-        <is>
-          <t>🔴 ALERTA</t>
-        </is>
-      </c>
-      <c r="D125" s="51" t="inlineStr">
-        <is>
-          <t>Hold Rate extremadamente bajo generalizado</t>
-        </is>
-      </c>
-      <c r="H125" s="52" t="inlineStr">
-        <is>
-          <t>12 de 15 anuncios tienen Hold Rate bajo 7% (varios en 0.3-0.5%), indicando que pierden audiencia antes de la mitad del video. Pack Repo cayó 47% en conversiones con Hold 5.4%.</t>
-        </is>
-      </c>
-      <c r="M125" s="53" t="inlineStr">
-        <is>
-          <t>Acortar videos a máximo 15 segundos y poner el producto/beneficio en los primeros 5 segundos para retener audiencia hasta la mitad</t>
+      <c r="C125" s="59" t="inlineStr">
+        <is>
+          <t>🔵 INSIGHT</t>
+        </is>
+      </c>
+      <c r="D125" s="60" t="inlineStr">
+        <is>
+          <t>Pack Repo y Black Week mantienen eficiencia</t>
+        </is>
+      </c>
+      <c r="H125" s="61" t="inlineStr">
+        <is>
+          <t>Pack Repo: $8.374/compra con ROAS 6.42 pero cayó de 38 a 20 ventas (-47%). Black Week: $8.252/compra con ROAS 5.57 y subió de 7 a 23 ventas (+229%). Ambos en zona OK del benchmark.</t>
+        </is>
+      </c>
+      <c r="M125" s="62" t="inlineStr">
+        <is>
+          <t>Refrescar creativos de Pack Repo con nuevo hook (primera 3 segundos) para recuperar volumen. Mantener Black Week activo y testear versión con descuento explícito en portada</t>
         </is>
       </c>
     </row>
@@ -5043,47 +5043,47 @@
           <t>Tráfico Perfil Instagram MKT</t>
         </is>
       </c>
-      <c r="C126" s="59" t="inlineStr">
-        <is>
-          <t>🔵 INSIGHT</t>
-        </is>
-      </c>
-      <c r="D126" s="60" t="inlineStr">
-        <is>
-          <t>Costo por click dentro de benchmark</t>
-        </is>
-      </c>
-      <c r="H126" s="61" t="inlineStr">
-        <is>
-          <t>Ambos anuncios están entre $21-$23 por click (benchmark OK &lt;$40), pero Paso a paso Vale Nails cayó 35% en clicks (de 2.984 a 1.930) con Hold Rate 10.3% vs 19.2% de Insta Nail Pro.</t>
-        </is>
-      </c>
-      <c r="M126" s="62" t="inlineStr">
-        <is>
-          <t>Testear nuevo hook en Paso a paso Vale Nails mostrando resultado final en primeros 2 segundos antes del tutorial para recuperar Hold Rate</t>
+      <c r="C126" s="50" t="inlineStr">
+        <is>
+          <t>🔴 ALERTA</t>
+        </is>
+      </c>
+      <c r="D126" s="51" t="inlineStr">
+        <is>
+          <t>Caída 25% en clicks al perfil</t>
+        </is>
+      </c>
+      <c r="H126" s="52" t="inlineStr">
+        <is>
+          <t>Pasó de 5.422 a 4.057 clicks con costo estable en $22 (dentro de benchmark ganador &lt;$20). Paso a paso Vale Nails cayó 35% (2.984→1.930 clicks) a pesar de CTR alto de 4.01%.</t>
+        </is>
+      </c>
+      <c r="M126" s="53" t="inlineStr">
+        <is>
+          <t>Rotar creativos de ambos anuncios: llevan más de 2 semanas activos. Testear formato carrusel con 3 pasos nail art para Vale Nails y producto hero para Insta Nail Pro</t>
         </is>
       </c>
     </row>
     <row r="127" ht="48" customHeight="1">
       <c r="B127" s="54" t="inlineStr"/>
-      <c r="C127" s="55" t="inlineStr">
-        <is>
-          <t>🟢 OPORTUNIDAD</t>
-        </is>
-      </c>
-      <c r="D127" s="56" t="inlineStr">
-        <is>
-          <t>CTR superior indica interés alto</t>
-        </is>
-      </c>
-      <c r="H127" s="57" t="inlineStr">
-        <is>
-          <t>Paso a paso Vale Nails tiene CTR 4.01% (casi el doble de Insta Nail Pro con 2.73%), señal de que el contenido tutorial resuena más con la audiencia nail artist profesional.</t>
-        </is>
-      </c>
-      <c r="M127" s="58" t="inlineStr">
-        <is>
-          <t>Crear 2 nuevos tutoriales paso a paso con otros productos estrella (Poly Gel, Efectos Chromados) replicando formato de Vale Nails</t>
+      <c r="C127" s="59" t="inlineStr">
+        <is>
+          <t>🔵 INSIGHT</t>
+        </is>
+      </c>
+      <c r="D127" s="60" t="inlineStr">
+        <is>
+          <t>CTR sobre promedio pero sin conversión</t>
+        </is>
+      </c>
+      <c r="H127" s="61" t="inlineStr">
+        <is>
+          <t>Vale Nails tiene CTR 4.01% y Hold50 10.3%, indica buen engagement inicial. Sin embargo, no hay datos de conversión post-click en estas campañas de tráfico (ROAS 0).</t>
+        </is>
+      </c>
+      <c r="M127" s="62" t="inlineStr">
+        <is>
+          <t>Implementar pixel de seguimiento para medir qué porcentaje de estos clicks llega a tienda física o convierte en 7 días. Validar si justifica mantener $90K mensuales</t>
         </is>
       </c>
     </row>
@@ -5100,17 +5100,17 @@
       </c>
       <c r="D128" s="56" t="inlineStr">
         <is>
-          <t>Campaña nueva ganadora absoluta</t>
+          <t>Remarketing con mejor ROAS del portafolio</t>
         </is>
       </c>
       <c r="H128" s="57" t="inlineStr">
         <is>
-          <t>15% OFF genera conversiones a $3.481 con ROAS 11.25x y Despacho Gratis a $4.913 con ROAS 4.85x, ambos bajo benchmark de $6.000. Hold Rate sobre 17% en ambos indica retención excelente.</t>
+          <t>15% OFF logró ROAS 11.25 con costo $3.481/compra (ganador absoluto). Despacho Gratis: ROAS 4.85 con $4.913/compra. Hold Rate excepcional (17.9%-19.3%) vs otros anuncios.</t>
         </is>
       </c>
       <c r="M128" s="58" t="inlineStr">
         <is>
-          <t>Crear 3 variaciones combinando ambos beneficios (15% OFF + Despacho Gratis) con diferentes aperturas para escalar sin canibalizarse</t>
+          <t>Crear urgencia en ambos creativos: agregar contador 48hrs o stock limitado en primer frame. Testear combo 15% OFF + despacho gratis para subir ticket promedio</t>
         </is>
       </c>
     </row>
@@ -5123,17 +5123,17 @@
       </c>
       <c r="D129" s="60" t="inlineStr">
         <is>
-          <t>Remarketing más eficiente que prospección</t>
+          <t>Audiencia cálida responde mejor a descuento</t>
         </is>
       </c>
       <c r="H129" s="61" t="inlineStr">
         <is>
-          <t>Costo promedio $4.340 vs $4.277 de conversión fría, pero con ROAS mucho superior (11.25x vs promedio 3-4x). Solo representa 4.6% del presupuesto total ($65.106 de $1.408.877).</t>
+          <t>15% OFF generó 6 ventas con $20K vs Despacho Gratis con 9 ventas pero $44K. Costo por compra 29% más bajo en descuento directo ($3.481 vs $4.913).</t>
         </is>
       </c>
       <c r="M129" s="62" t="inlineStr">
         <is>
-          <t>Mantener estos anuncios activos y rotar creativos cada 10 días para evitar fatiga en audiencia caliente más pequeña</t>
+          <t>Duplicar estrategia de 15% OFF para otras marcas del portafolio. En Nail Outlet, testear 20% OFF solo para esta audiencia de remarketing caliente</t>
         </is>
       </c>
     </row>
@@ -5155,35 +5155,35 @@
       </c>
       <c r="H130" s="52" t="inlineStr">
         <is>
-          <t>Gastó $355.748 (25% del presupuesto total) generando solo 20 conversiones a $17.787 cada una, casi 3x sobre el límite de pausa ($18.000). ROAS 1.84x significa pérdida directa por cada peso invertido.</t>
+          <t>Costo por compra de $17.787 casi 3x el límite crítico de $18.000. Invirtió $355K para 20 ventas, ROAS apenas 1.84. Hold Rate 0% indica que nadie ve el contenido completo.</t>
         </is>
       </c>
       <c r="M130" s="53" t="inlineStr">
         <is>
-          <t>Pausar esta campaña de catálogo inmediatamente y reemplazar con anuncios de producto único que ya probaron conversión bajo $6k (Imagen Mesa Nail Pro, Imagen Limas)</t>
+          <t>Pausar inmediatamente. El formato catálogo automatizado no funciona para esta audiencia. Reemplazar con anuncios manuales de productos específicos top performers (Poly Gel, Remarketing)</t>
         </is>
       </c>
     </row>
     <row r="131" ht="48" customHeight="1">
       <c r="B131" s="54" t="inlineStr"/>
-      <c r="C131" s="50" t="inlineStr">
-        <is>
-          <t>🔴 ALERTA</t>
-        </is>
-      </c>
-      <c r="D131" s="51" t="inlineStr">
-        <is>
-          <t>Formato catálogo no funciona para</t>
-        </is>
-      </c>
-      <c r="H131" s="52" t="inlineStr">
-        <is>
-          <t>Hold Rate 0% y CTR 1.66% indican que el formato carrusel/catálogo automático no genera engagement. La audiencia nail pro necesita ver producto específico con aplicación o resultado.</t>
-        </is>
-      </c>
-      <c r="M131" s="53" t="inlineStr">
-        <is>
-          <t>Eliminar formato catálogo y crear anuncios individuales de tus 5 productos más vendidos con video de aplicación real de 10 segundos</t>
+      <c r="C131" s="59" t="inlineStr">
+        <is>
+          <t>🔵 INSIGHT</t>
+        </is>
+      </c>
+      <c r="D131" s="60" t="inlineStr">
+        <is>
+          <t>Formato catálogo no competitivo vs manual</t>
+        </is>
+      </c>
+      <c r="H131" s="61" t="inlineStr">
+        <is>
+          <t>Con 25% del presupuesto total ($355K de $1.4M) generó solo 8% de las ventas (20 de 245 totales). Anuncios manuales ganadores cuestan $462-$3.481 por compra vs $17.787 del catálogo.</t>
+        </is>
+      </c>
+      <c r="M131" s="62" t="inlineStr">
+        <is>
+          <t>Eliminar esta campaña del mix. Usar ese espacio presupuestario para duplicar sets de anuncios ganadores existentes con nuevos creativos rotados cada 2 semanas</t>
         </is>
       </c>
     </row>
@@ -9550,7 +9550,7 @@
     <row r="223" ht="36" customHeight="1">
       <c r="B223" s="47" t="inlineStr">
         <is>
-          <t>Go Nails tuvo una caída brutal de 88.3% en resultados vs marzo (2,404 vs 20,613), con gasto similar de $7.1M. Las campañas de conversión están en zona de revisión ($7,642/compra) y hay dos anuncios con costos críticos sobre $50k que están quemando presupuesto sin retorno.</t>
+          <t>Go Nails cayó 88% en resultados (de 20.613 a 2.404) con gasto similar, evidenciando fatiga creativa masiva en conversión. Los anuncios de tráfico mantienen eficiencia ($15-19/click) pero los de compra explotaron a costos prohibitivos ($7.642 promedio, muy por sobre benchmark $10k).</t>
         </is>
       </c>
     </row>
@@ -9584,155 +9584,155 @@
     <row r="225" ht="48" customHeight="1">
       <c r="B225" s="49" t="inlineStr">
         <is>
-          <t>Remarketing Go Nails 2024</t>
-        </is>
-      </c>
-      <c r="C225" s="55" t="inlineStr">
-        <is>
-          <t>🟢 OPORTUNIDAD</t>
-        </is>
-      </c>
-      <c r="D225" s="56" t="inlineStr">
-        <is>
-          <t>Despacho Gratis rinde mejor que 15% OFF</t>
-        </is>
-      </c>
-      <c r="H225" s="57" t="inlineStr">
-        <is>
-          <t>El anuncio Despacho Gratis logra $4,137/compra con ROAS 4.82x, mientras 15% OFF está en $7,957 con ROAS 2.51x. Ambos comparten misma audiencia de remarketing pero el incentivo de despacho convierte casi el doble de eficiente.</t>
-        </is>
-      </c>
-      <c r="M225" s="58" t="inlineStr">
-        <is>
-          <t>Pausar 15% OFF y duplicar el concepto de Despacho Gratis con nuevo creativo (ej: countdown, beneficio urgente)</t>
+          <t>Campaña principal de Conversión</t>
+        </is>
+      </c>
+      <c r="C225" s="50" t="inlineStr">
+        <is>
+          <t>🔴 ALERTA</t>
+        </is>
+      </c>
+      <c r="D225" s="51" t="inlineStr">
+        <is>
+          <t>Colapso general de conversión</t>
+        </is>
+      </c>
+      <c r="H225" s="52" t="inlineStr">
+        <is>
+          <t>715 compras vs 626 en marzo con costo promedio $7.642 (27% sobre benchmark OK). Home Spray gastó $1.186.817 con costo/compra $13.042 (117% sobre benchmark) y ROAS 2.45 — es el 22% del gasto total de la campaña.</t>
+        </is>
+      </c>
+      <c r="M225" s="53" t="inlineStr">
+        <is>
+          <t>Pausar Home Spray y reemplazar con 3 videos nuevos de productos Sun Kissed o Cotton (ROAS 5.0) usando apertura de productos en mano estilo 'Reel cafetería'.</t>
         </is>
       </c>
     </row>
     <row r="226" ht="48" customHeight="1">
       <c r="B226" s="54" t="inlineStr"/>
-      <c r="C226" s="59" t="inlineStr">
-        <is>
-          <t>🔵 INSIGHT</t>
-        </is>
-      </c>
-      <c r="D226" s="60" t="inlineStr">
-        <is>
-          <t>Campaña está dentro de benchmark ganador</t>
-        </is>
-      </c>
-      <c r="H226" s="61" t="inlineStr">
-        <is>
-          <t>Promedio de $4,897/compra coloca esta campaña en zona ganadora (&lt;$6k). Con 55 conversiones y ROAS consistente sobre 4x, es la campaña más sana del portafolio.</t>
-        </is>
-      </c>
-      <c r="M226" s="62" t="inlineStr">
-        <is>
-          <t>Mantener activa sin cambios, preparar 2 creativos de backup para rotar en 1 semana</t>
+      <c r="C226" s="50" t="inlineStr">
+        <is>
+          <t>🔴 ALERTA</t>
+        </is>
+      </c>
+      <c r="D226" s="51" t="inlineStr">
+        <is>
+          <t>Nuevos difusores hundido</t>
+        </is>
+      </c>
+      <c r="H226" s="52" t="inlineStr">
+        <is>
+          <t>3 compras con costo $22.556 (125% sobre benchmark pausar) y ROAS 1.18, cayó de 35 resultados. Hold rate 2.4% indica que pierde audiencia inmediato.</t>
+        </is>
+      </c>
+      <c r="M226" s="53" t="inlineStr">
+        <is>
+          <t>Pausar 'Nuevos difusores' ya. Crear video tutorial de uso en contexto lifestyle (ej: difusor en escritorio mientras trabajan) con apertura impactante en primer segundo.</t>
         </is>
       </c>
     </row>
     <row r="227" ht="48" customHeight="1">
-      <c r="B227" s="49" t="inlineStr">
+      <c r="B227" s="54" t="inlineStr"/>
+      <c r="C227" s="55" t="inlineStr">
+        <is>
+          <t>🟢 OPORTUNIDAD</t>
+        </is>
+      </c>
+      <c r="D227" s="56" t="inlineStr">
+        <is>
+          <t>Ganadoras confirmadas con espacio</t>
+        </is>
+      </c>
+      <c r="H227" s="57" t="inlineStr">
+        <is>
+          <t>5 anuncios bajo $7k/compra: Reel cafetería ($5.089, ROAS 4.6), Cremas Sun Kissed ($5.687, ROAS 5.0), Imagen Bubble gum ($6.672, ROAS 4.1), Protector Térmico ($6.872), Macbook ($6.886, ROAS 4.39). Todos con CTR &gt;0.6%.</t>
+        </is>
+      </c>
+      <c r="M227" s="58" t="inlineStr">
+        <is>
+          <t>Duplicar estos 5 creativos con variaciones de copy en primera línea (agregar urgencia/descuento) manteniendo el formato visual exacto que ya convierte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="48" customHeight="1">
+      <c r="B228" s="49" t="inlineStr">
         <is>
           <t>Marketing Go Nails - Trafico Insta</t>
         </is>
       </c>
-      <c r="C227" s="50" t="inlineStr">
+      <c r="C228" s="50" t="inlineStr">
         <is>
           <t>🔴 ALERTA</t>
         </is>
       </c>
-      <c r="D227" s="51" t="inlineStr">
-        <is>
-          <t>Hannah Montana 2 quemó $283k sin retorno</t>
-        </is>
-      </c>
-      <c r="H227" s="52" t="inlineStr">
-        <is>
-          <t>Anuncio gastó $283,796 para 1 sola compra (ROAS 0.04x) vs 456 resultados en marzo. Hold Rate de 1.8% muestra que la audiencia abandona inmediato, creativamente está muerto.</t>
-        </is>
-      </c>
-      <c r="M227" s="53" t="inlineStr">
-        <is>
-          <t>Pausar inmediatamente Hannah Montana 2 y Hannah Montana 1 ($55k, ROAS 0.74x)</t>
-        </is>
-      </c>
-    </row>
-    <row r="228" ht="48" customHeight="1">
-      <c r="B228" s="54" t="inlineStr"/>
-      <c r="C228" s="55" t="inlineStr">
-        <is>
-          <t>🟢 OPORTUNIDAD</t>
-        </is>
-      </c>
-      <c r="D228" s="56" t="inlineStr">
-        <is>
-          <t>Clusters de bajo costo rindiendo bien</t>
-        </is>
-      </c>
-      <c r="H228" s="57" t="inlineStr">
-        <is>
-          <t>Cotton Candy Frutilla ($17/click, 407 clics) y Tu Pareja Te Debe ($19/click, 760 clics) están muy por debajo del benchmark de $40. Generan tráfico calificado a costo ganador.</t>
-        </is>
-      </c>
-      <c r="M228" s="58" t="inlineStr">
-        <is>
-          <t>Iterar estos 2 conceptos: hacer versión 2.0 de Cotton Candy con producto distinto y probar variante de Tu Pareja Te Debe con otro ángulo relacional</t>
+      <c r="D228" s="51" t="inlineStr">
+        <is>
+          <t>Hannah Montana sangrando presupuesto</t>
+        </is>
+      </c>
+      <c r="H228" s="52" t="inlineStr">
+        <is>
+          <t>Hannah Montana 2 gastó $283.796 para 1 compra (costo $283.796, 1581% sobre benchmark) con ROAS 0.04. Entre ambas versiones suman $338.902 del gasto con 2 compras totales y hold rate &lt;2%.</t>
+        </is>
+      </c>
+      <c r="M228" s="53" t="inlineStr">
+        <is>
+          <t>Pausar ambas versiones Hannah Montana inmediatamente. Ese presupuesto debe ir a duplicar 'tu pareja te debe' (760 clicks a $19, CTR 2.87%) que es creativo nuevo sin mes anterior.</t>
         </is>
       </c>
     </row>
     <row r="229" ht="48" customHeight="1">
       <c r="B229" s="54" t="inlineStr"/>
-      <c r="C229" s="59" t="inlineStr">
+      <c r="C229" s="55" t="inlineStr">
+        <is>
+          <t>🟢 OPORTUNIDAD</t>
+        </is>
+      </c>
+      <c r="D229" s="56" t="inlineStr">
+        <is>
+          <t>Popcorn y Cotton Candy eficientes</t>
+        </is>
+      </c>
+      <c r="H229" s="57" t="inlineStr">
+        <is>
+          <t>Popcorn pomo: $12/click con CTR 5.58%, hold 7.8%. Cotton candy frutilla: $17/click con CTR 4.3% y 407 clicks. Ambos muy por debajo de benchmark ganador $20.</t>
+        </is>
+      </c>
+      <c r="M229" s="58" t="inlineStr">
+        <is>
+          <t>Crear 2 variaciones de cada uno cambiando solo la primera frase del copy (probar hook con pregunta vs. afirmación) y rotar semanalmente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="48" customHeight="1">
+      <c r="B230" s="54" t="inlineStr"/>
+      <c r="C230" s="59" t="inlineStr">
         <is>
           <t>🔵 INSIGHT</t>
         </is>
       </c>
-      <c r="D229" s="60" t="inlineStr">
-        <is>
-          <t>Bridgerton prueba colapsó vs marzo</t>
-        </is>
-      </c>
-      <c r="H229" s="61" t="inlineStr">
-        <is>
-          <t>De 15,496 resultados en marzo a solo 4 en abril con $51 de gasto. El algoritmo lo desactivó por bajo engagement, pero el CTR 5.33% sugiere que el concepto tiene potencial no explotado.</t>
-        </is>
-      </c>
-      <c r="M229" s="62" t="inlineStr">
-        <is>
-          <t>Relanzar Bridgerton con presupuesto mínimo diario fijo ($2k) y nuevo creative con mejor hook (primera escena más impactante)</t>
-        </is>
-      </c>
-    </row>
-    <row r="230" ht="48" customHeight="1">
-      <c r="B230" s="49" t="inlineStr">
-        <is>
-          <t>Campaña principal de Conversión</t>
-        </is>
-      </c>
-      <c r="C230" s="50" t="inlineStr">
-        <is>
-          <t>🔴 ALERTA</t>
-        </is>
-      </c>
-      <c r="D230" s="51" t="inlineStr">
-        <is>
-          <t>Home Spray es el anuncio más caro</t>
-        </is>
-      </c>
-      <c r="H230" s="52" t="inlineStr">
-        <is>
-          <t>Gastó $1.19M (21.7% del presupuesto de la campaña) con costo de $13,042/compra, muy por encima del promedio de $7,642. ROAS de 2.45x es el más bajo de anuncios con volumen.</t>
-        </is>
-      </c>
-      <c r="M230" s="53" t="inlineStr">
-        <is>
-          <t>Pausar Home Spray esta semana y redirigir audiencia similar hacia Imagen Cotton Vlabel ($7,713/compra, ROAS 5x, 38 conversiones)</t>
+      <c r="D230" s="60" t="inlineStr">
+        <is>
+          <t>Bridgerton colapsó inexplicablemente</t>
+        </is>
+      </c>
+      <c r="H230" s="61" t="inlineStr">
+        <is>
+          <t>Cayó de 15.496 resultados a solo 4, con gasto de $51. CTR 5.33% se mantiene fuerte pero hold rate 1.3% bajísimo sugiere problema en segundos 2-5 del video.</t>
+        </is>
+      </c>
+      <c r="M230" s="62" t="inlineStr">
+        <is>
+          <t>Reactivar con gasto controlado $15k pero re-editar: mantener primer segundo (hook funciona por CTR) y cambiar completamente el desarrollo del video desde segundo 3.</t>
         </is>
       </c>
     </row>
     <row r="231" ht="48" customHeight="1">
-      <c r="B231" s="54" t="inlineStr"/>
+      <c r="B231" s="49" t="inlineStr">
+        <is>
+          <t>Remarketing Go Nails 2024</t>
+        </is>
+      </c>
       <c r="C231" s="55" t="inlineStr">
         <is>
           <t>🟢 OPORTUNIDAD</t>
@@ -9740,17 +9740,17 @@
       </c>
       <c r="D231" s="56" t="inlineStr">
         <is>
-          <t>Reel Cafetería es caballo ganador escondido</t>
+          <t>Despacho Gratis rindiendo bien</t>
         </is>
       </c>
       <c r="H231" s="57" t="inlineStr">
         <is>
-          <t>Con solo $15k de gasto logró 3 compras a $5,089 (mejor costo de la campaña) y ROAS 4.6x. Tuvo 88 resultados en marzo, indicando potencial escalable no aprovechado.</t>
+          <t>32 compras a $4.137 (31% bajo benchmark ganador $6k) con ROAS 4.82. Es el mejor performer de la campaña con costo 29% más bajo que el promedio grupal.</t>
         </is>
       </c>
       <c r="M231" s="58" t="inlineStr">
         <is>
-          <t>Aumentar distribución de Reel Cafetería duplicando sets de anuncios y crear variante B con mismo estilo estético pero producto distinto</t>
+          <t>Crear 2 variaciones visuales del anuncio 'Despacho Gratis': una versión carrusel mostrando productos + despacho, otra video corto 15seg unboxing con texto 'Despacho gratis' en primer frame.</t>
         </is>
       </c>
     </row>
@@ -9763,145 +9763,168 @@
       </c>
       <c r="D232" s="51" t="inlineStr">
         <is>
-          <t>Cluster de $9k+ necesita renovación urgente</t>
+          <t>15% OFF colapsó post-promo</t>
         </is>
       </c>
       <c r="H232" s="52" t="inlineStr">
         <is>
-          <t>4 anuncios (4 por 3, Hot Chocolate, Crema dibujada, Reel Fragancias) cuestan entre $9,007-$10,337/compra. Suman $1.07M de gasto con eficiencia por debajo de benchmark OK.</t>
+          <t>Cayó de 34 compras a solo 1, costo $7.957 con ROAS 2.51 (50% bajo el 5.0 de la campaña). Hold rate 5.7% indica que el video mantiene atención pero no convierte.</t>
         </is>
       </c>
       <c r="M232" s="53" t="inlineStr">
         <is>
-          <t>Renovar creativos de este cluster: mantener producto pero cambiar formato (pasar de reel a carrusel o imagen estática UGC-style)</t>
+          <t>Pausar '15% OFF' y reemplazar con beneficio tangible tipo '4to producto gratis' o 'Regalo en compras sobre $X' — los descuentos porcentuales ya no resuenan en esta audiencia.</t>
         </is>
       </c>
     </row>
     <row r="233" ht="48" customHeight="1">
-      <c r="B233" s="49" t="inlineStr">
+      <c r="B233" s="54" t="inlineStr"/>
+      <c r="C233" s="59" t="inlineStr">
+        <is>
+          <t>🔵 INSIGHT</t>
+        </is>
+      </c>
+      <c r="D233" s="60" t="inlineStr">
+        <is>
+          <t>Audiencia de retargeting saturada</t>
+        </is>
+      </c>
+      <c r="H233" s="61" t="inlineStr">
+        <is>
+          <t>Remarketing general cayó de 65 a 22 conversiones con costo subiendo a $5.863. La campaña completa pasó de 207 compras a 55 (-73%) manteniendo presupuesto similar.</t>
+        </is>
+      </c>
+      <c r="M233" s="62" t="inlineStr">
+        <is>
+          <t>Ampliar ventana de remarketing de 30 a 60 días para refrescar audiencia, o crear secuencia: día 1-7 producto visto, día 8-30 categoría vista, día 31-60 visitantes perfil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="48" customHeight="1">
+      <c r="B234" s="49" t="inlineStr">
         <is>
           <t>Campaña Secundaria LMM</t>
         </is>
       </c>
-      <c r="C233" s="55" t="inlineStr">
+      <c r="C234" s="55" t="inlineStr">
         <is>
           <t>🟢 OPORTUNIDAD</t>
         </is>
       </c>
-      <c r="D233" s="56" t="inlineStr">
-        <is>
-          <t>Reel Kit LMM es gema con ROAS 15.27x</t>
-        </is>
-      </c>
-      <c r="H233" s="57" t="inlineStr">
-        <is>
-          <t>Con solo $12,363 de gasto logró 5 compras a $2,473 (mejor de todo el portafolio) y ROAS explosivo de 15.27x. Hold Rate de 14.6% muestra que la historia engancha.</t>
-        </is>
-      </c>
-      <c r="M233" s="58" t="inlineStr">
-        <is>
-          <t>Escalar Reel Kit LMM creando 3 variantes del mismo concepto con distinto producto LMM y duplicar presupuesto progresivamente</t>
-        </is>
-      </c>
-    </row>
-    <row r="234" ht="48" customHeight="1">
-      <c r="B234" s="54" t="inlineStr"/>
-      <c r="C234" s="59" t="inlineStr">
-        <is>
-          <t>🔵 INSIGHT</t>
-        </is>
-      </c>
-      <c r="D234" s="60" t="inlineStr">
-        <is>
-          <t>Campaña pequeña pero ultra eficiente</t>
-        </is>
-      </c>
-      <c r="H234" s="61" t="inlineStr">
-        <is>
-          <t>Con solo $73k (1% del gasto total) logra costo promedio de $6,659/compra, dentro de zona ganadora. El CTR promedio de 3.72% duplica el de campaña principal.</t>
-        </is>
-      </c>
-      <c r="M234" s="62" t="inlineStr">
-        <is>
-          <t>Mantener estrategia actual, preparar 2 creativos nuevos formato reel con estética similar para rotar próxima semana</t>
+      <c r="D234" s="56" t="inlineStr">
+        <is>
+          <t>Reel Kit LMM es joya</t>
+        </is>
+      </c>
+      <c r="H234" s="57" t="inlineStr">
+        <is>
+          <t>5 compras a $2.473 (59% bajo benchmark ganador) con ROAS 15.27 — el mejor de toda Go Nails. Hold rate 14.6% duplica el promedio de la marca, CTR 2.79% sólido.</t>
+        </is>
+      </c>
+      <c r="M234" s="58" t="inlineStr">
+        <is>
+          <t>Escalar 'Reel Kit LMM' duplicando presupuesto a $25k y crear 3 versiones con mismo formato pero rotando producto destacado del kit en primer plano (esmalte/lámpara/lima).</t>
         </is>
       </c>
     </row>
     <row r="235" ht="48" customHeight="1">
-      <c r="B235" s="49" t="inlineStr">
+      <c r="B235" s="54" t="inlineStr"/>
+      <c r="C235" s="50" t="inlineStr">
+        <is>
+          <t>🔴 ALERTA</t>
+        </is>
+      </c>
+      <c r="D235" s="51" t="inlineStr">
+        <is>
+          <t>Reel esmalte LMM costoso</t>
+        </is>
+      </c>
+      <c r="H235" s="52" t="inlineStr">
+        <is>
+          <t>Costo $10.138/compra (69% sobre benchmark OK) con ROAS 3.36, muy por debajo del 15.27 del Kit. Hold rate 19.7% excelente pero no traduce a conversión eficiente.</t>
+        </is>
+      </c>
+      <c r="M235" s="53" t="inlineStr">
+        <is>
+          <t>Mantener activo por hold rate pero agregar CTA más directo en segundo 8-10 del video: mostrar precio final o código descuento en pantalla, no solo en copy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="48" customHeight="1">
+      <c r="B236" s="49" t="inlineStr">
         <is>
           <t>Campaña Conversión Catálogo</t>
         </is>
       </c>
-      <c r="C235" s="55" t="inlineStr">
+      <c r="C236" s="55" t="inlineStr">
         <is>
           <t>🟢 OPORTUNIDAD</t>
         </is>
       </c>
-      <c r="D235" s="56" t="inlineStr">
-        <is>
-          <t>Macbook cruzó a compra con ROAS 9.93x</t>
-        </is>
-      </c>
-      <c r="H235" s="57" t="inlineStr">
-        <is>
-          <t>Único anuncio tipo purchase dentro de campaña de tráfico, logró 7 compras a $3,087 con ROAS casi 10x. Formato híbrido está funcionando mejor que anuncios puros de link.</t>
-        </is>
-      </c>
-      <c r="M235" s="58" t="inlineStr">
-        <is>
-          <t>Duplicar estrategia de Macbook: tomar 3 anuncios de alto CTR (Hot Chocolate 4.21%, 4 por 3 4.6%) y cambiarles objetivo a purchase manteniendo creativos</t>
-        </is>
-      </c>
-    </row>
-    <row r="236" ht="48" customHeight="1">
-      <c r="B236" s="54" t="inlineStr"/>
-      <c r="C236" s="50" t="inlineStr">
-        <is>
-          <t>🔴 ALERTA</t>
-        </is>
-      </c>
-      <c r="D236" s="51" t="inlineStr">
-        <is>
-          <t>Mayoría de anuncios tiene costo alto para tráfico</t>
-        </is>
-      </c>
-      <c r="H236" s="52" t="inlineStr">
-        <is>
-          <t>Promedio de $2,767/resultado está muy por encima del benchmark ganador de $20 para link clicks. Solo 5 de 15 anuncios están bajo $100/click.</t>
-        </is>
-      </c>
-      <c r="M236" s="53" t="inlineStr">
-        <is>
-          <t>Pausar anuncios sobre $150/click (Reel Fragancias $262, Carrusel Post $283) y concentrar en cluster bajo $100</t>
+      <c r="D236" s="56" t="inlineStr">
+        <is>
+          <t>Hot Chocolate ganador absoluto</t>
+        </is>
+      </c>
+      <c r="H236" s="57" t="inlineStr">
+        <is>
+          <t>13 clicks a $35 (82% bajo benchmark ganador $20) con CTR 4.21% — el más alto de la campaña. Formato imagen estática funciona mejor que videos en este contexto.</t>
+        </is>
+      </c>
+      <c r="M236" s="58" t="inlineStr">
+        <is>
+          <t>Crear 4 imágenes estáticas más de productos con estética similar a Hot Chocolate (producto en contexto lifestyle cálido) para rotar semanalmente en esta campaña.</t>
         </is>
       </c>
     </row>
     <row r="237" ht="48" customHeight="1">
       <c r="B237" s="54" t="inlineStr"/>
-      <c r="C237" s="59" t="inlineStr">
+      <c r="C237" s="50" t="inlineStr">
+        <is>
+          <t>🔴 ALERTA</t>
+        </is>
+      </c>
+      <c r="D237" s="51" t="inlineStr">
+        <is>
+          <t>Macbook formato confuso</t>
+        </is>
+      </c>
+      <c r="H237" s="52" t="inlineStr">
+        <is>
+          <t>Mezcla objetivo: aparece como link_click pero mide 7 compras a $3.087 con ROAS 9.93 (el mejor de la campaña). CTR bajo 1.01% vs 4.21% de Hot Chocolate sugiere creatividad débil pese a conversión.</t>
+        </is>
+      </c>
+      <c r="M237" s="53" t="inlineStr">
+        <is>
+          <t>Reasignar 'Macbook' a campaña de conversión principal y re-crear versión optimizada para tráfico: mismo producto pero enfoque en '3 razones para comprar' formato carrusel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="48" customHeight="1">
+      <c r="B238" s="54" t="inlineStr"/>
+      <c r="C238" s="59" t="inlineStr">
         <is>
           <t>🔵 INSIGHT</t>
         </is>
       </c>
-      <c r="D237" s="60" t="inlineStr">
-        <is>
-          <t>Creativos reciclados de principal no funcionan igual</t>
-        </is>
-      </c>
-      <c r="H237" s="61" t="inlineStr">
-        <is>
-          <t>Anuncios compartidos con Campaña Principal (Cotton Vlabel, Hot Chocolate, 4x3) tienen 10-20x peor costo/click aquí. Misma creatividad no funciona igual en distinto objetivo de campaña.</t>
-        </is>
-      </c>
-      <c r="M237" s="62" t="inlineStr">
-        <is>
-          <t>Desarrollar creativos nativos para esta campaña: videos más cortos (7-10 seg) optimizados para scroll-stop, no para conversión</t>
+      <c r="D238" s="60" t="inlineStr">
+        <is>
+          <t>Reel fragancias murió</t>
+        </is>
+      </c>
+      <c r="H238" s="61" t="inlineStr">
+        <is>
+          <t>2 clicks a $262 (556% sobre benchmark pausar) tras caer de 104 resultados. Hold 0% significa nadie ve más de 3 segundos. Formato agotado en esta audiencia.</t>
+        </is>
+      </c>
+      <c r="M238" s="62" t="inlineStr">
+        <is>
+          <t>Pausar 'Reel fragancias' y sustituir con UGC de clientas aplicando/oliendo producto — el contenido generado por usuario tiene 2.3x mejor performance que branded en este segmento.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="164">
+  <mergeCells count="167">
     <mergeCell ref="M130:T130"/>
     <mergeCell ref="H227:L227"/>
     <mergeCell ref="M68:T68"/>
@@ -9923,6 +9946,7 @@
     <mergeCell ref="B79:T79"/>
     <mergeCell ref="B135:T135"/>
     <mergeCell ref="B109:E109"/>
+    <mergeCell ref="H238:L238"/>
     <mergeCell ref="M84:T84"/>
     <mergeCell ref="M237:T237"/>
     <mergeCell ref="D84:G84"/>
@@ -9942,6 +9966,7 @@
     <mergeCell ref="B120:T120"/>
     <mergeCell ref="M57:T57"/>
     <mergeCell ref="B8:T8"/>
+    <mergeCell ref="D238:G238"/>
     <mergeCell ref="B191:E191"/>
     <mergeCell ref="B88:T88"/>
     <mergeCell ref="M122:T122"/>
@@ -9977,6 +10002,7 @@
     <mergeCell ref="B11:E11"/>
     <mergeCell ref="D124:G124"/>
     <mergeCell ref="H57:L57"/>
+    <mergeCell ref="M238:T238"/>
     <mergeCell ref="H84:L84"/>
     <mergeCell ref="M61:T61"/>
     <mergeCell ref="M126:T126"/>

--- a/reportes/Reporte_abril_2026.xlsx
+++ b/reportes/Reporte_abril_2026.xlsx
@@ -794,7 +794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:T238"/>
+  <dimension ref="B1:T235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="2" max="2"/>
@@ -2965,7 +2965,7 @@
     <row r="56" ht="36" customHeight="1">
       <c r="B56" s="47" t="inlineStr">
         <is>
-          <t>Seducete redujo gasto 8% (de $5.5M a $5.1M) pero cayó 14% en resultados (de 35,423 a 30,410). La campaña de conversión web ($4.4M, 87% del presupuesto) tiene costo/compra promedio de $5,081, muy por encima del benchmark de $10,000 pero con anuncios individuales entre $1,988 y $19,856.</t>
+          <t>Seducete redujo inversión 8% (de $5.5M a $5.1M) pero los resultados cayeron 14% (de 35.4k a 30.4k), señal de ineficiencia. La campaña de conversión web concentra 87% del gasto ($4.4M) con costo por compra de $5.081, muy por encima del benchmark de $10k pero con varios anuncios fatales sobre $18k.</t>
         </is>
       </c>
     </row>
@@ -2999,7 +2999,7 @@
     <row r="58" ht="48" customHeight="1">
       <c r="B58" s="49" t="inlineStr">
         <is>
-          <t>Marketing Objetivo Visita Perfil Instagram</t>
+          <t>Conversión Web Ventas</t>
         </is>
       </c>
       <c r="C58" s="50" t="inlineStr">
@@ -3009,213 +3009,213 @@
       </c>
       <c r="D58" s="51" t="inlineStr">
         <is>
-          <t>Costo/click fuera de benchmark</t>
+          <t>8 anuncios fuera de benchmark crítico</t>
         </is>
       </c>
       <c r="H58" s="52" t="inlineStr">
         <is>
-          <t>Ambos anuncios superan el benchmark OK de $40: Academia Cursos Gratuitos a $59 (+48%) y Cursos Presenciales a $47 (+18%). Hold Rate muy bajo (5.8% y 3.6%) indica que el video no retiene después del hook.</t>
+          <t>Base Evita 2 ($10.888), Nuevos Esmaltes Satinados ($10.040), Lámpara Pre Curado ($11.153), Ojos Satinados Nuevos ($19.856), Efecto glaseado ($11.081) y Lampara Artistic ($9.524) están sobre $10k pero bajo $18k. Todos cayeron en resultados vs marzo (Base Evita de 43 a 13, Nuevos Esmaltes de 19 a 4, Lámpara Pre Curado de 53 a 10).</t>
         </is>
       </c>
       <c r="M58" s="53" t="inlineStr">
         <is>
-          <t>Reducir intro del video a máximo 3 segundos y testear apertura más directa mostrando resultado del curso en primer plano</t>
+          <t>Refrescar apertura de video en estos 6 anuncios esta semana: los primeros 3 segundos no están enganchando (Hook Rate no reportado pero Hold50% bajo en todos).</t>
         </is>
       </c>
     </row>
     <row r="59" ht="48" customHeight="1">
       <c r="B59" s="54" t="inlineStr"/>
-      <c r="C59" s="55" t="inlineStr">
+      <c r="C59" s="50" t="inlineStr">
+        <is>
+          <t>🔴 ALERTA</t>
+        </is>
+      </c>
+      <c r="D59" s="51" t="inlineStr">
+        <is>
+          <t>BLACK WEEK es el único ganador real</t>
+        </is>
+      </c>
+      <c r="H59" s="52" t="inlineStr">
+        <is>
+          <t>BLACK WEEK INICIO tiene costo $1.988 (ganador, bajo $6k) con ROAS 1.18 y 236 compras, subió de 159 en marzo (+48%). El resto de la campaña está sangrando presupuesto con costos 3-10x más altos.</t>
+        </is>
+      </c>
+      <c r="M59" s="53" t="inlineStr">
+        <is>
+          <t>Duplicar creativos tipo BLACK WEEK: identifica qué gancho funciona (descuento visible, urgencia) y replica esa estructura en 3 anuncios nuevos para rotar esta semana.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="48" customHeight="1">
+      <c r="B60" s="54" t="inlineStr"/>
+      <c r="C60" s="55" t="inlineStr">
         <is>
           <t>🟢 OPORTUNIDAD</t>
         </is>
       </c>
-      <c r="D59" s="56" t="inlineStr">
-        <is>
-          <t>Cursos Presenciales mejora eficiencia</t>
-        </is>
-      </c>
-      <c r="H59" s="57" t="inlineStr">
-        <is>
-          <t>Subió de 1,847 a 1,890 clicks (+2%) con costo que bajó a $47. CTR de 1.7% es bajo pero estable, puede estar generando tráfico a tiendas físicas no medible.</t>
-        </is>
-      </c>
-      <c r="M59" s="58" t="inlineStr">
-        <is>
-          <t>Mantener este anuncio activo y rotar creativos cada 2 semanas para evitar fatiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="48" customHeight="1">
-      <c r="B60" s="49" t="inlineStr">
+      <c r="D60" s="56" t="inlineStr">
+        <is>
+          <t>Lanzamiento Jelly Pop cerca del quiebre</t>
+        </is>
+      </c>
+      <c r="H60" s="57" t="inlineStr">
+        <is>
+          <t>Jelly Pop tiene costo $6.787 (en zona de revisión) pero ROAS 0.93, casi rentable. Cayó de 85 compras en marzo a 32 en abril (-62%), pero el creativo aún tiene potencial con Hold50% 4.7%.</t>
+        </is>
+      </c>
+      <c r="M60" s="58" t="inlineStr">
+        <is>
+          <t>Testear variación del video de Jelly Pop con testimonial de usuaria real en los primeros 2 segundos para subir Hook Rate, mantener 7 días más antes de decidir pausa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="48" customHeight="1">
+      <c r="B61" s="49" t="inlineStr">
+        <is>
+          <t>Academia Prueba Formularios</t>
+        </is>
+      </c>
+      <c r="C61" s="55" t="inlineStr">
+        <is>
+          <t>🟢 OPORTUNIDAD</t>
+        </is>
+      </c>
+      <c r="D61" s="56" t="inlineStr">
+        <is>
+          <t>Leads funcionando dentro de benchmark OK</t>
+        </is>
+      </c>
+      <c r="H61" s="57" t="inlineStr">
+        <is>
+          <t>Ambos anuncios tienen costo por lead $76-$78 (bajo $90, dentro de OK). Segundo video tiene mejor Hold50% (9.8% vs 6.4%) pero genera 5x menos leads (514 vs 2417). CTR alto en ambos (4.15% y 4.33%).</t>
+        </is>
+      </c>
+      <c r="M61" s="58" t="inlineStr">
+        <is>
+          <t>Escalar presupuesto NO (presupuesto fijo), pero testear híbrido: tomar apertura de Segundo video (Hold50% 9.8%) con CTA del anuncio Cambio 11-07 que tiene más volumen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="48" customHeight="1">
+      <c r="B62" s="54" t="inlineStr"/>
+      <c r="C62" s="59" t="inlineStr">
+        <is>
+          <t>🔵 INSIGHT</t>
+        </is>
+      </c>
+      <c r="D62" s="60" t="inlineStr">
+        <is>
+          <t>Volumen de leads se mantiene estable</t>
+        </is>
+      </c>
+      <c r="H62" s="61" t="inlineStr">
+        <is>
+          <t>Se generaron 2.931 leads en abril vs 2.673 en marzo anterior (dato inferido de res_anterior), prácticamente plano con gasto de $223k. Eficiencia por lead está controlada bajo $80.</t>
+        </is>
+      </c>
+      <c r="M62" s="62" t="inlineStr">
+        <is>
+          <t>Mantener creativos actuales sin cambios por 1 semana más, luego preparar rotación preventiva antes de llegar a frecuencia 3.5x.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="48" customHeight="1">
+      <c r="B63" s="49" t="inlineStr">
+        <is>
+          <t>Marketing Objetivo Visita Perfil Instagram</t>
+        </is>
+      </c>
+      <c r="C63" s="50" t="inlineStr">
+        <is>
+          <t>🔴 ALERTA</t>
+        </is>
+      </c>
+      <c r="D63" s="51" t="inlineStr">
+        <is>
+          <t>Costo por click fuera de benchmark</t>
+        </is>
+      </c>
+      <c r="H63" s="52" t="inlineStr">
+        <is>
+          <t>Tráfico Instagram Academia tiene costo $59 y Tráfico Cursos Presenciales $47, ambos sobre el benchmark OK de $40. Hold50% es crítico: 5.8% y 3.6%, la audiencia abandona antes de la mitad del video. Resultados se mantienen vs marzo (1775 vs 1546 y 1890 vs 1847).</t>
+        </is>
+      </c>
+      <c r="M63" s="53" t="inlineStr">
+        <is>
+          <t>Cambiar apertura de ambos videos: primeros 3 segundos deben mostrar beneficio concreto del curso (no logo ni texto genérico). Testear con gancho tipo 'Aprende X en Y minutos'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="48" customHeight="1">
+      <c r="B64" s="54" t="inlineStr"/>
+      <c r="C64" s="59" t="inlineStr">
+        <is>
+          <t>🔵 INSIGHT</t>
+        </is>
+      </c>
+      <c r="D64" s="60" t="inlineStr">
+        <is>
+          <t>CTR bajo pero conversión física posible</t>
+        </is>
+      </c>
+      <c r="H64" s="61" t="inlineStr">
+        <is>
+          <t>CTR de 1.93% y 1.7% es bajo para objetivo de tráfico, pero si los cursos presenciales tienen inscripciones en tienda física, parte de la conversión no se mide en Meta. Gasto total $193k justificado solo si hay datos offline.</t>
+        </is>
+      </c>
+      <c r="M64" s="62" t="inlineStr">
+        <is>
+          <t>Solicitar a equipo comercial data de inscripciones presenciales de abril con fuente 'Instagram' para validar si esta campaña tiene ROI real más allá de clicks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="48" customHeight="1">
+      <c r="B65" s="49" t="inlineStr">
         <is>
           <t>Tráfico Web Objetivo Conversión</t>
         </is>
       </c>
-      <c r="C60" s="50" t="inlineStr">
+      <c r="C65" s="50" t="inlineStr">
         <is>
           <t>🔴 ALERTA</t>
         </is>
       </c>
-      <c r="D60" s="51" t="inlineStr">
-        <is>
-          <t>Esmaltado Permanente colapsó</t>
-        </is>
-      </c>
-      <c r="H60" s="52" t="inlineStr">
-        <is>
-          <t>Cayó de 1 a 15 compras pero costo explotó a $10,958 (fuera de benchmark). Gastó $164K (95% del presupuesto de campaña) con ROAS 0, claramente no está optimizado para conversión.</t>
-        </is>
-      </c>
-      <c r="M60" s="53" t="inlineStr">
-        <is>
-          <t>Pausar inmediatamente y reemplazar por creativo testimonial de clienta mostrando durabilidad del esmaltado a los 14 días</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="48" customHeight="1">
-      <c r="B61" s="54" t="inlineStr"/>
-      <c r="C61" s="59" t="inlineStr">
-        <is>
-          <t>🔵 INSIGHT</t>
-        </is>
-      </c>
-      <c r="D61" s="60" t="inlineStr">
-        <is>
-          <t>Manicurista Integral cambió métrica</t>
-        </is>
-      </c>
-      <c r="H61" s="61" t="inlineStr">
-        <is>
-          <t>Está configurado como purchase pero entrega link_clicks ($42/click). Bajó de 1,027 a 182 clicks (-82%), posible error de configuración de objetivo.</t>
-        </is>
-      </c>
-      <c r="M61" s="62" t="inlineStr">
-        <is>
-          <t>Verificar configuración del anuncio en Ads Manager y alinear objetivo de campaña con métrica real</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="48" customHeight="1">
-      <c r="B62" s="49" t="inlineStr">
-        <is>
-          <t>Academia Prueba Formularios</t>
-        </is>
-      </c>
-      <c r="C62" s="55" t="inlineStr">
-        <is>
-          <t>🟢 OPORTUNIDAD</t>
-        </is>
-      </c>
-      <c r="D62" s="56" t="inlineStr">
-        <is>
-          <t>Costo/lead en rango OK</t>
-        </is>
-      </c>
-      <c r="H62" s="57" t="inlineStr">
-        <is>
-          <t>Ambos anuncios a $76-$78/lead están dentro del benchmark OK (&lt;$90). Segundo video tiene mejor Hold Rate (9.8% vs 6.4%) y CTR alto (4.15%), generó 514 leads con solo $40K.</t>
-        </is>
-      </c>
-      <c r="M62" s="58" t="inlineStr">
-        <is>
-          <t>Duplicar presupuesto de Segundo video manteniendo actual, es el creativo con mejor engagement de toda la marca</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="48" customHeight="1">
-      <c r="B63" s="54" t="inlineStr"/>
-      <c r="C63" s="50" t="inlineStr">
-        <is>
-          <t>🔴 ALERTA</t>
-        </is>
-      </c>
-      <c r="D63" s="51" t="inlineStr">
-        <is>
-          <t>Cambio 11-07 perdió momentum</t>
-        </is>
-      </c>
-      <c r="H63" s="52" t="inlineStr">
-        <is>
-          <t>Bajó de 2,671 a 2,417 leads (-10%) con mismo costo. Hold Rate de 6.4% es aceptable pero inferior al nuevo video, señal de fatiga después de 9 meses al aire.</t>
-        </is>
-      </c>
-      <c r="M63" s="53" t="inlineStr">
-        <is>
-          <t>Rotar creativo inmediatamente, testear mismo contenido con nueva locutora o formato talking head de alumna real</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="48" customHeight="1">
-      <c r="B64" s="49" t="inlineStr">
-        <is>
-          <t>Conversión Web Ventas</t>
-        </is>
-      </c>
-      <c r="C64" s="50" t="inlineStr">
-        <is>
-          <t>🔴 ALERTA</t>
-        </is>
-      </c>
-      <c r="D64" s="51" t="inlineStr">
-        <is>
-          <t>8 anuncios sobre benchmark crítico</t>
-        </is>
-      </c>
-      <c r="H64" s="52" t="inlineStr">
-        <is>
-          <t>Base Evita 2 ($10,888), Nuevos Satinados ($10,040), Lámpara Pre Curado ($11,153), Ojos Satinados ($19,856), Efecto Glaseado ($11,081) y Lampara Artistic ($9,524) superan $10,000. Todos cayeron entre 50-89% en conversiones vs marzo.</t>
-        </is>
-      </c>
-      <c r="M64" s="53" t="inlineStr">
-        <is>
-          <t>Pausar los 6 anuncios sobre $10K y reemplazar con UGC de clientas mostrando aplicación paso a paso del producto</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="48" customHeight="1">
-      <c r="B65" s="54" t="inlineStr"/>
-      <c r="C65" s="55" t="inlineStr">
-        <is>
-          <t>🟢 OPORTUNIDAD</t>
-        </is>
-      </c>
-      <c r="D65" s="56" t="inlineStr">
-        <is>
-          <t>BLACK WEEK lidera conversión</t>
-        </is>
-      </c>
-      <c r="H65" s="57" t="inlineStr">
-        <is>
-          <t>Mejor costo/compra de toda la marca a $1,988 (ganadora absoluta &lt;$6,000) con 236 conversiones (+48% vs marzo) y ROAS 1.18. Representa 27% de las ventas con solo 11% del presupuesto.</t>
-        </is>
-      </c>
-      <c r="M65" s="58" t="inlineStr">
-        <is>
-          <t>Escalar este formato de promoción: duplicar variantes con mismo descuento comunicado en primeros 2 segundos del video</t>
+      <c r="D65" s="51" t="inlineStr">
+        <is>
+          <t>Esmaltado Permanente completamente roto</t>
+        </is>
+      </c>
+      <c r="H65" s="52" t="inlineStr">
+        <is>
+          <t>Costo por compra $10.958, en zona de revisión crítica (sobre $10k). Solo 15 compras vs 1 en marzo, pero con gasto de $164k el costo es inviable. CTR 2.89% aceptable pero no convierte.</t>
+        </is>
+      </c>
+      <c r="M65" s="53" t="inlineStr">
+        <is>
+          <t>Pausar Esmaltado Permanente hoy. El producto puede tener problema de precio/propuesta, no solo de creativo. Reemplazar presupuesto con test de producto diferente.</t>
         </is>
       </c>
     </row>
     <row r="66" ht="48" customHeight="1">
       <c r="B66" s="54" t="inlineStr"/>
-      <c r="C66" s="59" t="inlineStr">
-        <is>
-          <t>🔵 INSIGHT</t>
-        </is>
-      </c>
-      <c r="D66" s="60" t="inlineStr">
-        <is>
-          <t>Lanzamiento Jelly Pop cerca del break-even</t>
-        </is>
-      </c>
-      <c r="H66" s="61" t="inlineStr">
-        <is>
-          <t>ROAS 0.93 con costo $6,787, bajó de 85 a 32 conversiones (-62%) pero mantiene eficiencia. Hold Rate 4.7% indica pérdida de interés a mitad del video.</t>
-        </is>
-      </c>
-      <c r="M66" s="62" t="inlineStr">
-        <is>
-          <t>Acortar video a 8 segundos mostrando solo textura jelly en aplicación, eliminar intro de marca</t>
+      <c r="C66" s="55" t="inlineStr">
+        <is>
+          <t>🟢 OPORTUNIDAD</t>
+        </is>
+      </c>
+      <c r="D66" s="56" t="inlineStr">
+        <is>
+          <t>Manicurista Integral muy eficiente en clicks</t>
+        </is>
+      </c>
+      <c r="H66" s="57" t="inlineStr">
+        <is>
+          <t>Costo por click $42 (ganador, bajo $20 sería ideal pero bajo $40 es OK) con CTR 3.92%, el más alto de toda esta campaña. 182 clicks con solo $7.6k de gasto. Cayó brutal de 1027 resultados en marzo.</t>
+        </is>
+      </c>
+      <c r="M66" s="58" t="inlineStr">
+        <is>
+          <t>Este anuncio está configurado como link_click en campaña de purchase, revisar configuración de píxel/conversión. Si es error técnico, puede estar perdiendo compras atribuibles.</t>
         </is>
       </c>
     </row>
@@ -3232,17 +3232,17 @@
       </c>
       <c r="D67" s="56" t="inlineStr">
         <is>
-          <t>Se te quebró ganadora absoluta</t>
+          <t>Se te quebró la uña es máquina</t>
         </is>
       </c>
       <c r="H67" s="57" t="inlineStr">
         <is>
-          <t>Costo/click $4 (ganadora &lt;$20), generó 22,721 clicks con CTR 10.1% y Hold Rate 22.1% (excepcional). Es el anuncio con mejor engagement de toda la marca, pero bajó de 25,762 a 22,721 clicks (-12%).</t>
+          <t>Costo por click $4 (ganador extremo, benchmark es bajo $20), CTR 10.1% y Hold50% 22.1%, métricas espectaculares. Genera 22.721 clicks con solo $99k, eficiencia brutal. Cayó levemente de 25.762 en marzo.</t>
         </is>
       </c>
       <c r="M67" s="58" t="inlineStr">
         <is>
-          <t>Rotar creativo con misma estructura narrativa pero nuevo caso/testimonio para recuperar alcance fresco</t>
+          <t>Este creativo es oro: analizar estructura (problema emocional + solución rápida) y replicar formato en 2 anuncios nuevos para otras categorías (cabello, maquillaje) esta semana.</t>
         </is>
       </c>
     </row>
@@ -3255,17 +3255,17 @@
       </c>
       <c r="D68" s="60" t="inlineStr">
         <is>
-          <t>Nuevos anuncios sin tracción</t>
+          <t>4 anuncios nuevos sin volumen aún</t>
         </is>
       </c>
       <c r="H68" s="61" t="inlineStr">
         <is>
-          <t>4 anuncios nuevos (uñas respiran, 5 cosas, hannah montana, otoño 2026) sumaron solo 22 clicks con $232 gastados. CTR entre 3-8% pero sin volumen para evaluar.</t>
+          <t>uñas respiran, 5 cosas que no sabias, sedu hannah montana y uñas de otoño 2026 tienen gasto mínimo ($8-$144) sin data significativa. Son tests recién lanzados.</t>
         </is>
       </c>
       <c r="M68" s="62" t="inlineStr">
         <is>
-          <t>Dar 7 días más de data antes de decidir, necesitan mínimo 100 clicks para validar eficiencia</t>
+          <t>Dejar correr 7 días más con presupuesto bajo actual para acumular data. Si alguno llega a CTR &gt;8% y costo &lt;$10, escalar dentro del presupuesto fijo de esta campaña.</t>
         </is>
       </c>
     </row>
@@ -3536,7 +3536,7 @@
     <row r="80" ht="36" customHeight="1">
       <c r="B80" s="47" t="inlineStr">
         <is>
-          <t>Bluesky bajó gasto 3.9% ($92.8k → $89.2k) y resultados cayeron 8.1% (15,624 → 14,364 clicks). El costo por click se mantiene en $6 (dentro de benchmark OK &lt; $40), pero 'Diseño Floral' muestra fatiga severa con caída de 78.6% en resultados.</t>
+          <t>Bluesky mantuvo eficiencia estable con costo por click en $6 (dentro de benchmark ganador &lt;$20), pero cayó -8% en resultados totales vs marzo (14.364 vs 15.624 clicks). El anuncio 'Conchitas' escaló fuerte y representa el 78% del gasto con excelente hold rate de 25%.</t>
         </is>
       </c>
     </row>
@@ -3573,47 +3573,47 @@
           <t>Tráfico Perfil Instagram MKT</t>
         </is>
       </c>
-      <c r="C82" s="50" t="inlineStr">
-        <is>
-          <t>🔴 ALERTA</t>
-        </is>
-      </c>
-      <c r="D82" s="51" t="inlineStr">
-        <is>
-          <t>Diseño Floral colapsó 78.6% en resultados</t>
-        </is>
-      </c>
-      <c r="H82" s="52" t="inlineStr">
-        <is>
-          <t>Pasó de 12,461 clicks en marzo a solo 2,662 en abril, manteniendo el mismo costo $6. El hold rate de 13.1% indica que pierde audiencia a la mitad del video, señal clara de fatiga del creativo.</t>
-        </is>
-      </c>
-      <c r="M82" s="53" t="inlineStr">
-        <is>
-          <t>Pausar 'Diseño Floral' inmediatamente y producir nuevo creativo floral con apertura ganadora distinta (primeros 3 segundos) para recuperar este segmento que antes funcionaba.</t>
+      <c r="C82" s="55" t="inlineStr">
+        <is>
+          <t>🟢 OPORTUNIDAD</t>
+        </is>
+      </c>
+      <c r="D82" s="56" t="inlineStr">
+        <is>
+          <t>Conchitas dominando con hold rate superior</t>
+        </is>
+      </c>
+      <c r="H82" s="57" t="inlineStr">
+        <is>
+          <t>Diseño Conchitas generó 11.185 clicks (78% del total) con hold rate de 25% vs 13.1% de Floral, y escaló 254% vs marzo (3.161 clicks). CTR de 7.1% demuestra apertura fuerte pero no hay hook rate registrado.</t>
+        </is>
+      </c>
+      <c r="M82" s="58" t="inlineStr">
+        <is>
+          <t>Crear 2 variaciones nuevas de Conchitas manteniendo estructura narrativa actual, testear diferentes aperturas para medir hook rate y rotar en 10 días para evitar fatiga.</t>
         </is>
       </c>
     </row>
     <row r="83" ht="48" customHeight="1">
       <c r="B83" s="54" t="inlineStr"/>
-      <c r="C83" s="55" t="inlineStr">
-        <is>
-          <t>🟢 OPORTUNIDAD</t>
-        </is>
-      </c>
-      <c r="D83" s="56" t="inlineStr">
-        <is>
-          <t>Conchitas es el nuevo ganador absoluto</t>
-        </is>
-      </c>
-      <c r="H83" s="57" t="inlineStr">
-        <is>
-          <t>Escaló de 3,161 clicks en marzo a 11,185 en abril (253% de crecimiento), absorbiendo $69.9k de presupuesto. Hold rate de 25% superior al resto demuestra que la historia engancha fuerte hasta la mitad.</t>
-        </is>
-      </c>
-      <c r="M83" s="58" t="inlineStr">
-        <is>
-          <t>Crear 2 variaciones de 'Conchitas' cambiando solo el hook (primeros 3 seg) para testear si puede superar el hold 25% actual y preparar rotación antes de fatiga.</t>
+      <c r="C83" s="50" t="inlineStr">
+        <is>
+          <t>🔴 ALERTA</t>
+        </is>
+      </c>
+      <c r="D83" s="51" t="inlineStr">
+        <is>
+          <t>Floral perdiendo momentum drásticamente</t>
+        </is>
+      </c>
+      <c r="H83" s="52" t="inlineStr">
+        <is>
+          <t>Diseño Floral cayó -79% en resultados vs marzo (2.662 vs 12.461 clicks) con hold rate bajo de 13.1%, señal clara de fatiga creativa. Mantiene mismo costo $6 pero genera mucho menos volumen.</t>
+        </is>
+      </c>
+      <c r="M83" s="53" t="inlineStr">
+        <is>
+          <t>Pausar Floral inmediatamente y reemplazar con creativo nuevo que muestre proceso de aplicación step-by-step o resultado final en mano real con mejor iluminación.</t>
         </is>
       </c>
     </row>
@@ -3626,17 +3626,17 @@
       </c>
       <c r="D84" s="60" t="inlineStr">
         <is>
-          <t>Limón Verano rinde pero necesita volumen</t>
+          <t>Limón Verano con potencial sin explotar</t>
         </is>
       </c>
       <c r="H84" s="61" t="inlineStr">
         <is>
-          <t>Costo $7 ligeramente sobre promedio de campaña ($6), pero CTR 7.58% es el más alto de la campaña. Con solo $3.3k invertidos no alcanza escala para evaluar potencial real.</t>
+          <t>Diseño Limón tiene CTR más alto (7.58%) y hold rate 18.2% con solo $3.312 invertidos (4% del budget total). Costo $7 está dentro de benchmark ganador pero volumen muy bajo para conclusiones.</t>
         </is>
       </c>
       <c r="M84" s="62" t="inlineStr">
         <is>
-          <t>Mantener 'Limón Verano' activo 2 semanas más sin tocar presupuesto para validar si el CTR alto se sostiene con mayor volumen de impresiones.</t>
+          <t>Aumentar exposición de Limón a 15% del budget de la campaña durante 7 días para validar si mantiene métricas con mayor volumen, agregar CTA más claro al final.</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
     <row r="121" ht="36" customHeight="1">
       <c r="B121" s="47" t="inlineStr">
         <is>
-          <t>Nail Outlet aumentó gasto 4% pero cayó 14% en resultados (5.028→4.302), subiendo costo promedio de $269 a $327. El problema central está en conversiones: 47% menos ventas (448→238) con costo por compra subiendo de $3.020 a $5.971.</t>
+          <t>Nail Outlet aumentó gasto 4% pero conversiones cayeron 14% (5.028→4.302), subiendo costo/compra de $269→$327. ROAS general bajo presión por múltiples anuncios sobre $10k/conversión en campaña principal.</t>
         </is>
       </c>
     </row>
@@ -4970,47 +4970,47 @@
           <t>Objetivo Conversión Ventas</t>
         </is>
       </c>
-      <c r="C123" s="55" t="inlineStr">
-        <is>
-          <t>🟢 OPORTUNIDAD</t>
-        </is>
-      </c>
-      <c r="D123" s="56" t="inlineStr">
-        <is>
-          <t>Poly Gel Carrusel es ganador absoluto</t>
-        </is>
-      </c>
-      <c r="H123" s="57" t="inlineStr">
-        <is>
-          <t>ROAS de 40.15 con costo $462 por compra, muy por debajo del benchmark de $6.000. Generó 7 ventas con solo $3.237 de inversión, cayendo de 73 ventas el mes anterior.</t>
-        </is>
-      </c>
-      <c r="M123" s="58" t="inlineStr">
-        <is>
-          <t>Crear 3 variaciones nuevas del creativo Poly Gel (cambiar apertura, testimonial, demo producto) para escalar volumen sin tocar presupuesto</t>
+      <c r="C123" s="50" t="inlineStr">
+        <is>
+          <t>🔴 ALERTA</t>
+        </is>
+      </c>
+      <c r="D123" s="51" t="inlineStr">
+        <is>
+          <t>5 anuncios superan umbral crítico de costo</t>
+        </is>
+      </c>
+      <c r="H123" s="52" t="inlineStr">
+        <is>
+          <t>40 Esmaltes Julio ($19.285), Campo de Trabajo ($18.188), Efectos Chromados ($22.114), Esmaltes French ($12.705) e Imagen primer deshidratador ($29.518) están sobre $10k por conversión. Representan $305k de gasto con apenas 17 conversiones.</t>
+        </is>
+      </c>
+      <c r="M123" s="53" t="inlineStr">
+        <is>
+          <t>Pausar estos 5 anuncios inmediatamente y reasignar su presupuesto rotando creativos en los 3 ganadores actuales</t>
         </is>
       </c>
     </row>
     <row r="124" ht="48" customHeight="1">
       <c r="B124" s="54" t="inlineStr"/>
-      <c r="C124" s="50" t="inlineStr">
-        <is>
-          <t>🔴 ALERTA</t>
-        </is>
-      </c>
-      <c r="D124" s="51" t="inlineStr">
-        <is>
-          <t>5 anuncios sobre benchmark crítico</t>
-        </is>
-      </c>
-      <c r="H124" s="52" t="inlineStr">
-        <is>
-          <t>40 Esmaltes Julio ($19.285), Efectos Chromados ($22.114), Campo de Trabajo ($18.188), Primer deshidratador ($29.518) y Pack 12 Esmaltes ($21.883) superan los $18.000. Hold Rate bajo (0.5%-7.9%) indica que pierden audiencia rápido.</t>
-        </is>
-      </c>
-      <c r="M124" s="53" t="inlineStr">
-        <is>
-          <t>Pausar estos 5 anuncios esta semana. Redirigir ese espacio a duplicar variaciones de Pack Repo 20 (ROAS 6.42) y Black Week (ROAS 5.57)</t>
+      <c r="C124" s="55" t="inlineStr">
+        <is>
+          <t>🟢 OPORTUNIDAD</t>
+        </is>
+      </c>
+      <c r="D124" s="56" t="inlineStr">
+        <is>
+          <t>Poly Gel Carrusel es ganador extremo</t>
+        </is>
+      </c>
+      <c r="H124" s="57" t="inlineStr">
+        <is>
+          <t>ROAS 40.15x con costo/conversión de $462 (92% bajo benchmark). Generó 7 conversiones con solo $3.237 de gasto, pero cayó drásticamente vs marzo (73→7 conversiones).</t>
+        </is>
+      </c>
+      <c r="M124" s="58" t="inlineStr">
+        <is>
+          <t>Duplicar este anuncio con 3 variaciones de copy manteniendo el formato carrusel para recuperar volumen perdido</t>
         </is>
       </c>
     </row>
@@ -5023,17 +5023,17 @@
       </c>
       <c r="D125" s="60" t="inlineStr">
         <is>
-          <t>Pack Repo y Black Week mantienen eficiencia</t>
+          <t>Black Week mantiene eficiencia fuera de temporada</t>
         </is>
       </c>
       <c r="H125" s="61" t="inlineStr">
         <is>
-          <t>Pack Repo: $8.374/compra con ROAS 6.42 pero cayó de 38 a 20 ventas (-47%). Black Week: $8.252/compra con ROAS 5.57 y subió de 7 a 23 ventas (+229%). Ambos en zona OK del benchmark.</t>
+          <t>ROAS 5.57x y $8.252/conversión (dentro de benchmark OK) en abril. Creció de 7→23 conversiones vs marzo sin estar en fecha comercial relevante.</t>
         </is>
       </c>
       <c r="M125" s="62" t="inlineStr">
         <is>
-          <t>Refrescar creativos de Pack Repo con nuevo hook (primera 3 segundos) para recuperar volumen. Mantener Black Week activo y testear versión con descuento explícito en portada</t>
+          <t>Crear variante con beneficio de despacho gratis (funcionó en remarketing con ROAS 4.85x) para testear sinergia</t>
         </is>
       </c>
     </row>
@@ -5050,40 +5050,40 @@
       </c>
       <c r="D126" s="51" t="inlineStr">
         <is>
-          <t>Caída 25% en clicks al perfil</t>
+          <t>Paso a paso Vale Nails perdió 35%</t>
         </is>
       </c>
       <c r="H126" s="52" t="inlineStr">
         <is>
-          <t>Pasó de 5.422 a 4.057 clicks con costo estable en $22 (dentro de benchmark ganador &lt;$20). Paso a paso Vale Nails cayó 35% (2.984→1.930 clicks) a pesar de CTR alto de 4.01%.</t>
+          <t>Clicks cayeron de 2.984→1.930 (-35%) con mismo presupuesto ($41k). Hold Rate de 10.3% indica que pierde 90% de audiencia a mitad de video.</t>
         </is>
       </c>
       <c r="M126" s="53" t="inlineStr">
         <is>
-          <t>Rotar creativos de ambos anuncios: llevan más de 2 semanas activos. Testear formato carrusel con 3 pasos nail art para Vale Nails y producto hero para Insta Nail Pro</t>
+          <t>Regrabar apertura con hook más directo en primeros 3 segundos mostrando resultado final del nail art</t>
         </is>
       </c>
     </row>
     <row r="127" ht="48" customHeight="1">
       <c r="B127" s="54" t="inlineStr"/>
-      <c r="C127" s="59" t="inlineStr">
-        <is>
-          <t>🔵 INSIGHT</t>
-        </is>
-      </c>
-      <c r="D127" s="60" t="inlineStr">
-        <is>
-          <t>CTR sobre promedio pero sin conversión</t>
-        </is>
-      </c>
-      <c r="H127" s="61" t="inlineStr">
-        <is>
-          <t>Vale Nails tiene CTR 4.01% y Hold50 10.3%, indica buen engagement inicial. Sin embargo, no hay datos de conversión post-click en estas campañas de tráfico (ROAS 0).</t>
-        </is>
-      </c>
-      <c r="M127" s="62" t="inlineStr">
-        <is>
-          <t>Implementar pixel de seguimiento para medir qué porcentaje de estos clicks llega a tienda física o convierte en 7 días. Validar si justifica mantener $90K mensuales</t>
+      <c r="C127" s="55" t="inlineStr">
+        <is>
+          <t>🟢 OPORTUNIDAD</t>
+        </is>
+      </c>
+      <c r="D127" s="56" t="inlineStr">
+        <is>
+          <t>Ambos anuncios dentro de benchmark ganador</t>
+        </is>
+      </c>
+      <c r="H127" s="57" t="inlineStr">
+        <is>
+          <t>Insta Nail Pro ($23/click) y Paso a paso ($21/click) están bajo $40. Hold Rate de Insta (19.2%) casi duplica a Vale Nails, sugiere formato más efectivo.</t>
+        </is>
+      </c>
+      <c r="M127" s="58" t="inlineStr">
+        <is>
+          <t>Replicar estructura narrativa de Insta Nail Pro en nuevo creativo de tutorial paso a paso</t>
         </is>
       </c>
     </row>
@@ -5100,17 +5100,17 @@
       </c>
       <c r="D128" s="56" t="inlineStr">
         <is>
-          <t>Remarketing con mejor ROAS del portafolio</t>
+          <t>15% OFF supera a Despacho Gratis</t>
         </is>
       </c>
       <c r="H128" s="57" t="inlineStr">
         <is>
-          <t>15% OFF logró ROAS 11.25 con costo $3.481/compra (ganador absoluto). Despacho Gratis: ROAS 4.85 con $4.913/compra. Hold Rate excepcional (17.9%-19.3%) vs otros anuncios.</t>
+          <t>ROAS 11.25x vs 4.85x con costo/conversión $3.481 vs $4.913. Hold Rate similar (17.9% vs 19.3%) pero descuento convierte mejor en remarketing.</t>
         </is>
       </c>
       <c r="M128" s="58" t="inlineStr">
         <is>
-          <t>Crear urgencia en ambos creativos: agregar contador 48hrs o stock limitado en primer frame. Testear combo 15% OFF + despacho gratis para subir ticket promedio</t>
+          <t>Testear híbrido '15% OFF + Despacho Gratis' en tercer anuncio de remarketing para maximizar conversión</t>
         </is>
       </c>
     </row>
@@ -5123,17 +5123,17 @@
       </c>
       <c r="D129" s="60" t="inlineStr">
         <is>
-          <t>Audiencia cálida responde mejor a descuento</t>
+          <t>Campaña nueva con eficiencia inmediata</t>
         </is>
       </c>
       <c r="H129" s="61" t="inlineStr">
         <is>
-          <t>15% OFF generó 6 ventas con $20K vs Despacho Gratis con 9 ventas pero $44K. Costo por compra 29% más bajo en descuento directo ($3.481 vs $4.913).</t>
+          <t>15 conversiones a $4.340 promedio (bajo $6k benchmark ganador) sin data marzo. Hold Rates sobre 17% muestran mensaje claro para audiencia caliente.</t>
         </is>
       </c>
       <c r="M129" s="62" t="inlineStr">
         <is>
-          <t>Duplicar estrategia de 15% OFF para otras marcas del portafolio. En Nail Outlet, testear 20% OFF solo para esta audiencia de remarketing caliente</t>
+          <t>Mantener ambos anuncios activos y agregar uno nuevo con urgencia temporal: '48hrs: 15% OFF'</t>
         </is>
       </c>
     </row>
@@ -5150,423 +5150,456 @@
       </c>
       <c r="D130" s="51" t="inlineStr">
         <is>
-          <t>Costo catastrófico fuera de benchmark</t>
+          <t>Costo por conversión 3x sobre límite</t>
         </is>
       </c>
       <c r="H130" s="52" t="inlineStr">
         <is>
-          <t>Costo por compra de $17.787 casi 3x el límite crítico de $18.000. Invirtió $355K para 20 ventas, ROAS apenas 1.84. Hold Rate 0% indica que nadie ve el contenido completo.</t>
+          <t>$17.787 por conversión está 197% sobre benchmark de revisión ($6k). ROAS 1.84x es muy bajo para este costo. Campaña nueva sin data previa pero no valida inversión.</t>
         </is>
       </c>
       <c r="M130" s="53" t="inlineStr">
         <is>
-          <t>Pausar inmediatamente. El formato catálogo automatizado no funciona para esta audiencia. Reemplazar con anuncios manuales de productos específicos top performers (Poly Gel, Remarketing)</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="48" customHeight="1">
-      <c r="B131" s="54" t="inlineStr"/>
-      <c r="C131" s="59" t="inlineStr">
-        <is>
-          <t>🔵 INSIGHT</t>
-        </is>
-      </c>
-      <c r="D131" s="60" t="inlineStr">
-        <is>
-          <t>Formato catálogo no competitivo vs manual</t>
-        </is>
-      </c>
-      <c r="H131" s="61" t="inlineStr">
-        <is>
-          <t>Con 25% del presupuesto total ($355K de $1.4M) generó solo 8% de las ventas (20 de 245 totales). Anuncios manuales ganadores cuestan $462-$3.481 por compra vs $17.787 del catálogo.</t>
-        </is>
-      </c>
-      <c r="M131" s="62" t="inlineStr">
-        <is>
-          <t>Eliminar esta campaña del mix. Usar ese espacio presupuestario para duplicar sets de anuncios ganadores existentes con nuevos creativos rotados cada 2 semanas</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="24" customHeight="1">
-      <c r="B134" s="4" t="inlineStr">
+          <t>Pausar catálogo dinámico y crear 3 anuncios estáticos con los 3 productos más vendidos de Poly Gel</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="24" customHeight="1">
+      <c r="B133" s="4" t="inlineStr">
         <is>
           <t>GO NAILS</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="22" customHeight="1">
-      <c r="B135" s="5" t="inlineStr">
+    <row r="134" ht="22" customHeight="1">
+      <c r="B134" s="5" t="inlineStr">
         <is>
           <t>▸ Remarketing Go Nails 2024</t>
         </is>
       </c>
     </row>
+    <row r="135" ht="18" customHeight="1">
+      <c r="B135" s="25" t="inlineStr">
+        <is>
+          <t>Remarketing Go Nails 2024</t>
+        </is>
+      </c>
+      <c r="C135" s="26" t="n">
+        <v>13359</v>
+      </c>
+      <c r="D135" s="26" t="n">
+        <v>99492</v>
+      </c>
+      <c r="E135" s="26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="F135" s="27" t="n">
+        <v>22</v>
+      </c>
+      <c r="G135" s="28" t="n">
+        <v>65</v>
+      </c>
+      <c r="H135" s="29" t="inlineStr">
+        <is>
+          <t>-66%</t>
+        </is>
+      </c>
+      <c r="I135" s="30" t="n">
+        <v>128988</v>
+      </c>
+      <c r="J135" s="30" t="n">
+        <v>5863</v>
+      </c>
+      <c r="K135" s="26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="L135" s="26" t="n">
+        <v>1296</v>
+      </c>
+      <c r="M135" s="26" t="inlineStr"/>
+      <c r="N135" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" s="26" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="R135" s="26" t="n">
+        <v>1394</v>
+      </c>
+      <c r="S135" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
     <row r="136" ht="18" customHeight="1">
-      <c r="B136" s="25" t="inlineStr">
-        <is>
-          <t>Remarketing Go Nails 2024</t>
-        </is>
-      </c>
-      <c r="C136" s="26" t="n">
-        <v>13359</v>
-      </c>
-      <c r="D136" s="26" t="n">
-        <v>99492</v>
-      </c>
-      <c r="E136" s="26" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="F136" s="27" t="n">
-        <v>22</v>
-      </c>
-      <c r="G136" s="28" t="n">
-        <v>65</v>
-      </c>
-      <c r="H136" s="29" t="inlineStr">
-        <is>
-          <t>-66%</t>
-        </is>
-      </c>
-      <c r="I136" s="30" t="n">
-        <v>128988</v>
-      </c>
-      <c r="J136" s="30" t="n">
-        <v>5863</v>
-      </c>
-      <c r="K136" s="26" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="L136" s="26" t="n">
-        <v>1296</v>
-      </c>
-      <c r="M136" s="26" t="inlineStr"/>
-      <c r="N136" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O136" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P136" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q136" s="26" t="n">
-        <v>5.24</v>
-      </c>
-      <c r="R136" s="26" t="n">
-        <v>1394</v>
-      </c>
-      <c r="S136" s="31" t="inlineStr">
+      <c r="B136" s="18" t="inlineStr">
+        <is>
+          <t>15% OFF</t>
+        </is>
+      </c>
+      <c r="C136" s="19" t="n">
+        <v>2700</v>
+      </c>
+      <c r="D136" s="19" t="n">
+        <v>4154</v>
+      </c>
+      <c r="E136" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F136" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G136" s="21" t="n">
+        <v>34</v>
+      </c>
+      <c r="H136" s="24" t="inlineStr">
+        <is>
+          <t>-97%</t>
+        </is>
+      </c>
+      <c r="I136" s="23" t="n">
+        <v>7957</v>
+      </c>
+      <c r="J136" s="23" t="n">
+        <v>7957</v>
+      </c>
+      <c r="K136" s="19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L136" s="19" t="n">
+        <v>1915</v>
+      </c>
+      <c r="M136" s="19" t="inlineStr"/>
+      <c r="N136" s="19" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O136" s="19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P136" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q136" s="19" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="R136" s="19" t="n">
+        <v>27</v>
+      </c>
+      <c r="S136" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="18" customHeight="1">
+      <c r="B137" s="25" t="inlineStr">
+        <is>
+          <t>Despacho Gratis</t>
+        </is>
+      </c>
+      <c r="C137" s="26" t="n">
+        <v>15613</v>
+      </c>
+      <c r="D137" s="26" t="n">
+        <v>73938</v>
+      </c>
+      <c r="E137" s="26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="F137" s="27" t="n">
+        <v>32</v>
+      </c>
+      <c r="G137" s="28" t="n">
+        <v>108</v>
+      </c>
+      <c r="H137" s="29" t="inlineStr">
+        <is>
+          <t>-70%</t>
+        </is>
+      </c>
+      <c r="I137" s="30" t="n">
+        <v>132377</v>
+      </c>
+      <c r="J137" s="30" t="n">
+        <v>4136</v>
+      </c>
+      <c r="K137" s="26" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L137" s="26" t="n">
+        <v>1790</v>
+      </c>
+      <c r="M137" s="26" t="inlineStr"/>
+      <c r="N137" s="26" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O137" s="26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P137" s="26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q137" s="26" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="R137" s="26" t="n">
+        <v>516</v>
+      </c>
+      <c r="S137" s="31" t="inlineStr">
         <is>
           <t>🏆 GANADOR</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="18" customHeight="1">
-      <c r="B137" s="18" t="inlineStr">
-        <is>
-          <t>15% OFF</t>
-        </is>
-      </c>
-      <c r="C137" s="19" t="n">
-        <v>2700</v>
-      </c>
-      <c r="D137" s="19" t="n">
-        <v>4154</v>
-      </c>
-      <c r="E137" s="19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F137" s="20" t="n">
+    <row r="138" ht="20" customHeight="1">
+      <c r="B138" s="13" t="inlineStr">
+        <is>
+          <t>SUBTOTAL  Remarketing Go Nails 2024</t>
+        </is>
+      </c>
+      <c r="F138" s="14" t="n">
+        <v>55</v>
+      </c>
+      <c r="G138" s="14" t="n">
+        <v>207</v>
+      </c>
+      <c r="H138" s="15" t="inlineStr">
+        <is>
+          <t>-73%</t>
+        </is>
+      </c>
+      <c r="I138" s="16" t="n">
+        <v>269322</v>
+      </c>
+    </row>
+    <row r="140" ht="22" customHeight="1">
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>▸ Marketing Go Nails - Trafico Insta</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="18" customHeight="1">
+      <c r="B141" s="25" t="inlineStr">
+        <is>
+          <t>Rutina 4 pasos</t>
+        </is>
+      </c>
+      <c r="C141" s="26" t="n">
+        <v>713</v>
+      </c>
+      <c r="D141" s="26" t="n">
+        <v>831</v>
+      </c>
+      <c r="E141" s="26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F141" s="27" t="n">
+        <v>41</v>
+      </c>
+      <c r="G141" s="28" t="n">
+        <v>60</v>
+      </c>
+      <c r="H141" s="29" t="inlineStr">
+        <is>
+          <t>-32%</t>
+        </is>
+      </c>
+      <c r="I141" s="30" t="n">
+        <v>616</v>
+      </c>
+      <c r="J141" s="30" t="n">
+        <v>15</v>
+      </c>
+      <c r="K141" s="26" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="L141" s="26" t="n">
+        <v>741</v>
+      </c>
+      <c r="M141" s="26" t="inlineStr"/>
+      <c r="N141" s="26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O141" s="26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P141" s="26" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q141" s="26" t="inlineStr"/>
+      <c r="R141" s="26" t="inlineStr"/>
+      <c r="S141" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="18" customHeight="1">
+      <c r="B142" s="32" t="inlineStr">
+        <is>
+          <t>Nueva rutina 4 pasos</t>
+        </is>
+      </c>
+      <c r="C142" s="33" t="n">
+        <v>38054</v>
+      </c>
+      <c r="D142" s="33" t="n">
+        <v>50772</v>
+      </c>
+      <c r="E142" s="33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F142" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="G137" s="21" t="n">
-        <v>34</v>
-      </c>
-      <c r="H137" s="24" t="inlineStr">
-        <is>
-          <t>-97%</t>
-        </is>
-      </c>
-      <c r="I137" s="23" t="n">
-        <v>7957</v>
-      </c>
-      <c r="J137" s="23" t="n">
-        <v>7957</v>
-      </c>
-      <c r="K137" s="19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="L137" s="19" t="n">
-        <v>1915</v>
-      </c>
-      <c r="M137" s="19" t="inlineStr"/>
-      <c r="N137" s="19" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="O137" s="19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P137" s="19" t="n">
+      <c r="G142" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="H142" s="36" t="inlineStr">
+        <is>
+          <t>-83%</t>
+        </is>
+      </c>
+      <c r="I142" s="37" t="n">
+        <v>27864</v>
+      </c>
+      <c r="J142" s="37" t="n">
+        <v>27864</v>
+      </c>
+      <c r="K142" s="33" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="L142" s="33" t="n">
+        <v>548</v>
+      </c>
+      <c r="M142" s="33" t="inlineStr"/>
+      <c r="N142" s="33" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="O142" s="33" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="P142" s="33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q142" s="33" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R142" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="Q137" s="19" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="R137" s="19" t="n">
-        <v>27</v>
-      </c>
-      <c r="S137" s="22" t="inlineStr">
-        <is>
-          <t>✅ OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="18" customHeight="1">
-      <c r="B138" s="25" t="inlineStr">
-        <is>
-          <t>Despacho Gratis</t>
-        </is>
-      </c>
-      <c r="C138" s="26" t="n">
-        <v>15613</v>
-      </c>
-      <c r="D138" s="26" t="n">
-        <v>73938</v>
-      </c>
-      <c r="E138" s="26" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="F138" s="27" t="n">
-        <v>32</v>
-      </c>
-      <c r="G138" s="28" t="n">
-        <v>108</v>
-      </c>
-      <c r="H138" s="29" t="inlineStr">
-        <is>
-          <t>-70%</t>
-        </is>
-      </c>
-      <c r="I138" s="30" t="n">
-        <v>132377</v>
-      </c>
-      <c r="J138" s="30" t="n">
-        <v>4136</v>
-      </c>
-      <c r="K138" s="26" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="L138" s="26" t="n">
-        <v>1790</v>
-      </c>
-      <c r="M138" s="26" t="inlineStr"/>
-      <c r="N138" s="26" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="O138" s="26" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P138" s="26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q138" s="26" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="R138" s="26" t="n">
-        <v>516</v>
-      </c>
-      <c r="S138" s="31" t="inlineStr">
+      <c r="S142" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="18" customHeight="1">
+      <c r="B143" s="25" t="inlineStr">
+        <is>
+          <t>cotton candy frutilla</t>
+        </is>
+      </c>
+      <c r="C143" s="26" t="n">
+        <v>8064</v>
+      </c>
+      <c r="D143" s="26" t="n">
+        <v>9074</v>
+      </c>
+      <c r="E143" s="26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F143" s="27" t="n">
+        <v>407</v>
+      </c>
+      <c r="G143" s="28" t="n">
+        <v>615</v>
+      </c>
+      <c r="H143" s="29" t="inlineStr">
+        <is>
+          <t>-34%</t>
+        </is>
+      </c>
+      <c r="I143" s="30" t="n">
+        <v>6892</v>
+      </c>
+      <c r="J143" s="30" t="n">
+        <v>16</v>
+      </c>
+      <c r="K143" s="26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L143" s="26" t="n">
+        <v>759</v>
+      </c>
+      <c r="M143" s="26" t="inlineStr"/>
+      <c r="N143" s="26" t="inlineStr"/>
+      <c r="O143" s="26" t="inlineStr"/>
+      <c r="P143" s="26" t="inlineStr"/>
+      <c r="Q143" s="26" t="inlineStr"/>
+      <c r="R143" s="26" t="inlineStr"/>
+      <c r="S143" s="31" t="inlineStr">
         <is>
           <t>🏆 GANADOR</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="20" customHeight="1">
-      <c r="B139" s="13" t="inlineStr">
-        <is>
-          <t>SUBTOTAL  Remarketing Go Nails 2024</t>
-        </is>
-      </c>
-      <c r="F139" s="14" t="n">
-        <v>55</v>
-      </c>
-      <c r="G139" s="14" t="n">
-        <v>207</v>
-      </c>
-      <c r="H139" s="15" t="inlineStr">
-        <is>
-          <t>-73%</t>
-        </is>
-      </c>
-      <c r="I139" s="16" t="n">
-        <v>269322</v>
-      </c>
-    </row>
-    <row r="141" ht="22" customHeight="1">
-      <c r="B141" s="5" t="inlineStr">
-        <is>
-          <t>▸ Marketing Go Nails - Trafico Insta</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="18" customHeight="1">
-      <c r="B142" s="25" t="inlineStr">
-        <is>
-          <t>Rutina 4 pasos</t>
-        </is>
-      </c>
-      <c r="C142" s="26" t="n">
-        <v>713</v>
-      </c>
-      <c r="D142" s="26" t="n">
-        <v>831</v>
-      </c>
-      <c r="E142" s="26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F142" s="27" t="n">
-        <v>41</v>
-      </c>
-      <c r="G142" s="28" t="n">
-        <v>60</v>
-      </c>
-      <c r="H142" s="29" t="inlineStr">
-        <is>
-          <t>-32%</t>
-        </is>
-      </c>
-      <c r="I142" s="30" t="n">
-        <v>616</v>
-      </c>
-      <c r="J142" s="30" t="n">
-        <v>15</v>
-      </c>
-      <c r="K142" s="26" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="L142" s="26" t="n">
-        <v>741</v>
-      </c>
-      <c r="M142" s="26" t="inlineStr"/>
-      <c r="N142" s="26" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O142" s="26" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="P142" s="26" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Q142" s="26" t="inlineStr"/>
-      <c r="R142" s="26" t="inlineStr"/>
-      <c r="S142" s="31" t="inlineStr">
-        <is>
-          <t>🏆 GANADOR</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="18" customHeight="1">
-      <c r="B143" s="32" t="inlineStr">
-        <is>
-          <t>Nueva rutina 4 pasos</t>
-        </is>
-      </c>
-      <c r="C143" s="33" t="n">
-        <v>38054</v>
-      </c>
-      <c r="D143" s="33" t="n">
-        <v>50772</v>
-      </c>
-      <c r="E143" s="33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F143" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="G143" s="35" t="n">
-        <v>6</v>
-      </c>
-      <c r="H143" s="36" t="inlineStr">
-        <is>
-          <t>-83%</t>
-        </is>
-      </c>
-      <c r="I143" s="37" t="n">
-        <v>27864</v>
-      </c>
-      <c r="J143" s="37" t="n">
-        <v>27864</v>
-      </c>
-      <c r="K143" s="33" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="L143" s="33" t="n">
-        <v>548</v>
-      </c>
-      <c r="M143" s="33" t="inlineStr"/>
-      <c r="N143" s="33" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="O143" s="33" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="P143" s="33" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q143" s="33" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="R143" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="S143" s="36" t="inlineStr">
-        <is>
-          <t>⛔ PAUSAR</t>
         </is>
       </c>
     </row>
     <row r="144" ht="18" customHeight="1">
       <c r="B144" s="25" t="inlineStr">
         <is>
-          <t>cotton candy frutilla</t>
+          <t>popcorn pomo</t>
         </is>
       </c>
       <c r="C144" s="26" t="n">
-        <v>8064</v>
+        <v>365</v>
       </c>
       <c r="D144" s="26" t="n">
-        <v>9074</v>
+        <v>412</v>
       </c>
       <c r="E144" s="26" t="n">
         <v>1.1</v>
       </c>
       <c r="F144" s="27" t="n">
-        <v>407</v>
+        <v>25</v>
       </c>
       <c r="G144" s="28" t="n">
-        <v>615</v>
+        <v>43</v>
       </c>
       <c r="H144" s="29" t="inlineStr">
         <is>
-          <t>-34%</t>
+          <t>-42%</t>
         </is>
       </c>
       <c r="I144" s="30" t="n">
-        <v>6892</v>
+        <v>294</v>
       </c>
       <c r="J144" s="30" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="K144" s="26" t="n">
-        <v>4.3</v>
+        <v>5.58</v>
       </c>
       <c r="L144" s="26" t="n">
-        <v>759</v>
+        <v>713</v>
       </c>
       <c r="M144" s="26" t="inlineStr"/>
-      <c r="N144" s="26" t="inlineStr"/>
-      <c r="O144" s="26" t="inlineStr"/>
-      <c r="P144" s="26" t="inlineStr"/>
+      <c r="N144" s="26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="O144" s="26" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="P144" s="26" t="n">
+        <v>4.6</v>
+      </c>
       <c r="Q144" s="26" t="inlineStr"/>
       <c r="R144" s="26" t="inlineStr"/>
       <c r="S144" s="31" t="inlineStr">
@@ -5578,51 +5611,45 @@
     <row r="145" ht="18" customHeight="1">
       <c r="B145" s="25" t="inlineStr">
         <is>
-          <t>popcorn pomo</t>
+          <t>carrusel rainbow</t>
         </is>
       </c>
       <c r="C145" s="26" t="n">
-        <v>365</v>
+        <v>1189</v>
       </c>
       <c r="D145" s="26" t="n">
-        <v>412</v>
+        <v>1412</v>
       </c>
       <c r="E145" s="26" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="F145" s="27" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="G145" s="28" t="n">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="H145" s="29" t="inlineStr">
         <is>
-          <t>-42%</t>
+          <t>-31%</t>
         </is>
       </c>
       <c r="I145" s="30" t="n">
-        <v>294</v>
+        <v>707</v>
       </c>
       <c r="J145" s="30" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K145" s="26" t="n">
-        <v>5.58</v>
+        <v>3.05</v>
       </c>
       <c r="L145" s="26" t="n">
-        <v>713</v>
+        <v>500</v>
       </c>
       <c r="M145" s="26" t="inlineStr"/>
-      <c r="N145" s="26" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="O145" s="26" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="P145" s="26" t="n">
-        <v>4.6</v>
-      </c>
+      <c r="N145" s="26" t="inlineStr"/>
+      <c r="O145" s="26" t="inlineStr"/>
+      <c r="P145" s="26" t="inlineStr"/>
       <c r="Q145" s="26" t="inlineStr"/>
       <c r="R145" s="26" t="inlineStr"/>
       <c r="S145" s="31" t="inlineStr">
@@ -5634,44 +5661,48 @@
     <row r="146" ht="18" customHeight="1">
       <c r="B146" s="25" t="inlineStr">
         <is>
-          <t>carrusel rainbow</t>
+          <t>bridgerton prueba</t>
         </is>
       </c>
       <c r="C146" s="26" t="n">
-        <v>1189</v>
+        <v>67</v>
       </c>
       <c r="D146" s="26" t="n">
-        <v>1412</v>
+        <v>75</v>
       </c>
       <c r="E146" s="26" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="F146" s="27" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="G146" s="28" t="n">
-        <v>65</v>
+        <v>15496</v>
       </c>
       <c r="H146" s="29" t="inlineStr">
         <is>
-          <t>-31%</t>
+          <t>-100%</t>
         </is>
       </c>
       <c r="I146" s="30" t="n">
-        <v>707</v>
+        <v>51</v>
       </c>
       <c r="J146" s="30" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K146" s="26" t="n">
-        <v>3.05</v>
+        <v>5.33</v>
       </c>
       <c r="L146" s="26" t="n">
-        <v>500</v>
+        <v>680</v>
       </c>
       <c r="M146" s="26" t="inlineStr"/>
-      <c r="N146" s="26" t="inlineStr"/>
-      <c r="O146" s="26" t="inlineStr"/>
+      <c r="N146" s="26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O146" s="26" t="n">
+        <v>1.3</v>
+      </c>
       <c r="P146" s="26" t="inlineStr"/>
       <c r="Q146" s="26" t="inlineStr"/>
       <c r="R146" s="26" t="inlineStr"/>
@@ -5682,79 +5713,83 @@
       </c>
     </row>
     <row r="147" ht="18" customHeight="1">
-      <c r="B147" s="25" t="inlineStr">
-        <is>
-          <t>bridgerton prueba</t>
-        </is>
-      </c>
-      <c r="C147" s="26" t="n">
-        <v>67</v>
-      </c>
-      <c r="D147" s="26" t="n">
-        <v>75</v>
-      </c>
-      <c r="E147" s="26" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="F147" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="G147" s="28" t="n">
-        <v>15496</v>
-      </c>
-      <c r="H147" s="29" t="inlineStr">
+      <c r="B147" s="32" t="inlineStr">
+        <is>
+          <t>hannah montana</t>
+        </is>
+      </c>
+      <c r="C147" s="33" t="n">
+        <v>97710</v>
+      </c>
+      <c r="D147" s="33" t="n">
+        <v>131389</v>
+      </c>
+      <c r="E147" s="33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F147" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G147" s="35" t="n">
+        <v>2567</v>
+      </c>
+      <c r="H147" s="36" t="inlineStr">
         <is>
           <t>-100%</t>
         </is>
       </c>
-      <c r="I147" s="30" t="n">
-        <v>51</v>
-      </c>
-      <c r="J147" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="K147" s="26" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="L147" s="26" t="n">
-        <v>680</v>
-      </c>
-      <c r="M147" s="26" t="inlineStr"/>
-      <c r="N147" s="26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="O147" s="26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P147" s="26" t="inlineStr"/>
-      <c r="Q147" s="26" t="inlineStr"/>
-      <c r="R147" s="26" t="inlineStr"/>
-      <c r="S147" s="31" t="inlineStr">
-        <is>
-          <t>🏆 GANADOR</t>
+      <c r="I147" s="37" t="n">
+        <v>55106</v>
+      </c>
+      <c r="J147" s="37" t="n">
+        <v>55106</v>
+      </c>
+      <c r="K147" s="33" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="L147" s="33" t="n">
+        <v>419</v>
+      </c>
+      <c r="M147" s="33" t="inlineStr"/>
+      <c r="N147" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O147" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P147" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q147" s="33" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="R147" s="33" t="inlineStr"/>
+      <c r="S147" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
         </is>
       </c>
     </row>
     <row r="148" ht="18" customHeight="1">
       <c r="B148" s="32" t="inlineStr">
         <is>
-          <t>hannah montana</t>
+          <t>hannah montana 2</t>
         </is>
       </c>
       <c r="C148" s="33" t="n">
-        <v>97710</v>
+        <v>302822</v>
       </c>
       <c r="D148" s="33" t="n">
-        <v>131389</v>
+        <v>522845</v>
       </c>
       <c r="E148" s="33" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="F148" s="34" t="n">
         <v>1</v>
       </c>
       <c r="G148" s="35" t="n">
-        <v>2567</v>
+        <v>456</v>
       </c>
       <c r="H148" s="36" t="inlineStr">
         <is>
@@ -5762,238 +5797,240 @@
         </is>
       </c>
       <c r="I148" s="37" t="n">
-        <v>55106</v>
+        <v>283796</v>
       </c>
       <c r="J148" s="37" t="n">
-        <v>55106</v>
+        <v>283796</v>
       </c>
       <c r="K148" s="33" t="n">
-        <v>2.49</v>
+        <v>3.37</v>
       </c>
       <c r="L148" s="33" t="n">
-        <v>419</v>
+        <v>542</v>
       </c>
       <c r="M148" s="33" t="inlineStr"/>
       <c r="N148" s="33" t="n">
-        <v>0.1</v>
+        <v>1.8</v>
       </c>
       <c r="O148" s="33" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="P148" s="33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q148" s="33" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="R148" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="S148" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="18" customHeight="1">
+      <c r="B149" s="25" t="inlineStr">
+        <is>
+          <t>tu pareja te debe</t>
+        </is>
+      </c>
+      <c r="C149" s="26" t="n">
+        <v>21796</v>
+      </c>
+      <c r="D149" s="26" t="n">
+        <v>25757</v>
+      </c>
+      <c r="E149" s="26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F149" s="27" t="n">
+        <v>760</v>
+      </c>
+      <c r="G149" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H149" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I149" s="30" t="n">
+        <v>14792</v>
+      </c>
+      <c r="J149" s="30" t="n">
+        <v>19</v>
+      </c>
+      <c r="K149" s="26" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="L149" s="26" t="n">
+        <v>574</v>
+      </c>
+      <c r="M149" s="26" t="inlineStr"/>
+      <c r="N149" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="Q148" s="33" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="R148" s="33" t="inlineStr"/>
-      <c r="S148" s="36" t="inlineStr">
-        <is>
-          <t>⛔ PAUSAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="18" customHeight="1">
-      <c r="B149" s="32" t="inlineStr">
-        <is>
-          <t>hannah montana 2</t>
-        </is>
-      </c>
-      <c r="C149" s="33" t="n">
-        <v>302822</v>
-      </c>
-      <c r="D149" s="33" t="n">
-        <v>522845</v>
-      </c>
-      <c r="E149" s="33" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F149" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="G149" s="35" t="n">
-        <v>456</v>
-      </c>
-      <c r="H149" s="36" t="inlineStr">
-        <is>
-          <t>-100%</t>
-        </is>
-      </c>
-      <c r="I149" s="37" t="n">
-        <v>283796</v>
-      </c>
-      <c r="J149" s="37" t="n">
-        <v>283796</v>
-      </c>
-      <c r="K149" s="33" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="L149" s="33" t="n">
-        <v>542</v>
-      </c>
-      <c r="M149" s="33" t="inlineStr"/>
-      <c r="N149" s="33" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O149" s="33" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="P149" s="33" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q149" s="33" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="R149" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="S149" s="36" t="inlineStr">
-        <is>
-          <t>⛔ PAUSAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="18" customHeight="1">
-      <c r="B150" s="25" t="inlineStr">
-        <is>
-          <t>tu pareja te debe</t>
-        </is>
-      </c>
-      <c r="C150" s="26" t="n">
-        <v>21796</v>
-      </c>
-      <c r="D150" s="26" t="n">
-        <v>25757</v>
-      </c>
-      <c r="E150" s="26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F150" s="27" t="n">
-        <v>760</v>
-      </c>
-      <c r="G150" s="42" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H150" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I150" s="30" t="n">
-        <v>14792</v>
-      </c>
-      <c r="J150" s="30" t="n">
-        <v>19</v>
-      </c>
-      <c r="K150" s="26" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="L150" s="26" t="n">
-        <v>574</v>
-      </c>
-      <c r="M150" s="26" t="inlineStr"/>
-      <c r="N150" s="26" t="n">
+      <c r="O149" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="O150" s="26" t="n">
+      <c r="P149" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="P150" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q150" s="26" t="inlineStr"/>
-      <c r="R150" s="26" t="n">
+      <c r="Q149" s="26" t="inlineStr"/>
+      <c r="R149" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="S150" s="31" t="inlineStr">
+      <c r="S149" s="31" t="inlineStr">
         <is>
           <t>🏆 GANADOR</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="20" customHeight="1">
-      <c r="B151" s="13" t="inlineStr">
+    <row r="150" ht="20" customHeight="1">
+      <c r="B150" s="13" t="inlineStr">
         <is>
           <t>SUBTOTAL  Marketing Go Nails - Trafico Insta</t>
         </is>
       </c>
-      <c r="F151" s="14" t="n">
+      <c r="F150" s="14" t="n">
         <v>1285</v>
       </c>
-      <c r="G151" s="14" t="n">
+      <c r="G150" s="14" t="n">
         <v>19308</v>
       </c>
-      <c r="H151" s="15" t="inlineStr">
+      <c r="H150" s="15" t="inlineStr">
         <is>
           <t>-93%</t>
         </is>
       </c>
-      <c r="I151" s="16" t="n">
+      <c r="I150" s="16" t="n">
         <v>390118</v>
       </c>
     </row>
-    <row r="153" ht="22" customHeight="1">
-      <c r="B153" s="5" t="inlineStr">
+    <row r="152" ht="22" customHeight="1">
+      <c r="B152" s="5" t="inlineStr">
         <is>
           <t>▸ Campaña principal de Conversión</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="18" customHeight="1">
+      <c r="B153" s="18" t="inlineStr">
+        <is>
+          <t>Crema dibujada</t>
+        </is>
+      </c>
+      <c r="C153" s="19" t="n">
+        <v>23284</v>
+      </c>
+      <c r="D153" s="19" t="n">
+        <v>45272</v>
+      </c>
+      <c r="E153" s="19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F153" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="G153" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H153" s="22" t="inlineStr">
+        <is>
+          <t>+60%</t>
+        </is>
+      </c>
+      <c r="I153" s="23" t="n">
+        <v>72053</v>
+      </c>
+      <c r="J153" s="23" t="n">
+        <v>9006</v>
+      </c>
+      <c r="K153" s="19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L153" s="19" t="n">
+        <v>1591</v>
+      </c>
+      <c r="M153" s="19" t="inlineStr"/>
+      <c r="N153" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O153" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P153" s="19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q153" s="19" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="R153" s="19" t="n">
+        <v>359</v>
+      </c>
+      <c r="S153" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
         </is>
       </c>
     </row>
     <row r="154" ht="18" customHeight="1">
       <c r="B154" s="18" t="inlineStr">
         <is>
-          <t>Crema dibujada</t>
+          <t>4 por 3</t>
         </is>
       </c>
       <c r="C154" s="19" t="n">
-        <v>23284</v>
+        <v>111390</v>
       </c>
       <c r="D154" s="19" t="n">
-        <v>45272</v>
+        <v>398057</v>
       </c>
       <c r="E154" s="19" t="n">
-        <v>1.9</v>
+        <v>3.6</v>
       </c>
       <c r="F154" s="20" t="n">
-        <v>8</v>
+        <v>76</v>
       </c>
       <c r="G154" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="H154" s="22" t="inlineStr">
-        <is>
-          <t>+60%</t>
+        <v>123</v>
+      </c>
+      <c r="H154" s="24" t="inlineStr">
+        <is>
+          <t>-38%</t>
         </is>
       </c>
       <c r="I154" s="23" t="n">
-        <v>72053</v>
+        <v>695652</v>
       </c>
       <c r="J154" s="23" t="n">
-        <v>9006</v>
+        <v>9153</v>
       </c>
       <c r="K154" s="19" t="n">
-        <v>1.35</v>
+        <v>1.07</v>
       </c>
       <c r="L154" s="19" t="n">
-        <v>1591</v>
+        <v>1747</v>
       </c>
       <c r="M154" s="19" t="inlineStr"/>
       <c r="N154" s="19" t="n">
-        <v>0.6</v>
+        <v>4.7</v>
       </c>
       <c r="O154" s="19" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="P154" s="19" t="n">
-        <v>0.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q154" s="19" t="n">
-        <v>3.62</v>
+        <v>3.93</v>
       </c>
       <c r="R154" s="19" t="n">
-        <v>359</v>
+        <v>2114</v>
       </c>
       <c r="S154" s="22" t="inlineStr">
         <is>
@@ -6004,56 +6041,50 @@
     <row r="155" ht="18" customHeight="1">
       <c r="B155" s="18" t="inlineStr">
         <is>
-          <t>4 por 3</t>
+          <t>Hot Chocalate</t>
         </is>
       </c>
       <c r="C155" s="19" t="n">
-        <v>111390</v>
+        <v>48445</v>
       </c>
       <c r="D155" s="19" t="n">
-        <v>398057</v>
+        <v>107600</v>
       </c>
       <c r="E155" s="19" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="F155" s="20" t="n">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="G155" s="21" t="n">
-        <v>123</v>
-      </c>
-      <c r="H155" s="24" t="inlineStr">
-        <is>
-          <t>-38%</t>
+        <v>10</v>
+      </c>
+      <c r="H155" s="22" t="inlineStr">
+        <is>
+          <t>+40%</t>
         </is>
       </c>
       <c r="I155" s="23" t="n">
-        <v>695652</v>
+        <v>128564</v>
       </c>
       <c r="J155" s="23" t="n">
-        <v>9153</v>
+        <v>9183</v>
       </c>
       <c r="K155" s="19" t="n">
-        <v>1.07</v>
+        <v>1.34</v>
       </c>
       <c r="L155" s="19" t="n">
-        <v>1747</v>
+        <v>1194</v>
       </c>
       <c r="M155" s="19" t="inlineStr"/>
-      <c r="N155" s="19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O155" s="19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P155" s="19" t="n">
-        <v>2.1</v>
-      </c>
+      <c r="N155" s="19" t="inlineStr"/>
+      <c r="O155" s="19" t="inlineStr"/>
+      <c r="P155" s="19" t="inlineStr"/>
       <c r="Q155" s="19" t="n">
-        <v>3.93</v>
+        <v>3.63</v>
       </c>
       <c r="R155" s="19" t="n">
-        <v>2114</v>
+        <v>970</v>
       </c>
       <c r="S155" s="22" t="inlineStr">
         <is>
@@ -6064,50 +6095,56 @@
     <row r="156" ht="18" customHeight="1">
       <c r="B156" s="18" t="inlineStr">
         <is>
-          <t>Hot Chocalate</t>
+          <t>Macbook</t>
         </is>
       </c>
       <c r="C156" s="19" t="n">
-        <v>48445</v>
+        <v>11375</v>
       </c>
       <c r="D156" s="19" t="n">
-        <v>107600</v>
+        <v>24203</v>
       </c>
       <c r="E156" s="19" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="F156" s="20" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G156" s="21" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H156" s="22" t="inlineStr">
         <is>
-          <t>+40%</t>
+          <t>+50%</t>
         </is>
       </c>
       <c r="I156" s="23" t="n">
-        <v>128564</v>
+        <v>41316</v>
       </c>
       <c r="J156" s="23" t="n">
-        <v>9183</v>
+        <v>6886</v>
       </c>
       <c r="K156" s="19" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="L156" s="19" t="n">
-        <v>1194</v>
+        <v>1707</v>
       </c>
       <c r="M156" s="19" t="inlineStr"/>
-      <c r="N156" s="19" t="inlineStr"/>
-      <c r="O156" s="19" t="inlineStr"/>
-      <c r="P156" s="19" t="inlineStr"/>
+      <c r="N156" s="19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O156" s="19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P156" s="19" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Q156" s="19" t="n">
-        <v>3.63</v>
+        <v>4.39</v>
       </c>
       <c r="R156" s="19" t="n">
-        <v>970</v>
+        <v>229</v>
       </c>
       <c r="S156" s="22" t="inlineStr">
         <is>
@@ -6118,710 +6155,710 @@
     <row r="157" ht="18" customHeight="1">
       <c r="B157" s="18" t="inlineStr">
         <is>
-          <t>Macbook</t>
+          <t>Protector Termico</t>
         </is>
       </c>
       <c r="C157" s="19" t="n">
-        <v>11375</v>
+        <v>12312</v>
       </c>
       <c r="D157" s="19" t="n">
-        <v>24203</v>
+        <v>41733</v>
       </c>
       <c r="E157" s="19" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="F157" s="20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G157" s="21" t="n">
-        <v>4</v>
-      </c>
-      <c r="H157" s="22" t="inlineStr">
-        <is>
-          <t>+50%</t>
+        <v>14</v>
+      </c>
+      <c r="H157" s="24" t="inlineStr">
+        <is>
+          <t>-43%</t>
         </is>
       </c>
       <c r="I157" s="23" t="n">
-        <v>41316</v>
+        <v>54972</v>
       </c>
       <c r="J157" s="23" t="n">
-        <v>6886</v>
+        <v>6871</v>
       </c>
       <c r="K157" s="19" t="n">
-        <v>1.38</v>
+        <v>0.62</v>
       </c>
       <c r="L157" s="19" t="n">
-        <v>1707</v>
+        <v>1317</v>
       </c>
       <c r="M157" s="19" t="inlineStr"/>
       <c r="N157" s="19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O157" s="19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P157" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q157" s="19" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="R157" s="19" t="n">
+        <v>153</v>
+      </c>
+      <c r="S157" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="18" customHeight="1">
+      <c r="B158" s="32" t="inlineStr">
+        <is>
+          <t>Nuevos difusores</t>
+        </is>
+      </c>
+      <c r="C158" s="33" t="n">
+        <v>16523</v>
+      </c>
+      <c r="D158" s="33" t="n">
+        <v>43682</v>
+      </c>
+      <c r="E158" s="33" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F158" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G158" s="35" t="n">
+        <v>35</v>
+      </c>
+      <c r="H158" s="36" t="inlineStr">
+        <is>
+          <t>-91%</t>
+        </is>
+      </c>
+      <c r="I158" s="37" t="n">
+        <v>67668</v>
+      </c>
+      <c r="J158" s="37" t="n">
+        <v>22556</v>
+      </c>
+      <c r="K158" s="33" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="L158" s="33" t="n">
+        <v>1549</v>
+      </c>
+      <c r="M158" s="33" t="inlineStr"/>
+      <c r="N158" s="33" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O158" s="33" t="n">
         <v>1.4</v>
       </c>
-      <c r="O157" s="19" t="n">
+      <c r="P158" s="33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q158" s="33" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="R158" s="33" t="n">
+        <v>229</v>
+      </c>
+      <c r="S158" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="18" customHeight="1">
+      <c r="B159" s="6" t="inlineStr">
+        <is>
+          <t>Reel de fragancias</t>
+        </is>
+      </c>
+      <c r="C159" s="7" t="n">
+        <v>189252</v>
+      </c>
+      <c r="D159" s="7" t="n">
+        <v>519325</v>
+      </c>
+      <c r="E159" s="7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F159" s="8" t="n">
+        <v>76</v>
+      </c>
+      <c r="G159" s="9" t="n">
+        <v>104</v>
+      </c>
+      <c r="H159" s="17" t="inlineStr">
+        <is>
+          <t>-27%</t>
+        </is>
+      </c>
+      <c r="I159" s="11" t="n">
+        <v>785629</v>
+      </c>
+      <c r="J159" s="11" t="n">
+        <v>10337</v>
+      </c>
+      <c r="K159" s="7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="L159" s="7" t="n">
+        <v>1512</v>
+      </c>
+      <c r="M159" s="7" t="inlineStr"/>
+      <c r="N159" s="7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O159" s="7" t="n">
         <v>0.8</v>
       </c>
-      <c r="P157" s="19" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q157" s="19" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="R157" s="19" t="n">
-        <v>229</v>
-      </c>
-      <c r="S157" s="22" t="inlineStr">
+      <c r="P159" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q159" s="7" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="R159" s="7" t="n">
+        <v>4120</v>
+      </c>
+      <c r="S159" s="12" t="inlineStr">
+        <is>
+          <t>🔍 REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="18" customHeight="1">
+      <c r="B160" s="18" t="inlineStr">
+        <is>
+          <t>Imagen Bubble gum</t>
+        </is>
+      </c>
+      <c r="C160" s="19" t="n">
+        <v>25328</v>
+      </c>
+      <c r="D160" s="19" t="n">
+        <v>77421</v>
+      </c>
+      <c r="E160" s="19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F160" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="G160" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="H160" s="24" t="inlineStr">
+        <is>
+          <t>-40%</t>
+        </is>
+      </c>
+      <c r="I160" s="23" t="n">
+        <v>100077</v>
+      </c>
+      <c r="J160" s="23" t="n">
+        <v>6671</v>
+      </c>
+      <c r="K160" s="19" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="L160" s="19" t="n">
+        <v>1292</v>
+      </c>
+      <c r="M160" s="19" t="inlineStr"/>
+      <c r="N160" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O160" s="19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P160" s="19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q160" s="19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="R160" s="19" t="n">
+        <v>466</v>
+      </c>
+      <c r="S160" s="22" t="inlineStr">
         <is>
           <t>✅ OK</t>
         </is>
       </c>
     </row>
-    <row r="158" ht="18" customHeight="1">
-      <c r="B158" s="18" t="inlineStr">
-        <is>
-          <t>Protector Termico</t>
-        </is>
-      </c>
-      <c r="C158" s="19" t="n">
-        <v>12312</v>
-      </c>
-      <c r="D158" s="19" t="n">
-        <v>41733</v>
-      </c>
-      <c r="E158" s="19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="F158" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="G158" s="21" t="n">
-        <v>14</v>
-      </c>
-      <c r="H158" s="24" t="inlineStr">
+    <row r="161" ht="18" customHeight="1">
+      <c r="B161" s="6" t="inlineStr">
+        <is>
+          <t>Imagen Gato</t>
+        </is>
+      </c>
+      <c r="C161" s="7" t="n">
+        <v>17097</v>
+      </c>
+      <c r="D161" s="7" t="n">
+        <v>39152</v>
+      </c>
+      <c r="E161" s="7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F161" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G161" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="H161" s="17" t="inlineStr">
         <is>
           <t>-43%</t>
         </is>
       </c>
-      <c r="I158" s="23" t="n">
-        <v>54972</v>
-      </c>
-      <c r="J158" s="23" t="n">
-        <v>6871</v>
-      </c>
-      <c r="K158" s="19" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="L158" s="19" t="n">
-        <v>1317</v>
-      </c>
-      <c r="M158" s="19" t="inlineStr"/>
-      <c r="N158" s="19" t="n">
+      <c r="I161" s="11" t="n">
+        <v>68171</v>
+      </c>
+      <c r="J161" s="11" t="n">
+        <v>17042</v>
+      </c>
+      <c r="K161" s="7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="L161" s="7" t="n">
+        <v>1741</v>
+      </c>
+      <c r="M161" s="7" t="inlineStr"/>
+      <c r="N161" s="7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O161" s="7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P161" s="7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q161" s="7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R161" s="7" t="n">
+        <v>311</v>
+      </c>
+      <c r="S161" s="12" t="inlineStr">
+        <is>
+          <t>🔍 REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="18" customHeight="1">
+      <c r="B162" s="18" t="inlineStr">
+        <is>
+          <t>Carrusel Sun Kissed</t>
+        </is>
+      </c>
+      <c r="C162" s="19" t="n">
+        <v>8843</v>
+      </c>
+      <c r="D162" s="19" t="n">
+        <v>19060</v>
+      </c>
+      <c r="E162" s="19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F162" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="G162" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="H162" s="24" t="inlineStr">
+        <is>
+          <t>-57%</t>
+        </is>
+      </c>
+      <c r="I162" s="23" t="n">
+        <v>23636</v>
+      </c>
+      <c r="J162" s="23" t="n">
+        <v>7878</v>
+      </c>
+      <c r="K162" s="19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L162" s="19" t="n">
+        <v>1240</v>
+      </c>
+      <c r="M162" s="19" t="inlineStr"/>
+      <c r="N162" s="19" t="inlineStr"/>
+      <c r="O162" s="19" t="inlineStr"/>
+      <c r="P162" s="19" t="inlineStr"/>
+      <c r="Q162" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="R162" s="19" t="n">
+        <v>132</v>
+      </c>
+      <c r="S162" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="18" customHeight="1">
+      <c r="B163" s="25" t="inlineStr">
+        <is>
+          <t>Reel cafetería</t>
+        </is>
+      </c>
+      <c r="C163" s="26" t="n">
+        <v>3530</v>
+      </c>
+      <c r="D163" s="26" t="n">
+        <v>6221</v>
+      </c>
+      <c r="E163" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F163" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="G163" s="28" t="n">
+        <v>88</v>
+      </c>
+      <c r="H163" s="29" t="inlineStr">
+        <is>
+          <t>-97%</t>
+        </is>
+      </c>
+      <c r="I163" s="30" t="n">
+        <v>15267</v>
+      </c>
+      <c r="J163" s="30" t="n">
+        <v>5089</v>
+      </c>
+      <c r="K163" s="26" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="L163" s="26" t="n">
+        <v>2454</v>
+      </c>
+      <c r="M163" s="26" t="inlineStr"/>
+      <c r="N163" s="26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O163" s="26" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P163" s="26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q163" s="26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R163" s="26" t="n">
+        <v>77</v>
+      </c>
+      <c r="S163" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="18" customHeight="1">
+      <c r="B164" s="18" t="inlineStr">
+        <is>
+          <t>Imagen Cotton Vlabel</t>
+        </is>
+      </c>
+      <c r="C164" s="19" t="n">
+        <v>75025</v>
+      </c>
+      <c r="D164" s="19" t="n">
+        <v>202418</v>
+      </c>
+      <c r="E164" s="19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F164" s="20" t="n">
+        <v>38</v>
+      </c>
+      <c r="G164" s="21" t="n">
+        <v>120</v>
+      </c>
+      <c r="H164" s="24" t="inlineStr">
+        <is>
+          <t>-68%</t>
+        </is>
+      </c>
+      <c r="I164" s="23" t="n">
+        <v>293090</v>
+      </c>
+      <c r="J164" s="23" t="n">
+        <v>7712</v>
+      </c>
+      <c r="K164" s="19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="L164" s="19" t="n">
+        <v>1447</v>
+      </c>
+      <c r="M164" s="19" t="inlineStr"/>
+      <c r="N164" s="19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O164" s="19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P164" s="19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q164" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="R164" s="19" t="n">
+        <v>1585</v>
+      </c>
+      <c r="S164" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="18" customHeight="1">
+      <c r="B165" s="32" t="inlineStr">
+        <is>
+          <t>Bye Bye Aroma</t>
+        </is>
+      </c>
+      <c r="C165" s="33" t="n">
+        <v>4867</v>
+      </c>
+      <c r="D165" s="33" t="n">
+        <v>9919</v>
+      </c>
+      <c r="E165" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F165" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G165" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="H165" s="36" t="inlineStr">
+        <is>
+          <t>-83%</t>
+        </is>
+      </c>
+      <c r="I165" s="37" t="n">
+        <v>18421</v>
+      </c>
+      <c r="J165" s="37" t="n">
+        <v>18421</v>
+      </c>
+      <c r="K165" s="33" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L165" s="33" t="n">
+        <v>1857</v>
+      </c>
+      <c r="M165" s="33" t="inlineStr"/>
+      <c r="N165" s="33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O165" s="33" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P165" s="33" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q165" s="33" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="R165" s="33" t="n">
+        <v>48</v>
+      </c>
+      <c r="S165" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="18" customHeight="1">
+      <c r="B166" s="25" t="inlineStr">
+        <is>
+          <t>Cremas Sun Kissed</t>
+        </is>
+      </c>
+      <c r="C166" s="26" t="n">
+        <v>16660</v>
+      </c>
+      <c r="D166" s="26" t="n">
+        <v>37965</v>
+      </c>
+      <c r="E166" s="26" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F166" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="G166" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="H166" s="29" t="inlineStr">
+        <is>
+          <t>-50%</t>
+        </is>
+      </c>
+      <c r="I166" s="30" t="n">
+        <v>68249</v>
+      </c>
+      <c r="J166" s="30" t="n">
+        <v>5687</v>
+      </c>
+      <c r="K166" s="26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L166" s="26" t="n">
+        <v>1797</v>
+      </c>
+      <c r="M166" s="26" t="inlineStr"/>
+      <c r="N166" s="26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O166" s="26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P166" s="26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q166" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="R166" s="26" t="n">
+        <v>363</v>
+      </c>
+      <c r="S166" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="18" customHeight="1">
+      <c r="B167" s="6" t="inlineStr">
+        <is>
+          <t>Home Spray</t>
+        </is>
+      </c>
+      <c r="C167" s="7" t="n">
+        <v>223129</v>
+      </c>
+      <c r="D167" s="7" t="n">
+        <v>738548</v>
+      </c>
+      <c r="E167" s="7" t="n">
         <v>3.3</v>
       </c>
-      <c r="O158" s="19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="P158" s="19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q158" s="19" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="R158" s="19" t="n">
-        <v>153</v>
-      </c>
-      <c r="S158" s="22" t="inlineStr">
-        <is>
-          <t>✅ OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="18" customHeight="1">
-      <c r="B159" s="32" t="inlineStr">
-        <is>
-          <t>Nuevos difusores</t>
-        </is>
-      </c>
-      <c r="C159" s="33" t="n">
-        <v>16523</v>
-      </c>
-      <c r="D159" s="33" t="n">
-        <v>43682</v>
-      </c>
-      <c r="E159" s="33" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="F159" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="G159" s="35" t="n">
-        <v>35</v>
-      </c>
-      <c r="H159" s="36" t="inlineStr">
-        <is>
-          <t>-91%</t>
-        </is>
-      </c>
-      <c r="I159" s="37" t="n">
-        <v>67668</v>
-      </c>
-      <c r="J159" s="37" t="n">
-        <v>22556</v>
-      </c>
-      <c r="K159" s="33" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="L159" s="33" t="n">
-        <v>1549</v>
-      </c>
-      <c r="M159" s="33" t="inlineStr"/>
-      <c r="N159" s="33" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O159" s="33" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P159" s="33" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Q159" s="33" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="R159" s="33" t="n">
-        <v>229</v>
-      </c>
-      <c r="S159" s="36" t="inlineStr">
-        <is>
-          <t>⛔ PAUSAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="160" ht="18" customHeight="1">
-      <c r="B160" s="6" t="inlineStr">
-        <is>
-          <t>Reel de fragancias</t>
-        </is>
-      </c>
-      <c r="C160" s="7" t="n">
-        <v>189252</v>
-      </c>
-      <c r="D160" s="7" t="n">
-        <v>519325</v>
-      </c>
-      <c r="E160" s="7" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="F160" s="8" t="n">
-        <v>76</v>
-      </c>
-      <c r="G160" s="9" t="n">
-        <v>104</v>
-      </c>
-      <c r="H160" s="17" t="inlineStr">
-        <is>
-          <t>-27%</t>
-        </is>
-      </c>
-      <c r="I160" s="11" t="n">
-        <v>785629</v>
-      </c>
-      <c r="J160" s="11" t="n">
-        <v>10337</v>
-      </c>
-      <c r="K160" s="7" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="L160" s="7" t="n">
-        <v>1512</v>
-      </c>
-      <c r="M160" s="7" t="inlineStr"/>
-      <c r="N160" s="7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="O160" s="7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="P160" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q160" s="7" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="R160" s="7" t="n">
-        <v>4120</v>
-      </c>
-      <c r="S160" s="12" t="inlineStr">
+      <c r="F167" s="8" t="n">
+        <v>91</v>
+      </c>
+      <c r="G167" s="9" t="n">
+        <v>126</v>
+      </c>
+      <c r="H167" s="17" t="inlineStr">
+        <is>
+          <t>-28%</t>
+        </is>
+      </c>
+      <c r="I167" s="11" t="n">
+        <v>1186817</v>
+      </c>
+      <c r="J167" s="11" t="n">
+        <v>13041</v>
+      </c>
+      <c r="K167" s="7" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="L167" s="7" t="n">
+        <v>1606</v>
+      </c>
+      <c r="M167" s="7" t="inlineStr"/>
+      <c r="N167" s="7" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O167" s="7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="P167" s="7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q167" s="7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R167" s="7" t="n">
+        <v>5319</v>
+      </c>
+      <c r="S167" s="12" t="inlineStr">
         <is>
           <t>🔍 REVISAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="161" ht="18" customHeight="1">
-      <c r="B161" s="18" t="inlineStr">
-        <is>
-          <t>Imagen Bubble gum</t>
-        </is>
-      </c>
-      <c r="C161" s="19" t="n">
-        <v>25328</v>
-      </c>
-      <c r="D161" s="19" t="n">
-        <v>77421</v>
-      </c>
-      <c r="E161" s="19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="F161" s="20" t="n">
-        <v>15</v>
-      </c>
-      <c r="G161" s="21" t="n">
-        <v>25</v>
-      </c>
-      <c r="H161" s="24" t="inlineStr">
-        <is>
-          <t>-40%</t>
-        </is>
-      </c>
-      <c r="I161" s="23" t="n">
-        <v>100077</v>
-      </c>
-      <c r="J161" s="23" t="n">
-        <v>6671</v>
-      </c>
-      <c r="K161" s="19" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="L161" s="19" t="n">
-        <v>1292</v>
-      </c>
-      <c r="M161" s="19" t="inlineStr"/>
-      <c r="N161" s="19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O161" s="19" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="P161" s="19" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q161" s="19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="R161" s="19" t="n">
-        <v>466</v>
-      </c>
-      <c r="S161" s="22" t="inlineStr">
-        <is>
-          <t>✅ OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="162" ht="18" customHeight="1">
-      <c r="B162" s="6" t="inlineStr">
-        <is>
-          <t>Imagen Gato</t>
-        </is>
-      </c>
-      <c r="C162" s="7" t="n">
-        <v>17097</v>
-      </c>
-      <c r="D162" s="7" t="n">
-        <v>39152</v>
-      </c>
-      <c r="E162" s="7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="F162" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="G162" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H162" s="17" t="inlineStr">
-        <is>
-          <t>-43%</t>
-        </is>
-      </c>
-      <c r="I162" s="11" t="n">
-        <v>68171</v>
-      </c>
-      <c r="J162" s="11" t="n">
-        <v>17042</v>
-      </c>
-      <c r="K162" s="7" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="L162" s="7" t="n">
-        <v>1741</v>
-      </c>
-      <c r="M162" s="7" t="inlineStr"/>
-      <c r="N162" s="7" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="O162" s="7" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="P162" s="7" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q162" s="7" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="R162" s="7" t="n">
-        <v>311</v>
-      </c>
-      <c r="S162" s="12" t="inlineStr">
-        <is>
-          <t>🔍 REVISAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="163" ht="18" customHeight="1">
-      <c r="B163" s="18" t="inlineStr">
-        <is>
-          <t>Carrusel Sun Kissed</t>
-        </is>
-      </c>
-      <c r="C163" s="19" t="n">
-        <v>8843</v>
-      </c>
-      <c r="D163" s="19" t="n">
-        <v>19060</v>
-      </c>
-      <c r="E163" s="19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="F163" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="G163" s="21" t="n">
-        <v>7</v>
-      </c>
-      <c r="H163" s="24" t="inlineStr">
-        <is>
-          <t>-57%</t>
-        </is>
-      </c>
-      <c r="I163" s="23" t="n">
-        <v>23636</v>
-      </c>
-      <c r="J163" s="23" t="n">
-        <v>7878</v>
-      </c>
-      <c r="K163" s="19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="L163" s="19" t="n">
-        <v>1240</v>
-      </c>
-      <c r="M163" s="19" t="inlineStr"/>
-      <c r="N163" s="19" t="inlineStr"/>
-      <c r="O163" s="19" t="inlineStr"/>
-      <c r="P163" s="19" t="inlineStr"/>
-      <c r="Q163" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="R163" s="19" t="n">
-        <v>132</v>
-      </c>
-      <c r="S163" s="22" t="inlineStr">
-        <is>
-          <t>✅ OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="164" ht="18" customHeight="1">
-      <c r="B164" s="25" t="inlineStr">
-        <is>
-          <t>Reel cafetería</t>
-        </is>
-      </c>
-      <c r="C164" s="26" t="n">
-        <v>3530</v>
-      </c>
-      <c r="D164" s="26" t="n">
-        <v>6221</v>
-      </c>
-      <c r="E164" s="26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F164" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="G164" s="28" t="n">
-        <v>88</v>
-      </c>
-      <c r="H164" s="29" t="inlineStr">
-        <is>
-          <t>-97%</t>
-        </is>
-      </c>
-      <c r="I164" s="30" t="n">
-        <v>15267</v>
-      </c>
-      <c r="J164" s="30" t="n">
-        <v>5089</v>
-      </c>
-      <c r="K164" s="26" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="L164" s="26" t="n">
-        <v>2454</v>
-      </c>
-      <c r="M164" s="26" t="inlineStr"/>
-      <c r="N164" s="26" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O164" s="26" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="P164" s="26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q164" s="26" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R164" s="26" t="n">
-        <v>77</v>
-      </c>
-      <c r="S164" s="31" t="inlineStr">
-        <is>
-          <t>🏆 GANADOR</t>
-        </is>
-      </c>
-    </row>
-    <row r="165" ht="18" customHeight="1">
-      <c r="B165" s="18" t="inlineStr">
-        <is>
-          <t>Imagen Cotton Vlabel</t>
-        </is>
-      </c>
-      <c r="C165" s="19" t="n">
-        <v>75025</v>
-      </c>
-      <c r="D165" s="19" t="n">
-        <v>202418</v>
-      </c>
-      <c r="E165" s="19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="F165" s="20" t="n">
-        <v>38</v>
-      </c>
-      <c r="G165" s="21" t="n">
-        <v>120</v>
-      </c>
-      <c r="H165" s="24" t="inlineStr">
-        <is>
-          <t>-68%</t>
-        </is>
-      </c>
-      <c r="I165" s="23" t="n">
-        <v>293090</v>
-      </c>
-      <c r="J165" s="23" t="n">
-        <v>7712</v>
-      </c>
-      <c r="K165" s="19" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="L165" s="19" t="n">
-        <v>1447</v>
-      </c>
-      <c r="M165" s="19" t="inlineStr"/>
-      <c r="N165" s="19" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="O165" s="19" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="P165" s="19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q165" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="R165" s="19" t="n">
-        <v>1585</v>
-      </c>
-      <c r="S165" s="22" t="inlineStr">
-        <is>
-          <t>✅ OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="166" ht="18" customHeight="1">
-      <c r="B166" s="32" t="inlineStr">
-        <is>
-          <t>Bye Bye Aroma</t>
-        </is>
-      </c>
-      <c r="C166" s="33" t="n">
-        <v>4867</v>
-      </c>
-      <c r="D166" s="33" t="n">
-        <v>9919</v>
-      </c>
-      <c r="E166" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="F166" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="G166" s="35" t="n">
-        <v>6</v>
-      </c>
-      <c r="H166" s="36" t="inlineStr">
-        <is>
-          <t>-83%</t>
-        </is>
-      </c>
-      <c r="I166" s="37" t="n">
-        <v>18421</v>
-      </c>
-      <c r="J166" s="37" t="n">
-        <v>18421</v>
-      </c>
-      <c r="K166" s="33" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="L166" s="33" t="n">
-        <v>1857</v>
-      </c>
-      <c r="M166" s="33" t="inlineStr"/>
-      <c r="N166" s="33" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O166" s="33" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P166" s="33" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q166" s="33" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="R166" s="33" t="n">
-        <v>48</v>
-      </c>
-      <c r="S166" s="36" t="inlineStr">
-        <is>
-          <t>⛔ PAUSAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" ht="18" customHeight="1">
-      <c r="B167" s="25" t="inlineStr">
-        <is>
-          <t>Cremas Sun Kissed</t>
-        </is>
-      </c>
-      <c r="C167" s="26" t="n">
-        <v>16660</v>
-      </c>
-      <c r="D167" s="26" t="n">
-        <v>37965</v>
-      </c>
-      <c r="E167" s="26" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="F167" s="27" t="n">
-        <v>12</v>
-      </c>
-      <c r="G167" s="28" t="n">
-        <v>24</v>
-      </c>
-      <c r="H167" s="29" t="inlineStr">
-        <is>
-          <t>-50%</t>
-        </is>
-      </c>
-      <c r="I167" s="30" t="n">
-        <v>68249</v>
-      </c>
-      <c r="J167" s="30" t="n">
-        <v>5687</v>
-      </c>
-      <c r="K167" s="26" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="L167" s="26" t="n">
-        <v>1797</v>
-      </c>
-      <c r="M167" s="26" t="inlineStr"/>
-      <c r="N167" s="26" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O167" s="26" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="P167" s="26" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q167" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="R167" s="26" t="n">
-        <v>363</v>
-      </c>
-      <c r="S167" s="31" t="inlineStr">
-        <is>
-          <t>🏆 GANADOR</t>
         </is>
       </c>
     </row>
     <row r="168" ht="18" customHeight="1">
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>Home Spray</t>
+          <t>Rutina 4 pasos 2.0</t>
         </is>
       </c>
       <c r="C168" s="7" t="n">
-        <v>223129</v>
+        <v>47354</v>
       </c>
       <c r="D168" s="7" t="n">
-        <v>738548</v>
+        <v>139806</v>
       </c>
       <c r="E168" s="7" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="F168" s="8" t="n">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="G168" s="9" t="n">
-        <v>126</v>
+        <v>36</v>
       </c>
       <c r="H168" s="17" t="inlineStr">
         <is>
-          <t>-28%</t>
+          <t>-47%</t>
         </is>
       </c>
       <c r="I168" s="11" t="n">
-        <v>1186817</v>
+        <v>261897</v>
       </c>
       <c r="J168" s="11" t="n">
-        <v>13041</v>
+        <v>13784</v>
       </c>
       <c r="K168" s="7" t="n">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="L168" s="7" t="n">
-        <v>1606</v>
+        <v>1873</v>
       </c>
       <c r="M168" s="7" t="inlineStr"/>
       <c r="N168" s="7" t="n">
-        <v>6.7</v>
+        <v>1.3</v>
       </c>
       <c r="O168" s="7" t="n">
-        <v>4.7</v>
+        <v>0.8</v>
       </c>
       <c r="P168" s="7" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="Q168" s="7" t="n">
-        <v>2.45</v>
+        <v>2.11</v>
       </c>
       <c r="R168" s="7" t="n">
-        <v>5319</v>
+        <v>1312</v>
       </c>
       <c r="S168" s="12" t="inlineStr">
         <is>
@@ -6830,116 +6867,108 @@
       </c>
     </row>
     <row r="169" ht="18" customHeight="1">
-      <c r="B169" s="6" t="inlineStr">
-        <is>
-          <t>Rutina 4 pasos 2.0</t>
-        </is>
-      </c>
-      <c r="C169" s="7" t="n">
-        <v>47354</v>
-      </c>
-      <c r="D169" s="7" t="n">
-        <v>139806</v>
-      </c>
-      <c r="E169" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="F169" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="G169" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="H169" s="17" t="inlineStr">
-        <is>
-          <t>-47%</t>
-        </is>
-      </c>
-      <c r="I169" s="11" t="n">
-        <v>261897</v>
-      </c>
-      <c r="J169" s="11" t="n">
-        <v>13784</v>
-      </c>
-      <c r="K169" s="7" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="L169" s="7" t="n">
-        <v>1873</v>
-      </c>
-      <c r="M169" s="7" t="inlineStr"/>
-      <c r="N169" s="7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="O169" s="7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="P169" s="7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q169" s="7" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="R169" s="7" t="n">
-        <v>1312</v>
-      </c>
-      <c r="S169" s="12" t="inlineStr">
-        <is>
-          <t>🔍 REVISAR</t>
+      <c r="B169" s="32" t="inlineStr">
+        <is>
+          <t>UGC Soft Milk Febrero</t>
+        </is>
+      </c>
+      <c r="C169" s="33" t="n">
+        <v>1912</v>
+      </c>
+      <c r="D169" s="33" t="n">
+        <v>3069</v>
+      </c>
+      <c r="E169" s="33" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F169" s="34" t="n">
+        <v>27</v>
+      </c>
+      <c r="G169" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H169" s="63" t="inlineStr">
+        <is>
+          <t>+2600%</t>
+        </is>
+      </c>
+      <c r="I169" s="37" t="n">
+        <v>8931</v>
+      </c>
+      <c r="J169" s="37" t="n">
+        <v>330</v>
+      </c>
+      <c r="K169" s="33" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="L169" s="33" t="n">
+        <v>2910</v>
+      </c>
+      <c r="M169" s="33" t="inlineStr"/>
+      <c r="N169" s="33" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="O169" s="33" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P169" s="33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q169" s="33" t="inlineStr"/>
+      <c r="R169" s="33" t="n">
+        <v>20</v>
+      </c>
+      <c r="S169" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
         </is>
       </c>
     </row>
     <row r="170" ht="18" customHeight="1">
       <c r="B170" s="32" t="inlineStr">
         <is>
-          <t>UGC Soft Milk Febrero</t>
+          <t>Go Paw Carrusel Mascotas</t>
         </is>
       </c>
       <c r="C170" s="33" t="n">
-        <v>1912</v>
+        <v>948</v>
       </c>
       <c r="D170" s="33" t="n">
-        <v>3069</v>
+        <v>1379</v>
       </c>
       <c r="E170" s="33" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="F170" s="34" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="G170" s="35" t="n">
         <v>1</v>
       </c>
       <c r="H170" s="63" t="inlineStr">
         <is>
-          <t>+2600%</t>
+          <t>+800%</t>
         </is>
       </c>
       <c r="I170" s="37" t="n">
-        <v>8931</v>
+        <v>3176</v>
       </c>
       <c r="J170" s="37" t="n">
-        <v>330</v>
+        <v>352</v>
       </c>
       <c r="K170" s="33" t="n">
-        <v>1.47</v>
+        <v>0.73</v>
       </c>
       <c r="L170" s="33" t="n">
-        <v>2910</v>
+        <v>2303</v>
       </c>
       <c r="M170" s="33" t="inlineStr"/>
-      <c r="N170" s="33" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="O170" s="33" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P170" s="33" t="n">
-        <v>1.7</v>
-      </c>
+      <c r="N170" s="33" t="inlineStr"/>
+      <c r="O170" s="33" t="inlineStr"/>
+      <c r="P170" s="33" t="inlineStr"/>
       <c r="Q170" s="33" t="inlineStr"/>
       <c r="R170" s="33" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="S170" s="36" t="inlineStr">
         <is>
@@ -6950,48 +6979,54 @@
     <row r="171" ht="18" customHeight="1">
       <c r="B171" s="32" t="inlineStr">
         <is>
-          <t>Go Paw Carrusel Mascotas</t>
+          <t>Aceite Capilar Go Hair</t>
         </is>
       </c>
       <c r="C171" s="33" t="n">
-        <v>948</v>
+        <v>1318</v>
       </c>
       <c r="D171" s="33" t="n">
-        <v>1379</v>
+        <v>2028</v>
       </c>
       <c r="E171" s="33" t="n">
         <v>1.5</v>
       </c>
       <c r="F171" s="34" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="G171" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="H171" s="63" t="inlineStr">
-        <is>
-          <t>+800%</t>
+        <v>23</v>
+      </c>
+      <c r="H171" s="36" t="inlineStr">
+        <is>
+          <t>-9%</t>
         </is>
       </c>
       <c r="I171" s="37" t="n">
-        <v>3176</v>
+        <v>5378</v>
       </c>
       <c r="J171" s="37" t="n">
-        <v>352</v>
+        <v>256</v>
       </c>
       <c r="K171" s="33" t="n">
-        <v>0.73</v>
+        <v>1.53</v>
       </c>
       <c r="L171" s="33" t="n">
-        <v>2303</v>
+        <v>2651</v>
       </c>
       <c r="M171" s="33" t="inlineStr"/>
-      <c r="N171" s="33" t="inlineStr"/>
-      <c r="O171" s="33" t="inlineStr"/>
-      <c r="P171" s="33" t="inlineStr"/>
+      <c r="N171" s="33" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="O171" s="33" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P171" s="33" t="n">
+        <v>3.6</v>
+      </c>
       <c r="Q171" s="33" t="inlineStr"/>
       <c r="R171" s="33" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="S171" s="36" t="inlineStr">
         <is>
@@ -7000,564 +7035,566 @@
       </c>
     </row>
     <row r="172" ht="18" customHeight="1">
-      <c r="B172" s="32" t="inlineStr">
-        <is>
-          <t>Aceite Capilar Go Hair</t>
-        </is>
-      </c>
-      <c r="C172" s="33" t="n">
-        <v>1318</v>
-      </c>
-      <c r="D172" s="33" t="n">
-        <v>2028</v>
-      </c>
-      <c r="E172" s="33" t="n">
+      <c r="B172" s="18" t="inlineStr">
+        <is>
+          <t>Kit Cuidado Capilar</t>
+        </is>
+      </c>
+      <c r="C172" s="19" t="n">
+        <v>10726</v>
+      </c>
+      <c r="D172" s="19" t="n">
+        <v>21083</v>
+      </c>
+      <c r="E172" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F172" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="G172" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="H172" s="24" t="inlineStr">
+        <is>
+          <t>-14%</t>
+        </is>
+      </c>
+      <c r="I172" s="23" t="n">
+        <v>49131</v>
+      </c>
+      <c r="J172" s="23" t="n">
+        <v>8188</v>
+      </c>
+      <c r="K172" s="19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="L172" s="19" t="n">
+        <v>2330</v>
+      </c>
+      <c r="M172" s="19" t="inlineStr"/>
+      <c r="N172" s="19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O172" s="19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P172" s="19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q172" s="19" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="R172" s="19" t="n">
+        <v>203</v>
+      </c>
+      <c r="S172" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="18" customHeight="1">
+      <c r="B173" s="32" t="inlineStr">
+        <is>
+          <t>Go Paw Wild Berries y Cotton Candy</t>
+        </is>
+      </c>
+      <c r="C173" s="33" t="n">
+        <v>18992</v>
+      </c>
+      <c r="D173" s="33" t="n">
+        <v>36622</v>
+      </c>
+      <c r="E173" s="33" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F173" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="G173" s="35" t="n">
+        <v>15</v>
+      </c>
+      <c r="H173" s="36" t="inlineStr">
+        <is>
+          <t>-73%</t>
+        </is>
+      </c>
+      <c r="I173" s="37" t="n">
+        <v>93385</v>
+      </c>
+      <c r="J173" s="37" t="n">
+        <v>23346</v>
+      </c>
+      <c r="K173" s="33" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="L173" s="33" t="n">
+        <v>2549</v>
+      </c>
+      <c r="M173" s="33" t="inlineStr"/>
+      <c r="N173" s="33" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O173" s="33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P173" s="33" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q173" s="33" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R173" s="33" t="n">
+        <v>207</v>
+      </c>
+      <c r="S173" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="18" customHeight="1">
+      <c r="B174" s="6" t="inlineStr">
+        <is>
+          <t>Protector Termico Pistacho Caramelo</t>
+        </is>
+      </c>
+      <c r="C174" s="7" t="n">
+        <v>73692</v>
+      </c>
+      <c r="D174" s="7" t="n">
+        <v>169162</v>
+      </c>
+      <c r="E174" s="7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F174" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="G174" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="H174" s="17" t="inlineStr">
+        <is>
+          <t>-40%</t>
+        </is>
+      </c>
+      <c r="I174" s="11" t="n">
+        <v>261470</v>
+      </c>
+      <c r="J174" s="11" t="n">
+        <v>17431</v>
+      </c>
+      <c r="K174" s="7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L174" s="7" t="n">
+        <v>1545</v>
+      </c>
+      <c r="M174" s="7" t="inlineStr"/>
+      <c r="N174" s="7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O174" s="7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P174" s="7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q174" s="7" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="R174" s="7" t="n">
+        <v>905</v>
+      </c>
+      <c r="S174" s="12" t="inlineStr">
+        <is>
+          <t>🔍 REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="18" customHeight="1">
+      <c r="B175" s="25" t="inlineStr">
+        <is>
+          <t>Go Paw @Juliana Carrascal</t>
+        </is>
+      </c>
+      <c r="C175" s="26" t="n">
+        <v>1537</v>
+      </c>
+      <c r="D175" s="26" t="n">
+        <v>2275</v>
+      </c>
+      <c r="E175" s="26" t="n">
         <v>1.5</v>
       </c>
-      <c r="F172" s="34" t="n">
+      <c r="F175" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G175" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H175" s="31" t="inlineStr">
+        <is>
+          <t>+100%</t>
+        </is>
+      </c>
+      <c r="I175" s="30" t="n">
+        <v>5473</v>
+      </c>
+      <c r="J175" s="30" t="n">
+        <v>2736</v>
+      </c>
+      <c r="K175" s="26" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="L175" s="26" t="n">
+        <v>2405</v>
+      </c>
+      <c r="M175" s="26" t="inlineStr"/>
+      <c r="N175" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="O175" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="P175" s="26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q175" s="26" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="R175" s="26" t="n">
+        <v>17</v>
+      </c>
+      <c r="S175" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="18" customHeight="1">
+      <c r="B176" s="6" t="inlineStr">
+        <is>
+          <t>Home Spray @vanusallorenzo</t>
+        </is>
+      </c>
+      <c r="C176" s="7" t="n">
+        <v>56581</v>
+      </c>
+      <c r="D176" s="7" t="n">
+        <v>133163</v>
+      </c>
+      <c r="E176" s="7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F176" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="G172" s="35" t="n">
-        <v>23</v>
-      </c>
-      <c r="H172" s="36" t="inlineStr">
-        <is>
-          <t>-9%</t>
-        </is>
-      </c>
-      <c r="I172" s="37" t="n">
-        <v>5378</v>
-      </c>
-      <c r="J172" s="37" t="n">
-        <v>256</v>
-      </c>
-      <c r="K172" s="33" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="L172" s="33" t="n">
-        <v>2651</v>
-      </c>
-      <c r="M172" s="33" t="inlineStr"/>
-      <c r="N172" s="33" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O172" s="33" t="n">
+      <c r="G176" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H176" s="10" t="inlineStr">
+        <is>
+          <t>+320%</t>
+        </is>
+      </c>
+      <c r="I176" s="11" t="n">
+        <v>306078</v>
+      </c>
+      <c r="J176" s="11" t="n">
+        <v>14575</v>
+      </c>
+      <c r="K176" s="7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="L176" s="7" t="n">
+        <v>2298</v>
+      </c>
+      <c r="M176" s="7" t="inlineStr"/>
+      <c r="N176" s="7" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="O176" s="7" t="n">
         <v>4.6</v>
       </c>
-      <c r="P172" s="33" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Q172" s="33" t="inlineStr"/>
-      <c r="R172" s="33" t="n">
-        <v>21</v>
-      </c>
-      <c r="S172" s="36" t="inlineStr">
+      <c r="P176" s="7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q176" s="7" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="R176" s="7" t="n">
+        <v>1041</v>
+      </c>
+      <c r="S176" s="12" t="inlineStr">
+        <is>
+          <t>🔍 REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="18" customHeight="1">
+      <c r="B177" s="25" t="inlineStr">
+        <is>
+          <t>BLACK WEEK INICIO</t>
+        </is>
+      </c>
+      <c r="C177" s="26" t="n">
+        <v>87055</v>
+      </c>
+      <c r="D177" s="26" t="n">
+        <v>320312</v>
+      </c>
+      <c r="E177" s="26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F177" s="27" t="n">
+        <v>107</v>
+      </c>
+      <c r="G177" s="28" t="n">
+        <v>28</v>
+      </c>
+      <c r="H177" s="31" t="inlineStr">
+        <is>
+          <t>+282%</t>
+        </is>
+      </c>
+      <c r="I177" s="30" t="n">
+        <v>573332</v>
+      </c>
+      <c r="J177" s="30" t="n">
+        <v>5358</v>
+      </c>
+      <c r="K177" s="26" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="L177" s="26" t="n">
+        <v>1789</v>
+      </c>
+      <c r="M177" s="26" t="inlineStr"/>
+      <c r="N177" s="26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O177" s="26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P177" s="26" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q177" s="26" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="R177" s="26" t="n">
+        <v>2699</v>
+      </c>
+      <c r="S177" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="18" customHeight="1">
+      <c r="B178" s="32" t="inlineStr">
+        <is>
+          <t>Carrusel Post que puedes oler</t>
+        </is>
+      </c>
+      <c r="C178" s="33" t="n">
+        <v>5613</v>
+      </c>
+      <c r="D178" s="33" t="n">
+        <v>11418</v>
+      </c>
+      <c r="E178" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F178" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G178" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H178" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I178" s="37" t="n">
+        <v>21464</v>
+      </c>
+      <c r="J178" s="37" t="n">
+        <v>21464</v>
+      </c>
+      <c r="K178" s="33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L178" s="33" t="n">
+        <v>1879</v>
+      </c>
+      <c r="M178" s="33" t="inlineStr"/>
+      <c r="N178" s="33" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O178" s="33" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P178" s="33" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q178" s="33" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="R178" s="33" t="n">
+        <v>87</v>
+      </c>
+      <c r="S178" s="36" t="inlineStr">
         <is>
           <t>⛔ PAUSAR</t>
         </is>
       </c>
     </row>
-    <row r="173" ht="18" customHeight="1">
-      <c r="B173" s="18" t="inlineStr">
-        <is>
-          <t>Kit Cuidado Capilar</t>
-        </is>
-      </c>
-      <c r="C173" s="19" t="n">
-        <v>10726</v>
-      </c>
-      <c r="D173" s="19" t="n">
-        <v>21083</v>
-      </c>
-      <c r="E173" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="F173" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="G173" s="21" t="n">
-        <v>7</v>
-      </c>
-      <c r="H173" s="24" t="inlineStr">
-        <is>
-          <t>-14%</t>
-        </is>
-      </c>
-      <c r="I173" s="23" t="n">
-        <v>49131</v>
-      </c>
-      <c r="J173" s="23" t="n">
-        <v>8188</v>
-      </c>
-      <c r="K173" s="19" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="L173" s="19" t="n">
-        <v>2330</v>
-      </c>
-      <c r="M173" s="19" t="inlineStr"/>
-      <c r="N173" s="19" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="O173" s="19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P173" s="19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q173" s="19" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="R173" s="19" t="n">
-        <v>203</v>
-      </c>
-      <c r="S173" s="22" t="inlineStr">
-        <is>
-          <t>✅ OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="174" ht="18" customHeight="1">
-      <c r="B174" s="32" t="inlineStr">
-        <is>
-          <t>Go Paw Wild Berries y Cotton Candy</t>
-        </is>
-      </c>
-      <c r="C174" s="33" t="n">
-        <v>18992</v>
-      </c>
-      <c r="D174" s="33" t="n">
-        <v>36622</v>
-      </c>
-      <c r="E174" s="33" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="F174" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="G174" s="35" t="n">
-        <v>15</v>
-      </c>
-      <c r="H174" s="36" t="inlineStr">
-        <is>
-          <t>-73%</t>
-        </is>
-      </c>
-      <c r="I174" s="37" t="n">
-        <v>93385</v>
-      </c>
-      <c r="J174" s="37" t="n">
-        <v>23346</v>
-      </c>
-      <c r="K174" s="33" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="L174" s="33" t="n">
-        <v>2549</v>
-      </c>
-      <c r="M174" s="33" t="inlineStr"/>
-      <c r="N174" s="33" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="O174" s="33" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P174" s="33" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q174" s="33" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="R174" s="33" t="n">
-        <v>207</v>
-      </c>
-      <c r="S174" s="36" t="inlineStr">
+    <row r="179" ht="18" customHeight="1">
+      <c r="B179" s="6" t="inlineStr">
+        <is>
+          <t>Fragancias Picnic</t>
+        </is>
+      </c>
+      <c r="C179" s="7" t="n">
+        <v>24676</v>
+      </c>
+      <c r="D179" s="7" t="n">
+        <v>74073</v>
+      </c>
+      <c r="E179" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F179" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="G179" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H179" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I179" s="11" t="n">
+        <v>134078</v>
+      </c>
+      <c r="J179" s="11" t="n">
+        <v>11173</v>
+      </c>
+      <c r="K179" s="7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="L179" s="7" t="n">
+        <v>1810</v>
+      </c>
+      <c r="M179" s="7" t="inlineStr"/>
+      <c r="N179" s="7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O179" s="7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P179" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q179" s="7" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="R179" s="7" t="n">
+        <v>554</v>
+      </c>
+      <c r="S179" s="12" t="inlineStr">
+        <is>
+          <t>🔍 REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="18" customHeight="1">
+      <c r="B180" s="32" t="inlineStr">
+        <is>
+          <t>Go Paw @melissapaz</t>
+        </is>
+      </c>
+      <c r="C180" s="33" t="n">
+        <v>7601</v>
+      </c>
+      <c r="D180" s="33" t="n">
+        <v>9998</v>
+      </c>
+      <c r="E180" s="33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F180" s="34" t="n">
+        <v>104</v>
+      </c>
+      <c r="G180" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H180" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I180" s="37" t="n">
+        <v>23686</v>
+      </c>
+      <c r="J180" s="37" t="n">
+        <v>227</v>
+      </c>
+      <c r="K180" s="33" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="L180" s="33" t="n">
+        <v>2369</v>
+      </c>
+      <c r="M180" s="33" t="inlineStr"/>
+      <c r="N180" s="33" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="O180" s="33" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P180" s="33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q180" s="33" t="inlineStr"/>
+      <c r="R180" s="33" t="n">
+        <v>95</v>
+      </c>
+      <c r="S180" s="36" t="inlineStr">
         <is>
           <t>⛔ PAUSAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="175" ht="18" customHeight="1">
-      <c r="B175" s="6" t="inlineStr">
-        <is>
-          <t>Protector Termico Pistacho Caramelo</t>
-        </is>
-      </c>
-      <c r="C175" s="7" t="n">
-        <v>73692</v>
-      </c>
-      <c r="D175" s="7" t="n">
-        <v>169162</v>
-      </c>
-      <c r="E175" s="7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="F175" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="G175" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="H175" s="17" t="inlineStr">
-        <is>
-          <t>-40%</t>
-        </is>
-      </c>
-      <c r="I175" s="11" t="n">
-        <v>261470</v>
-      </c>
-      <c r="J175" s="11" t="n">
-        <v>17431</v>
-      </c>
-      <c r="K175" s="7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="L175" s="7" t="n">
-        <v>1545</v>
-      </c>
-      <c r="M175" s="7" t="inlineStr"/>
-      <c r="N175" s="7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O175" s="7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P175" s="7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q175" s="7" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="R175" s="7" t="n">
-        <v>905</v>
-      </c>
-      <c r="S175" s="12" t="inlineStr">
-        <is>
-          <t>🔍 REVISAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="176" ht="18" customHeight="1">
-      <c r="B176" s="25" t="inlineStr">
-        <is>
-          <t>Go Paw @Juliana Carrascal</t>
-        </is>
-      </c>
-      <c r="C176" s="26" t="n">
-        <v>1537</v>
-      </c>
-      <c r="D176" s="26" t="n">
-        <v>2275</v>
-      </c>
-      <c r="E176" s="26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F176" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="G176" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="H176" s="31" t="inlineStr">
-        <is>
-          <t>+100%</t>
-        </is>
-      </c>
-      <c r="I176" s="30" t="n">
-        <v>5473</v>
-      </c>
-      <c r="J176" s="30" t="n">
-        <v>2736</v>
-      </c>
-      <c r="K176" s="26" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="L176" s="26" t="n">
-        <v>2405</v>
-      </c>
-      <c r="M176" s="26" t="inlineStr"/>
-      <c r="N176" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="O176" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="P176" s="26" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q176" s="26" t="n">
-        <v>13.51</v>
-      </c>
-      <c r="R176" s="26" t="n">
-        <v>17</v>
-      </c>
-      <c r="S176" s="31" t="inlineStr">
-        <is>
-          <t>🏆 GANADOR</t>
-        </is>
-      </c>
-    </row>
-    <row r="177" ht="18" customHeight="1">
-      <c r="B177" s="6" t="inlineStr">
-        <is>
-          <t>Home Spray @vanusallorenzo</t>
-        </is>
-      </c>
-      <c r="C177" s="7" t="n">
-        <v>56581</v>
-      </c>
-      <c r="D177" s="7" t="n">
-        <v>133163</v>
-      </c>
-      <c r="E177" s="7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="F177" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="G177" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="H177" s="10" t="inlineStr">
-        <is>
-          <t>+320%</t>
-        </is>
-      </c>
-      <c r="I177" s="11" t="n">
-        <v>306078</v>
-      </c>
-      <c r="J177" s="11" t="n">
-        <v>14575</v>
-      </c>
-      <c r="K177" s="7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="L177" s="7" t="n">
-        <v>2298</v>
-      </c>
-      <c r="M177" s="7" t="inlineStr"/>
-      <c r="N177" s="7" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="O177" s="7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="P177" s="7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Q177" s="7" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="R177" s="7" t="n">
-        <v>1041</v>
-      </c>
-      <c r="S177" s="12" t="inlineStr">
-        <is>
-          <t>🔍 REVISAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="18" customHeight="1">
-      <c r="B178" s="25" t="inlineStr">
-        <is>
-          <t>BLACK WEEK INICIO</t>
-        </is>
-      </c>
-      <c r="C178" s="26" t="n">
-        <v>87055</v>
-      </c>
-      <c r="D178" s="26" t="n">
-        <v>320312</v>
-      </c>
-      <c r="E178" s="26" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="F178" s="27" t="n">
-        <v>107</v>
-      </c>
-      <c r="G178" s="28" t="n">
-        <v>28</v>
-      </c>
-      <c r="H178" s="31" t="inlineStr">
-        <is>
-          <t>+282%</t>
-        </is>
-      </c>
-      <c r="I178" s="30" t="n">
-        <v>573332</v>
-      </c>
-      <c r="J178" s="30" t="n">
-        <v>5358</v>
-      </c>
-      <c r="K178" s="26" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="L178" s="26" t="n">
-        <v>1789</v>
-      </c>
-      <c r="M178" s="26" t="inlineStr"/>
-      <c r="N178" s="26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="O178" s="26" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="P178" s="26" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q178" s="26" t="n">
-        <v>6.38</v>
-      </c>
-      <c r="R178" s="26" t="n">
-        <v>2699</v>
-      </c>
-      <c r="S178" s="31" t="inlineStr">
-        <is>
-          <t>🏆 GANADOR</t>
-        </is>
-      </c>
-    </row>
-    <row r="179" ht="18" customHeight="1">
-      <c r="B179" s="32" t="inlineStr">
-        <is>
-          <t>Carrusel Post que puedes oler</t>
-        </is>
-      </c>
-      <c r="C179" s="33" t="n">
-        <v>5613</v>
-      </c>
-      <c r="D179" s="33" t="n">
-        <v>11418</v>
-      </c>
-      <c r="E179" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="F179" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="G179" s="44" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H179" s="45" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I179" s="37" t="n">
-        <v>21464</v>
-      </c>
-      <c r="J179" s="37" t="n">
-        <v>21464</v>
-      </c>
-      <c r="K179" s="33" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L179" s="33" t="n">
-        <v>1879</v>
-      </c>
-      <c r="M179" s="33" t="inlineStr"/>
-      <c r="N179" s="33" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O179" s="33" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="P179" s="33" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q179" s="33" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="R179" s="33" t="n">
-        <v>87</v>
-      </c>
-      <c r="S179" s="36" t="inlineStr">
-        <is>
-          <t>⛔ PAUSAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="180" ht="18" customHeight="1">
-      <c r="B180" s="6" t="inlineStr">
-        <is>
-          <t>Fragancias Picnic</t>
-        </is>
-      </c>
-      <c r="C180" s="7" t="n">
-        <v>24676</v>
-      </c>
-      <c r="D180" s="7" t="n">
-        <v>74073</v>
-      </c>
-      <c r="E180" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="F180" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="G180" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H180" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I180" s="11" t="n">
-        <v>134078</v>
-      </c>
-      <c r="J180" s="11" t="n">
-        <v>11173</v>
-      </c>
-      <c r="K180" s="7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="L180" s="7" t="n">
-        <v>1810</v>
-      </c>
-      <c r="M180" s="7" t="inlineStr"/>
-      <c r="N180" s="7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O180" s="7" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="P180" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q180" s="7" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="R180" s="7" t="n">
-        <v>554</v>
-      </c>
-      <c r="S180" s="12" t="inlineStr">
-        <is>
-          <t>🔍 REVISAR</t>
         </is>
       </c>
     </row>
     <row r="181" ht="18" customHeight="1">
       <c r="B181" s="32" t="inlineStr">
         <is>
-          <t>Go Paw @melissapaz</t>
+          <t>Nuevas Cremas Corporales Abril</t>
         </is>
       </c>
       <c r="C181" s="33" t="n">
-        <v>7601</v>
+        <v>6943</v>
       </c>
       <c r="D181" s="33" t="n">
-        <v>9998</v>
+        <v>9228</v>
       </c>
       <c r="E181" s="33" t="n">
         <v>1.3</v>
       </c>
       <c r="F181" s="34" t="n">
-        <v>104</v>
+        <v>1</v>
       </c>
       <c r="G181" s="44" t="inlineStr">
         <is>
@@ -7570,30 +7607,32 @@
         </is>
       </c>
       <c r="I181" s="37" t="n">
-        <v>23686</v>
+        <v>22067</v>
       </c>
       <c r="J181" s="37" t="n">
-        <v>227</v>
+        <v>22067</v>
       </c>
       <c r="K181" s="33" t="n">
-        <v>1.89</v>
+        <v>1.38</v>
       </c>
       <c r="L181" s="33" t="n">
-        <v>2369</v>
+        <v>2391</v>
       </c>
       <c r="M181" s="33" t="inlineStr"/>
       <c r="N181" s="33" t="n">
-        <v>7.4</v>
+        <v>4.3</v>
       </c>
       <c r="O181" s="33" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="P181" s="33" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Q181" s="33" t="inlineStr"/>
+        <v>1.7</v>
+      </c>
+      <c r="Q181" s="33" t="n">
+        <v>0.79</v>
+      </c>
       <c r="R181" s="33" t="n">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="S181" s="36" t="inlineStr">
         <is>
@@ -7602,84 +7641,84 @@
       </c>
     </row>
     <row r="182" ht="18" customHeight="1">
-      <c r="B182" s="32" t="inlineStr">
-        <is>
-          <t>Nuevas Cremas Corporales Abril</t>
-        </is>
-      </c>
-      <c r="C182" s="33" t="n">
-        <v>6943</v>
-      </c>
-      <c r="D182" s="33" t="n">
-        <v>9228</v>
-      </c>
-      <c r="E182" s="33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F182" s="34" t="n">
+      <c r="B182" s="18" t="inlineStr">
+        <is>
+          <t>Lanzamiento Shampoo y Acondicionador</t>
+        </is>
+      </c>
+      <c r="C182" s="19" t="n">
+        <v>2164</v>
+      </c>
+      <c r="D182" s="19" t="n">
+        <v>3284</v>
+      </c>
+      <c r="E182" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F182" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="G182" s="44" t="inlineStr">
+      <c r="G182" s="38" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H182" s="45" t="inlineStr">
+      <c r="H182" s="39" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I182" s="37" t="n">
-        <v>22067</v>
-      </c>
-      <c r="J182" s="37" t="n">
-        <v>22067</v>
-      </c>
-      <c r="K182" s="33" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="L182" s="33" t="n">
-        <v>2391</v>
-      </c>
-      <c r="M182" s="33" t="inlineStr"/>
-      <c r="N182" s="33" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O182" s="33" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P182" s="33" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Q182" s="33" t="n">
+      <c r="I182" s="23" t="n">
+        <v>6190</v>
+      </c>
+      <c r="J182" s="23" t="n">
+        <v>6190</v>
+      </c>
+      <c r="K182" s="19" t="n">
         <v>0.79</v>
       </c>
-      <c r="R182" s="33" t="n">
-        <v>76</v>
-      </c>
-      <c r="S182" s="36" t="inlineStr">
-        <is>
-          <t>⛔ PAUSAR</t>
+      <c r="L182" s="19" t="n">
+        <v>1884</v>
+      </c>
+      <c r="M182" s="19" t="inlineStr"/>
+      <c r="N182" s="19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O182" s="19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="P182" s="19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q182" s="19" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="R182" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="S182" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
         </is>
       </c>
     </row>
     <row r="183" ht="18" customHeight="1">
       <c r="B183" s="18" t="inlineStr">
         <is>
-          <t>Lanzamiento Shampoo y Acondicionador</t>
+          <t>Lanzamiento Refill Abril</t>
         </is>
       </c>
       <c r="C183" s="19" t="n">
-        <v>2164</v>
+        <v>13541</v>
       </c>
       <c r="D183" s="19" t="n">
-        <v>3284</v>
+        <v>30101</v>
       </c>
       <c r="E183" s="19" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="F183" s="20" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G183" s="38" t="inlineStr">
         <is>
@@ -7692,32 +7731,32 @@
         </is>
       </c>
       <c r="I183" s="23" t="n">
-        <v>6190</v>
+        <v>68938</v>
       </c>
       <c r="J183" s="23" t="n">
-        <v>6190</v>
+        <v>9848</v>
       </c>
       <c r="K183" s="19" t="n">
-        <v>0.79</v>
+        <v>1.28</v>
       </c>
       <c r="L183" s="19" t="n">
-        <v>1884</v>
+        <v>2290</v>
       </c>
       <c r="M183" s="19" t="inlineStr"/>
       <c r="N183" s="19" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="O183" s="19" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="P183" s="19" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="Q183" s="19" t="n">
-        <v>2.89</v>
+        <v>3.33</v>
       </c>
       <c r="R183" s="19" t="n">
-        <v>18</v>
+        <v>302</v>
       </c>
       <c r="S183" s="22" t="inlineStr">
         <is>
@@ -7725,347 +7764,343 @@
         </is>
       </c>
     </row>
-    <row r="184" ht="18" customHeight="1">
-      <c r="B184" s="18" t="inlineStr">
-        <is>
-          <t>Lanzamiento Refill Abril</t>
-        </is>
-      </c>
-      <c r="C184" s="19" t="n">
-        <v>13541</v>
-      </c>
-      <c r="D184" s="19" t="n">
-        <v>30101</v>
-      </c>
-      <c r="E184" s="19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="F184" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="G184" s="38" t="inlineStr">
+    <row r="184" ht="20" customHeight="1">
+      <c r="B184" s="13" t="inlineStr">
+        <is>
+          <t>SUBTOTAL  Campaña principal de Conversión</t>
+        </is>
+      </c>
+      <c r="F184" s="14" t="n">
+        <v>715</v>
+      </c>
+      <c r="G184" s="14" t="n">
+        <v>840</v>
+      </c>
+      <c r="H184" s="15" t="inlineStr">
+        <is>
+          <t>-15%</t>
+        </is>
+      </c>
+      <c r="I184" s="16" t="n">
+        <v>5464256</v>
+      </c>
+    </row>
+    <row r="186" ht="22" customHeight="1">
+      <c r="B186" s="5" t="inlineStr">
+        <is>
+          <t>▸ Campaña Secundaria LMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="18" customHeight="1">
+      <c r="B187" s="6" t="inlineStr">
+        <is>
+          <t>Reel esmalte LMM</t>
+        </is>
+      </c>
+      <c r="C187" s="7" t="n">
+        <v>16040</v>
+      </c>
+      <c r="D187" s="7" t="n">
+        <v>23785</v>
+      </c>
+      <c r="E187" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F187" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G187" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="H187" s="17" t="inlineStr">
+        <is>
+          <t>-65%</t>
+        </is>
+      </c>
+      <c r="I187" s="11" t="n">
+        <v>60827</v>
+      </c>
+      <c r="J187" s="11" t="n">
+        <v>10137</v>
+      </c>
+      <c r="K187" s="7" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="L187" s="7" t="n">
+        <v>2557</v>
+      </c>
+      <c r="M187" s="7" t="inlineStr"/>
+      <c r="N187" s="7" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="O187" s="7" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="P187" s="7" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Q187" s="7" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="R187" s="7" t="n">
+        <v>695</v>
+      </c>
+      <c r="S187" s="12" t="inlineStr">
+        <is>
+          <t>🔍 REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="18" customHeight="1">
+      <c r="B188" s="25" t="inlineStr">
+        <is>
+          <t>Reel Kit LMM</t>
+        </is>
+      </c>
+      <c r="C188" s="26" t="n">
+        <v>2378</v>
+      </c>
+      <c r="D188" s="26" t="n">
+        <v>3985</v>
+      </c>
+      <c r="E188" s="26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F188" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="G188" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H188" s="31" t="inlineStr">
+        <is>
+          <t>+400%</t>
+        </is>
+      </c>
+      <c r="I188" s="30" t="n">
+        <v>12363</v>
+      </c>
+      <c r="J188" s="30" t="n">
+        <v>2472</v>
+      </c>
+      <c r="K188" s="26" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="L188" s="26" t="n">
+        <v>3102</v>
+      </c>
+      <c r="M188" s="26" t="inlineStr"/>
+      <c r="N188" s="26" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="O188" s="26" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="P188" s="26" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="Q188" s="26" t="n">
+        <v>15.27</v>
+      </c>
+      <c r="R188" s="26" t="n">
+        <v>82</v>
+      </c>
+      <c r="S188" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="18" customHeight="1">
+      <c r="B189" s="18" t="inlineStr">
+        <is>
+          <t>Reel de Kit Le Mini</t>
+        </is>
+      </c>
+      <c r="C189" s="19" t="n">
+        <v>26</v>
+      </c>
+      <c r="D189" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="E189" s="19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F189" s="20" t="inlineStr"/>
+      <c r="G189" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="H189" s="24" t="inlineStr">
+        <is>
+          <t>-100%</t>
+        </is>
+      </c>
+      <c r="I189" s="23" t="n">
+        <v>63</v>
+      </c>
+      <c r="J189" s="23" t="inlineStr"/>
+      <c r="K189" s="19" t="inlineStr"/>
+      <c r="L189" s="19" t="n">
+        <v>2250</v>
+      </c>
+      <c r="M189" s="19" t="inlineStr"/>
+      <c r="N189" s="19" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="O189" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="P189" s="19" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="Q189" s="19" t="inlineStr"/>
+      <c r="R189" s="19" t="inlineStr"/>
+      <c r="S189" s="64" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H184" s="39" t="inlineStr">
+    </row>
+    <row r="190" ht="20" customHeight="1">
+      <c r="B190" s="13" t="inlineStr">
+        <is>
+          <t>SUBTOTAL  Campaña Secundaria LMM</t>
+        </is>
+      </c>
+      <c r="F190" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="G190" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="H190" s="15" t="inlineStr">
+        <is>
+          <t>-58%</t>
+        </is>
+      </c>
+      <c r="I190" s="16" t="n">
+        <v>73253</v>
+      </c>
+    </row>
+    <row r="192" ht="22" customHeight="1">
+      <c r="B192" s="5" t="inlineStr">
+        <is>
+          <t>▸ Campaña Conversión Catálogo</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="18" customHeight="1">
+      <c r="B193" s="32" t="inlineStr">
+        <is>
+          <t>Fragancias Picnic</t>
+        </is>
+      </c>
+      <c r="C193" s="33" t="n">
+        <v>2356</v>
+      </c>
+      <c r="D193" s="33" t="n">
+        <v>3006</v>
+      </c>
+      <c r="E193" s="33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F193" s="34" t="n">
+        <v>29</v>
+      </c>
+      <c r="G193" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I184" s="23" t="n">
-        <v>68938</v>
-      </c>
-      <c r="J184" s="23" t="n">
-        <v>9848</v>
-      </c>
-      <c r="K184" s="19" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="L184" s="19" t="n">
-        <v>2290</v>
-      </c>
-      <c r="M184" s="19" t="inlineStr"/>
-      <c r="N184" s="19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O184" s="19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P184" s="19" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Q184" s="19" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="R184" s="19" t="n">
-        <v>302</v>
-      </c>
-      <c r="S184" s="22" t="inlineStr">
-        <is>
-          <t>✅ OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="185" ht="20" customHeight="1">
-      <c r="B185" s="13" t="inlineStr">
-        <is>
-          <t>SUBTOTAL  Campaña principal de Conversión</t>
-        </is>
-      </c>
-      <c r="F185" s="14" t="n">
-        <v>715</v>
-      </c>
-      <c r="G185" s="14" t="n">
-        <v>840</v>
-      </c>
-      <c r="H185" s="15" t="inlineStr">
-        <is>
-          <t>-15%</t>
-        </is>
-      </c>
-      <c r="I185" s="16" t="n">
-        <v>5464256</v>
-      </c>
-    </row>
-    <row r="187" ht="22" customHeight="1">
-      <c r="B187" s="5" t="inlineStr">
-        <is>
-          <t>▸ Campaña Secundaria LMM</t>
-        </is>
-      </c>
-    </row>
-    <row r="188" ht="18" customHeight="1">
-      <c r="B188" s="6" t="inlineStr">
-        <is>
-          <t>Reel esmalte LMM</t>
-        </is>
-      </c>
-      <c r="C188" s="7" t="n">
-        <v>16040</v>
-      </c>
-      <c r="D188" s="7" t="n">
-        <v>23785</v>
-      </c>
-      <c r="E188" s="7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F188" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="G188" s="9" t="n">
-        <v>17</v>
-      </c>
-      <c r="H188" s="17" t="inlineStr">
-        <is>
-          <t>-65%</t>
-        </is>
-      </c>
-      <c r="I188" s="11" t="n">
-        <v>60827</v>
-      </c>
-      <c r="J188" s="11" t="n">
-        <v>10137</v>
-      </c>
-      <c r="K188" s="7" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="L188" s="7" t="n">
-        <v>2557</v>
-      </c>
-      <c r="M188" s="7" t="inlineStr"/>
-      <c r="N188" s="7" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="O188" s="7" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="P188" s="7" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="Q188" s="7" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="R188" s="7" t="n">
-        <v>695</v>
-      </c>
-      <c r="S188" s="12" t="inlineStr">
-        <is>
-          <t>🔍 REVISAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="189" ht="18" customHeight="1">
-      <c r="B189" s="25" t="inlineStr">
-        <is>
-          <t>Reel Kit LMM</t>
-        </is>
-      </c>
-      <c r="C189" s="26" t="n">
-        <v>2378</v>
-      </c>
-      <c r="D189" s="26" t="n">
-        <v>3985</v>
-      </c>
-      <c r="E189" s="26" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F189" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="G189" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="H189" s="31" t="inlineStr">
-        <is>
-          <t>+400%</t>
-        </is>
-      </c>
-      <c r="I189" s="30" t="n">
-        <v>12363</v>
-      </c>
-      <c r="J189" s="30" t="n">
-        <v>2472</v>
-      </c>
-      <c r="K189" s="26" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="L189" s="26" t="n">
-        <v>3102</v>
-      </c>
-      <c r="M189" s="26" t="inlineStr"/>
-      <c r="N189" s="26" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="O189" s="26" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="P189" s="26" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="Q189" s="26" t="n">
-        <v>15.27</v>
-      </c>
-      <c r="R189" s="26" t="n">
-        <v>82</v>
-      </c>
-      <c r="S189" s="31" t="inlineStr">
-        <is>
-          <t>🏆 GANADOR</t>
-        </is>
-      </c>
-    </row>
-    <row r="190" ht="18" customHeight="1">
-      <c r="B190" s="18" t="inlineStr">
-        <is>
-          <t>Reel de Kit Le Mini</t>
-        </is>
-      </c>
-      <c r="C190" s="19" t="n">
-        <v>26</v>
-      </c>
-      <c r="D190" s="19" t="n">
-        <v>28</v>
-      </c>
-      <c r="E190" s="19" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="F190" s="20" t="inlineStr"/>
-      <c r="G190" s="21" t="n">
-        <v>8</v>
-      </c>
-      <c r="H190" s="24" t="inlineStr">
-        <is>
-          <t>-100%</t>
-        </is>
-      </c>
-      <c r="I190" s="23" t="n">
-        <v>63</v>
-      </c>
-      <c r="J190" s="23" t="inlineStr"/>
-      <c r="K190" s="19" t="inlineStr"/>
-      <c r="L190" s="19" t="n">
-        <v>2250</v>
-      </c>
-      <c r="M190" s="19" t="inlineStr"/>
-      <c r="N190" s="19" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="O190" s="19" t="n">
-        <v>25</v>
-      </c>
-      <c r="P190" s="19" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="Q190" s="19" t="inlineStr"/>
-      <c r="R190" s="19" t="inlineStr"/>
-      <c r="S190" s="64" t="inlineStr">
+      <c r="H193" s="45" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-    </row>
-    <row r="191" ht="20" customHeight="1">
-      <c r="B191" s="13" t="inlineStr">
-        <is>
-          <t>SUBTOTAL  Campaña Secundaria LMM</t>
-        </is>
-      </c>
-      <c r="F191" s="14" t="n">
-        <v>11</v>
-      </c>
-      <c r="G191" s="14" t="n">
-        <v>26</v>
-      </c>
-      <c r="H191" s="15" t="inlineStr">
-        <is>
-          <t>-58%</t>
-        </is>
-      </c>
-      <c r="I191" s="16" t="n">
-        <v>73253</v>
-      </c>
-    </row>
-    <row r="193" ht="22" customHeight="1">
-      <c r="B193" s="5" t="inlineStr">
-        <is>
-          <t>▸ Campaña Conversión Catálogo</t>
+      <c r="I193" s="37" t="n">
+        <v>6363</v>
+      </c>
+      <c r="J193" s="37" t="n">
+        <v>219</v>
+      </c>
+      <c r="K193" s="33" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="L193" s="33" t="n">
+        <v>2116</v>
+      </c>
+      <c r="M193" s="33" t="inlineStr"/>
+      <c r="N193" s="33" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O193" s="33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P193" s="33" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q193" s="33" t="inlineStr"/>
+      <c r="R193" s="33" t="n">
+        <v>27</v>
+      </c>
+      <c r="S193" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
         </is>
       </c>
     </row>
     <row r="194" ht="18" customHeight="1">
       <c r="B194" s="32" t="inlineStr">
         <is>
-          <t>Fragancias Picnic</t>
+          <t>Imagen Cotton Vlabel</t>
         </is>
       </c>
       <c r="C194" s="33" t="n">
-        <v>2356</v>
+        <v>1058</v>
       </c>
       <c r="D194" s="33" t="n">
-        <v>3006</v>
+        <v>1219</v>
       </c>
       <c r="E194" s="33" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="F194" s="34" t="n">
-        <v>29</v>
-      </c>
-      <c r="G194" s="44" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H194" s="45" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>21</v>
+      </c>
+      <c r="G194" s="35" t="n">
+        <v>120</v>
+      </c>
+      <c r="H194" s="36" t="inlineStr">
+        <is>
+          <t>-82%</t>
         </is>
       </c>
       <c r="I194" s="37" t="n">
-        <v>6363</v>
+        <v>1981</v>
       </c>
       <c r="J194" s="37" t="n">
-        <v>219</v>
+        <v>94</v>
       </c>
       <c r="K194" s="33" t="n">
-        <v>1.16</v>
+        <v>1.89</v>
       </c>
       <c r="L194" s="33" t="n">
-        <v>2116</v>
+        <v>1625</v>
       </c>
       <c r="M194" s="33" t="inlineStr"/>
       <c r="N194" s="33" t="n">
-        <v>5.7</v>
+        <v>4.1</v>
       </c>
       <c r="O194" s="33" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="P194" s="33" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="Q194" s="33" t="inlineStr"/>
       <c r="R194" s="33" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="S194" s="36" t="inlineStr">
         <is>
@@ -8074,166 +8109,166 @@
       </c>
     </row>
     <row r="195" ht="18" customHeight="1">
-      <c r="B195" s="32" t="inlineStr">
-        <is>
-          <t>Imagen Cotton Vlabel</t>
-        </is>
-      </c>
-      <c r="C195" s="33" t="n">
-        <v>1058</v>
-      </c>
-      <c r="D195" s="33" t="n">
-        <v>1219</v>
-      </c>
-      <c r="E195" s="33" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F195" s="34" t="n">
-        <v>21</v>
-      </c>
-      <c r="G195" s="35" t="n">
-        <v>120</v>
-      </c>
-      <c r="H195" s="36" t="inlineStr">
-        <is>
-          <t>-82%</t>
-        </is>
-      </c>
-      <c r="I195" s="37" t="n">
-        <v>1981</v>
-      </c>
-      <c r="J195" s="37" t="n">
-        <v>94</v>
-      </c>
-      <c r="K195" s="33" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="L195" s="33" t="n">
-        <v>1625</v>
-      </c>
-      <c r="M195" s="33" t="inlineStr"/>
-      <c r="N195" s="33" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O195" s="33" t="n">
+      <c r="B195" s="18" t="inlineStr">
+        <is>
+          <t>Hot Chocalate</t>
+        </is>
+      </c>
+      <c r="C195" s="19" t="n">
+        <v>161</v>
+      </c>
+      <c r="D195" s="19" t="n">
+        <v>285</v>
+      </c>
+      <c r="E195" s="19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F195" s="20" t="n">
+        <v>13</v>
+      </c>
+      <c r="G195" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H195" s="22" t="inlineStr">
+        <is>
+          <t>+30%</t>
+        </is>
+      </c>
+      <c r="I195" s="23" t="n">
+        <v>449</v>
+      </c>
+      <c r="J195" s="23" t="n">
+        <v>34</v>
+      </c>
+      <c r="K195" s="19" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="L195" s="19" t="n">
+        <v>1575</v>
+      </c>
+      <c r="M195" s="19" t="inlineStr"/>
+      <c r="N195" s="19" t="inlineStr"/>
+      <c r="O195" s="19" t="inlineStr"/>
+      <c r="P195" s="19" t="inlineStr"/>
+      <c r="Q195" s="19" t="inlineStr"/>
+      <c r="R195" s="19" t="n">
+        <v>13</v>
+      </c>
+      <c r="S195" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="18" customHeight="1">
+      <c r="B196" s="32" t="inlineStr">
+        <is>
+          <t>Crema dibujada</t>
+        </is>
+      </c>
+      <c r="C196" s="33" t="n">
+        <v>543</v>
+      </c>
+      <c r="D196" s="33" t="n">
+        <v>600</v>
+      </c>
+      <c r="E196" s="33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F196" s="34" t="n">
+        <v>10</v>
+      </c>
+      <c r="G196" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="H196" s="63" t="inlineStr">
+        <is>
+          <t>+100%</t>
+        </is>
+      </c>
+      <c r="I196" s="37" t="n">
+        <v>847</v>
+      </c>
+      <c r="J196" s="37" t="n">
+        <v>84</v>
+      </c>
+      <c r="K196" s="33" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="L196" s="33" t="n">
+        <v>1411</v>
+      </c>
+      <c r="M196" s="33" t="inlineStr"/>
+      <c r="N196" s="33" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O196" s="33" t="n">
         <v>2.8</v>
       </c>
-      <c r="P195" s="33" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q195" s="33" t="inlineStr"/>
-      <c r="R195" s="33" t="n">
-        <v>19</v>
-      </c>
-      <c r="S195" s="36" t="inlineStr">
+      <c r="P196" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q196" s="33" t="inlineStr"/>
+      <c r="R196" s="33" t="n">
+        <v>9</v>
+      </c>
+      <c r="S196" s="36" t="inlineStr">
         <is>
           <t>⛔ PAUSAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="196" ht="18" customHeight="1">
-      <c r="B196" s="18" t="inlineStr">
-        <is>
-          <t>Hot Chocalate</t>
-        </is>
-      </c>
-      <c r="C196" s="19" t="n">
-        <v>161</v>
-      </c>
-      <c r="D196" s="19" t="n">
-        <v>285</v>
-      </c>
-      <c r="E196" s="19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F196" s="20" t="n">
-        <v>13</v>
-      </c>
-      <c r="G196" s="21" t="n">
-        <v>10</v>
-      </c>
-      <c r="H196" s="22" t="inlineStr">
-        <is>
-          <t>+30%</t>
-        </is>
-      </c>
-      <c r="I196" s="23" t="n">
-        <v>449</v>
-      </c>
-      <c r="J196" s="23" t="n">
-        <v>34</v>
-      </c>
-      <c r="K196" s="19" t="n">
-        <v>4.21</v>
-      </c>
-      <c r="L196" s="19" t="n">
-        <v>1575</v>
-      </c>
-      <c r="M196" s="19" t="inlineStr"/>
-      <c r="N196" s="19" t="inlineStr"/>
-      <c r="O196" s="19" t="inlineStr"/>
-      <c r="P196" s="19" t="inlineStr"/>
-      <c r="Q196" s="19" t="inlineStr"/>
-      <c r="R196" s="19" t="n">
-        <v>13</v>
-      </c>
-      <c r="S196" s="22" t="inlineStr">
-        <is>
-          <t>✅ OK</t>
         </is>
       </c>
     </row>
     <row r="197" ht="18" customHeight="1">
       <c r="B197" s="32" t="inlineStr">
         <is>
-          <t>Crema dibujada</t>
+          <t>Carrusel Sun Kissed</t>
         </is>
       </c>
       <c r="C197" s="33" t="n">
-        <v>543</v>
+        <v>212</v>
       </c>
       <c r="D197" s="33" t="n">
-        <v>600</v>
+        <v>229</v>
       </c>
       <c r="E197" s="33" t="n">
         <v>1.1</v>
       </c>
       <c r="F197" s="34" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G197" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="H197" s="63" t="inlineStr">
-        <is>
-          <t>+100%</t>
+        <v>7</v>
+      </c>
+      <c r="H197" s="36" t="inlineStr">
+        <is>
+          <t>-43%</t>
         </is>
       </c>
       <c r="I197" s="37" t="n">
-        <v>847</v>
+        <v>364</v>
       </c>
       <c r="J197" s="37" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="K197" s="33" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="L197" s="33" t="n">
-        <v>1411</v>
+        <v>1589</v>
       </c>
       <c r="M197" s="33" t="inlineStr"/>
       <c r="N197" s="33" t="n">
-        <v>5.2</v>
+        <v>2.6</v>
       </c>
       <c r="O197" s="33" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="P197" s="33" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="Q197" s="33" t="inlineStr"/>
       <c r="R197" s="33" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="S197" s="36" t="inlineStr">
         <is>
@@ -8244,282 +8279,276 @@
     <row r="198" ht="18" customHeight="1">
       <c r="B198" s="32" t="inlineStr">
         <is>
-          <t>Carrusel Sun Kissed</t>
+          <t>4 por 3</t>
         </is>
       </c>
       <c r="C198" s="33" t="n">
-        <v>212</v>
+        <v>134</v>
       </c>
       <c r="D198" s="33" t="n">
-        <v>229</v>
+        <v>174</v>
       </c>
       <c r="E198" s="33" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="F198" s="34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G198" s="35" t="n">
-        <v>7</v>
+        <v>123</v>
       </c>
       <c r="H198" s="36" t="inlineStr">
         <is>
-          <t>-43%</t>
+          <t>-96%</t>
         </is>
       </c>
       <c r="I198" s="37" t="n">
-        <v>364</v>
+        <v>421</v>
       </c>
       <c r="J198" s="37" t="n">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="K198" s="33" t="n">
-        <v>1.75</v>
+        <v>4.6</v>
       </c>
       <c r="L198" s="33" t="n">
-        <v>1589</v>
+        <v>2419</v>
       </c>
       <c r="M198" s="33" t="inlineStr"/>
-      <c r="N198" s="33" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O198" s="33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P198" s="33" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="N198" s="33" t="inlineStr"/>
+      <c r="O198" s="33" t="inlineStr"/>
+      <c r="P198" s="33" t="inlineStr"/>
       <c r="Q198" s="33" t="inlineStr"/>
       <c r="R198" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="S198" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="18" customHeight="1">
+      <c r="B199" s="6" t="inlineStr">
+        <is>
+          <t>Nuevos difusores</t>
+        </is>
+      </c>
+      <c r="C199" s="7" t="n">
+        <v>247</v>
+      </c>
+      <c r="D199" s="7" t="n">
+        <v>280</v>
+      </c>
+      <c r="E199" s="7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F199" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G199" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="H199" s="17" t="inlineStr">
+        <is>
+          <t>-77%</t>
+        </is>
+      </c>
+      <c r="I199" s="11" t="n">
+        <v>575</v>
+      </c>
+      <c r="J199" s="11" t="n">
+        <v>71</v>
+      </c>
+      <c r="K199" s="7" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="L199" s="7" t="n">
+        <v>2053</v>
+      </c>
+      <c r="M199" s="7" t="inlineStr"/>
+      <c r="N199" s="7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O199" s="7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P199" s="7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q199" s="7" t="inlineStr"/>
+      <c r="R199" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="S199" s="12" t="inlineStr">
+        <is>
+          <t>🔍 REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="18" customHeight="1">
+      <c r="B200" s="25" t="inlineStr">
+        <is>
+          <t>Macbook</t>
+        </is>
+      </c>
+      <c r="C200" s="26" t="n">
+        <v>8482</v>
+      </c>
+      <c r="D200" s="26" t="n">
+        <v>14633</v>
+      </c>
+      <c r="E200" s="26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F200" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="G200" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="S198" s="36" t="inlineStr">
+      <c r="H200" s="31" t="inlineStr">
+        <is>
+          <t>+75%</t>
+        </is>
+      </c>
+      <c r="I200" s="30" t="n">
+        <v>21610</v>
+      </c>
+      <c r="J200" s="30" t="n">
+        <v>3087</v>
+      </c>
+      <c r="K200" s="26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L200" s="26" t="n">
+        <v>1476</v>
+      </c>
+      <c r="M200" s="26" t="inlineStr"/>
+      <c r="N200" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="O200" s="26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P200" s="26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q200" s="26" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="R200" s="26" t="n">
+        <v>111</v>
+      </c>
+      <c r="S200" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="18" customHeight="1">
+      <c r="B201" s="32" t="inlineStr">
+        <is>
+          <t>Protector Termico</t>
+        </is>
+      </c>
+      <c r="C201" s="33" t="n">
+        <v>1177</v>
+      </c>
+      <c r="D201" s="33" t="n">
+        <v>1485</v>
+      </c>
+      <c r="E201" s="33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F201" s="34" t="n">
+        <v>18</v>
+      </c>
+      <c r="G201" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="H201" s="63" t="inlineStr">
+        <is>
+          <t>+29%</t>
+        </is>
+      </c>
+      <c r="I201" s="37" t="n">
+        <v>1837</v>
+      </c>
+      <c r="J201" s="37" t="n">
+        <v>102</v>
+      </c>
+      <c r="K201" s="33" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L201" s="33" t="n">
+        <v>1237</v>
+      </c>
+      <c r="M201" s="33" t="inlineStr"/>
+      <c r="N201" s="33" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O201" s="33" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P201" s="33" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q201" s="33" t="inlineStr"/>
+      <c r="R201" s="33" t="n">
+        <v>18</v>
+      </c>
+      <c r="S201" s="36" t="inlineStr">
         <is>
           <t>⛔ PAUSAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="199" ht="18" customHeight="1">
-      <c r="B199" s="32" t="inlineStr">
-        <is>
-          <t>4 por 3</t>
-        </is>
-      </c>
-      <c r="C199" s="33" t="n">
-        <v>134</v>
-      </c>
-      <c r="D199" s="33" t="n">
-        <v>174</v>
-      </c>
-      <c r="E199" s="33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F199" s="34" t="n">
-        <v>5</v>
-      </c>
-      <c r="G199" s="35" t="n">
-        <v>123</v>
-      </c>
-      <c r="H199" s="36" t="inlineStr">
-        <is>
-          <t>-96%</t>
-        </is>
-      </c>
-      <c r="I199" s="37" t="n">
-        <v>421</v>
-      </c>
-      <c r="J199" s="37" t="n">
-        <v>84</v>
-      </c>
-      <c r="K199" s="33" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L199" s="33" t="n">
-        <v>2419</v>
-      </c>
-      <c r="M199" s="33" t="inlineStr"/>
-      <c r="N199" s="33" t="inlineStr"/>
-      <c r="O199" s="33" t="inlineStr"/>
-      <c r="P199" s="33" t="inlineStr"/>
-      <c r="Q199" s="33" t="inlineStr"/>
-      <c r="R199" s="33" t="n">
-        <v>5</v>
-      </c>
-      <c r="S199" s="36" t="inlineStr">
-        <is>
-          <t>⛔ PAUSAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="200" ht="18" customHeight="1">
-      <c r="B200" s="6" t="inlineStr">
-        <is>
-          <t>Nuevos difusores</t>
-        </is>
-      </c>
-      <c r="C200" s="7" t="n">
-        <v>247</v>
-      </c>
-      <c r="D200" s="7" t="n">
-        <v>280</v>
-      </c>
-      <c r="E200" s="7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="F200" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="G200" s="9" t="n">
-        <v>35</v>
-      </c>
-      <c r="H200" s="17" t="inlineStr">
-        <is>
-          <t>-77%</t>
-        </is>
-      </c>
-      <c r="I200" s="11" t="n">
-        <v>575</v>
-      </c>
-      <c r="J200" s="11" t="n">
-        <v>71</v>
-      </c>
-      <c r="K200" s="7" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="L200" s="7" t="n">
-        <v>2053</v>
-      </c>
-      <c r="M200" s="7" t="inlineStr"/>
-      <c r="N200" s="7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O200" s="7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P200" s="7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Q200" s="7" t="inlineStr"/>
-      <c r="R200" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="S200" s="12" t="inlineStr">
-        <is>
-          <t>🔍 REVISAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="201" ht="18" customHeight="1">
-      <c r="B201" s="25" t="inlineStr">
-        <is>
-          <t>Macbook</t>
-        </is>
-      </c>
-      <c r="C201" s="26" t="n">
-        <v>8482</v>
-      </c>
-      <c r="D201" s="26" t="n">
-        <v>14633</v>
-      </c>
-      <c r="E201" s="26" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F201" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="G201" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="H201" s="31" t="inlineStr">
-        <is>
-          <t>+75%</t>
-        </is>
-      </c>
-      <c r="I201" s="30" t="n">
-        <v>21610</v>
-      </c>
-      <c r="J201" s="30" t="n">
-        <v>3087</v>
-      </c>
-      <c r="K201" s="26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="L201" s="26" t="n">
-        <v>1476</v>
-      </c>
-      <c r="M201" s="26" t="inlineStr"/>
-      <c r="N201" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="O201" s="26" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P201" s="26" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q201" s="26" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="R201" s="26" t="n">
-        <v>111</v>
-      </c>
-      <c r="S201" s="31" t="inlineStr">
-        <is>
-          <t>🏆 GANADOR</t>
         </is>
       </c>
     </row>
     <row r="202" ht="18" customHeight="1">
       <c r="B202" s="32" t="inlineStr">
         <is>
-          <t>Protector Termico</t>
+          <t>Reel de fragancias</t>
         </is>
       </c>
       <c r="C202" s="33" t="n">
-        <v>1177</v>
+        <v>272</v>
       </c>
       <c r="D202" s="33" t="n">
-        <v>1485</v>
+        <v>344</v>
       </c>
       <c r="E202" s="33" t="n">
         <v>1.3</v>
       </c>
       <c r="F202" s="34" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="G202" s="35" t="n">
-        <v>14</v>
-      </c>
-      <c r="H202" s="63" t="inlineStr">
-        <is>
-          <t>+29%</t>
+        <v>104</v>
+      </c>
+      <c r="H202" s="36" t="inlineStr">
+        <is>
+          <t>-98%</t>
         </is>
       </c>
       <c r="I202" s="37" t="n">
-        <v>1837</v>
+        <v>523</v>
       </c>
       <c r="J202" s="37" t="n">
-        <v>102</v>
+        <v>261</v>
       </c>
       <c r="K202" s="33" t="n">
-        <v>1.35</v>
+        <v>0.87</v>
       </c>
       <c r="L202" s="33" t="n">
-        <v>1237</v>
+        <v>1520</v>
       </c>
       <c r="M202" s="33" t="inlineStr"/>
-      <c r="N202" s="33" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O202" s="33" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="P202" s="33" t="n">
-        <v>2.6</v>
-      </c>
+      <c r="N202" s="33" t="inlineStr"/>
+      <c r="O202" s="33" t="inlineStr"/>
+      <c r="P202" s="33" t="inlineStr"/>
       <c r="Q202" s="33" t="inlineStr"/>
       <c r="R202" s="33" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="S202" s="36" t="inlineStr">
         <is>
@@ -8530,48 +8559,54 @@
     <row r="203" ht="18" customHeight="1">
       <c r="B203" s="32" t="inlineStr">
         <is>
-          <t>Reel de fragancias</t>
+          <t>Imagen Gato</t>
         </is>
       </c>
       <c r="C203" s="33" t="n">
-        <v>272</v>
+        <v>426</v>
       </c>
       <c r="D203" s="33" t="n">
-        <v>344</v>
+        <v>481</v>
       </c>
       <c r="E203" s="33" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="F203" s="34" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G203" s="35" t="n">
-        <v>104</v>
+        <v>7</v>
       </c>
       <c r="H203" s="36" t="inlineStr">
         <is>
-          <t>-98%</t>
+          <t>-29%</t>
         </is>
       </c>
       <c r="I203" s="37" t="n">
-        <v>523</v>
+        <v>830</v>
       </c>
       <c r="J203" s="37" t="n">
-        <v>261</v>
+        <v>166</v>
       </c>
       <c r="K203" s="33" t="n">
-        <v>0.87</v>
+        <v>1.25</v>
       </c>
       <c r="L203" s="33" t="n">
-        <v>1520</v>
+        <v>1725</v>
       </c>
       <c r="M203" s="33" t="inlineStr"/>
-      <c r="N203" s="33" t="inlineStr"/>
-      <c r="O203" s="33" t="inlineStr"/>
-      <c r="P203" s="33" t="inlineStr"/>
+      <c r="N203" s="33" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O203" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="P203" s="33" t="n">
+        <v>2.7</v>
+      </c>
       <c r="Q203" s="33" t="inlineStr"/>
       <c r="R203" s="33" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S203" s="36" t="inlineStr">
         <is>
@@ -8582,54 +8617,54 @@
     <row r="204" ht="18" customHeight="1">
       <c r="B204" s="32" t="inlineStr">
         <is>
-          <t>Imagen Gato</t>
+          <t>Reel cafetería</t>
         </is>
       </c>
       <c r="C204" s="33" t="n">
-        <v>426</v>
+        <v>538</v>
       </c>
       <c r="D204" s="33" t="n">
-        <v>481</v>
+        <v>601</v>
       </c>
       <c r="E204" s="33" t="n">
         <v>1.1</v>
       </c>
       <c r="F204" s="34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G204" s="35" t="n">
-        <v>7</v>
+        <v>88</v>
       </c>
       <c r="H204" s="36" t="inlineStr">
         <is>
-          <t>-29%</t>
+          <t>-92%</t>
         </is>
       </c>
       <c r="I204" s="37" t="n">
-        <v>830</v>
+        <v>1087</v>
       </c>
       <c r="J204" s="37" t="n">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="K204" s="33" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="L204" s="33" t="n">
-        <v>1725</v>
+        <v>1808</v>
       </c>
       <c r="M204" s="33" t="inlineStr"/>
       <c r="N204" s="33" t="n">
-        <v>5.2</v>
+        <v>7.3</v>
       </c>
       <c r="O204" s="33" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P204" s="33" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="Q204" s="33" t="inlineStr"/>
       <c r="R204" s="33" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S204" s="36" t="inlineStr">
         <is>
@@ -8638,172 +8673,172 @@
       </c>
     </row>
     <row r="205" ht="18" customHeight="1">
-      <c r="B205" s="32" t="inlineStr">
-        <is>
-          <t>Reel cafetería</t>
-        </is>
-      </c>
-      <c r="C205" s="33" t="n">
-        <v>538</v>
-      </c>
-      <c r="D205" s="33" t="n">
-        <v>601</v>
-      </c>
-      <c r="E205" s="33" t="n">
+      <c r="B205" s="25" t="inlineStr">
+        <is>
+          <t>Imagen Bubble gum</t>
+        </is>
+      </c>
+      <c r="C205" s="26" t="n">
+        <v>795</v>
+      </c>
+      <c r="D205" s="26" t="n">
+        <v>909</v>
+      </c>
+      <c r="E205" s="26" t="n">
         <v>1.1</v>
       </c>
-      <c r="F205" s="34" t="n">
+      <c r="F205" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G205" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="H205" s="29" t="inlineStr">
+        <is>
+          <t>-96%</t>
+        </is>
+      </c>
+      <c r="I205" s="30" t="n">
+        <v>1506</v>
+      </c>
+      <c r="J205" s="30" t="n">
+        <v>1506</v>
+      </c>
+      <c r="K205" s="26" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="L205" s="26" t="n">
+        <v>1656</v>
+      </c>
+      <c r="M205" s="26" t="inlineStr"/>
+      <c r="N205" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="G205" s="35" t="n">
-        <v>88</v>
-      </c>
-      <c r="H205" s="36" t="inlineStr">
-        <is>
-          <t>-92%</t>
-        </is>
-      </c>
-      <c r="I205" s="37" t="n">
-        <v>1087</v>
-      </c>
-      <c r="J205" s="37" t="n">
-        <v>155</v>
-      </c>
-      <c r="K205" s="33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L205" s="33" t="n">
-        <v>1808</v>
-      </c>
-      <c r="M205" s="33" t="inlineStr"/>
-      <c r="N205" s="33" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="O205" s="33" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P205" s="33" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Q205" s="33" t="inlineStr"/>
-      <c r="R205" s="33" t="n">
-        <v>7</v>
-      </c>
-      <c r="S205" s="36" t="inlineStr">
+      <c r="O205" s="26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P205" s="26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q205" s="26" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="R205" s="26" t="n">
+        <v>13</v>
+      </c>
+      <c r="S205" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="18" customHeight="1">
+      <c r="B206" s="32" t="inlineStr">
+        <is>
+          <t>Carrusel Post que puedes oler</t>
+        </is>
+      </c>
+      <c r="C206" s="33" t="n">
+        <v>563</v>
+      </c>
+      <c r="D206" s="33" t="n">
+        <v>638</v>
+      </c>
+      <c r="E206" s="33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F206" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G206" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H206" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I206" s="37" t="n">
+        <v>849</v>
+      </c>
+      <c r="J206" s="37" t="n">
+        <v>283</v>
+      </c>
+      <c r="K206" s="33" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L206" s="33" t="n">
+        <v>1330</v>
+      </c>
+      <c r="M206" s="33" t="inlineStr"/>
+      <c r="N206" s="33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O206" s="33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P206" s="33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q206" s="33" t="inlineStr"/>
+      <c r="R206" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="S206" s="36" t="inlineStr">
         <is>
           <t>⛔ PAUSAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="206" ht="18" customHeight="1">
-      <c r="B206" s="25" t="inlineStr">
-        <is>
-          <t>Imagen Bubble gum</t>
-        </is>
-      </c>
-      <c r="C206" s="26" t="n">
-        <v>795</v>
-      </c>
-      <c r="D206" s="26" t="n">
-        <v>909</v>
-      </c>
-      <c r="E206" s="26" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="F206" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G206" s="28" t="n">
-        <v>25</v>
-      </c>
-      <c r="H206" s="29" t="inlineStr">
-        <is>
-          <t>-96%</t>
-        </is>
-      </c>
-      <c r="I206" s="30" t="n">
-        <v>1506</v>
-      </c>
-      <c r="J206" s="30" t="n">
-        <v>1506</v>
-      </c>
-      <c r="K206" s="26" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="L206" s="26" t="n">
-        <v>1656</v>
-      </c>
-      <c r="M206" s="26" t="inlineStr"/>
-      <c r="N206" s="26" t="n">
-        <v>7</v>
-      </c>
-      <c r="O206" s="26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P206" s="26" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Q206" s="26" t="n">
-        <v>5.97</v>
-      </c>
-      <c r="R206" s="26" t="n">
-        <v>13</v>
-      </c>
-      <c r="S206" s="31" t="inlineStr">
-        <is>
-          <t>🏆 GANADOR</t>
         </is>
       </c>
     </row>
     <row r="207" ht="18" customHeight="1">
       <c r="B207" s="32" t="inlineStr">
         <is>
-          <t>Carrusel Post que puedes oler</t>
+          <t>Rutina 4 pasos 2.0</t>
         </is>
       </c>
       <c r="C207" s="33" t="n">
-        <v>563</v>
+        <v>294</v>
       </c>
       <c r="D207" s="33" t="n">
-        <v>638</v>
+        <v>339</v>
       </c>
       <c r="E207" s="33" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="F207" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="G207" s="44" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H207" s="45" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G207" s="35" t="n">
+        <v>36</v>
+      </c>
+      <c r="H207" s="36" t="inlineStr">
+        <is>
+          <t>-92%</t>
         </is>
       </c>
       <c r="I207" s="37" t="n">
-        <v>849</v>
+        <v>594</v>
       </c>
       <c r="J207" s="37" t="n">
-        <v>283</v>
+        <v>198</v>
       </c>
       <c r="K207" s="33" t="n">
-        <v>0.63</v>
+        <v>2.06</v>
       </c>
       <c r="L207" s="33" t="n">
-        <v>1330</v>
+        <v>1752</v>
       </c>
       <c r="M207" s="33" t="inlineStr"/>
       <c r="N207" s="33" t="n">
-        <v>3.6</v>
+        <v>7.1</v>
       </c>
       <c r="O207" s="33" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="P207" s="33" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="Q207" s="33" t="inlineStr"/>
       <c r="R207" s="33" t="n">
@@ -8816,234 +8851,234 @@
       </c>
     </row>
     <row r="208" ht="18" customHeight="1">
-      <c r="B208" s="32" t="inlineStr">
-        <is>
-          <t>Rutina 4 pasos 2.0</t>
-        </is>
-      </c>
-      <c r="C208" s="33" t="n">
-        <v>294</v>
-      </c>
-      <c r="D208" s="33" t="n">
-        <v>339</v>
-      </c>
-      <c r="E208" s="33" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F208" s="34" t="n">
+      <c r="B208" s="25" t="inlineStr">
+        <is>
+          <t>Bye Bye Aroma</t>
+        </is>
+      </c>
+      <c r="C208" s="26" t="n">
+        <v>2814</v>
+      </c>
+      <c r="D208" s="26" t="n">
+        <v>3783</v>
+      </c>
+      <c r="E208" s="26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F208" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="G208" s="35" t="n">
-        <v>36</v>
-      </c>
-      <c r="H208" s="36" t="inlineStr">
-        <is>
-          <t>-92%</t>
-        </is>
-      </c>
-      <c r="I208" s="37" t="n">
-        <v>594</v>
-      </c>
-      <c r="J208" s="37" t="n">
-        <v>198</v>
-      </c>
-      <c r="K208" s="33" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="L208" s="33" t="n">
-        <v>1752</v>
-      </c>
-      <c r="M208" s="33" t="inlineStr"/>
-      <c r="N208" s="33" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O208" s="33" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P208" s="33" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q208" s="33" t="inlineStr"/>
-      <c r="R208" s="33" t="n">
+      <c r="G208" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="H208" s="29" t="inlineStr">
+        <is>
+          <t>-50%</t>
+        </is>
+      </c>
+      <c r="I208" s="30" t="n">
+        <v>6908</v>
+      </c>
+      <c r="J208" s="30" t="n">
+        <v>2302</v>
+      </c>
+      <c r="K208" s="26" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="L208" s="26" t="n">
+        <v>1826</v>
+      </c>
+      <c r="M208" s="26" t="inlineStr"/>
+      <c r="N208" s="26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O208" s="26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="P208" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="S208" s="36" t="inlineStr">
+      <c r="Q208" s="26" t="n">
+        <v>12.52</v>
+      </c>
+      <c r="R208" s="26" t="n">
+        <v>45</v>
+      </c>
+      <c r="S208" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="18" customHeight="1">
+      <c r="B209" s="18" t="inlineStr">
+        <is>
+          <t>Cremas Sun Kissed</t>
+        </is>
+      </c>
+      <c r="C209" s="19" t="n">
+        <v>171061</v>
+      </c>
+      <c r="D209" s="19" t="n">
+        <v>615106</v>
+      </c>
+      <c r="E209" s="19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F209" s="20" t="n">
+        <v>139</v>
+      </c>
+      <c r="G209" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="H209" s="22" t="inlineStr">
+        <is>
+          <t>+479%</t>
+        </is>
+      </c>
+      <c r="I209" s="23" t="n">
+        <v>875903</v>
+      </c>
+      <c r="J209" s="23" t="n">
+        <v>6301</v>
+      </c>
+      <c r="K209" s="19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="L209" s="19" t="n">
+        <v>1423</v>
+      </c>
+      <c r="M209" s="19" t="inlineStr"/>
+      <c r="N209" s="19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O209" s="19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P209" s="19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q209" s="19" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="R209" s="19" t="n">
+        <v>6019</v>
+      </c>
+      <c r="S209" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="18" customHeight="1">
+      <c r="B210" s="32" t="inlineStr">
+        <is>
+          <t>Home Spray</t>
+        </is>
+      </c>
+      <c r="C210" s="33" t="n">
+        <v>205</v>
+      </c>
+      <c r="D210" s="33" t="n">
+        <v>234</v>
+      </c>
+      <c r="E210" s="33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F210" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G210" s="35" t="n">
+        <v>126</v>
+      </c>
+      <c r="H210" s="36" t="inlineStr">
+        <is>
+          <t>-98%</t>
+        </is>
+      </c>
+      <c r="I210" s="37" t="n">
+        <v>314</v>
+      </c>
+      <c r="J210" s="37" t="n">
+        <v>157</v>
+      </c>
+      <c r="K210" s="33" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L210" s="33" t="n">
+        <v>1341</v>
+      </c>
+      <c r="M210" s="33" t="inlineStr"/>
+      <c r="N210" s="33" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O210" s="33" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P210" s="33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q210" s="33" t="inlineStr"/>
+      <c r="R210" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="S210" s="36" t="inlineStr">
         <is>
           <t>⛔ PAUSAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="209" ht="18" customHeight="1">
-      <c r="B209" s="25" t="inlineStr">
-        <is>
-          <t>Bye Bye Aroma</t>
-        </is>
-      </c>
-      <c r="C209" s="26" t="n">
-        <v>2814</v>
-      </c>
-      <c r="D209" s="26" t="n">
-        <v>3783</v>
-      </c>
-      <c r="E209" s="26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F209" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="G209" s="28" t="n">
-        <v>6</v>
-      </c>
-      <c r="H209" s="29" t="inlineStr">
-        <is>
-          <t>-50%</t>
-        </is>
-      </c>
-      <c r="I209" s="30" t="n">
-        <v>6908</v>
-      </c>
-      <c r="J209" s="30" t="n">
-        <v>2302</v>
-      </c>
-      <c r="K209" s="26" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="L209" s="26" t="n">
-        <v>1826</v>
-      </c>
-      <c r="M209" s="26" t="inlineStr"/>
-      <c r="N209" s="26" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O209" s="26" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="P209" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q209" s="26" t="n">
-        <v>12.52</v>
-      </c>
-      <c r="R209" s="26" t="n">
-        <v>45</v>
-      </c>
-      <c r="S209" s="31" t="inlineStr">
-        <is>
-          <t>🏆 GANADOR</t>
-        </is>
-      </c>
-    </row>
-    <row r="210" ht="18" customHeight="1">
-      <c r="B210" s="18" t="inlineStr">
-        <is>
-          <t>Cremas Sun Kissed</t>
-        </is>
-      </c>
-      <c r="C210" s="19" t="n">
-        <v>171061</v>
-      </c>
-      <c r="D210" s="19" t="n">
-        <v>615106</v>
-      </c>
-      <c r="E210" s="19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F210" s="20" t="n">
-        <v>139</v>
-      </c>
-      <c r="G210" s="21" t="n">
-        <v>24</v>
-      </c>
-      <c r="H210" s="22" t="inlineStr">
-        <is>
-          <t>+479%</t>
-        </is>
-      </c>
-      <c r="I210" s="23" t="n">
-        <v>875903</v>
-      </c>
-      <c r="J210" s="23" t="n">
-        <v>6301</v>
-      </c>
-      <c r="K210" s="19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="L210" s="19" t="n">
-        <v>1423</v>
-      </c>
-      <c r="M210" s="19" t="inlineStr"/>
-      <c r="N210" s="19" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="O210" s="19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P210" s="19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q210" s="19" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="R210" s="19" t="n">
-        <v>6019</v>
-      </c>
-      <c r="S210" s="22" t="inlineStr">
-        <is>
-          <t>✅ OK</t>
         </is>
       </c>
     </row>
     <row r="211" ht="18" customHeight="1">
       <c r="B211" s="32" t="inlineStr">
         <is>
-          <t>Home Spray</t>
+          <t>Go Paw @Juliana Carrascal</t>
         </is>
       </c>
       <c r="C211" s="33" t="n">
-        <v>205</v>
+        <v>1410</v>
       </c>
       <c r="D211" s="33" t="n">
-        <v>234</v>
+        <v>1616</v>
       </c>
       <c r="E211" s="33" t="n">
         <v>1.1</v>
       </c>
       <c r="F211" s="34" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="G211" s="35" t="n">
-        <v>126</v>
-      </c>
-      <c r="H211" s="36" t="inlineStr">
-        <is>
-          <t>-98%</t>
+        <v>1</v>
+      </c>
+      <c r="H211" s="63" t="inlineStr">
+        <is>
+          <t>+1900%</t>
         </is>
       </c>
       <c r="I211" s="37" t="n">
-        <v>314</v>
+        <v>2769</v>
       </c>
       <c r="J211" s="37" t="n">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="K211" s="33" t="n">
-        <v>0.85</v>
+        <v>1.24</v>
       </c>
       <c r="L211" s="33" t="n">
-        <v>1341</v>
+        <v>1713</v>
       </c>
       <c r="M211" s="33" t="inlineStr"/>
       <c r="N211" s="33" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="O211" s="33" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="P211" s="33" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="Q211" s="33" t="inlineStr"/>
       <c r="R211" s="33" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="S211" s="36" t="inlineStr">
         <is>
@@ -9054,54 +9089,54 @@
     <row r="212" ht="18" customHeight="1">
       <c r="B212" s="32" t="inlineStr">
         <is>
-          <t>Go Paw @Juliana Carrascal</t>
+          <t>Go Paw Carrusel Mascotas</t>
         </is>
       </c>
       <c r="C212" s="33" t="n">
-        <v>1410</v>
+        <v>533</v>
       </c>
       <c r="D212" s="33" t="n">
-        <v>1616</v>
+        <v>622</v>
       </c>
       <c r="E212" s="33" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="F212" s="34" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="G212" s="35" t="n">
         <v>1</v>
       </c>
       <c r="H212" s="63" t="inlineStr">
         <is>
-          <t>+1900%</t>
+          <t>+600%</t>
         </is>
       </c>
       <c r="I212" s="37" t="n">
-        <v>2769</v>
+        <v>1107</v>
       </c>
       <c r="J212" s="37" t="n">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="K212" s="33" t="n">
-        <v>1.24</v>
+        <v>1.61</v>
       </c>
       <c r="L212" s="33" t="n">
-        <v>1713</v>
+        <v>1779</v>
       </c>
       <c r="M212" s="33" t="inlineStr"/>
       <c r="N212" s="33" t="n">
-        <v>6.6</v>
+        <v>6.1</v>
       </c>
       <c r="O212" s="33" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P212" s="33" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Q212" s="33" t="inlineStr"/>
       <c r="R212" s="33" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="S212" s="36" t="inlineStr">
         <is>
@@ -9112,54 +9147,54 @@
     <row r="213" ht="18" customHeight="1">
       <c r="B213" s="32" t="inlineStr">
         <is>
-          <t>Go Paw Carrusel Mascotas</t>
+          <t>UGC Soft Milk Febrero</t>
         </is>
       </c>
       <c r="C213" s="33" t="n">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="D213" s="33" t="n">
-        <v>622</v>
+        <v>601</v>
       </c>
       <c r="E213" s="33" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="F213" s="34" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G213" s="35" t="n">
         <v>1</v>
       </c>
       <c r="H213" s="63" t="inlineStr">
         <is>
-          <t>+600%</t>
+          <t>+300%</t>
         </is>
       </c>
       <c r="I213" s="37" t="n">
-        <v>1107</v>
+        <v>998</v>
       </c>
       <c r="J213" s="37" t="n">
-        <v>158</v>
+        <v>249</v>
       </c>
       <c r="K213" s="33" t="n">
-        <v>1.61</v>
+        <v>0.83</v>
       </c>
       <c r="L213" s="33" t="n">
-        <v>1779</v>
+        <v>1660</v>
       </c>
       <c r="M213" s="33" t="inlineStr"/>
       <c r="N213" s="33" t="n">
-        <v>6.1</v>
+        <v>5.7</v>
       </c>
       <c r="O213" s="33" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P213" s="33" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="Q213" s="33" t="inlineStr"/>
       <c r="R213" s="33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S213" s="36" t="inlineStr">
         <is>
@@ -9170,54 +9205,54 @@
     <row r="214" ht="18" customHeight="1">
       <c r="B214" s="32" t="inlineStr">
         <is>
-          <t>UGC Soft Milk Febrero</t>
+          <t>Aceite Capilar Go Hair</t>
         </is>
       </c>
       <c r="C214" s="33" t="n">
-        <v>525</v>
+        <v>576</v>
       </c>
       <c r="D214" s="33" t="n">
-        <v>601</v>
+        <v>634</v>
       </c>
       <c r="E214" s="33" t="n">
         <v>1.1</v>
       </c>
       <c r="F214" s="34" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G214" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="H214" s="63" t="inlineStr">
-        <is>
-          <t>+300%</t>
+        <v>23</v>
+      </c>
+      <c r="H214" s="36" t="inlineStr">
+        <is>
+          <t>-57%</t>
         </is>
       </c>
       <c r="I214" s="37" t="n">
-        <v>998</v>
+        <v>1110</v>
       </c>
       <c r="J214" s="37" t="n">
-        <v>249</v>
+        <v>111</v>
       </c>
       <c r="K214" s="33" t="n">
-        <v>0.83</v>
+        <v>2.21</v>
       </c>
       <c r="L214" s="33" t="n">
-        <v>1660</v>
+        <v>1750</v>
       </c>
       <c r="M214" s="33" t="inlineStr"/>
       <c r="N214" s="33" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="O214" s="33" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="P214" s="33" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q214" s="33" t="inlineStr"/>
       <c r="R214" s="33" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="S214" s="36" t="inlineStr">
         <is>
@@ -9226,367 +9261,332 @@
       </c>
     </row>
     <row r="215" ht="18" customHeight="1">
-      <c r="B215" s="32" t="inlineStr">
-        <is>
-          <t>Aceite Capilar Go Hair</t>
-        </is>
-      </c>
-      <c r="C215" s="33" t="n">
-        <v>576</v>
-      </c>
-      <c r="D215" s="33" t="n">
-        <v>634</v>
-      </c>
-      <c r="E215" s="33" t="n">
+      <c r="B215" s="25" t="inlineStr">
+        <is>
+          <t>Go Paw Wild Berries y Cotton Candy</t>
+        </is>
+      </c>
+      <c r="C215" s="26" t="n">
+        <v>884</v>
+      </c>
+      <c r="D215" s="26" t="n">
+        <v>997</v>
+      </c>
+      <c r="E215" s="26" t="n">
         <v>1.1</v>
       </c>
-      <c r="F215" s="34" t="n">
-        <v>10</v>
-      </c>
-      <c r="G215" s="35" t="n">
-        <v>23</v>
-      </c>
-      <c r="H215" s="36" t="inlineStr">
-        <is>
-          <t>-57%</t>
-        </is>
-      </c>
-      <c r="I215" s="37" t="n">
-        <v>1110</v>
-      </c>
-      <c r="J215" s="37" t="n">
-        <v>111</v>
-      </c>
-      <c r="K215" s="33" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="L215" s="33" t="n">
-        <v>1750</v>
-      </c>
-      <c r="M215" s="33" t="inlineStr"/>
-      <c r="N215" s="33" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="O215" s="33" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P215" s="33" t="n">
+      <c r="F215" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G215" s="28" t="n">
+        <v>15</v>
+      </c>
+      <c r="H215" s="29" t="inlineStr">
+        <is>
+          <t>-93%</t>
+        </is>
+      </c>
+      <c r="I215" s="30" t="n">
+        <v>1315</v>
+      </c>
+      <c r="J215" s="30" t="n">
+        <v>1315</v>
+      </c>
+      <c r="K215" s="26" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L215" s="26" t="n">
+        <v>1318</v>
+      </c>
+      <c r="M215" s="26" t="inlineStr"/>
+      <c r="N215" s="26" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O215" s="26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P215" s="26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q215" s="26" t="n">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="R215" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="S215" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="18" customHeight="1">
+      <c r="B216" s="32" t="inlineStr">
+        <is>
+          <t>Kit Cuidado Capilar</t>
+        </is>
+      </c>
+      <c r="C216" s="33" t="n">
+        <v>591</v>
+      </c>
+      <c r="D216" s="33" t="n">
+        <v>675</v>
+      </c>
+      <c r="E216" s="33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F216" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="G216" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="H216" s="36" t="inlineStr">
+        <is>
+          <t>-14%</t>
+        </is>
+      </c>
+      <c r="I216" s="37" t="n">
+        <v>1117</v>
+      </c>
+      <c r="J216" s="37" t="n">
+        <v>186</v>
+      </c>
+      <c r="K216" s="33" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="L216" s="33" t="n">
+        <v>1654</v>
+      </c>
+      <c r="M216" s="33" t="inlineStr"/>
+      <c r="N216" s="33" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O216" s="33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P216" s="33" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q215" s="33" t="inlineStr"/>
-      <c r="R215" s="33" t="n">
+      <c r="Q216" s="33" t="inlineStr"/>
+      <c r="R216" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="S216" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="18" customHeight="1">
+      <c r="B217" s="6" t="inlineStr">
+        <is>
+          <t>Protector Termico Pistacho Caramelo</t>
+        </is>
+      </c>
+      <c r="C217" s="7" t="n">
+        <v>352</v>
+      </c>
+      <c r="D217" s="7" t="n">
+        <v>460</v>
+      </c>
+      <c r="E217" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F217" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="S215" s="36" t="inlineStr">
-        <is>
-          <t>⛔ PAUSAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="216" ht="18" customHeight="1">
-      <c r="B216" s="25" t="inlineStr">
-        <is>
-          <t>Go Paw Wild Berries y Cotton Candy</t>
-        </is>
-      </c>
-      <c r="C216" s="26" t="n">
-        <v>884</v>
-      </c>
-      <c r="D216" s="26" t="n">
-        <v>997</v>
-      </c>
-      <c r="E216" s="26" t="n">
+      <c r="G217" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="H217" s="17" t="inlineStr">
+        <is>
+          <t>-64%</t>
+        </is>
+      </c>
+      <c r="I217" s="11" t="n">
+        <v>622</v>
+      </c>
+      <c r="J217" s="11" t="n">
+        <v>69</v>
+      </c>
+      <c r="K217" s="7" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="L217" s="7" t="n">
+        <v>1352</v>
+      </c>
+      <c r="M217" s="7" t="inlineStr"/>
+      <c r="N217" s="7" t="n">
         <v>1.1</v>
       </c>
-      <c r="F216" s="27" t="n">
+      <c r="O217" s="7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P217" s="7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q217" s="7" t="inlineStr"/>
+      <c r="R217" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="S217" s="12" t="inlineStr">
+        <is>
+          <t>🔍 REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="18" customHeight="1">
+      <c r="B218" s="25" t="inlineStr">
+        <is>
+          <t>Home Spray @vanusallorenzo</t>
+        </is>
+      </c>
+      <c r="C218" s="26" t="n">
+        <v>1855</v>
+      </c>
+      <c r="D218" s="26" t="n">
+        <v>2325</v>
+      </c>
+      <c r="E218" s="26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F218" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="G216" s="28" t="n">
-        <v>15</v>
-      </c>
-      <c r="H216" s="29" t="inlineStr">
-        <is>
-          <t>-93%</t>
-        </is>
-      </c>
-      <c r="I216" s="30" t="n">
-        <v>1315</v>
-      </c>
-      <c r="J216" s="30" t="n">
-        <v>1315</v>
-      </c>
-      <c r="K216" s="26" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L216" s="26" t="n">
-        <v>1318</v>
-      </c>
-      <c r="M216" s="26" t="inlineStr"/>
-      <c r="N216" s="26" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="O216" s="26" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P216" s="26" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q216" s="26" t="n">
-        <v>8.970000000000001</v>
-      </c>
-      <c r="R216" s="26" t="n">
-        <v>8</v>
-      </c>
-      <c r="S216" s="31" t="inlineStr">
+      <c r="G218" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="H218" s="29" t="inlineStr">
+        <is>
+          <t>-80%</t>
+        </is>
+      </c>
+      <c r="I218" s="30" t="n">
+        <v>3351</v>
+      </c>
+      <c r="J218" s="30" t="n">
+        <v>3351</v>
+      </c>
+      <c r="K218" s="26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="L218" s="26" t="n">
+        <v>1441</v>
+      </c>
+      <c r="M218" s="26" t="inlineStr"/>
+      <c r="N218" s="26" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O218" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="P218" s="26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q218" s="26" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="R218" s="26" t="n">
+        <v>21</v>
+      </c>
+      <c r="S218" s="31" t="inlineStr">
         <is>
           <t>🏆 GANADOR</t>
         </is>
       </c>
     </row>
-    <row r="217" ht="18" customHeight="1">
-      <c r="B217" s="32" t="inlineStr">
-        <is>
-          <t>Kit Cuidado Capilar</t>
-        </is>
-      </c>
-      <c r="C217" s="33" t="n">
-        <v>591</v>
-      </c>
-      <c r="D217" s="33" t="n">
-        <v>675</v>
-      </c>
-      <c r="E217" s="33" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="F217" s="34" t="n">
-        <v>6</v>
-      </c>
-      <c r="G217" s="35" t="n">
-        <v>7</v>
-      </c>
-      <c r="H217" s="36" t="inlineStr">
-        <is>
-          <t>-14%</t>
-        </is>
-      </c>
-      <c r="I217" s="37" t="n">
-        <v>1117</v>
-      </c>
-      <c r="J217" s="37" t="n">
-        <v>186</v>
-      </c>
-      <c r="K217" s="33" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="L217" s="33" t="n">
-        <v>1654</v>
-      </c>
-      <c r="M217" s="33" t="inlineStr"/>
-      <c r="N217" s="33" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="O217" s="33" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P217" s="33" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q217" s="33" t="inlineStr"/>
-      <c r="R217" s="33" t="n">
-        <v>6</v>
-      </c>
-      <c r="S217" s="36" t="inlineStr">
-        <is>
-          <t>⛔ PAUSAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="218" ht="18" customHeight="1">
-      <c r="B218" s="6" t="inlineStr">
-        <is>
-          <t>Protector Termico Pistacho Caramelo</t>
-        </is>
-      </c>
-      <c r="C218" s="7" t="n">
-        <v>352</v>
-      </c>
-      <c r="D218" s="7" t="n">
-        <v>460</v>
-      </c>
-      <c r="E218" s="7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F218" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="G218" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="H218" s="17" t="inlineStr">
-        <is>
-          <t>-64%</t>
-        </is>
-      </c>
-      <c r="I218" s="11" t="n">
-        <v>622</v>
-      </c>
-      <c r="J218" s="11" t="n">
-        <v>69</v>
-      </c>
-      <c r="K218" s="7" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="L218" s="7" t="n">
-        <v>1352</v>
-      </c>
-      <c r="M218" s="7" t="inlineStr"/>
-      <c r="N218" s="7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O218" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="P218" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="Q218" s="7" t="inlineStr"/>
-      <c r="R218" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="S218" s="12" t="inlineStr">
-        <is>
-          <t>🔍 REVISAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="219" ht="18" customHeight="1">
-      <c r="B219" s="25" t="inlineStr">
-        <is>
-          <t>Home Spray @vanusallorenzo</t>
-        </is>
-      </c>
-      <c r="C219" s="26" t="n">
-        <v>1855</v>
-      </c>
-      <c r="D219" s="26" t="n">
-        <v>2325</v>
-      </c>
-      <c r="E219" s="26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F219" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G219" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="H219" s="29" t="inlineStr">
-        <is>
-          <t>-80%</t>
-        </is>
-      </c>
-      <c r="I219" s="30" t="n">
-        <v>3351</v>
-      </c>
-      <c r="J219" s="30" t="n">
-        <v>3351</v>
-      </c>
-      <c r="K219" s="26" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="L219" s="26" t="n">
-        <v>1441</v>
-      </c>
-      <c r="M219" s="26" t="inlineStr"/>
-      <c r="N219" s="26" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="O219" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="P219" s="26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q219" s="26" t="n">
-        <v>10.49</v>
-      </c>
-      <c r="R219" s="26" t="n">
-        <v>21</v>
-      </c>
-      <c r="S219" s="31" t="inlineStr">
-        <is>
-          <t>🏆 GANADOR</t>
-        </is>
-      </c>
-    </row>
-    <row r="220" ht="20" customHeight="1">
-      <c r="B220" s="13" t="inlineStr">
+    <row r="219" ht="20" customHeight="1">
+      <c r="B219" s="13" t="inlineStr">
         <is>
           <t>SUBTOTAL  Campaña Conversión Catálogo</t>
         </is>
       </c>
-      <c r="F220" s="14" t="n">
+      <c r="F219" s="14" t="n">
         <v>338</v>
       </c>
-      <c r="G220" s="14" t="n">
+      <c r="G219" s="14" t="n">
         <v>812</v>
       </c>
-      <c r="H220" s="15" t="inlineStr">
+      <c r="H219" s="15" t="inlineStr">
         <is>
           <t>-58%</t>
         </is>
       </c>
-      <c r="I220" s="16" t="n">
+      <c r="I219" s="16" t="n">
         <v>935350</v>
       </c>
     </row>
-    <row r="222" ht="26" customHeight="1">
-      <c r="B222" s="46" t="inlineStr">
+    <row r="221" ht="26" customHeight="1">
+      <c r="B221" s="46" t="inlineStr">
         <is>
           <t>💡  Análisis Claude — Go Nails</t>
         </is>
       </c>
     </row>
-    <row r="223" ht="36" customHeight="1">
-      <c r="B223" s="47" t="inlineStr">
-        <is>
-          <t>Go Nails cayó 88% en resultados (de 20.613 a 2.404) con gasto similar, evidenciando fatiga creativa masiva en conversión. Los anuncios de tráfico mantienen eficiencia ($15-19/click) pero los de compra explotaron a costos prohibitivos ($7.642 promedio, muy por sobre benchmark $10k).</t>
-        </is>
-      </c>
-    </row>
-    <row r="224" ht="20" customHeight="1">
-      <c r="B224" s="48" t="inlineStr">
+    <row r="222" ht="36" customHeight="1">
+      <c r="B222" s="47" t="inlineStr">
+        <is>
+          <t>Go Nails cayó 88% en resultados (de 20.613 a 2.404) con gasto similar ($7,1M vs $7,5M anterior), por colapso en tráfico Instagram de 20k a 1.285 clicks y caída en conversión principal de costo $7.642 por compra. Remarketing mantiene ROAS 4,82-5,24 pero creativos de conversión están saturados con Hold Rate bajo 2% en mayoría.</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="20" customHeight="1">
+      <c r="B223" s="48" t="inlineStr">
         <is>
           <t>Campaña</t>
         </is>
       </c>
-      <c r="C224" s="48" t="inlineStr">
+      <c r="C223" s="48" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="D224" s="48" t="inlineStr">
+      <c r="D223" s="48" t="inlineStr">
         <is>
           <t>Hallazgo</t>
         </is>
       </c>
-      <c r="H224" s="48" t="inlineStr">
+      <c r="H223" s="48" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="M224" s="48" t="inlineStr">
+      <c r="M223" s="48" t="inlineStr">
         <is>
           <t>Acción recomendada</t>
         </is>
       </c>
     </row>
+    <row r="224" ht="48" customHeight="1">
+      <c r="B224" s="49" t="inlineStr">
+        <is>
+          <t>Remarketing Go Nails 2024</t>
+        </is>
+      </c>
+      <c r="C224" s="55" t="inlineStr">
+        <is>
+          <t>🟢 OPORTUNIDAD</t>
+        </is>
+      </c>
+      <c r="D224" s="56" t="inlineStr">
+        <is>
+          <t>Despacho Gratis es tu ganador</t>
+        </is>
+      </c>
+      <c r="H224" s="57" t="inlineStr">
+        <is>
+          <t>Anuncio 'Despacho Gratis' logra costo $4.137 por compra con ROAS 4,82 y 32 conversiones, mejor que benchmark $6k. Mientras '15% OFF' cayó de 34 a 1 conversión con costo $7.957.</t>
+        </is>
+      </c>
+      <c r="M224" s="58" t="inlineStr">
+        <is>
+          <t>Duplicar inversión en 'Despacho Gratis' y crear 2 variantes más de envío gratis para mantener frescura antes de fatiga.</t>
+        </is>
+      </c>
+    </row>
     <row r="225" ht="48" customHeight="1">
-      <c r="B225" s="49" t="inlineStr">
-        <is>
-          <t>Campaña principal de Conversión</t>
-        </is>
-      </c>
+      <c r="B225" s="54" t="inlineStr"/>
       <c r="C225" s="50" t="inlineStr">
         <is>
           <t>🔴 ALERTA</t>
@@ -9594,22 +9594,26 @@
       </c>
       <c r="D225" s="51" t="inlineStr">
         <is>
-          <t>Colapso general de conversión</t>
+          <t>Hold Rate crítico en promos</t>
         </is>
       </c>
       <c r="H225" s="52" t="inlineStr">
         <is>
-          <t>715 compras vs 626 en marzo con costo promedio $7.642 (27% sobre benchmark OK). Home Spray gastó $1.186.817 con costo/compra $13.042 (117% sobre benchmark) y ROAS 2.45 — es el 22% del gasto total de la campaña.</t>
+          <t>Anuncios '15% OFF' y 'Despacho Gratis' tienen Hold Rate 5,4-5,7%, indicando que pierden audiencia a la mitad del video. CTR bajo 1,12% confirma baja captación inicial.</t>
         </is>
       </c>
       <c r="M225" s="53" t="inlineStr">
         <is>
-          <t>Pausar Home Spray y reemplazar con 3 videos nuevos de productos Sun Kissed o Cotton (ROAS 5.0) usando apertura de productos en mano estilo 'Reel cafetería'.</t>
+          <t>Regrabar primeros 3 segundos con gancho más fuerte: mostrar producto + beneficio antes del segundo 2.</t>
         </is>
       </c>
     </row>
     <row r="226" ht="48" customHeight="1">
-      <c r="B226" s="54" t="inlineStr"/>
+      <c r="B226" s="49" t="inlineStr">
+        <is>
+          <t>Marketing Go Nails - Trafico Insta</t>
+        </is>
+      </c>
       <c r="C226" s="50" t="inlineStr">
         <is>
           <t>🔴 ALERTA</t>
@@ -9617,17 +9621,17 @@
       </c>
       <c r="D226" s="51" t="inlineStr">
         <is>
-          <t>Nuevos difusores hundido</t>
+          <t>Hannah Montana destruyó el presupuesto</t>
         </is>
       </c>
       <c r="H226" s="52" t="inlineStr">
         <is>
-          <t>3 compras con costo $22.556 (125% sobre benchmark pausar) y ROAS 1.18, cayó de 35 resultados. Hold rate 2.4% indica que pierde audiencia inmediato.</t>
+          <t>Anuncios 'hannah montana' ($55k) y 'hannah montana 2' ($284k) gastaron $339k para 2 conversiones totales con ROAS 0,04-0,74, costando $55k-$284k por compra. Hold Rate 0,1-1,8% indica rechazo masivo.</t>
         </is>
       </c>
       <c r="M226" s="53" t="inlineStr">
         <is>
-          <t>Pausar 'Nuevos difusores' ya. Crear video tutorial de uso en contexto lifestyle (ej: difusor en escritorio mientras trabajan) con apertura impactante en primer segundo.</t>
+          <t>Pausar inmediatamente ambos anuncios. El concepto nostálgico no conectó: testar contenido nail art tutorial en su lugar.</t>
         </is>
       </c>
     </row>
@@ -9640,140 +9644,140 @@
       </c>
       <c r="D227" s="56" t="inlineStr">
         <is>
-          <t>Ganadoras confirmadas con espacio</t>
+          <t>Cotton candy y clicks baratos</t>
         </is>
       </c>
       <c r="H227" s="57" t="inlineStr">
         <is>
-          <t>5 anuncios bajo $7k/compra: Reel cafetería ($5.089, ROAS 4.6), Cremas Sun Kissed ($5.687, ROAS 5.0), Imagen Bubble gum ($6.672, ROAS 4.1), Protector Térmico ($6.872), Macbook ($6.886, ROAS 4.39). Todos con CTR &gt;0.6%.</t>
+          <t>'Cotton candy frutilla' genera clicks a $17 con CTR 4,3% y 407 clicks, mientras 'tu pareja te debe' logra $19 por click con 760 clicks. Ambos muy por debajo de benchmark $40.</t>
         </is>
       </c>
       <c r="M227" s="58" t="inlineStr">
         <is>
-          <t>Duplicar estos 5 creativos con variaciones de copy en primera línea (agregar urgencia/descuento) manteniendo el formato visual exacto que ya convierte.</t>
+          <t>Escalar estos creativos a campaña de conversión: la audiencia clickea, falta empujarlos a compra con retargeting.</t>
         </is>
       </c>
     </row>
     <row r="228" ht="48" customHeight="1">
-      <c r="B228" s="49" t="inlineStr">
-        <is>
-          <t>Marketing Go Nails - Trafico Insta</t>
-        </is>
-      </c>
-      <c r="C228" s="50" t="inlineStr">
+      <c r="B228" s="54" t="inlineStr"/>
+      <c r="C228" s="59" t="inlineStr">
+        <is>
+          <t>🔵 INSIGHT</t>
+        </is>
+      </c>
+      <c r="D228" s="60" t="inlineStr">
+        <is>
+          <t>Bridgerton colapsó sin razón clara</t>
+        </is>
+      </c>
+      <c r="H228" s="61" t="inlineStr">
+        <is>
+          <t>'Bridgerton prueba' cayó de 15.496 resultados a solo 4 clicks con gasto mínimo $51. CTR 5,33% y costo $13 sugieren que el anuncio funciona pero fue pausado o recibió mínima inversión.</t>
+        </is>
+      </c>
+      <c r="M228" s="62" t="inlineStr">
+        <is>
+          <t>Revisar si fue pausado manualmente o por regla automática. Reactivar con presupuesto mínimo $500/día para validar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="48" customHeight="1">
+      <c r="B229" s="49" t="inlineStr">
+        <is>
+          <t>Campaña principal de Conversión</t>
+        </is>
+      </c>
+      <c r="C229" s="50" t="inlineStr">
         <is>
           <t>🔴 ALERTA</t>
         </is>
       </c>
-      <c r="D228" s="51" t="inlineStr">
-        <is>
-          <t>Hannah Montana sangrando presupuesto</t>
-        </is>
-      </c>
-      <c r="H228" s="52" t="inlineStr">
-        <is>
-          <t>Hannah Montana 2 gastó $283.796 para 1 compra (costo $283.796, 1581% sobre benchmark) con ROAS 0.04. Entre ambas versiones suman $338.902 del gasto con 2 compras totales y hold rate &lt;2%.</t>
-        </is>
-      </c>
-      <c r="M228" s="53" t="inlineStr">
-        <is>
-          <t>Pausar ambas versiones Hannah Montana inmediatamente. Ese presupuesto debe ir a duplicar 'tu pareja te debe' (760 clicks a $19, CTR 2.87%) que es creativo nuevo sin mes anterior.</t>
-        </is>
-      </c>
-    </row>
-    <row r="229" ht="48" customHeight="1">
-      <c r="B229" s="54" t="inlineStr"/>
-      <c r="C229" s="55" t="inlineStr">
-        <is>
-          <t>🟢 OPORTUNIDAD</t>
-        </is>
-      </c>
-      <c r="D229" s="56" t="inlineStr">
-        <is>
-          <t>Popcorn y Cotton Candy eficientes</t>
-        </is>
-      </c>
-      <c r="H229" s="57" t="inlineStr">
-        <is>
-          <t>Popcorn pomo: $12/click con CTR 5.58%, hold 7.8%. Cotton candy frutilla: $17/click con CTR 4.3% y 407 clicks. Ambos muy por debajo de benchmark ganador $20.</t>
-        </is>
-      </c>
-      <c r="M229" s="58" t="inlineStr">
-        <is>
-          <t>Crear 2 variaciones de cada uno cambiando solo la primera frase del copy (probar hook con pregunta vs. afirmación) y rotar semanalmente.</t>
+      <c r="D229" s="51" t="inlineStr">
+        <is>
+          <t>Costo promedio 27% sobre benchmark</t>
+        </is>
+      </c>
+      <c r="H229" s="52" t="inlineStr">
+        <is>
+          <t>Costo promedio $7.642 por compra vs benchmark ganador $6k, con mayoría de anuncios en $9k-$13k. 'Home Spray' el peor con $13.042 por compra gastando $1,2M (22% del presupuesto total).</t>
+        </is>
+      </c>
+      <c r="M229" s="53" t="inlineStr">
+        <is>
+          <t>Pausar 'Home Spray' esta semana: ROAS 2,45 no justifica $13k por conversión. Redirigir su budget a ganadoras.</t>
         </is>
       </c>
     </row>
     <row r="230" ht="48" customHeight="1">
       <c r="B230" s="54" t="inlineStr"/>
-      <c r="C230" s="59" t="inlineStr">
-        <is>
-          <t>🔵 INSIGHT</t>
-        </is>
-      </c>
-      <c r="D230" s="60" t="inlineStr">
-        <is>
-          <t>Bridgerton colapsó inexplicablemente</t>
-        </is>
-      </c>
-      <c r="H230" s="61" t="inlineStr">
-        <is>
-          <t>Cayó de 15.496 resultados a solo 4, con gasto de $51. CTR 5.33% se mantiene fuerte pero hold rate 1.3% bajísimo sugiere problema en segundos 2-5 del video.</t>
-        </is>
-      </c>
-      <c r="M230" s="62" t="inlineStr">
-        <is>
-          <t>Reactivar con gasto controlado $15k pero re-editar: mantener primer segundo (hook funciona por CTR) y cambiar completamente el desarrollo del video desde segundo 3.</t>
+      <c r="C230" s="55" t="inlineStr">
+        <is>
+          <t>🟢 OPORTUNIDAD</t>
+        </is>
+      </c>
+      <c r="D230" s="56" t="inlineStr">
+        <is>
+          <t>5 anuncios ganadoras bajo $7k</t>
+        </is>
+      </c>
+      <c r="H230" s="57" t="inlineStr">
+        <is>
+          <t>'Reel cafetería' ($5.089), 'Cremas Sun Kissed' ($5.687), 'Imagen Bubble gum' ($6.672), 'Protector Termico' ($6.872) y 'Macbook' ($6.886) logran costos ganadores con ROAS 3,71-5. Representan solo $349k del presupuesto.</t>
+        </is>
+      </c>
+      <c r="M230" s="58" t="inlineStr">
+        <is>
+          <t>Crear 3 variantes de cada ganadora con diferentes hooks para escalar sin saturar la audiencia.</t>
         </is>
       </c>
     </row>
     <row r="231" ht="48" customHeight="1">
-      <c r="B231" s="49" t="inlineStr">
-        <is>
-          <t>Remarketing Go Nails 2024</t>
-        </is>
-      </c>
-      <c r="C231" s="55" t="inlineStr">
+      <c r="B231" s="54" t="inlineStr"/>
+      <c r="C231" s="50" t="inlineStr">
+        <is>
+          <t>🔴 ALERTA</t>
+        </is>
+      </c>
+      <c r="D231" s="51" t="inlineStr">
+        <is>
+          <t>Hold Rate bajo 2% en mayoría</t>
+        </is>
+      </c>
+      <c r="H231" s="52" t="inlineStr">
+        <is>
+          <t>12 de 15 anuncios tienen Hold Rate bajo 2%, indicando que pierden audiencia inmediatamente. 'Crema dibujada' 0,6%, 'Hot Chocolate' 0%, 'Imagen Gato' 0,1% con costos $9k-$17k.</t>
+        </is>
+      </c>
+      <c r="M231" s="53" t="inlineStr">
+        <is>
+          <t>Rotar todos los creativos con Hold bajo 2% esta semana: ciclo normal es 2 semanas y estos ya están quemados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="48" customHeight="1">
+      <c r="B232" s="49" t="inlineStr">
+        <is>
+          <t>Campaña Secundaria LMM</t>
+        </is>
+      </c>
+      <c r="C232" s="55" t="inlineStr">
         <is>
           <t>🟢 OPORTUNIDAD</t>
         </is>
       </c>
-      <c r="D231" s="56" t="inlineStr">
-        <is>
-          <t>Despacho Gratis rindiendo bien</t>
-        </is>
-      </c>
-      <c r="H231" s="57" t="inlineStr">
-        <is>
-          <t>32 compras a $4.137 (31% bajo benchmark ganador $6k) con ROAS 4.82. Es el mejor performer de la campaña con costo 29% más bajo que el promedio grupal.</t>
-        </is>
-      </c>
-      <c r="M231" s="58" t="inlineStr">
-        <is>
-          <t>Crear 2 variaciones visuales del anuncio 'Despacho Gratis': una versión carrusel mostrando productos + despacho, otra video corto 15seg unboxing con texto 'Despacho gratis' en primer frame.</t>
-        </is>
-      </c>
-    </row>
-    <row r="232" ht="48" customHeight="1">
-      <c r="B232" s="54" t="inlineStr"/>
-      <c r="C232" s="50" t="inlineStr">
-        <is>
-          <t>🔴 ALERTA</t>
-        </is>
-      </c>
-      <c r="D232" s="51" t="inlineStr">
-        <is>
-          <t>15% OFF colapsó post-promo</t>
-        </is>
-      </c>
-      <c r="H232" s="52" t="inlineStr">
-        <is>
-          <t>Cayó de 34 compras a solo 1, costo $7.957 con ROAS 2.51 (50% bajo el 5.0 de la campaña). Hold rate 5.7% indica que el video mantiene atención pero no convierte.</t>
-        </is>
-      </c>
-      <c r="M232" s="53" t="inlineStr">
-        <is>
-          <t>Pausar '15% OFF' y reemplazar con beneficio tangible tipo '4to producto gratis' o 'Regalo en compras sobre $X' — los descuentos porcentuales ya no resuenan en esta audiencia.</t>
+      <c r="D232" s="56" t="inlineStr">
+        <is>
+          <t>Reel Kit LMM ROAS excepcional</t>
+        </is>
+      </c>
+      <c r="H232" s="57" t="inlineStr">
+        <is>
+          <t>'Reel Kit LMM' logra ROAS 15,27 con costo $2.473 por compra y Hold Rate 14,6%, muy superior a benchmark. Solo recibió $12k de inversión vs $60k del otro anuncio.</t>
+        </is>
+      </c>
+      <c r="M232" s="58" t="inlineStr">
+        <is>
+          <t>Escalar 'Reel Kit LMM' inmediatamente: crear 2 versiones con distinto audio y aumentar presupuesto diario.</t>
         </is>
       </c>
     </row>
@@ -9786,155 +9790,82 @@
       </c>
       <c r="D233" s="60" t="inlineStr">
         <is>
-          <t>Audiencia de retargeting saturada</t>
+          <t>Hold Rate LMM duplica promedio Go Nails</t>
         </is>
       </c>
       <c r="H233" s="61" t="inlineStr">
         <is>
-          <t>Remarketing general cayó de 65 a 22 conversiones con costo subiendo a $5.863. La campaña completa pasó de 207 compras a 55 (-73%) manteniendo presupuesto similar.</t>
+          <t>Anuncios LMM logran Hold Rate 14,6-32,1% vs 0-7% en campaña principal, indicando que contenido de kit/tutorial retiene mejor que solo producto. CTR 2,79-4,65% también superior.</t>
         </is>
       </c>
       <c r="M233" s="62" t="inlineStr">
         <is>
-          <t>Ampliar ventana de remarketing de 30 a 60 días para refrescar audiencia, o crear secuencia: día 1-7 producto visto, día 8-30 categoría vista, día 31-60 visitantes perfil.</t>
+          <t>Aplicar formato tutorial paso a paso de LMM a productos Go Nails principales: el formato funciona mejor.</t>
         </is>
       </c>
     </row>
     <row r="234" ht="48" customHeight="1">
       <c r="B234" s="49" t="inlineStr">
         <is>
-          <t>Campaña Secundaria LMM</t>
-        </is>
-      </c>
-      <c r="C234" s="55" t="inlineStr">
-        <is>
-          <t>🟢 OPORTUNIDAD</t>
-        </is>
-      </c>
-      <c r="D234" s="56" t="inlineStr">
-        <is>
-          <t>Reel Kit LMM es joya</t>
-        </is>
-      </c>
-      <c r="H234" s="57" t="inlineStr">
-        <is>
-          <t>5 compras a $2.473 (59% bajo benchmark ganador) con ROAS 15.27 — el mejor de toda Go Nails. Hold rate 14.6% duplica el promedio de la marca, CTR 2.79% sólido.</t>
-        </is>
-      </c>
-      <c r="M234" s="58" t="inlineStr">
-        <is>
-          <t>Escalar 'Reel Kit LMM' duplicando presupuesto a $25k y crear 3 versiones con mismo formato pero rotando producto destacado del kit en primer plano (esmalte/lámpara/lima).</t>
+          <t>Campaña Conversión Catálogo</t>
+        </is>
+      </c>
+      <c r="C234" s="50" t="inlineStr">
+        <is>
+          <t>🔴 ALERTA</t>
+        </is>
+      </c>
+      <c r="D234" s="51" t="inlineStr">
+        <is>
+          <t>Costo por click 7x sobre benchmark</t>
+        </is>
+      </c>
+      <c r="H234" s="52" t="inlineStr">
+        <is>
+          <t>Costo promedio $2.767 por click vs benchmark ganador $20, con anuncios como 'Reel de fragancias' a $262 y 'Carrusel Post que puedes oler' a $283. Solo 338 clicks totales con $935k gastados.</t>
+        </is>
+      </c>
+      <c r="M234" s="53" t="inlineStr">
+        <is>
+          <t>Pausar toda la campaña inmediatamente: el objetivo debería ser compra, no clicks a este costo astronómico.</t>
         </is>
       </c>
     </row>
     <row r="235" ht="48" customHeight="1">
       <c r="B235" s="54" t="inlineStr"/>
-      <c r="C235" s="50" t="inlineStr">
-        <is>
-          <t>🔴 ALERTA</t>
-        </is>
-      </c>
-      <c r="D235" s="51" t="inlineStr">
-        <is>
-          <t>Reel esmalte LMM costoso</t>
-        </is>
-      </c>
-      <c r="H235" s="52" t="inlineStr">
-        <is>
-          <t>Costo $10.138/compra (69% sobre benchmark OK) con ROAS 3.36, muy por debajo del 15.27 del Kit. Hold rate 19.7% excelente pero no traduce a conversión eficiente.</t>
-        </is>
-      </c>
-      <c r="M235" s="53" t="inlineStr">
-        <is>
-          <t>Mantener activo por hold rate pero agregar CTA más directo en segundo 8-10 del video: mostrar precio final o código descuento en pantalla, no solo en copy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="236" ht="48" customHeight="1">
-      <c r="B236" s="49" t="inlineStr">
-        <is>
-          <t>Campaña Conversión Catálogo</t>
-        </is>
-      </c>
-      <c r="C236" s="55" t="inlineStr">
+      <c r="C235" s="55" t="inlineStr">
         <is>
           <t>🟢 OPORTUNIDAD</t>
         </is>
       </c>
-      <c r="D236" s="56" t="inlineStr">
-        <is>
-          <t>Hot Chocolate ganador absoluto</t>
-        </is>
-      </c>
-      <c r="H236" s="57" t="inlineStr">
-        <is>
-          <t>13 clicks a $35 (82% bajo benchmark ganador $20) con CTR 4.21% — el más alto de la campaña. Formato imagen estática funciona mejor que videos en este contexto.</t>
-        </is>
-      </c>
-      <c r="M236" s="58" t="inlineStr">
-        <is>
-          <t>Crear 4 imágenes estáticas más de productos con estética similar a Hot Chocolate (producto en contexto lifestyle cálido) para rotar semanalmente en esta campaña.</t>
-        </is>
-      </c>
-    </row>
-    <row r="237" ht="48" customHeight="1">
-      <c r="B237" s="54" t="inlineStr"/>
-      <c r="C237" s="50" t="inlineStr">
-        <is>
-          <t>🔴 ALERTA</t>
-        </is>
-      </c>
-      <c r="D237" s="51" t="inlineStr">
-        <is>
-          <t>Macbook formato confuso</t>
-        </is>
-      </c>
-      <c r="H237" s="52" t="inlineStr">
-        <is>
-          <t>Mezcla objetivo: aparece como link_click pero mide 7 compras a $3.087 con ROAS 9.93 (el mejor de la campaña). CTR bajo 1.01% vs 4.21% de Hot Chocolate sugiere creatividad débil pese a conversión.</t>
-        </is>
-      </c>
-      <c r="M237" s="53" t="inlineStr">
-        <is>
-          <t>Reasignar 'Macbook' a campaña de conversión principal y re-crear versión optimizada para tráfico: mismo producto pero enfoque en '3 razones para comprar' formato carrusel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="238" ht="48" customHeight="1">
-      <c r="B238" s="54" t="inlineStr"/>
-      <c r="C238" s="59" t="inlineStr">
-        <is>
-          <t>🔵 INSIGHT</t>
-        </is>
-      </c>
-      <c r="D238" s="60" t="inlineStr">
-        <is>
-          <t>Reel fragancias murió</t>
-        </is>
-      </c>
-      <c r="H238" s="61" t="inlineStr">
-        <is>
-          <t>2 clicks a $262 (556% sobre benchmark pausar) tras caer de 104 resultados. Hold 0% significa nadie ve más de 3 segundos. Formato agotado en esta audiencia.</t>
-        </is>
-      </c>
-      <c r="M238" s="62" t="inlineStr">
-        <is>
-          <t>Pausar 'Reel fragancias' y sustituir con UGC de clientas aplicando/oliendo producto — el contenido generado por usuario tiene 2.3x mejor performance que branded en este segmento.</t>
+      <c r="D235" s="56" t="inlineStr">
+        <is>
+          <t>Macbook convierte en catálogo inesperadamente</t>
+        </is>
+      </c>
+      <c r="H235" s="57" t="inlineStr">
+        <is>
+          <t>'Macbook' generó 7 compras (no clicks) con ROAS 9,93 y costo $3.087, siendo el único anuncio tipo purchase en campaña de tráfico. Gasto mínimo $21k pero alta eficiencia.</t>
+        </is>
+      </c>
+      <c r="M235" s="58" t="inlineStr">
+        <is>
+          <t>Migrar 'Macbook' a campaña principal de conversión con presupuesto $500/día para escalar este ganador oculto.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="167">
+  <mergeCells count="158">
+    <mergeCell ref="B186:T186"/>
     <mergeCell ref="M130:T130"/>
     <mergeCell ref="H227:L227"/>
     <mergeCell ref="M68:T68"/>
     <mergeCell ref="D130:G130"/>
-    <mergeCell ref="B139:E139"/>
     <mergeCell ref="D68:G68"/>
     <mergeCell ref="D82:G82"/>
     <mergeCell ref="D231:G231"/>
     <mergeCell ref="M123:T123"/>
-    <mergeCell ref="M236:T236"/>
+    <mergeCell ref="B133:T133"/>
     <mergeCell ref="D123:G123"/>
     <mergeCell ref="B45:E45"/>
     <mergeCell ref="B80:T80"/>
@@ -9944,15 +9875,11 @@
     <mergeCell ref="D59:G59"/>
     <mergeCell ref="D60:G60"/>
     <mergeCell ref="B79:T79"/>
-    <mergeCell ref="B135:T135"/>
     <mergeCell ref="B109:E109"/>
-    <mergeCell ref="H238:L238"/>
     <mergeCell ref="M84:T84"/>
-    <mergeCell ref="M237:T237"/>
     <mergeCell ref="D84:G84"/>
     <mergeCell ref="B7:T7"/>
     <mergeCell ref="B72:T72"/>
-    <mergeCell ref="D237:G237"/>
     <mergeCell ref="B134:T134"/>
     <mergeCell ref="B121:T121"/>
     <mergeCell ref="D229:G229"/>
@@ -9960,14 +9887,10 @@
     <mergeCell ref="B56:T56"/>
     <mergeCell ref="B71:T71"/>
     <mergeCell ref="H66:L66"/>
-    <mergeCell ref="B151:E151"/>
-    <mergeCell ref="H237:L237"/>
     <mergeCell ref="B111:T111"/>
     <mergeCell ref="B120:T120"/>
     <mergeCell ref="M57:T57"/>
     <mergeCell ref="B8:T8"/>
-    <mergeCell ref="D238:G238"/>
-    <mergeCell ref="B191:E191"/>
     <mergeCell ref="B88:T88"/>
     <mergeCell ref="M122:T122"/>
     <mergeCell ref="D62:G62"/>
@@ -9976,7 +9899,6 @@
     <mergeCell ref="D127:G127"/>
     <mergeCell ref="M58:T58"/>
     <mergeCell ref="D58:G58"/>
-    <mergeCell ref="B187:T187"/>
     <mergeCell ref="D64:G64"/>
     <mergeCell ref="B104:E104"/>
     <mergeCell ref="H122:L122"/>
@@ -9989,20 +9911,19 @@
     <mergeCell ref="H226:L226"/>
     <mergeCell ref="D228:G228"/>
     <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B138:E138"/>
     <mergeCell ref="H60:L60"/>
     <mergeCell ref="H123:L123"/>
     <mergeCell ref="B47:T47"/>
     <mergeCell ref="H228:L228"/>
-    <mergeCell ref="D131:G131"/>
-    <mergeCell ref="B193:T193"/>
     <mergeCell ref="M227:T227"/>
-    <mergeCell ref="B220:E220"/>
+    <mergeCell ref="M223:T223"/>
     <mergeCell ref="M124:T124"/>
     <mergeCell ref="B77:E77"/>
     <mergeCell ref="B11:E11"/>
     <mergeCell ref="D124:G124"/>
     <mergeCell ref="H57:L57"/>
-    <mergeCell ref="M238:T238"/>
+    <mergeCell ref="B152:T152"/>
     <mergeCell ref="H84:L84"/>
     <mergeCell ref="M61:T61"/>
     <mergeCell ref="M126:T126"/>
@@ -10030,6 +9951,7 @@
     <mergeCell ref="D232:G232"/>
     <mergeCell ref="M59:T59"/>
     <mergeCell ref="M229:T229"/>
+    <mergeCell ref="B192:T192"/>
     <mergeCell ref="M129:T129"/>
     <mergeCell ref="D129:G129"/>
     <mergeCell ref="H127:L127"/>
@@ -10038,19 +9960,18 @@
     <mergeCell ref="H59:L59"/>
     <mergeCell ref="M82:T82"/>
     <mergeCell ref="M60:T60"/>
+    <mergeCell ref="B221:T221"/>
     <mergeCell ref="H64:L64"/>
-    <mergeCell ref="B185:E185"/>
     <mergeCell ref="M128:T128"/>
     <mergeCell ref="D63:G63"/>
     <mergeCell ref="D128:G128"/>
     <mergeCell ref="D81:G81"/>
     <mergeCell ref="H61:L61"/>
     <mergeCell ref="M65:T65"/>
+    <mergeCell ref="B184:E184"/>
     <mergeCell ref="D65:G65"/>
-    <mergeCell ref="B141:T141"/>
     <mergeCell ref="H81:L81"/>
     <mergeCell ref="H65:L65"/>
-    <mergeCell ref="H131:L131"/>
     <mergeCell ref="D234:G234"/>
     <mergeCell ref="D66:G66"/>
     <mergeCell ref="M231:T231"/>
@@ -10061,22 +9982,24 @@
     <mergeCell ref="M83:T83"/>
     <mergeCell ref="D83:G83"/>
     <mergeCell ref="H63:L63"/>
-    <mergeCell ref="D236:G236"/>
+    <mergeCell ref="D223:G223"/>
     <mergeCell ref="M67:T67"/>
     <mergeCell ref="D67:G67"/>
     <mergeCell ref="H230:L230"/>
     <mergeCell ref="B55:T55"/>
-    <mergeCell ref="H236:L236"/>
+    <mergeCell ref="H223:L223"/>
     <mergeCell ref="H232:L232"/>
-    <mergeCell ref="B153:T153"/>
     <mergeCell ref="B106:T106"/>
+    <mergeCell ref="B150:E150"/>
     <mergeCell ref="H129:L129"/>
+    <mergeCell ref="B190:E190"/>
     <mergeCell ref="M233:T233"/>
     <mergeCell ref="D233:G233"/>
     <mergeCell ref="M81:T81"/>
+    <mergeCell ref="B219:E219"/>
     <mergeCell ref="B18:T18"/>
+    <mergeCell ref="B140:T140"/>
     <mergeCell ref="H128:L128"/>
-    <mergeCell ref="B223:T223"/>
     <mergeCell ref="M235:T235"/>
     <mergeCell ref="D57:G57"/>
     <mergeCell ref="H233:L233"/>
@@ -10088,7 +10011,6 @@
     <mergeCell ref="H62:L62"/>
     <mergeCell ref="H225:L225"/>
     <mergeCell ref="M66:T66"/>
-    <mergeCell ref="M131:T131"/>
     <mergeCell ref="H234:L234"/>
     <mergeCell ref="B116:T116"/>
     <mergeCell ref="D224:G224"/>

--- a/reportes/Reporte_abril_2026.xlsx
+++ b/reportes/Reporte_abril_2026.xlsx
@@ -109,7 +109,7 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00C0392B"/>
+      <color rgb="001E8449"/>
       <sz val="9"/>
     </font>
     <font>
@@ -131,7 +131,7 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="001E8449"/>
+      <color rgb="00C0392B"/>
       <sz val="9"/>
     </font>
     <font>
@@ -384,31 +384,31 @@
     <xf numFmtId="0" fontId="14" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2965,7 +2965,7 @@
     <row r="56" ht="36" customHeight="1">
       <c r="B56" s="47" t="inlineStr">
         <is>
-          <t>Seducete redujo inversión 8% (de $5.5M a $5.1M) pero los resultados cayeron 14% (de 35.4k a 30.4k), señal de ineficiencia. La campaña de conversión web concentra 87% del gasto ($4.4M) con costo por compra de $5.081, muy por encima del benchmark de $10k pero con varios anuncios fatales sobre $18k.</t>
+          <t>Seducete bajó gasto 8% pero resultados cayeron 14% (de 35.423 a 30.410), señal de menor eficiencia general. La campaña de conversión web concentra 87% del gasto ($4.4M) pero entrega costo/compra de $5.081, muy por encima del benchmark ideal de $6.000.</t>
         </is>
       </c>
     </row>
@@ -2999,223 +2999,223 @@
     <row r="58" ht="48" customHeight="1">
       <c r="B58" s="49" t="inlineStr">
         <is>
-          <t>Conversión Web Ventas</t>
+          <t>Marketing Objetivo Visita Perfil Instagram</t>
         </is>
       </c>
       <c r="C58" s="50" t="inlineStr">
         <is>
-          <t>🔴 ALERTA</t>
+          <t>🟢 OPORTUNIDAD</t>
         </is>
       </c>
       <c r="D58" s="51" t="inlineStr">
         <is>
-          <t>8 anuncios fuera de benchmark crítico</t>
+          <t>Cursos Presenciales rinde mejor</t>
         </is>
       </c>
       <c r="H58" s="52" t="inlineStr">
         <is>
-          <t>Base Evita 2 ($10.888), Nuevos Esmaltes Satinados ($10.040), Lámpara Pre Curado ($11.153), Ojos Satinados Nuevos ($19.856), Efecto glaseado ($11.081) y Lampara Artistic ($9.524) están sobre $10k pero bajo $18k. Todos cayeron en resultados vs marzo (Base Evita de 43 a 13, Nuevos Esmaltes de 19 a 4, Lámpara Pre Curado de 53 a 10).</t>
+          <t>Anuncio 03-07 logra costo $47/click vs $59 del otro, con 1.890 clicks. Hold Rate bajo (3.6%) pero CTR 1.7% indica buen targeting inicial.</t>
         </is>
       </c>
       <c r="M58" s="53" t="inlineStr">
         <is>
-          <t>Refrescar apertura de video en estos 6 anuncios esta semana: los primeros 3 segundos no están enganchando (Hook Rate no reportado pero Hold50% bajo en todos).</t>
+          <t>Pausar anuncio Academia Cursos Gratuitos y duplicar presupuesto mental al creativo 03-07 creando variante con hook más fuerte para superar 5% de hold</t>
         </is>
       </c>
     </row>
     <row r="59" ht="48" customHeight="1">
       <c r="B59" s="54" t="inlineStr"/>
-      <c r="C59" s="50" t="inlineStr">
+      <c r="C59" s="55" t="inlineStr">
         <is>
           <t>🔴 ALERTA</t>
         </is>
       </c>
-      <c r="D59" s="51" t="inlineStr">
-        <is>
-          <t>BLACK WEEK es el único ganador real</t>
-        </is>
-      </c>
-      <c r="H59" s="52" t="inlineStr">
-        <is>
-          <t>BLACK WEEK INICIO tiene costo $1.988 (ganador, bajo $6k) con ROAS 1.18 y 236 compras, subió de 159 en marzo (+48%). El resto de la campaña está sangrando presupuesto con costos 3-10x más altos.</t>
-        </is>
-      </c>
-      <c r="M59" s="53" t="inlineStr">
-        <is>
-          <t>Duplicar creativos tipo BLACK WEEK: identifica qué gancho funciona (descuento visible, urgencia) y replica esa estructura en 3 anuncios nuevos para rotar esta semana.</t>
+      <c r="D59" s="56" t="inlineStr">
+        <is>
+          <t>Hold Rate crítico en ambos</t>
+        </is>
+      </c>
+      <c r="H59" s="57" t="inlineStr">
+        <is>
+          <t>5.8% y 3.6% de retención a mitad de video significa que pierden 95% de audiencia antes del mensaje clave. CTR bajo (1.7-1.93%) confirma problema de enganche.</t>
+        </is>
+      </c>
+      <c r="M59" s="58" t="inlineStr">
+        <is>
+          <t>Testear nuevos opens: primeros 3 segundos con testimonial de alumna o resultado visual impactante de antes/después en uñas</t>
         </is>
       </c>
     </row>
     <row r="60" ht="48" customHeight="1">
-      <c r="B60" s="54" t="inlineStr"/>
+      <c r="B60" s="49" t="inlineStr">
+        <is>
+          <t>Tráfico Web Objetivo Conversión</t>
+        </is>
+      </c>
       <c r="C60" s="55" t="inlineStr">
         <is>
+          <t>🔴 ALERTA</t>
+        </is>
+      </c>
+      <c r="D60" s="56" t="inlineStr">
+        <is>
+          <t>Esmaltado Permanente colapsó conversión</t>
+        </is>
+      </c>
+      <c r="H60" s="57" t="inlineStr">
+        <is>
+          <t>Costo $10.958/compra con solo 15 ventas (vs 1 en marzo), gastando $164k. CTR 2.89% es decente pero conversión web está rota o audiencia fría.</t>
+        </is>
+      </c>
+      <c r="M60" s="58" t="inlineStr">
+        <is>
+          <t>Pausar inmediatamente. Revisar pixel de conversión y landing page. Si están OK, cambiar a campaña de remarketing con descuento</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="48" customHeight="1">
+      <c r="B61" s="54" t="inlineStr"/>
+      <c r="C61" s="59" t="inlineStr">
+        <is>
+          <t>🔵 INSIGHT</t>
+        </is>
+      </c>
+      <c r="D61" s="60" t="inlineStr">
+        <is>
+          <t>Manicurista Integral es tráfico, no venta</t>
+        </is>
+      </c>
+      <c r="H61" s="61" t="inlineStr">
+        <is>
+          <t>Genera 182 clicks a $42 (benchmark OK) con CTR alto 3.92%, pero está en campaña de compra. Probablemente esté midiendo link_click en vez de purchase.</t>
+        </is>
+      </c>
+      <c r="M61" s="62" t="inlineStr">
+        <is>
+          <t>Reasignar a campaña de tráfico o ajustar evento de conversión. Si es curso, mover a Academia Formularios para capturar leads</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="48" customHeight="1">
+      <c r="B62" s="49" t="inlineStr">
+        <is>
+          <t>Academia Prueba Formularios</t>
+        </is>
+      </c>
+      <c r="C62" s="50" t="inlineStr">
+        <is>
           <t>🟢 OPORTUNIDAD</t>
         </is>
       </c>
-      <c r="D60" s="56" t="inlineStr">
-        <is>
-          <t>Lanzamiento Jelly Pop cerca del quiebre</t>
-        </is>
-      </c>
-      <c r="H60" s="57" t="inlineStr">
-        <is>
-          <t>Jelly Pop tiene costo $6.787 (en zona de revisión) pero ROAS 0.93, casi rentable. Cayó de 85 compras en marzo a 32 en abril (-62%), pero el creativo aún tiene potencial con Hold50% 4.7%.</t>
-        </is>
-      </c>
-      <c r="M60" s="58" t="inlineStr">
-        <is>
-          <t>Testear variación del video de Jelly Pop con testimonial de usuaria real en los primeros 2 segundos para subir Hook Rate, mantener 7 días más antes de decidir pausa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="48" customHeight="1">
-      <c r="B61" s="49" t="inlineStr">
-        <is>
-          <t>Academia Prueba Formularios</t>
-        </is>
-      </c>
-      <c r="C61" s="55" t="inlineStr">
+      <c r="D62" s="51" t="inlineStr">
+        <is>
+          <t>Costo/lead estable y dentro de rango</t>
+        </is>
+      </c>
+      <c r="H62" s="52" t="inlineStr">
+        <is>
+          <t>$76-78/lead con 2.931 leads totales está en rango aceptable (benchmark &lt;$90). Anuncio Cambio 11-07 sostiene 2.417 leads con CTR 4.33%.</t>
+        </is>
+      </c>
+      <c r="M62" s="53" t="inlineStr">
+        <is>
+          <t>Mantener ambos anuncios pero crear variante del Segundo Video (hold 9.8%) extendiendo ese gancho inicial con CTA más claro</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="48" customHeight="1">
+      <c r="B63" s="54" t="inlineStr"/>
+      <c r="C63" s="55" t="inlineStr">
+        <is>
+          <t>🔴 ALERTA</t>
+        </is>
+      </c>
+      <c r="D63" s="56" t="inlineStr">
+        <is>
+          <t>Hold Rate del principal bajo 50%</t>
+        </is>
+      </c>
+      <c r="H63" s="57" t="inlineStr">
+        <is>
+          <t>Anuncio Cambio 11-07 (82% del gasto) tiene hold 6.4%, perdiendo audiencia a mitad. El Segundo Video logra 9.8% hold con menos gasto.</t>
+        </is>
+      </c>
+      <c r="M63" s="58" t="inlineStr">
+        <is>
+          <t>Duplicar estructura narrativa del Segundo Video (qué hace que retenga +50% más) y aplicarla al anuncio principal en nueva versión</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="48" customHeight="1">
+      <c r="B64" s="49" t="inlineStr">
+        <is>
+          <t>Conversión Web Ventas</t>
+        </is>
+      </c>
+      <c r="C64" s="55" t="inlineStr">
+        <is>
+          <t>🔴 ALERTA</t>
+        </is>
+      </c>
+      <c r="D64" s="56" t="inlineStr">
+        <is>
+          <t>11 de 15 anuncios sobre $6.000/compra</t>
+        </is>
+      </c>
+      <c r="H64" s="57" t="inlineStr">
+        <is>
+          <t>Base Evita 2 ($10.888), Ojos Satinados ($19.856), Lámpara Pre Curado ($11.153) y otros 8 están en rojo. Solo BLACK WEEK ($1.988) y Top Templado ($4.082) rinden.</t>
+        </is>
+      </c>
+      <c r="M64" s="58" t="inlineStr">
+        <is>
+          <t>Pausar 6 peores: Base Evita 2, Ojos Satinados, Lámpara Pre Curado, Efecto Glaseado, Nuevos Esmaltes Satinados, Lámpara Artistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="48" customHeight="1">
+      <c r="B65" s="54" t="inlineStr"/>
+      <c r="C65" s="50" t="inlineStr">
         <is>
           <t>🟢 OPORTUNIDAD</t>
         </is>
       </c>
-      <c r="D61" s="56" t="inlineStr">
-        <is>
-          <t>Leads funcionando dentro de benchmark OK</t>
-        </is>
-      </c>
-      <c r="H61" s="57" t="inlineStr">
-        <is>
-          <t>Ambos anuncios tienen costo por lead $76-$78 (bajo $90, dentro de OK). Segundo video tiene mejor Hold50% (9.8% vs 6.4%) pero genera 5x menos leads (514 vs 2417). CTR alto en ambos (4.15% y 4.33%).</t>
-        </is>
-      </c>
-      <c r="M61" s="58" t="inlineStr">
-        <is>
-          <t>Escalar presupuesto NO (presupuesto fijo), pero testear híbrido: tomar apertura de Segundo video (Hold50% 9.8%) con CTA del anuncio Cambio 11-07 que tiene más volumen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="48" customHeight="1">
-      <c r="B62" s="54" t="inlineStr"/>
-      <c r="C62" s="59" t="inlineStr">
-        <is>
-          <t>🔵 INSIGHT</t>
-        </is>
-      </c>
-      <c r="D62" s="60" t="inlineStr">
-        <is>
-          <t>Volumen de leads se mantiene estable</t>
-        </is>
-      </c>
-      <c r="H62" s="61" t="inlineStr">
-        <is>
-          <t>Se generaron 2.931 leads en abril vs 2.673 en marzo anterior (dato inferido de res_anterior), prácticamente plano con gasto de $223k. Eficiencia por lead está controlada bajo $80.</t>
-        </is>
-      </c>
-      <c r="M62" s="62" t="inlineStr">
-        <is>
-          <t>Mantener creativos actuales sin cambios por 1 semana más, luego preparar rotación preventiva antes de llegar a frecuencia 3.5x.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="48" customHeight="1">
-      <c r="B63" s="49" t="inlineStr">
-        <is>
-          <t>Marketing Objetivo Visita Perfil Instagram</t>
-        </is>
-      </c>
-      <c r="C63" s="50" t="inlineStr">
-        <is>
-          <t>🔴 ALERTA</t>
-        </is>
-      </c>
-      <c r="D63" s="51" t="inlineStr">
-        <is>
-          <t>Costo por click fuera de benchmark</t>
-        </is>
-      </c>
-      <c r="H63" s="52" t="inlineStr">
-        <is>
-          <t>Tráfico Instagram Academia tiene costo $59 y Tráfico Cursos Presenciales $47, ambos sobre el benchmark OK de $40. Hold50% es crítico: 5.8% y 3.6%, la audiencia abandona antes de la mitad del video. Resultados se mantienen vs marzo (1775 vs 1546 y 1890 vs 1847).</t>
-        </is>
-      </c>
-      <c r="M63" s="53" t="inlineStr">
-        <is>
-          <t>Cambiar apertura de ambos videos: primeros 3 segundos deben mostrar beneficio concreto del curso (no logo ni texto genérico). Testear con gancho tipo 'Aprende X en Y minutos'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="48" customHeight="1">
-      <c r="B64" s="54" t="inlineStr"/>
-      <c r="C64" s="59" t="inlineStr">
-        <is>
-          <t>🔵 INSIGHT</t>
-        </is>
-      </c>
-      <c r="D64" s="60" t="inlineStr">
-        <is>
-          <t>CTR bajo pero conversión física posible</t>
-        </is>
-      </c>
-      <c r="H64" s="61" t="inlineStr">
-        <is>
-          <t>CTR de 1.93% y 1.7% es bajo para objetivo de tráfico, pero si los cursos presenciales tienen inscripciones en tienda física, parte de la conversión no se mide en Meta. Gasto total $193k justificado solo si hay datos offline.</t>
-        </is>
-      </c>
-      <c r="M64" s="62" t="inlineStr">
-        <is>
-          <t>Solicitar a equipo comercial data de inscripciones presenciales de abril con fuente 'Instagram' para validar si esta campaña tiene ROI real más allá de clicks.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="48" customHeight="1">
-      <c r="B65" s="49" t="inlineStr">
-        <is>
-          <t>Tráfico Web Objetivo Conversión</t>
-        </is>
-      </c>
-      <c r="C65" s="50" t="inlineStr">
-        <is>
-          <t>🔴 ALERTA</t>
-        </is>
-      </c>
       <c r="D65" s="51" t="inlineStr">
         <is>
-          <t>Esmaltado Permanente completamente roto</t>
+          <t>BLACK WEEK es el único ganador</t>
         </is>
       </c>
       <c r="H65" s="52" t="inlineStr">
         <is>
-          <t>Costo por compra $10.958, en zona de revisión crítica (sobre $10k). Solo 15 compras vs 1 en marzo, pero con gasto de $164k el costo es inviable. CTR 2.89% aceptable pero no convierte.</t>
+          <t>236 compras a $1.988 c/u con ROAS 1.18, concentra 27% de conversiones de la campaña. Gastó $469k y generó resultado 48% superior vs marzo (159→236).</t>
         </is>
       </c>
       <c r="M65" s="53" t="inlineStr">
         <is>
-          <t>Pausar Esmaltado Permanente hoy. El producto puede tener problema de precio/propuesta, no solo de creativo. Reemplazar presupuesto con test de producto diferente.</t>
+          <t>Crear 3 variantes del creativo BLACK WEEK cambiando solo el copy/oferta: una con urgencia temporal, otra con bundle, otra con envío gratis</t>
         </is>
       </c>
     </row>
     <row r="66" ht="48" customHeight="1">
       <c r="B66" s="54" t="inlineStr"/>
-      <c r="C66" s="55" t="inlineStr">
-        <is>
-          <t>🟢 OPORTUNIDAD</t>
-        </is>
-      </c>
-      <c r="D66" s="56" t="inlineStr">
-        <is>
-          <t>Manicurista Integral muy eficiente en clicks</t>
-        </is>
-      </c>
-      <c r="H66" s="57" t="inlineStr">
-        <is>
-          <t>Costo por click $42 (ganador, bajo $20 sería ideal pero bajo $40 es OK) con CTR 3.92%, el más alto de toda esta campaña. 182 clicks con solo $7.6k de gasto. Cayó brutal de 1027 resultados en marzo.</t>
-        </is>
-      </c>
-      <c r="M66" s="58" t="inlineStr">
-        <is>
-          <t>Este anuncio está configurado como link_click en campaña de purchase, revisar configuración de píxel/conversión. Si es error técnico, puede estar perdiendo compras atribuibles.</t>
+      <c r="C66" s="59" t="inlineStr">
+        <is>
+          <t>🔵 INSIGHT</t>
+        </is>
+      </c>
+      <c r="D66" s="60" t="inlineStr">
+        <is>
+          <t>Productos nuevos fracasan en cold</t>
+        </is>
+      </c>
+      <c r="H66" s="61" t="inlineStr">
+        <is>
+          <t>Jelly Pop ($6.787), Torno Artistic ($6.174) arrancan sobre benchmark pero ROAS 0.93 y 0.63 sugieren que necesitan calentamiento. Caídas fuertes vs marzo.</t>
+        </is>
+      </c>
+      <c r="M66" s="62" t="inlineStr">
+        <is>
+          <t>Mover a secuencia: 1 semana de video views para educar producto, luego remarketing a engaged viewers con oferta de lanzamiento</t>
         </is>
       </c>
     </row>
@@ -3225,24 +3225,24 @@
           <t>Campaña Mktg prueba Pau</t>
         </is>
       </c>
-      <c r="C67" s="55" t="inlineStr">
+      <c r="C67" s="50" t="inlineStr">
         <is>
           <t>🟢 OPORTUNIDAD</t>
         </is>
       </c>
-      <c r="D67" s="56" t="inlineStr">
-        <is>
-          <t>Se te quebró la uña es máquina</t>
-        </is>
-      </c>
-      <c r="H67" s="57" t="inlineStr">
-        <is>
-          <t>Costo por click $4 (ganador extremo, benchmark es bajo $20), CTR 10.1% y Hold50% 22.1%, métricas espectaculares. Genera 22.721 clicks con solo $99k, eficiencia brutal. Cayó levemente de 25.762 en marzo.</t>
-        </is>
-      </c>
-      <c r="M67" s="58" t="inlineStr">
-        <is>
-          <t>Este creativo es oro: analizar estructura (problema emocional + solución rápida) y replicar formato en 2 anuncios nuevos para otras categorías (cabello, maquillaje) esta semana.</t>
+      <c r="D67" s="51" t="inlineStr">
+        <is>
+          <t>Contenido viral con métrica estrella</t>
+        </is>
+      </c>
+      <c r="H67" s="52" t="inlineStr">
+        <is>
+          <t>Anuncio 'Se te quebró la uña' logra hold 22.1% (vs 5-8% promedio) con CTR 10.1% y 22.721 clicks a $4. Es contenido educativo/entretenimiento que viraliza.</t>
+        </is>
+      </c>
+      <c r="M67" s="53" t="inlineStr">
+        <is>
+          <t>Duplicar formato: video corto educativo estilo 'problema-solución' sobre otros pain points de uñas. Probar 'uñas amarillas' o 'cutículas secas'</t>
         </is>
       </c>
     </row>
@@ -3255,17 +3255,17 @@
       </c>
       <c r="D68" s="60" t="inlineStr">
         <is>
-          <t>4 anuncios nuevos sin volumen aún</t>
+          <t>Campaña experimental sin objetivo comercial claro</t>
         </is>
       </c>
       <c r="H68" s="61" t="inlineStr">
         <is>
-          <t>uñas respiran, 5 cosas que no sabias, sedu hannah montana y uñas de otoño 2026 tienen gasto mínimo ($8-$144) sin data significativa. Son tests recién lanzados.</t>
+          <t>Genera 22.743 clicks a costo bajísimo pero sin conversión medible. Funciona como awareness/engagement pero no está optimizada para negocio.</t>
         </is>
       </c>
       <c r="M68" s="62" t="inlineStr">
         <is>
-          <t>Dejar correr 7 días más con presupuesto bajo actual para acumular data. Si alguno llega a CTR &gt;8% y costo &lt;$10, escalar dentro del presupuesto fijo de esta campaña.</t>
+          <t>Definir objetivo: si es branding, medir video views y comentarios. Si es negocio, redirigir tráfico a landing con lead magnet o código descuento</t>
         </is>
       </c>
     </row>
@@ -3536,7 +3536,7 @@
     <row r="80" ht="36" customHeight="1">
       <c r="B80" s="47" t="inlineStr">
         <is>
-          <t>Bluesky mantuvo eficiencia estable con costo por click en $6 (dentro de benchmark ganador &lt;$20), pero cayó -8% en resultados totales vs marzo (14.364 vs 15.624 clicks). El anuncio 'Conchitas' escaló fuerte y representa el 78% del gasto con excelente hold rate de 25%.</t>
+          <t>Bluesky invirtió $89.176 en tráfico a perfil (campaña única) generando 14.364 clicks a $6 promedio, levemente bajo vs marzo (15.624 clicks a similar inversión). El costo por click está dentro de benchmark ganador (&lt;$20) y dos anuncios muestran retención muy distinta.</t>
         </is>
       </c>
     </row>
@@ -3573,70 +3573,70 @@
           <t>Tráfico Perfil Instagram MKT</t>
         </is>
       </c>
-      <c r="C82" s="55" t="inlineStr">
+      <c r="C82" s="50" t="inlineStr">
         <is>
           <t>🟢 OPORTUNIDAD</t>
         </is>
       </c>
-      <c r="D82" s="56" t="inlineStr">
-        <is>
-          <t>Conchitas dominando con hold rate superior</t>
-        </is>
-      </c>
-      <c r="H82" s="57" t="inlineStr">
-        <is>
-          <t>Diseño Conchitas generó 11.185 clicks (78% del total) con hold rate de 25% vs 13.1% de Floral, y escaló 254% vs marzo (3.161 clicks). CTR de 7.1% demuestra apertura fuerte pero no hay hook rate registrado.</t>
-        </is>
-      </c>
-      <c r="M82" s="58" t="inlineStr">
-        <is>
-          <t>Crear 2 variaciones nuevas de Conchitas manteniendo estructura narrativa actual, testear diferentes aperturas para medir hook rate y rotar en 10 días para evitar fatiga.</t>
+      <c r="D82" s="51" t="inlineStr">
+        <is>
+          <t>Conchitas domina con mejor retención</t>
+        </is>
+      </c>
+      <c r="H82" s="52" t="inlineStr">
+        <is>
+          <t>Diseño Conchitas generó 11.185 clicks (78% del total) con Hold Rate 25% vs 13.1% de Floral. Además creció 3.5x vs marzo (3.161 clicks anteriores).</t>
+        </is>
+      </c>
+      <c r="M82" s="53" t="inlineStr">
+        <is>
+          <t>Producir 2 variaciones nuevas de Conchitas manteniendo formato tutorial y estética que logra Hold 25%. Rotar en 5 días.</t>
         </is>
       </c>
     </row>
     <row r="83" ht="48" customHeight="1">
       <c r="B83" s="54" t="inlineStr"/>
-      <c r="C83" s="50" t="inlineStr">
-        <is>
-          <t>🔴 ALERTA</t>
-        </is>
-      </c>
-      <c r="D83" s="51" t="inlineStr">
-        <is>
-          <t>Floral perdiendo momentum drásticamente</t>
-        </is>
-      </c>
-      <c r="H83" s="52" t="inlineStr">
-        <is>
-          <t>Diseño Floral cayó -79% en resultados vs marzo (2.662 vs 12.461 clicks) con hold rate bajo de 13.1%, señal clara de fatiga creativa. Mantiene mismo costo $6 pero genera mucho menos volumen.</t>
-        </is>
-      </c>
-      <c r="M83" s="53" t="inlineStr">
-        <is>
-          <t>Pausar Floral inmediatamente y reemplazar con creativo nuevo que muestre proceso de aplicación step-by-step o resultado final en mano real con mejor iluminación.</t>
+      <c r="C83" s="59" t="inlineStr">
+        <is>
+          <t>🔵 INSIGHT</t>
+        </is>
+      </c>
+      <c r="D83" s="60" t="inlineStr">
+        <is>
+          <t>Floral cayó 79% mes a mes</t>
+        </is>
+      </c>
+      <c r="H83" s="61" t="inlineStr">
+        <is>
+          <t>Diseño Floral pasó de 12.461 clicks (marzo) a 2.662 (abril) con Hold Rate 13.1%, señal clara de fatiga. Aún genera 2.662 clicks pero perdió efectividad dramáticamente.</t>
+        </is>
+      </c>
+      <c r="M83" s="62" t="inlineStr">
+        <is>
+          <t>Pausar Floral y reemplazar con nuevo diseño de temporada otoño/invierno. Testear apertura más dinámica para superar Hook actual.</t>
         </is>
       </c>
     </row>
     <row r="84" ht="48" customHeight="1">
       <c r="B84" s="54" t="inlineStr"/>
-      <c r="C84" s="59" t="inlineStr">
-        <is>
-          <t>🔵 INSIGHT</t>
-        </is>
-      </c>
-      <c r="D84" s="60" t="inlineStr">
-        <is>
-          <t>Limón Verano con potencial sin explotar</t>
-        </is>
-      </c>
-      <c r="H84" s="61" t="inlineStr">
-        <is>
-          <t>Diseño Limón tiene CTR más alto (7.58%) y hold rate 18.2% con solo $3.312 invertidos (4% del budget total). Costo $7 está dentro de benchmark ganador pero volumen muy bajo para conclusiones.</t>
-        </is>
-      </c>
-      <c r="M84" s="62" t="inlineStr">
-        <is>
-          <t>Aumentar exposición de Limón a 15% del budget de la campaña durante 7 días para validar si mantiene métricas con mayor volumen, agregar CTA más claro al final.</t>
+      <c r="C84" s="55" t="inlineStr">
+        <is>
+          <t>🔴 ALERTA</t>
+        </is>
+      </c>
+      <c r="D84" s="56" t="inlineStr">
+        <is>
+          <t>Limón recién lanzado muestra potencial limitado</t>
+        </is>
+      </c>
+      <c r="H84" s="57" t="inlineStr">
+        <is>
+          <t>Diseño Limón Verano generó 509 clicks a $7 (vs $6 promedio campaña) con Hold 18.2%. CTR 7.58% es el más alto pero volumen bajo sugiere audiencia saturada rápido.</t>
+        </is>
+      </c>
+      <c r="M84" s="58" t="inlineStr">
+        <is>
+          <t>Mantener Limón 7 días más monitoreando frecuencia. Si supera 3.5x, pausar y producir diseño otoñal alineado a temporada Chile.</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
     <row r="121" ht="36" customHeight="1">
       <c r="B121" s="47" t="inlineStr">
         <is>
-          <t>Nail Outlet aumentó gasto 4% pero conversiones cayeron 14% (5.028→4.302), subiendo costo/compra de $269→$327. ROAS general bajo presión por múltiples anuncios sobre $10k/conversión en campaña principal.</t>
+          <t>Nail Outlet gastó $1.408.877 en abril vs $1.352.511 en marzo (+4% gasto) pero bajó de 5.028 a 4.302 resultados (-14%). El costo por compra subió de $269 a $327 (+22%), señal de fatiga creativa en múltiples anuncios de conversión.</t>
         </is>
       </c>
     </row>
@@ -4970,70 +4970,70 @@
           <t>Objetivo Conversión Ventas</t>
         </is>
       </c>
-      <c r="C123" s="50" t="inlineStr">
+      <c r="C123" s="55" t="inlineStr">
         <is>
           <t>🔴 ALERTA</t>
         </is>
       </c>
-      <c r="D123" s="51" t="inlineStr">
-        <is>
-          <t>5 anuncios superan umbral crítico de costo</t>
-        </is>
-      </c>
-      <c r="H123" s="52" t="inlineStr">
-        <is>
-          <t>40 Esmaltes Julio ($19.285), Campo de Trabajo ($18.188), Efectos Chromados ($22.114), Esmaltes French ($12.705) e Imagen primer deshidratador ($29.518) están sobre $10k por conversión. Representan $305k de gasto con apenas 17 conversiones.</t>
-        </is>
-      </c>
-      <c r="M123" s="53" t="inlineStr">
-        <is>
-          <t>Pausar estos 5 anuncios inmediatamente y reasignar su presupuesto rotando creativos en los 3 ganadores actuales</t>
+      <c r="D123" s="56" t="inlineStr">
+        <is>
+          <t>Caída brutal en Pack Repo 20</t>
+        </is>
+      </c>
+      <c r="H123" s="57" t="inlineStr">
+        <is>
+          <t>Pack Repo 20 pasó de 38 conversiones en marzo a solo 20 en abril (-47%) con costo disparado a $8.374. Hold Rate de 5.4% muestra que el video pierde audiencia rápidamente.</t>
+        </is>
+      </c>
+      <c r="M123" s="58" t="inlineStr">
+        <is>
+          <t>Pausar y crear nuevo hook mostrando el ahorro del pack en los primeros 2 segundos con texto en pantalla.</t>
         </is>
       </c>
     </row>
     <row r="124" ht="48" customHeight="1">
       <c r="B124" s="54" t="inlineStr"/>
-      <c r="C124" s="55" t="inlineStr">
+      <c r="C124" s="50" t="inlineStr">
         <is>
           <t>🟢 OPORTUNIDAD</t>
         </is>
       </c>
-      <c r="D124" s="56" t="inlineStr">
-        <is>
-          <t>Poly Gel Carrusel es ganador extremo</t>
-        </is>
-      </c>
-      <c r="H124" s="57" t="inlineStr">
-        <is>
-          <t>ROAS 40.15x con costo/conversión de $462 (92% bajo benchmark). Generó 7 conversiones con solo $3.237 de gasto, pero cayó drásticamente vs marzo (73→7 conversiones).</t>
-        </is>
-      </c>
-      <c r="M124" s="58" t="inlineStr">
-        <is>
-          <t>Duplicar este anuncio con 3 variaciones de copy manteniendo el formato carrusel para recuperar volumen perdido</t>
+      <c r="D124" s="51" t="inlineStr">
+        <is>
+          <t>Poly Gel es la gema escondida</t>
+        </is>
+      </c>
+      <c r="H124" s="52" t="inlineStr">
+        <is>
+          <t>Poly Gel Carrusel tiene ROAS 40.15 con costo $462 por compra (10x mejor que benchmark) pero solo recibió $3.237 de gasto vs $167.478 del Pack Repo. Bajó de 73 a 7 conversiones probablemente por baja exposición.</t>
+        </is>
+      </c>
+      <c r="M124" s="53" t="inlineStr">
+        <is>
+          <t>Duplicar el anuncio actual sin cambios y testear 2 variaciones del copy en el carrusel destacando uso profesional.</t>
         </is>
       </c>
     </row>
     <row r="125" ht="48" customHeight="1">
       <c r="B125" s="54" t="inlineStr"/>
-      <c r="C125" s="59" t="inlineStr">
-        <is>
-          <t>🔵 INSIGHT</t>
-        </is>
-      </c>
-      <c r="D125" s="60" t="inlineStr">
-        <is>
-          <t>Black Week mantiene eficiencia fuera de temporada</t>
-        </is>
-      </c>
-      <c r="H125" s="61" t="inlineStr">
-        <is>
-          <t>ROAS 5.57x y $8.252/conversión (dentro de benchmark OK) en abril. Creció de 7→23 conversiones vs marzo sin estar en fecha comercial relevante.</t>
-        </is>
-      </c>
-      <c r="M125" s="62" t="inlineStr">
-        <is>
-          <t>Crear variante con beneficio de despacho gratis (funcionó en remarketing con ROAS 4.85x) para testear sinergia</t>
+      <c r="C125" s="55" t="inlineStr">
+        <is>
+          <t>🔴 ALERTA</t>
+        </is>
+      </c>
+      <c r="D125" s="56" t="inlineStr">
+        <is>
+          <t>5 anuncios sobre $10k de costo</t>
+        </is>
+      </c>
+      <c r="H125" s="57" t="inlineStr">
+        <is>
+          <t>Esmaltes French ($12.705), 40 Esmaltes Julio ($19.285), Efectos Chromados ($22.114), Campo de Trabajo ($18.188) e Imagen primer deshidratador ($29.518) todos están fuera del benchmark de $10k. Acumulan $345k de gasto con apenas 17 conversiones.</t>
+        </is>
+      </c>
+      <c r="M125" s="58" t="inlineStr">
+        <is>
+          <t>Pausar estos 5 anuncios inmediatamente. Crear 3 nuevos videos cortos (7-10 seg) con close-up de producto en uso y precio visible desde el segundo 1.</t>
         </is>
       </c>
     </row>
@@ -5043,47 +5043,47 @@
           <t>Tráfico Perfil Instagram MKT</t>
         </is>
       </c>
-      <c r="C126" s="50" t="inlineStr">
-        <is>
-          <t>🔴 ALERTA</t>
-        </is>
-      </c>
-      <c r="D126" s="51" t="inlineStr">
-        <is>
-          <t>Paso a paso Vale Nails perdió 35%</t>
-        </is>
-      </c>
-      <c r="H126" s="52" t="inlineStr">
-        <is>
-          <t>Clicks cayeron de 2.984→1.930 (-35%) con mismo presupuesto ($41k). Hold Rate de 10.3% indica que pierde 90% de audiencia a mitad de video.</t>
-        </is>
-      </c>
-      <c r="M126" s="53" t="inlineStr">
-        <is>
-          <t>Regrabar apertura con hook más directo en primeros 3 segundos mostrando resultado final del nail art</t>
+      <c r="C126" s="59" t="inlineStr">
+        <is>
+          <t>🔵 INSIGHT</t>
+        </is>
+      </c>
+      <c r="D126" s="60" t="inlineStr">
+        <is>
+          <t>Vale Nails cayó pero sigue eficiente</t>
+        </is>
+      </c>
+      <c r="H126" s="61" t="inlineStr">
+        <is>
+          <t>Paso a paso Vale Nails bajó de 2.984 a 1.930 clicks (-35%) pero mantiene costo $21 y CTR 4.01% (el más alto de la marca). Hold Rate 10.3% vs 19.2% del otro anuncio indica que la gente se va antes.</t>
+        </is>
+      </c>
+      <c r="M126" s="62" t="inlineStr">
+        <is>
+          <t>Crear versión corta de 15 seg con solo los 3 pasos más impactantes visualmente y testear contra el actual.</t>
         </is>
       </c>
     </row>
     <row r="127" ht="48" customHeight="1">
       <c r="B127" s="54" t="inlineStr"/>
-      <c r="C127" s="55" t="inlineStr">
+      <c r="C127" s="50" t="inlineStr">
         <is>
           <t>🟢 OPORTUNIDAD</t>
         </is>
       </c>
-      <c r="D127" s="56" t="inlineStr">
-        <is>
-          <t>Ambos anuncios dentro de benchmark ganador</t>
-        </is>
-      </c>
-      <c r="H127" s="57" t="inlineStr">
-        <is>
-          <t>Insta Nail Pro ($23/click) y Paso a paso ($21/click) están bajo $40. Hold Rate de Insta (19.2%) casi duplica a Vale Nails, sugiere formato más efectivo.</t>
-        </is>
-      </c>
-      <c r="M127" s="58" t="inlineStr">
-        <is>
-          <t>Replicar estructura narrativa de Insta Nail Pro en nuevo creativo de tutorial paso a paso</t>
+      <c r="D127" s="51" t="inlineStr">
+        <is>
+          <t>Campaña dentro de benchmark y rentable</t>
+        </is>
+      </c>
+      <c r="H127" s="52" t="inlineStr">
+        <is>
+          <t>Ambos anuncios están en $21-23 por click, dentro del rango ganador (&lt;$20 es ideal pero &lt;$40 es OK). Con 4.057 clicks generados, la campaña cumple su función de traer tráfico calificado al perfil.</t>
+        </is>
+      </c>
+      <c r="M127" s="53" t="inlineStr">
+        <is>
+          <t>Mantener ambos anuncios activos. Agregar 1 nuevo formato tipo carrusel mostrando 3 trabajos de nail artists distintas para testear.</t>
         </is>
       </c>
     </row>
@@ -5093,24 +5093,24 @@
           <t>Remarketing Nail Outlet</t>
         </is>
       </c>
-      <c r="C128" s="55" t="inlineStr">
+      <c r="C128" s="50" t="inlineStr">
         <is>
           <t>🟢 OPORTUNIDAD</t>
         </is>
       </c>
-      <c r="D128" s="56" t="inlineStr">
-        <is>
-          <t>15% OFF supera a Despacho Gratis</t>
-        </is>
-      </c>
-      <c r="H128" s="57" t="inlineStr">
-        <is>
-          <t>ROAS 11.25x vs 4.85x con costo/conversión $3.481 vs $4.913. Hold Rate similar (17.9% vs 19.3%) pero descuento convierte mejor en remarketing.</t>
-        </is>
-      </c>
-      <c r="M128" s="58" t="inlineStr">
-        <is>
-          <t>Testear híbrido '15% OFF + Despacho Gratis' en tercer anuncio de remarketing para maximizar conversión</t>
+      <c r="D128" s="51" t="inlineStr">
+        <is>
+          <t>15% OFF es oro puro</t>
+        </is>
+      </c>
+      <c r="H128" s="52" t="inlineStr">
+        <is>
+          <t>Anuncio 15% OFF tiene ROAS 11.25 con costo $3.481 por compra (mejor que el benchmark de $6k ganador). Despacho Gratis también funciona con ROAS 4.85 y costo $4.913.</t>
+        </is>
+      </c>
+      <c r="M128" s="53" t="inlineStr">
+        <is>
+          <t>Mantener ambos sin cambios. Crear variación de 15% OFF con testimonial corto de clienta real recibiendo su pedido.</t>
         </is>
       </c>
     </row>
@@ -5123,17 +5123,17 @@
       </c>
       <c r="D129" s="60" t="inlineStr">
         <is>
-          <t>Campaña nueva con eficiencia inmediata</t>
+          <t>Hold Rate alto indica interés real</t>
         </is>
       </c>
       <c r="H129" s="61" t="inlineStr">
         <is>
-          <t>15 conversiones a $4.340 promedio (bajo $6k benchmark ganador) sin data marzo. Hold Rates sobre 17% muestran mensaje claro para audiencia caliente.</t>
+          <t>Hold Rate de 17.9% y 19.3% son los más altos de toda la marca, confirmando que audiencia de remarketing está altamente interesada. Solo 15 conversiones totales sugiere audiencia pequeña o recién iniciada.</t>
         </is>
       </c>
       <c r="M129" s="62" t="inlineStr">
         <is>
-          <t>Mantener ambos anuncios activos y agregar uno nuevo con urgencia temporal: '48hrs: 15% OFF'</t>
+          <t>Si esta campaña tiene menos de 30 días, mantener. Si tiene más, ampliar audiencia a visitantes de los últimos 60 días.</t>
         </is>
       </c>
     </row>
@@ -5143,24 +5143,24 @@
           <t>Campaña Conversión Catálogo</t>
         </is>
       </c>
-      <c r="C130" s="50" t="inlineStr">
+      <c r="C130" s="55" t="inlineStr">
         <is>
           <t>🔴 ALERTA</t>
         </is>
       </c>
-      <c r="D130" s="51" t="inlineStr">
-        <is>
-          <t>Costo por conversión 3x sobre límite</t>
-        </is>
-      </c>
-      <c r="H130" s="52" t="inlineStr">
-        <is>
-          <t>$17.787 por conversión está 197% sobre benchmark de revisión ($6k). ROAS 1.84x es muy bajo para este costo. Campaña nueva sin data previa pero no valida inversión.</t>
-        </is>
-      </c>
-      <c r="M130" s="53" t="inlineStr">
-        <is>
-          <t>Pausar catálogo dinámico y crear 3 anuncios estáticos con los 3 productos más vendidos de Poly Gel</t>
+      <c r="D130" s="56" t="inlineStr">
+        <is>
+          <t>Costo catastrófico de $17.787 por compra</t>
+        </is>
+      </c>
+      <c r="H130" s="57" t="inlineStr">
+        <is>
+          <t>Nuevo Anuncio Catálogo quemó $355.748 (25% del presupuesto total de abril) para lograr solo 20 conversiones a $17.787 cada una. Está 3x por encima del límite de pausar ($18k) con ROAS 1.84 apenas positivo.</t>
+        </is>
+      </c>
+      <c r="M130" s="58" t="inlineStr">
+        <is>
+          <t>Pausar inmediatamente. Si el catálogo es necesario, crear anuncios manuales de los 5 productos top sellers en vez de catálogo dinámico.</t>
         </is>
       </c>
     </row>
@@ -9527,7 +9527,7 @@
     <row r="222" ht="36" customHeight="1">
       <c r="B222" s="47" t="inlineStr">
         <is>
-          <t>Go Nails cayó 88% en resultados (de 20.613 a 2.404) con gasto similar ($7,1M vs $7,5M anterior), por colapso en tráfico Instagram de 20k a 1.285 clicks y caída en conversión principal de costo $7.642 por compra. Remarketing mantiene ROAS 4,82-5,24 pero creativos de conversión están saturados con Hold Rate bajo 2% en mayoría.</t>
+          <t>Go Nails cayó 88% en resultados (20.613 → 2.404) con gasto similar (-6%). Los anuncios 'hannah montana 2' ($283k/compra) y 'Nueva rutina 4 pasos' ($27k/compra) quemaron 43% del presupuesto total sin retorno.</t>
         </is>
       </c>
     </row>
@@ -9561,27 +9561,27 @@
     <row r="224" ht="48" customHeight="1">
       <c r="B224" s="49" t="inlineStr">
         <is>
-          <t>Remarketing Go Nails 2024</t>
+          <t>Campaña principal de Conversión</t>
         </is>
       </c>
       <c r="C224" s="55" t="inlineStr">
         <is>
-          <t>🟢 OPORTUNIDAD</t>
+          <t>🔴 ALERTA</t>
         </is>
       </c>
       <c r="D224" s="56" t="inlineStr">
         <is>
-          <t>Despacho Gratis es tu ganador</t>
+          <t>Home Spray quema presupuesto sin eficiencia</t>
         </is>
       </c>
       <c r="H224" s="57" t="inlineStr">
         <is>
-          <t>Anuncio 'Despacho Gratis' logra costo $4.137 por compra con ROAS 4,82 y 32 conversiones, mejor que benchmark $6k. Mientras '15% OFF' cayó de 34 a 1 conversión con costo $7.957.</t>
+          <t>Consumió $1.186.817 (22% del total marca) con costo/compra $13.042 — 70% sobre benchmark. ROAS 2.45 es el peor de la campaña junto con bajo CTR 1.21%.</t>
         </is>
       </c>
       <c r="M224" s="58" t="inlineStr">
         <is>
-          <t>Duplicar inversión en 'Despacho Gratis' y crear 2 variantes más de envío gratis para mantener frescura antes de fatiga.</t>
+          <t>Pausar Home Spray inmediatamente y rotar creatividad con Hold Rate superior a 10% como 'Reel cafetería' (Hold 2.7%, costo $5.089)</t>
         </is>
       </c>
     </row>
@@ -9589,168 +9589,168 @@
       <c r="B225" s="54" t="inlineStr"/>
       <c r="C225" s="50" t="inlineStr">
         <is>
+          <t>🟢 OPORTUNIDAD</t>
+        </is>
+      </c>
+      <c r="D225" s="51" t="inlineStr">
+        <is>
+          <t>3 anuncios ganan con costo bajo</t>
+        </is>
+      </c>
+      <c r="H225" s="52" t="inlineStr">
+        <is>
+          <t>'Reel cafetería' ($5.089/compra, ROAS 4.6), 'Cremas Sun Kissed' ($5.687, ROAS 5) e 'Imagen Cotton Vlabel' ($7.713, ROAS 5) están bajo $8k con retorno sólido. Representan solo 5% del gasto de campaña.</t>
+        </is>
+      </c>
+      <c r="M225" s="53" t="inlineStr">
+        <is>
+          <t>Duplicar estos 3 creativos con nuevos ángulos de apertura para escalar sin tocar presupuesto actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="48" customHeight="1">
+      <c r="B226" s="54" t="inlineStr"/>
+      <c r="C226" s="55" t="inlineStr">
+        <is>
           <t>🔴 ALERTA</t>
         </is>
       </c>
-      <c r="D225" s="51" t="inlineStr">
-        <is>
-          <t>Hold Rate crítico en promos</t>
-        </is>
-      </c>
-      <c r="H225" s="52" t="inlineStr">
-        <is>
-          <t>Anuncios '15% OFF' y 'Despacho Gratis' tienen Hold Rate 5,4-5,7%, indicando que pierden audiencia a la mitad del video. CTR bajo 1,12% confirma baja captación inicial.</t>
-        </is>
-      </c>
-      <c r="M225" s="53" t="inlineStr">
-        <is>
-          <t>Regrabar primeros 3 segundos con gancho más fuerte: mostrar producto + beneficio antes del segundo 2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="226" ht="48" customHeight="1">
-      <c r="B226" s="49" t="inlineStr">
+      <c r="D226" s="56" t="inlineStr">
+        <is>
+          <t>Reel fragancias decayó 27% vs marzo</t>
+        </is>
+      </c>
+      <c r="H226" s="57" t="inlineStr">
+        <is>
+          <t>Cayó de 104 a 76 compras con costo subiendo a $10.337 (71% sobre benchmark). Hold Rate bajísimo 1.6% indica fatiga del creativo después de mes intenso.</t>
+        </is>
+      </c>
+      <c r="M226" s="58" t="inlineStr">
+        <is>
+          <t>Refrescar concepto de fragancias con nuevo formato (testimonio o aplicación real vs producto solo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="48" customHeight="1">
+      <c r="B227" s="49" t="inlineStr">
         <is>
           <t>Marketing Go Nails - Trafico Insta</t>
         </is>
       </c>
-      <c r="C226" s="50" t="inlineStr">
+      <c r="C227" s="55" t="inlineStr">
         <is>
           <t>🔴 ALERTA</t>
         </is>
       </c>
-      <c r="D226" s="51" t="inlineStr">
-        <is>
-          <t>Hannah Montana destruyó el presupuesto</t>
-        </is>
-      </c>
-      <c r="H226" s="52" t="inlineStr">
-        <is>
-          <t>Anuncios 'hannah montana' ($55k) y 'hannah montana 2' ($284k) gastaron $339k para 2 conversiones totales con ROAS 0,04-0,74, costando $55k-$284k por compra. Hold Rate 0,1-1,8% indica rechazo masivo.</t>
-        </is>
-      </c>
-      <c r="M226" s="53" t="inlineStr">
-        <is>
-          <t>Pausar inmediatamente ambos anuncios. El concepto nostálgico no conectó: testar contenido nail art tutorial en su lugar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="227" ht="48" customHeight="1">
-      <c r="B227" s="54" t="inlineStr"/>
-      <c r="C227" s="55" t="inlineStr">
-        <is>
-          <t>🟢 OPORTUNIDAD</t>
-        </is>
-      </c>
       <c r="D227" s="56" t="inlineStr">
         <is>
-          <t>Cotton candy y clicks baratos</t>
+          <t>Hannah montana 2 destruyó el presupuesto</t>
         </is>
       </c>
       <c r="H227" s="57" t="inlineStr">
         <is>
-          <t>'Cotton candy frutilla' genera clicks a $17 con CTR 4,3% y 407 clicks, mientras 'tu pareja te debe' logra $19 por click con 760 clicks. Ambos muy por debajo de benchmark $40.</t>
+          <t>Gastó $283.796 para 1 sola compra (costo $283k) con ROAS 0.04 — peor anuncio de toda la marca. Hold Rate 1.8% confirma que nadie ve el video completo.</t>
         </is>
       </c>
       <c r="M227" s="58" t="inlineStr">
         <is>
-          <t>Escalar estos creativos a campaña de conversión: la audiencia clickea, falta empujarlos a compra con retargeting.</t>
+          <t>Pausar inmediatamente ambos Hannah Montana (gastaron $338k combinados). Concepto nostálgico no funciona para esta audiencia</t>
         </is>
       </c>
     </row>
     <row r="228" ht="48" customHeight="1">
       <c r="B228" s="54" t="inlineStr"/>
-      <c r="C228" s="59" t="inlineStr">
+      <c r="C228" s="50" t="inlineStr">
+        <is>
+          <t>🟢 OPORTUNIDAD</t>
+        </is>
+      </c>
+      <c r="D228" s="51" t="inlineStr">
+        <is>
+          <t>Cotton candy y tu pareja generan clicks</t>
+        </is>
+      </c>
+      <c r="H228" s="52" t="inlineStr">
+        <is>
+          <t>'Cotton candy frutilla' entregó 407 clicks a $17 c/u (57% bajo benchmark) con CTR 4.3%. 'Tu pareja te debe' logró 760 clicks a $19 c/u, anuncio nuevo este mes.</t>
+        </is>
+      </c>
+      <c r="M228" s="53" t="inlineStr">
+        <is>
+          <t>Iterar estos 2 conceptos con CTA más claro hacia compra en vez de solo visita perfil</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="48" customHeight="1">
+      <c r="B229" s="54" t="inlineStr"/>
+      <c r="C229" s="59" t="inlineStr">
         <is>
           <t>🔵 INSIGHT</t>
         </is>
       </c>
-      <c r="D228" s="60" t="inlineStr">
+      <c r="D229" s="60" t="inlineStr">
         <is>
           <t>Bridgerton colapsó sin razón clara</t>
         </is>
       </c>
-      <c r="H228" s="61" t="inlineStr">
-        <is>
-          <t>'Bridgerton prueba' cayó de 15.496 resultados a solo 4 clicks con gasto mínimo $51. CTR 5,33% y costo $13 sugieren que el anuncio funciona pero fue pausado o recibió mínima inversión.</t>
-        </is>
-      </c>
-      <c r="M228" s="62" t="inlineStr">
-        <is>
-          <t>Revisar si fue pausado manualmente o por regla automática. Reactivar con presupuesto mínimo $500/día para validar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="229" ht="48" customHeight="1">
-      <c r="B229" s="49" t="inlineStr">
-        <is>
-          <t>Campaña principal de Conversión</t>
-        </is>
-      </c>
-      <c r="C229" s="50" t="inlineStr">
-        <is>
-          <t>🔴 ALERTA</t>
-        </is>
-      </c>
-      <c r="D229" s="51" t="inlineStr">
-        <is>
-          <t>Costo promedio 27% sobre benchmark</t>
-        </is>
-      </c>
-      <c r="H229" s="52" t="inlineStr">
-        <is>
-          <t>Costo promedio $7.642 por compra vs benchmark ganador $6k, con mayoría de anuncios en $9k-$13k. 'Home Spray' el peor con $13.042 por compra gastando $1,2M (22% del presupuesto total).</t>
-        </is>
-      </c>
-      <c r="M229" s="53" t="inlineStr">
-        <is>
-          <t>Pausar 'Home Spray' esta semana: ROAS 2,45 no justifica $13k por conversión. Redirigir su budget a ganadoras.</t>
+      <c r="H229" s="61" t="inlineStr">
+        <is>
+          <t>Pasó de 15.496 clicks en marzo a solo 4 en abril con gasto mínimo $51. CTR 5.33% sugiere que el concepto aún funciona pero fue desprioritizado por el algoritmo.</t>
+        </is>
+      </c>
+      <c r="M229" s="62" t="inlineStr">
+        <is>
+          <t>Relanzar Bridgerton con presupuesto mínimo ($5k) para validar si el concepto sigue vigente o perdió relevancia cultural</t>
         </is>
       </c>
     </row>
     <row r="230" ht="48" customHeight="1">
-      <c r="B230" s="54" t="inlineStr"/>
-      <c r="C230" s="55" t="inlineStr">
+      <c r="B230" s="49" t="inlineStr">
+        <is>
+          <t>Remarketing Go Nails 2024</t>
+        </is>
+      </c>
+      <c r="C230" s="50" t="inlineStr">
         <is>
           <t>🟢 OPORTUNIDAD</t>
         </is>
       </c>
-      <c r="D230" s="56" t="inlineStr">
-        <is>
-          <t>5 anuncios ganadoras bajo $7k</t>
-        </is>
-      </c>
-      <c r="H230" s="57" t="inlineStr">
-        <is>
-          <t>'Reel cafetería' ($5.089), 'Cremas Sun Kissed' ($5.687), 'Imagen Bubble gum' ($6.672), 'Protector Termico' ($6.872) y 'Macbook' ($6.886) logran costos ganadores con ROAS 3,71-5. Representan solo $349k del presupuesto.</t>
-        </is>
-      </c>
-      <c r="M230" s="58" t="inlineStr">
-        <is>
-          <t>Crear 3 variantes de cada ganadora con diferentes hooks para escalar sin saturar la audiencia.</t>
+      <c r="D230" s="51" t="inlineStr">
+        <is>
+          <t>Despacho Gratis es el ganador absoluto</t>
+        </is>
+      </c>
+      <c r="H230" s="52" t="inlineStr">
+        <is>
+          <t>Costo $4.137/compra (31% bajo benchmark) con ROAS 4.82 y 32 conversiones. Es el anuncio más eficiente de toda la marca en abril.</t>
+        </is>
+      </c>
+      <c r="M230" s="53" t="inlineStr">
+        <is>
+          <t>Crear 2 variaciones del concepto 'Despacho Gratis' (con urgencia temporal + con monto mínimo) para rotar cada semana</t>
         </is>
       </c>
     </row>
     <row r="231" ht="48" customHeight="1">
       <c r="B231" s="54" t="inlineStr"/>
-      <c r="C231" s="50" t="inlineStr">
+      <c r="C231" s="55" t="inlineStr">
         <is>
           <t>🔴 ALERTA</t>
         </is>
       </c>
-      <c r="D231" s="51" t="inlineStr">
-        <is>
-          <t>Hold Rate bajo 2% en mayoría</t>
-        </is>
-      </c>
-      <c r="H231" s="52" t="inlineStr">
-        <is>
-          <t>12 de 15 anuncios tienen Hold Rate bajo 2%, indicando que pierden audiencia inmediatamente. 'Crema dibujada' 0,6%, 'Hot Chocolate' 0%, 'Imagen Gato' 0,1% con costos $9k-$17k.</t>
-        </is>
-      </c>
-      <c r="M231" s="53" t="inlineStr">
-        <is>
-          <t>Rotar todos los creativos con Hold bajo 2% esta semana: ciclo normal es 2 semanas y estos ya están quemados.</t>
+      <c r="D231" s="56" t="inlineStr">
+        <is>
+          <t>15% OFF colapsó 97% vs marzo</t>
+        </is>
+      </c>
+      <c r="H231" s="57" t="inlineStr">
+        <is>
+          <t>Cayó de 34 a 1 compra con costo $7.957 (33% sobre benchmark) y ROAS 2.51. Hold Rate 5.7% muestra que la audiencia abandona rápido.</t>
+        </is>
+      </c>
+      <c r="M231" s="58" t="inlineStr">
+        <is>
+          <t>Pausar 15% OFF y reemplazar con descuento más agresivo (20-25%) o bundle tipo '4x3' que ya probó funcionar</t>
         </is>
       </c>
     </row>
@@ -9760,47 +9760,47 @@
           <t>Campaña Secundaria LMM</t>
         </is>
       </c>
-      <c r="C232" s="55" t="inlineStr">
+      <c r="C232" s="50" t="inlineStr">
         <is>
           <t>🟢 OPORTUNIDAD</t>
         </is>
       </c>
-      <c r="D232" s="56" t="inlineStr">
-        <is>
-          <t>Reel Kit LMM ROAS excepcional</t>
-        </is>
-      </c>
-      <c r="H232" s="57" t="inlineStr">
-        <is>
-          <t>'Reel Kit LMM' logra ROAS 15,27 con costo $2.473 por compra y Hold Rate 14,6%, muy superior a benchmark. Solo recibió $12k de inversión vs $60k del otro anuncio.</t>
-        </is>
-      </c>
-      <c r="M232" s="58" t="inlineStr">
-        <is>
-          <t>Escalar 'Reel Kit LMM' inmediatamente: crear 2 versiones con distinto audio y aumentar presupuesto diario.</t>
+      <c r="D232" s="51" t="inlineStr">
+        <is>
+          <t>Reel Kit LMM es joya oculta</t>
+        </is>
+      </c>
+      <c r="H232" s="52" t="inlineStr">
+        <is>
+          <t>ROAS 15.27 con costo $2.473/compra (59% bajo benchmark) y Hold Rate 14.6% — el mejor engagement de toda la marca. Solo gastó $12k en el mes.</t>
+        </is>
+      </c>
+      <c r="M232" s="53" t="inlineStr">
+        <is>
+          <t>Escalar Reel Kit LMM triplicando exposición con audiencias similares a compradoras actuales</t>
         </is>
       </c>
     </row>
     <row r="233" ht="48" customHeight="1">
       <c r="B233" s="54" t="inlineStr"/>
-      <c r="C233" s="59" t="inlineStr">
-        <is>
-          <t>🔵 INSIGHT</t>
-        </is>
-      </c>
-      <c r="D233" s="60" t="inlineStr">
-        <is>
-          <t>Hold Rate LMM duplica promedio Go Nails</t>
-        </is>
-      </c>
-      <c r="H233" s="61" t="inlineStr">
-        <is>
-          <t>Anuncios LMM logran Hold Rate 14,6-32,1% vs 0-7% en campaña principal, indicando que contenido de kit/tutorial retiene mejor que solo producto. CTR 2,79-4,65% también superior.</t>
-        </is>
-      </c>
-      <c r="M233" s="62" t="inlineStr">
-        <is>
-          <t>Aplicar formato tutorial paso a paso de LMM a productos Go Nails principales: el formato funciona mejor.</t>
+      <c r="C233" s="55" t="inlineStr">
+        <is>
+          <t>🔴 ALERTA</t>
+        </is>
+      </c>
+      <c r="D233" s="56" t="inlineStr">
+        <is>
+          <t>Reel esmalte LMM pierde eficiencia rápido</t>
+        </is>
+      </c>
+      <c r="H233" s="57" t="inlineStr">
+        <is>
+          <t>Costo subió a $10.138/compra (69% sobre benchmark) con ROAS 3.36 pese a Hold Rate excepcional 19.7%. Frecuencia alta probable tras 17 compras en marzo.</t>
+        </is>
+      </c>
+      <c r="M233" s="58" t="inlineStr">
+        <is>
+          <t>Mantener por una semana más monitoreando frecuencia. Si supera 4x, pausar y crear versión 2.0 con nuevo producto LMM</t>
         </is>
       </c>
     </row>
@@ -9812,45 +9812,45 @@
       </c>
       <c r="C234" s="50" t="inlineStr">
         <is>
-          <t>🔴 ALERTA</t>
+          <t>🟢 OPORTUNIDAD</t>
         </is>
       </c>
       <c r="D234" s="51" t="inlineStr">
         <is>
-          <t>Costo por click 7x sobre benchmark</t>
+          <t>Macbook tiene mejor ROAS de catálogo</t>
         </is>
       </c>
       <c r="H234" s="52" t="inlineStr">
         <is>
-          <t>Costo promedio $2.767 por click vs benchmark ganador $20, con anuncios como 'Reel de fragancias' a $262 y 'Carrusel Post que puedes oler' a $283. Solo 338 clicks totales con $935k gastados.</t>
+          <t>ROAS 9.93 con 7 compras a $3.087 c/u (49% bajo benchmark para compras). Es anuncio mixto link_click/purchase y está funcionando en ambos objetivos.</t>
         </is>
       </c>
       <c r="M234" s="53" t="inlineStr">
         <is>
-          <t>Pausar toda la campaña inmediatamente: el objetivo debería ser compra, no clicks a este costo astronómico.</t>
+          <t>Duplicar concepto Macbook con otros productos lifestyle (escritorio, café, rutina matutina) para aprovechar formato ganador</t>
         </is>
       </c>
     </row>
     <row r="235" ht="48" customHeight="1">
       <c r="B235" s="54" t="inlineStr"/>
-      <c r="C235" s="55" t="inlineStr">
-        <is>
-          <t>🟢 OPORTUNIDAD</t>
-        </is>
-      </c>
-      <c r="D235" s="56" t="inlineStr">
-        <is>
-          <t>Macbook convierte en catálogo inesperadamente</t>
-        </is>
-      </c>
-      <c r="H235" s="57" t="inlineStr">
-        <is>
-          <t>'Macbook' generó 7 compras (no clicks) con ROAS 9,93 y costo $3.087, siendo el único anuncio tipo purchase en campaña de tráfico. Gasto mínimo $21k pero alta eficiencia.</t>
-        </is>
-      </c>
-      <c r="M235" s="58" t="inlineStr">
-        <is>
-          <t>Migrar 'Macbook' a campaña principal de conversión con presupuesto $500/día para escalar este ganador oculto.</t>
+      <c r="C235" s="59" t="inlineStr">
+        <is>
+          <t>🔵 INSIGHT</t>
+        </is>
+      </c>
+      <c r="D235" s="60" t="inlineStr">
+        <is>
+          <t>Costos de click están inflados 250%</t>
+        </is>
+      </c>
+      <c r="H235" s="61" t="inlineStr">
+        <is>
+          <t>Costo promedio $2.767/click está 6.817% sobre benchmark ($40). Solo 'Hot Chocolate' ($35/click) y 'Nuevos difusores' ($72/click) están cerca del rango aceptable.</t>
+        </is>
+      </c>
+      <c r="M235" s="62" t="inlineStr">
+        <is>
+          <t>Revisar configuración de campaña: probable targeting muy específico o bid strategy incorrecta. Ampliar audiencia o cambiar a Advantage+</t>
         </is>
       </c>
     </row>

--- a/reportes/Reporte_abril_2026.xlsx
+++ b/reportes/Reporte_abril_2026.xlsx
@@ -235,7 +235,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -422,6 +422,12 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -788,7 +794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:T68"/>
+  <dimension ref="B1:T288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="2" max="2"/>
@@ -2959,7 +2965,7 @@
     <row r="56" ht="36" customHeight="1">
       <c r="B56" s="47" t="inlineStr">
         <is>
-          <t>Seducete redujo gasto 8% ($5.1M vs $5.5M) pero resultados cayeron 14% (30,410 vs 35,423). La campaña BLACK WEEK lidera conversiones con ROAS 1.18 y CPC $1,988, mientras anuncios de productos específicos superan los $10,000/conversión.</t>
+          <t>Seducete gastó $5.1M en abril (7.6% menos que marzo) pero los resultados cayeron 14% (de 35,423 a 30,410). La eficiencia se deterioró: costo por compra subió de ~$3,800 a $5,081 en la campaña principal de ventas.</t>
         </is>
       </c>
     </row>
@@ -3003,17 +3009,17 @@
       </c>
       <c r="D58" s="51" t="inlineStr">
         <is>
-          <t>Hold Rate crítico en ambos anuncios</t>
+          <t>Costo por click alto en Academia</t>
         </is>
       </c>
       <c r="H58" s="52" t="inlineStr">
         <is>
-          <t>Academia Cursos Gratuitos tiene hold50 5.8% y Cursos Presenciales 3.6%, muy por debajo del 8% mínimo. La audiencia abandona antes de la mitad del video.</t>
+          <t>El anuncio de Cursos Gratuitos tiene costo de $59/click, 48% sobre benchmark OK ($40). Hold Rate de 5.8% indica que el video pierde audiencia rápido.</t>
         </is>
       </c>
       <c r="M58" s="53" t="inlineStr">
         <is>
-          <t>Cambiar los primeros 3 segundos de ambos videos con hook más directo mostrando beneficio del curso desde el frame 1</t>
+          <t>Cambiar apertura del video: mostrar el beneficio del curso en los primeros 2 segundos para mejorar Hold Rate</t>
         </is>
       </c>
     </row>
@@ -3026,17 +3032,17 @@
       </c>
       <c r="D59" s="56" t="inlineStr">
         <is>
-          <t>CPC dentro de benchmark</t>
+          <t>Cursos Presenciales dentro de benchmark</t>
         </is>
       </c>
       <c r="H59" s="57" t="inlineStr">
         <is>
-          <t>Cursos Presenciales logró CPC $47 (ganador &lt;$40) y Academia $59 (OK &lt;$80). Generaron 3,665 clicks con presupuesto eficiente.</t>
+          <t>Costo de $47/click está en rango ganador (&lt;$20 sería ideal pero &lt;$40 es OK). Generó 1,890 clicks con CTR 1.7%, levemente mejor que el mes anterior (1,847).</t>
         </is>
       </c>
       <c r="M59" s="58" t="inlineStr">
         <is>
-          <t>Mantener estos anuncios activos pero rotar creativos en 2 semanas para evitar fatiga</t>
+          <t>Duplicar este anuncio con variante mostrando testimonios de alumnas para testear si mejora CTR</t>
         </is>
       </c>
     </row>
@@ -3053,17 +3059,17 @@
       </c>
       <c r="D60" s="51" t="inlineStr">
         <is>
-          <t>Esmaltado Permanente fuera de control</t>
+          <t>Esmaltado Permanente colapsó con costo crítico</t>
         </is>
       </c>
       <c r="H60" s="52" t="inlineStr">
         <is>
-          <t>CPA $10,958 vs benchmark $18k máximo - pero solo 15 conversiones vs 1 en marzo. El creativo tiene CTR 2.89% y hold50 5.8% aceptable.</t>
+          <t>Costo por compra de $10,958 está 500% sobre benchmark pausable ($18k es límite). Solo 15 conversiones vs 1 en marzo, pero con inversión masiva de $164k.</t>
         </is>
       </c>
       <c r="M60" s="53" t="inlineStr">
         <is>
-          <t>Pausar inmediatamente. Crear nuevo video con testimonial de clienta mostrando resultado final en los primeros 2 segundos</t>
+          <t>Pausar anuncio inmediatamente y rotar creativo: testear formato antes/después con cliente real aplicando el producto</t>
         </is>
       </c>
     </row>
@@ -3076,17 +3082,17 @@
       </c>
       <c r="D61" s="60" t="inlineStr">
         <is>
-          <t>Manicurista Carrusel perdió 82% resultados</t>
+          <t>Manicurista Carrusel genera clicks baratos</t>
         </is>
       </c>
       <c r="H61" s="61" t="inlineStr">
         <is>
-          <t>De 1,027 clicks en marzo a 182 en abril. CPC $42 es ganador pero hold50 0.5% indica que el carrusel no retiene atención.</t>
+          <t>CTR 3.92% es excelente y costo $42/click está en rango ganador. Generó 182 clicks pero cayó dramáticamente vs marzo (1,027 clicks).</t>
         </is>
       </c>
       <c r="M61" s="62" t="inlineStr">
         <is>
-          <t>Reemplazar carrusel estático por video corto 7 segundos mostrando transformación antes/después</t>
+          <t>Este anuncio está en campaña incorrecta (objetivo purchase pero optimiza link_click). Moverlo a campaña de tráfico puro</t>
         </is>
       </c>
     </row>
@@ -3103,40 +3109,40 @@
       </c>
       <c r="D62" s="56" t="inlineStr">
         <is>
-          <t>CPL $76 dentro de rango OK</t>
+          <t>Ambos anuncios dentro de benchmark OK</t>
         </is>
       </c>
       <c r="H62" s="57" t="inlineStr">
         <is>
-          <t>2,931 leads con CPL $76 (benchmark OK &lt;$90). Segundo video tiene mejor hold50 9.8% vs 6.4% del anuncio principal.</t>
+          <t>Costo por lead de $76-$78 está en rango aceptable (&lt;$90). CTR sobre 4% es fuerte. Segundo video tiene mejor Hold Rate (9.8% vs 6.4%).</t>
         </is>
       </c>
       <c r="M62" s="58" t="inlineStr">
         <is>
-          <t>Duplicar presupuesto del Segundo video en nueva variación A/B con CTA más fuerte en segundo 5</t>
+          <t>Aumentar peso del Segundo video con mejor Hold: crear variante B agregando subtítulos para mejorar retención</t>
         </is>
       </c>
     </row>
     <row r="63" ht="48" customHeight="1">
       <c r="B63" s="54" t="inlineStr"/>
-      <c r="C63" s="50" t="inlineStr">
-        <is>
-          <t>🔴 ALERTA</t>
-        </is>
-      </c>
-      <c r="D63" s="51" t="inlineStr">
-        <is>
-          <t>Cambio 11-07 perdiendo tracción</t>
-        </is>
-      </c>
-      <c r="H63" s="52" t="inlineStr">
-        <is>
-          <t>Cayó de 2,671 a 2,417 leads (-9.5%) pero mantiene CPL $76 estable. CTR 4.33% es fuerte pero hold50 6.4% está en el límite.</t>
-        </is>
-      </c>
-      <c r="M63" s="53" t="inlineStr">
-        <is>
-          <t>Preparar nuevo creativo para rotar en 1 semana - probar formato pregunta/respuesta sobre objeciones del curso</t>
+      <c r="C63" s="59" t="inlineStr">
+        <is>
+          <t>🔵 INSIGHT</t>
+        </is>
+      </c>
+      <c r="D63" s="60" t="inlineStr">
+        <is>
+          <t>Formularios mantuvo volumen estable</t>
+        </is>
+      </c>
+      <c r="H63" s="61" t="inlineStr">
+        <is>
+          <t>Generó 2,931 leads en abril vs 2,673 en marzo (9.7% más). Eficiencia se mantuvo estable a pesar de menor inversión total.</t>
+        </is>
+      </c>
+      <c r="M63" s="62" t="inlineStr">
+        <is>
+          <t>Mantener creativos actuales pero preparar rotación en 1 semana (están cerca del ciclo de 2 semanas)</t>
         </is>
       </c>
     </row>
@@ -3153,17 +3159,17 @@
       </c>
       <c r="D64" s="51" t="inlineStr">
         <is>
-          <t>8 anuncios superan $10k CPA crítico</t>
+          <t>9 de 15 anuncios sobre benchmark pausable</t>
         </is>
       </c>
       <c r="H64" s="52" t="inlineStr">
         <is>
-          <t>Base Evita ($10,888), Nuevos Satinados ($10,040), Lámpara Pre Curado ($11,153), Ojos Satinados ($19,856), Efecto glaseado ($11,081) destruyen presupuesto. Suman $610k gastados.</t>
+          <t>Base Evita 2 ($10,888), Ojos Satinados Nuevos ($19,856), Efecto Glaseado ($11,081), Lámpara Pre Curado ($11,153) y otros 5 están sobre $10k. Benchmark pausable es $18k.</t>
         </is>
       </c>
       <c r="M64" s="53" t="inlineStr">
         <is>
-          <t>Pausar estos 5 anuncios HOY. Redirigir ese presupuesto fijo a escalar BLACK WEEK que tiene ROAS 1.18 y CPC $1,988</t>
+          <t>Pausar estos 9 anuncios esta semana y concentrar inversión en los 3 ganadores: BLACK WEEK, Lanzamiento Jelly Pop y Torno Artistic</t>
         </is>
       </c>
     </row>
@@ -3176,40 +3182,40 @@
       </c>
       <c r="D65" s="56" t="inlineStr">
         <is>
-          <t>BLACK WEEK único anuncio rentable</t>
+          <t>BLACK WEEK es el único ganador claro</t>
         </is>
       </c>
       <c r="H65" s="57" t="inlineStr">
         <is>
-          <t>ROAS 1.18, CPA $1,988 (ganador &lt;$6k), 236 conversiones vs 159 en marzo (+48%). Es el mejor performer de toda la marca.</t>
+          <t>Costo $1,988/compra (10x mejor que promedio campaña), ROAS 1.18 y generó 236 conversiones (27% del total). Subió 48% vs marzo (159 conversiones).</t>
         </is>
       </c>
       <c r="M65" s="58" t="inlineStr">
         <is>
-          <t>Crear 3 variaciones de este creativo manteniendo estructura pero cambiando producto destacado y testimonial</t>
+          <t>Crear 2 variantes de este creativo cambiando CTA y precio de entrada para escalar performance</t>
         </is>
       </c>
     </row>
     <row r="66" ht="48" customHeight="1">
       <c r="B66" s="54" t="inlineStr"/>
-      <c r="C66" s="59" t="inlineStr">
-        <is>
-          <t>🔵 INSIGHT</t>
-        </is>
-      </c>
-      <c r="D66" s="60" t="inlineStr">
-        <is>
-          <t>Hold Rate correlaciona con ROAS</t>
-        </is>
-      </c>
-      <c r="H66" s="61" t="inlineStr">
-        <is>
-          <t>Jo Nail Artist tiene hold50 10.3% y Sedu Tips 10.1% pero CPA sigue alto ($5,575 y $5,752). El problema no es retención sino propuesta de valor.</t>
-        </is>
-      </c>
-      <c r="M66" s="62" t="inlineStr">
-        <is>
-          <t>Rehacer ambos videos enfocando primeros 3 segundos en beneficio funcional no en demostración técnica</t>
+      <c r="C66" s="50" t="inlineStr">
+        <is>
+          <t>🔴 ALERTA</t>
+        </is>
+      </c>
+      <c r="D66" s="51" t="inlineStr">
+        <is>
+          <t>Caída generalizada en conversiones vs marzo</t>
+        </is>
+      </c>
+      <c r="H66" s="52" t="inlineStr">
+        <is>
+          <t>10 de 15 anuncios bajaron conversiones vs marzo. Top Templado cayó 63% (111→41), Higienizantes 53% (123→58), Carrusel Uñas 75% (204→51).</t>
+        </is>
+      </c>
+      <c r="M66" s="53" t="inlineStr">
+        <is>
+          <t>Auditar fatiga de audiencia: revisar frecuencia en Business Manager y preparar batch de 8 creativos nuevos para rotar en 3 días</t>
         </is>
       </c>
     </row>
@@ -3226,17 +3232,17 @@
       </c>
       <c r="D67" s="56" t="inlineStr">
         <is>
-          <t>Se te quebró la uña es ganadora</t>
+          <t>Se te quebró la uña es ganador absoluto</t>
         </is>
       </c>
       <c r="H67" s="57" t="inlineStr">
         <is>
-          <t>CPC $4 (ganador &lt;$20), CTR 10.1% excepcional, hold50 22.1% brutal - 22,721 clicks. Es el anuncio con mejor engagement de toda Seducete.</t>
+          <t>Costo $4/click (5x mejor que benchmark ganador $20), CTR 10.1% es extraordinario, Hold Rate 22.1% es excepcional. Generó 22,721 clicks con solo $99k.</t>
         </is>
       </c>
       <c r="M67" s="58" t="inlineStr">
         <is>
-          <t>Crear landing page específica para este tráfico y convertir campaña a objetivo conversión manteniendo este creativo</t>
+          <t>Escalar este formato: crear serie de 3 videos más con mismo estilo resolviendo otros pain points (uñas amarillas, despegue de esmalte)</t>
         </is>
       </c>
     </row>
@@ -3249,73 +3255,8449 @@
       </c>
       <c r="D68" s="60" t="inlineStr">
         <is>
-          <t>Nuevos tests sin volumen suficiente</t>
+          <t>Nuevo contenido sin presupuesto suficiente</t>
         </is>
       </c>
       <c r="H68" s="61" t="inlineStr">
         <is>
-          <t>4 anuncios nuevos (uñas respiran, 5 cosas, hannah montana, otoño 2026) con gasto &lt;$200 y &lt;10 clicks cada uno. No hay data para decidir.</t>
+          <t>4 anuncios nuevos (uñas respiran, hannah montana, otoño 2026, 5 cosas) tienen gasto mínimo ($8-$144) y no alcanzaron fase de aprendizaje.</t>
         </is>
       </c>
       <c r="M68" s="62" t="inlineStr">
         <is>
-          <t>Dar 7 días más a estos tests con gasto mínimo o pausar para concentrar en el anuncio ganador</t>
+          <t>Estos tests necesitan mínimo $10k c/u para evaluar. Consolidar los 4 en 1 solo anuncio tipo carrusel y darle 2 semanas</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="24" customHeight="1">
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>BLUESKY</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="22" customHeight="1">
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>▸ Tráfico Perfil Instagram MKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="18" customHeight="1">
+      <c r="B73" s="25" t="inlineStr">
+        <is>
+          <t>Diseño Floral</t>
+        </is>
+      </c>
+      <c r="C73" s="26" t="n">
+        <v>30753</v>
+      </c>
+      <c r="D73" s="26" t="n">
+        <v>37195</v>
+      </c>
+      <c r="E73" s="26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F73" s="27" t="n">
+        <v>2662</v>
+      </c>
+      <c r="G73" s="28" t="n">
+        <v>12461</v>
+      </c>
+      <c r="H73" s="29" t="inlineStr">
+        <is>
+          <t>-79%</t>
+        </is>
+      </c>
+      <c r="I73" s="30" t="n">
+        <v>15873</v>
+      </c>
+      <c r="J73" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="K73" s="26" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="L73" s="26" t="n">
+        <v>426</v>
+      </c>
+      <c r="M73" s="26" t="inlineStr"/>
+      <c r="N73" s="26" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="O73" s="26" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="P73" s="26" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q73" s="26" t="inlineStr"/>
+      <c r="R73" s="26" t="inlineStr"/>
+      <c r="S73" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="B74" s="25" t="inlineStr">
+        <is>
+          <t>Diseño Conchitas</t>
+        </is>
+      </c>
+      <c r="C74" s="26" t="n">
+        <v>94307</v>
+      </c>
+      <c r="D74" s="26" t="n">
+        <v>156620</v>
+      </c>
+      <c r="E74" s="26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F74" s="27" t="n">
+        <v>11185</v>
+      </c>
+      <c r="G74" s="28" t="n">
+        <v>3161</v>
+      </c>
+      <c r="H74" s="31" t="inlineStr">
+        <is>
+          <t>+254%</t>
+        </is>
+      </c>
+      <c r="I74" s="30" t="n">
+        <v>69955</v>
+      </c>
+      <c r="J74" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="K74" s="26" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="L74" s="26" t="n">
+        <v>446</v>
+      </c>
+      <c r="M74" s="26" t="inlineStr"/>
+      <c r="N74" s="26" t="n">
+        <v>25</v>
+      </c>
+      <c r="O74" s="26" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="P74" s="26" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q74" s="26" t="inlineStr"/>
+      <c r="R74" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="S74" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="18" customHeight="1">
+      <c r="B75" s="25" t="inlineStr">
+        <is>
+          <t>diseño limon verano</t>
+        </is>
+      </c>
+      <c r="C75" s="26" t="n">
+        <v>6181</v>
+      </c>
+      <c r="D75" s="26" t="n">
+        <v>6691</v>
+      </c>
+      <c r="E75" s="26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F75" s="27" t="n">
+        <v>509</v>
+      </c>
+      <c r="G75" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="H75" s="31" t="inlineStr">
+        <is>
+          <t>+25350%</t>
+        </is>
+      </c>
+      <c r="I75" s="30" t="n">
+        <v>3312</v>
+      </c>
+      <c r="J75" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="K75" s="26" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="L75" s="26" t="n">
+        <v>494</v>
+      </c>
+      <c r="M75" s="26" t="inlineStr"/>
+      <c r="N75" s="26" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="O75" s="26" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="P75" s="26" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="Q75" s="26" t="inlineStr"/>
+      <c r="R75" s="26" t="inlineStr"/>
+      <c r="S75" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="18" customHeight="1">
+      <c r="B76" s="25" t="inlineStr">
+        <is>
+          <t>prueba 1 tendencia</t>
+        </is>
+      </c>
+      <c r="C76" s="26" t="n">
+        <v>71</v>
+      </c>
+      <c r="D76" s="26" t="n">
+        <v>77</v>
+      </c>
+      <c r="E76" s="26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F76" s="27" t="n">
+        <v>8</v>
+      </c>
+      <c r="G76" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H76" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I76" s="30" t="n">
+        <v>36</v>
+      </c>
+      <c r="J76" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="K76" s="26" t="n">
+        <v>10.39</v>
+      </c>
+      <c r="L76" s="26" t="n">
+        <v>467</v>
+      </c>
+      <c r="M76" s="26" t="inlineStr"/>
+      <c r="N76" s="26" t="inlineStr"/>
+      <c r="O76" s="26" t="inlineStr"/>
+      <c r="P76" s="26" t="inlineStr"/>
+      <c r="Q76" s="26" t="inlineStr"/>
+      <c r="R76" s="26" t="inlineStr"/>
+      <c r="S76" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="B77" s="13" t="inlineStr">
+        <is>
+          <t>SUBTOTAL  Tráfico Perfil Instagram MKT</t>
+        </is>
+      </c>
+      <c r="F77" s="14" t="n">
+        <v>14364</v>
+      </c>
+      <c r="G77" s="14" t="n">
+        <v>15624</v>
+      </c>
+      <c r="H77" s="15" t="inlineStr">
+        <is>
+          <t>-8%</t>
+        </is>
+      </c>
+      <c r="I77" s="16" t="n">
+        <v>89176</v>
+      </c>
+    </row>
+    <row r="79" ht="26" customHeight="1">
+      <c r="B79" s="46" t="inlineStr">
+        <is>
+          <t>💡  Análisis Claude — Bluesky</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="36" customHeight="1">
+      <c r="B80" s="47" t="inlineStr">
+        <is>
+          <t>Bluesky invirtió $89.176 en abril generando 14.364 clicks ($6/click), levemente bajo vs marzo (15.624 clicks, $92.817). El creativo 'Diseño Conchitas' concentra el 78% del gasto y muestra engagement superior con Hold Rate 25% vs 13.1% de 'Diseño Floral'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="B81" s="48" t="inlineStr">
+        <is>
+          <t>Campaña</t>
+        </is>
+      </c>
+      <c r="C81" s="48" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="D81" s="48" t="inlineStr">
+        <is>
+          <t>Hallazgo</t>
+        </is>
+      </c>
+      <c r="H81" s="48" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="M81" s="48" t="inlineStr">
+        <is>
+          <t>Acción recomendada</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="48" customHeight="1">
+      <c r="B82" s="49" t="inlineStr">
+        <is>
+          <t>Tráfico Perfil Instagram MKT</t>
+        </is>
+      </c>
+      <c r="C82" s="55" t="inlineStr">
+        <is>
+          <t>🟢 OPORTUNIDAD</t>
+        </is>
+      </c>
+      <c r="D82" s="56" t="inlineStr">
+        <is>
+          <t>Conchitas domina con engagement superior</t>
+        </is>
+      </c>
+      <c r="H82" s="57" t="inlineStr">
+        <is>
+          <t>'Diseño Conchitas' generó 11.185 clicks (78% del total) con Hold Rate 25% vs 13.1% de 'Floral', y escaló 254% vs marzo (3.161 clicks). El CTR 7.1% está sobre benchmark con costo $6/click en rango OK.</t>
+        </is>
+      </c>
+      <c r="M82" s="58" t="inlineStr">
+        <is>
+          <t>Crear 2 variaciones nuevas del concepto 'Conchitas' esta semana probando distintos call-to-actions para mantener frescura antes de fatiga (frecuencia no disponible pero es el creativo dominante hace 2 meses).</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="48" customHeight="1">
+      <c r="B83" s="54" t="inlineStr"/>
+      <c r="C83" s="50" t="inlineStr">
+        <is>
+          <t>🔴 ALERTA</t>
+        </is>
+      </c>
+      <c r="D83" s="51" t="inlineStr">
+        <is>
+          <t>Floral perdió 79% efectividad mensual</t>
+        </is>
+      </c>
+      <c r="H83" s="52" t="inlineStr">
+        <is>
+          <t>'Diseño Floral' cayó de 12.461 clicks (marzo) a 2.662 (abril) con Hold Rate crítico 13.1%. Invirtió $15.873 (18% presupuesto) con misma eficiencia $6/click pero engagement bajo indica fatiga creativa.</t>
+        </is>
+      </c>
+      <c r="M83" s="53" t="inlineStr">
+        <is>
+          <t>Pausar 'Diseño Floral' inmediatamente y reasignar ese espacio a test de 'Diseño limón verano' que tiene CTR 7.58% (el más alto) pero solo $3.312 de inversión exploratoria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="48" customHeight="1">
+      <c r="B84" s="54" t="inlineStr"/>
+      <c r="C84" s="59" t="inlineStr">
+        <is>
+          <t>🔵 INSIGHT</t>
+        </is>
+      </c>
+      <c r="D84" s="60" t="inlineStr">
+        <is>
+          <t>Limón muestra potencial sin explotar</t>
+        </is>
+      </c>
+      <c r="H84" s="61" t="inlineStr">
+        <is>
+          <t>'Diseño limón verano' tiene el CTR más alto (7.58%), Hold Rate 18.2% aceptable y costo $7/click (dentro de rango). Solo recibió $3.312 (4% presupuesto) generando 509 clicks vs 2 en marzo.</t>
+        </is>
+      </c>
+      <c r="M84" s="62" t="inlineStr">
+        <is>
+          <t>Escalar 'Limón verano' ocupando el espacio de 'Floral' pausado. Crear una versión B del limón cambiando el hook de los primeros 3 segundos para validar si el concepto estacional sostiene volumen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="24" customHeight="1">
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>NAIL OUTLET</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="22" customHeight="1">
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>▸ Objetivo Conversión Ventas</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="18" customHeight="1">
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>Esmaltes French Nail Pro</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="n">
+        <v>12055</v>
+      </c>
+      <c r="D89" s="7" t="n">
+        <v>38382</v>
+      </c>
+      <c r="E89" s="7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F89" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G89" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="H89" s="17" t="inlineStr">
+        <is>
+          <t>-57%</t>
+        </is>
+      </c>
+      <c r="I89" s="11" t="n">
+        <v>76227</v>
+      </c>
+      <c r="J89" s="11" t="n">
+        <v>12704</v>
+      </c>
+      <c r="K89" s="7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="L89" s="7" t="n">
+        <v>1986</v>
+      </c>
+      <c r="M89" s="7" t="inlineStr"/>
+      <c r="N89" s="7" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="O89" s="7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="P89" s="7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q89" s="7" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="R89" s="7" t="n">
+        <v>285</v>
+      </c>
+      <c r="S89" s="12" t="inlineStr">
+        <is>
+          <t>🔍 REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="18" customHeight="1">
+      <c r="B90" s="32" t="inlineStr">
+        <is>
+          <t>40 Esmaltes Julio</t>
+        </is>
+      </c>
+      <c r="C90" s="33" t="n">
+        <v>12455</v>
+      </c>
+      <c r="D90" s="33" t="n">
+        <v>32741</v>
+      </c>
+      <c r="E90" s="33" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F90" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G90" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="H90" s="36" t="inlineStr">
+        <is>
+          <t>-40%</t>
+        </is>
+      </c>
+      <c r="I90" s="37" t="n">
+        <v>57856</v>
+      </c>
+      <c r="J90" s="37" t="n">
+        <v>19285</v>
+      </c>
+      <c r="K90" s="33" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="L90" s="33" t="n">
+        <v>1767</v>
+      </c>
+      <c r="M90" s="33" t="inlineStr"/>
+      <c r="N90" s="33" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O90" s="33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P90" s="33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q90" s="33" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="R90" s="33" t="n">
+        <v>260</v>
+      </c>
+      <c r="S90" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="18" customHeight="1">
+      <c r="B91" s="18" t="inlineStr">
+        <is>
+          <t>Pack Repo 20 Agosto</t>
+        </is>
+      </c>
+      <c r="C91" s="19" t="n">
+        <v>24479</v>
+      </c>
+      <c r="D91" s="19" t="n">
+        <v>93364</v>
+      </c>
+      <c r="E91" s="19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F91" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="G91" s="21" t="n">
+        <v>38</v>
+      </c>
+      <c r="H91" s="24" t="inlineStr">
+        <is>
+          <t>-47%</t>
+        </is>
+      </c>
+      <c r="I91" s="23" t="n">
+        <v>167478</v>
+      </c>
+      <c r="J91" s="23" t="n">
+        <v>8373</v>
+      </c>
+      <c r="K91" s="19" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="L91" s="19" t="n">
+        <v>1793</v>
+      </c>
+      <c r="M91" s="19" t="inlineStr"/>
+      <c r="N91" s="19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O91" s="19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P91" s="19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q91" s="19" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="R91" s="19" t="n">
+        <v>823</v>
+      </c>
+      <c r="S91" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="18" customHeight="1">
+      <c r="B92" s="32" t="inlineStr">
+        <is>
+          <t>Efectos Chromados</t>
+        </is>
+      </c>
+      <c r="C92" s="33" t="n">
+        <v>5408</v>
+      </c>
+      <c r="D92" s="33" t="n">
+        <v>10991</v>
+      </c>
+      <c r="E92" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F92" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="H92" s="36" t="inlineStr">
+        <is>
+          <t>-88%</t>
+        </is>
+      </c>
+      <c r="I92" s="37" t="n">
+        <v>22114</v>
+      </c>
+      <c r="J92" s="37" t="n">
+        <v>22114</v>
+      </c>
+      <c r="K92" s="33" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="L92" s="33" t="n">
+        <v>2012</v>
+      </c>
+      <c r="M92" s="33" t="inlineStr"/>
+      <c r="N92" s="33" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O92" s="33" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P92" s="33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q92" s="33" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R92" s="33" t="n">
+        <v>107</v>
+      </c>
+      <c r="S92" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="B93" s="32" t="inlineStr">
+        <is>
+          <t>Campo de Trabajo</t>
+        </is>
+      </c>
+      <c r="C93" s="33" t="n">
+        <v>18936</v>
+      </c>
+      <c r="D93" s="33" t="n">
+        <v>51295</v>
+      </c>
+      <c r="E93" s="33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F93" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="G93" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="H93" s="36" t="inlineStr">
+        <is>
+          <t>-64%</t>
+        </is>
+      </c>
+      <c r="I93" s="37" t="n">
+        <v>90941</v>
+      </c>
+      <c r="J93" s="37" t="n">
+        <v>18188</v>
+      </c>
+      <c r="K93" s="33" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="L93" s="33" t="n">
+        <v>1772</v>
+      </c>
+      <c r="M93" s="33" t="inlineStr"/>
+      <c r="N93" s="33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O93" s="33" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P93" s="33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q93" s="33" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="R93" s="33" t="n">
+        <v>567</v>
+      </c>
+      <c r="S93" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="18" customHeight="1">
+      <c r="B94" s="32" t="inlineStr">
+        <is>
+          <t>Ojo de Gato</t>
+        </is>
+      </c>
+      <c r="C94" s="33" t="n">
+        <v>794</v>
+      </c>
+      <c r="D94" s="33" t="n">
+        <v>1037</v>
+      </c>
+      <c r="E94" s="33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F94" s="34" t="n">
+        <v>18</v>
+      </c>
+      <c r="G94" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="H94" s="63" t="inlineStr">
+        <is>
+          <t>+157%</t>
+        </is>
+      </c>
+      <c r="I94" s="37" t="n">
+        <v>4115</v>
+      </c>
+      <c r="J94" s="37" t="n">
+        <v>228</v>
+      </c>
+      <c r="K94" s="33" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="L94" s="33" t="n">
+        <v>3968</v>
+      </c>
+      <c r="M94" s="33" t="inlineStr"/>
+      <c r="N94" s="33" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O94" s="33" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P94" s="33" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q94" s="33" t="inlineStr"/>
+      <c r="R94" s="33" t="n">
+        <v>15</v>
+      </c>
+      <c r="S94" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="18" customHeight="1">
+      <c r="B95" s="18" t="inlineStr">
+        <is>
+          <t>Carrusel TPO Chile</t>
+        </is>
+      </c>
+      <c r="C95" s="19" t="n">
+        <v>4805</v>
+      </c>
+      <c r="D95" s="19" t="n">
+        <v>12499</v>
+      </c>
+      <c r="E95" s="19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F95" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="G95" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H95" s="24" t="inlineStr">
+        <is>
+          <t>-75%</t>
+        </is>
+      </c>
+      <c r="I95" s="23" t="n">
+        <v>25343</v>
+      </c>
+      <c r="J95" s="23" t="n">
+        <v>8447</v>
+      </c>
+      <c r="K95" s="19" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="L95" s="19" t="n">
+        <v>2027</v>
+      </c>
+      <c r="M95" s="19" t="inlineStr"/>
+      <c r="N95" s="19" t="inlineStr"/>
+      <c r="O95" s="19" t="inlineStr"/>
+      <c r="P95" s="19" t="inlineStr"/>
+      <c r="Q95" s="19" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="R95" s="19" t="n">
+        <v>139</v>
+      </c>
+      <c r="S95" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="18" customHeight="1">
+      <c r="B96" s="32" t="inlineStr">
+        <is>
+          <t>Imagen primer deshidratador</t>
+        </is>
+      </c>
+      <c r="C96" s="33" t="n">
+        <v>15325</v>
+      </c>
+      <c r="D96" s="33" t="n">
+        <v>36143</v>
+      </c>
+      <c r="E96" s="33" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F96" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G96" s="35" t="n">
+        <v>13</v>
+      </c>
+      <c r="H96" s="36" t="inlineStr">
+        <is>
+          <t>-85%</t>
+        </is>
+      </c>
+      <c r="I96" s="37" t="n">
+        <v>59036</v>
+      </c>
+      <c r="J96" s="37" t="n">
+        <v>29518</v>
+      </c>
+      <c r="K96" s="33" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="L96" s="33" t="n">
+        <v>1633</v>
+      </c>
+      <c r="M96" s="33" t="inlineStr"/>
+      <c r="N96" s="33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O96" s="33" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P96" s="33" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q96" s="33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R96" s="33" t="n">
+        <v>568</v>
+      </c>
+      <c r="S96" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="18" customHeight="1">
+      <c r="B97" s="25" t="inlineStr">
+        <is>
+          <t>Poly Gel Carrusel</t>
+        </is>
+      </c>
+      <c r="C97" s="26" t="n">
+        <v>1003</v>
+      </c>
+      <c r="D97" s="26" t="n">
+        <v>2028</v>
+      </c>
+      <c r="E97" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F97" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="G97" s="28" t="n">
+        <v>73</v>
+      </c>
+      <c r="H97" s="29" t="inlineStr">
+        <is>
+          <t>-90%</t>
+        </is>
+      </c>
+      <c r="I97" s="30" t="n">
+        <v>3237</v>
+      </c>
+      <c r="J97" s="30" t="n">
+        <v>462</v>
+      </c>
+      <c r="K97" s="26" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="L97" s="26" t="n">
+        <v>1596</v>
+      </c>
+      <c r="M97" s="26" t="inlineStr"/>
+      <c r="N97" s="26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O97" s="26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P97" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q97" s="26" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="R97" s="26" t="n">
+        <v>21</v>
+      </c>
+      <c r="S97" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="18" customHeight="1">
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>Reel Ojo de Gato</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="n">
+        <v>3199</v>
+      </c>
+      <c r="D98" s="7" t="n">
+        <v>7605</v>
+      </c>
+      <c r="E98" s="7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F98" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H98" s="17" t="inlineStr">
+        <is>
+          <t>-50%</t>
+        </is>
+      </c>
+      <c r="I98" s="11" t="n">
+        <v>12486</v>
+      </c>
+      <c r="J98" s="11" t="n">
+        <v>12486</v>
+      </c>
+      <c r="K98" s="7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L98" s="7" t="n">
+        <v>1641</v>
+      </c>
+      <c r="M98" s="7" t="inlineStr"/>
+      <c r="N98" s="7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O98" s="7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="P98" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q98" s="7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R98" s="7" t="n">
+        <v>106</v>
+      </c>
+      <c r="S98" s="12" t="inlineStr">
+        <is>
+          <t>🔍 REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="18" customHeight="1">
+      <c r="B99" s="25" t="inlineStr">
+        <is>
+          <t>Imagen Mesa Nail Pro</t>
+        </is>
+      </c>
+      <c r="C99" s="26" t="n">
+        <v>17596</v>
+      </c>
+      <c r="D99" s="26" t="n">
+        <v>58494</v>
+      </c>
+      <c r="E99" s="26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F99" s="27" t="n">
+        <v>22</v>
+      </c>
+      <c r="G99" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="H99" s="31" t="inlineStr">
+        <is>
+          <t>+120%</t>
+        </is>
+      </c>
+      <c r="I99" s="30" t="n">
+        <v>108515</v>
+      </c>
+      <c r="J99" s="30" t="n">
+        <v>4932</v>
+      </c>
+      <c r="K99" s="26" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="L99" s="26" t="n">
+        <v>1855</v>
+      </c>
+      <c r="M99" s="26" t="inlineStr"/>
+      <c r="N99" s="26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O99" s="26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P99" s="26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q99" s="26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R99" s="26" t="n">
+        <v>1037</v>
+      </c>
+      <c r="S99" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="18" customHeight="1">
+      <c r="B100" s="25" t="inlineStr">
+        <is>
+          <t>Imagen Limas y herramientas</t>
+        </is>
+      </c>
+      <c r="C100" s="26" t="n">
+        <v>6704</v>
+      </c>
+      <c r="D100" s="26" t="n">
+        <v>17694</v>
+      </c>
+      <c r="E100" s="26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F100" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="G100" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="H100" s="31" t="inlineStr">
+        <is>
+          <t>+250%</t>
+        </is>
+      </c>
+      <c r="I100" s="30" t="n">
+        <v>22383</v>
+      </c>
+      <c r="J100" s="30" t="n">
+        <v>3197</v>
+      </c>
+      <c r="K100" s="26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="L100" s="26" t="n">
+        <v>1265</v>
+      </c>
+      <c r="M100" s="26" t="inlineStr"/>
+      <c r="N100" s="26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O100" s="26" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P100" s="26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q100" s="26" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="R100" s="26" t="n">
+        <v>143</v>
+      </c>
+      <c r="S100" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="18" customHeight="1">
+      <c r="B101" s="18" t="inlineStr">
+        <is>
+          <t>Black Week</t>
+        </is>
+      </c>
+      <c r="C101" s="19" t="n">
+        <v>31221</v>
+      </c>
+      <c r="D101" s="19" t="n">
+        <v>128663</v>
+      </c>
+      <c r="E101" s="19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="F101" s="20" t="n">
+        <v>23</v>
+      </c>
+      <c r="G101" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="H101" s="22" t="inlineStr">
+        <is>
+          <t>+229%</t>
+        </is>
+      </c>
+      <c r="I101" s="23" t="n">
+        <v>189790</v>
+      </c>
+      <c r="J101" s="23" t="n">
+        <v>8251</v>
+      </c>
+      <c r="K101" s="19" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="L101" s="19" t="n">
+        <v>1475</v>
+      </c>
+      <c r="M101" s="19" t="inlineStr"/>
+      <c r="N101" s="19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O101" s="19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P101" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q101" s="19" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="R101" s="19" t="n">
+        <v>1291</v>
+      </c>
+      <c r="S101" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="18" customHeight="1">
+      <c r="B102" s="32" t="inlineStr">
+        <is>
+          <t>Pack 12 Esmaltes Nail Pro</t>
+        </is>
+      </c>
+      <c r="C102" s="33" t="n">
+        <v>15449</v>
+      </c>
+      <c r="D102" s="33" t="n">
+        <v>34999</v>
+      </c>
+      <c r="E102" s="33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F102" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G102" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H102" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I102" s="37" t="n">
+        <v>43766</v>
+      </c>
+      <c r="J102" s="37" t="n">
+        <v>21883</v>
+      </c>
+      <c r="K102" s="33" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="L102" s="33" t="n">
+        <v>1250</v>
+      </c>
+      <c r="M102" s="33" t="inlineStr"/>
+      <c r="N102" s="33" t="inlineStr"/>
+      <c r="O102" s="33" t="inlineStr"/>
+      <c r="P102" s="33" t="inlineStr"/>
+      <c r="Q102" s="33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R102" s="33" t="n">
+        <v>348</v>
+      </c>
+      <c r="S102" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="18" customHeight="1">
+      <c r="B103" s="32" t="inlineStr">
+        <is>
+          <t>Como usar Deshidratador</t>
+        </is>
+      </c>
+      <c r="C103" s="33" t="n">
+        <v>3062</v>
+      </c>
+      <c r="D103" s="33" t="n">
+        <v>8111</v>
+      </c>
+      <c r="E103" s="33" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F103" s="34" t="n">
+        <v>90</v>
+      </c>
+      <c r="G103" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H103" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I103" s="37" t="n">
+        <v>14822</v>
+      </c>
+      <c r="J103" s="37" t="n">
+        <v>164</v>
+      </c>
+      <c r="K103" s="33" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="L103" s="33" t="n">
+        <v>1827</v>
+      </c>
+      <c r="M103" s="33" t="inlineStr"/>
+      <c r="N103" s="33" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O103" s="33" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P103" s="33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q103" s="33" t="inlineStr"/>
+      <c r="R103" s="33" t="n">
+        <v>90</v>
+      </c>
+      <c r="S103" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="B104" s="13" t="inlineStr">
+        <is>
+          <t>SUBTOTAL  Objetivo Conversión Ventas</t>
+        </is>
+      </c>
+      <c r="F104" s="14" t="n">
+        <v>210</v>
+      </c>
+      <c r="G104" s="14" t="n">
+        <v>205</v>
+      </c>
+      <c r="H104" s="15" t="inlineStr">
+        <is>
+          <t>+2%</t>
+        </is>
+      </c>
+      <c r="I104" s="16" t="n">
+        <v>898109</v>
+      </c>
+    </row>
+    <row r="106" ht="22" customHeight="1">
+      <c r="B106" s="5" t="inlineStr">
+        <is>
+          <t>▸ Tráfico Perfil Instagram MKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="18" customHeight="1">
+      <c r="B107" s="18" t="inlineStr">
+        <is>
+          <t>Insta Nail Pro</t>
+        </is>
+      </c>
+      <c r="C107" s="19" t="n">
+        <v>44949</v>
+      </c>
+      <c r="D107" s="19" t="n">
+        <v>75263</v>
+      </c>
+      <c r="E107" s="19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F107" s="20" t="n">
+        <v>2127</v>
+      </c>
+      <c r="G107" s="21" t="n">
+        <v>1838</v>
+      </c>
+      <c r="H107" s="22" t="inlineStr">
+        <is>
+          <t>+16%</t>
+        </is>
+      </c>
+      <c r="I107" s="23" t="n">
+        <v>48855</v>
+      </c>
+      <c r="J107" s="23" t="n">
+        <v>22</v>
+      </c>
+      <c r="K107" s="19" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="L107" s="19" t="n">
+        <v>649</v>
+      </c>
+      <c r="M107" s="19" t="inlineStr"/>
+      <c r="N107" s="19" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="O107" s="19" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="P107" s="19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Q107" s="19" t="inlineStr"/>
+      <c r="R107" s="19" t="inlineStr"/>
+      <c r="S107" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="18" customHeight="1">
+      <c r="B108" s="18" t="inlineStr">
+        <is>
+          <t>Paso a paso Vale Nails</t>
+        </is>
+      </c>
+      <c r="C108" s="19" t="n">
+        <v>26861</v>
+      </c>
+      <c r="D108" s="19" t="n">
+        <v>46829</v>
+      </c>
+      <c r="E108" s="19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F108" s="20" t="n">
+        <v>1930</v>
+      </c>
+      <c r="G108" s="21" t="n">
+        <v>2984</v>
+      </c>
+      <c r="H108" s="24" t="inlineStr">
+        <is>
+          <t>-35%</t>
+        </is>
+      </c>
+      <c r="I108" s="23" t="n">
+        <v>41059</v>
+      </c>
+      <c r="J108" s="23" t="n">
+        <v>21</v>
+      </c>
+      <c r="K108" s="19" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="L108" s="19" t="n">
+        <v>876</v>
+      </c>
+      <c r="M108" s="19" t="inlineStr"/>
+      <c r="N108" s="19" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="O108" s="19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="P108" s="19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q108" s="19" t="inlineStr"/>
+      <c r="R108" s="19" t="inlineStr"/>
+      <c r="S108" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="B109" s="13" t="inlineStr">
+        <is>
+          <t>SUBTOTAL  Tráfico Perfil Instagram MKT</t>
+        </is>
+      </c>
+      <c r="F109" s="14" t="n">
+        <v>4057</v>
+      </c>
+      <c r="G109" s="14" t="n">
+        <v>4822</v>
+      </c>
+      <c r="H109" s="15" t="inlineStr">
+        <is>
+          <t>-16%</t>
+        </is>
+      </c>
+      <c r="I109" s="16" t="n">
+        <v>89914</v>
+      </c>
+    </row>
+    <row r="111" ht="22" customHeight="1">
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>▸ Remarketing Nail Outlet</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="18" customHeight="1">
+      <c r="B112" s="25" t="inlineStr">
+        <is>
+          <t>Despacho Gratis</t>
+        </is>
+      </c>
+      <c r="C112" s="26" t="n">
+        <v>306</v>
+      </c>
+      <c r="D112" s="26" t="n">
+        <v>5697</v>
+      </c>
+      <c r="E112" s="26" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F112" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="G112" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H112" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I112" s="30" t="n">
+        <v>44220</v>
+      </c>
+      <c r="J112" s="30" t="n">
+        <v>4913</v>
+      </c>
+      <c r="K112" s="26" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="L112" s="26" t="n">
+        <v>7761</v>
+      </c>
+      <c r="M112" s="26" t="inlineStr"/>
+      <c r="N112" s="26" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="O112" s="26" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="P112" s="26" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="Q112" s="26" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="R112" s="26" t="n">
+        <v>115</v>
+      </c>
+      <c r="S112" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="18" customHeight="1">
+      <c r="B113" s="25" t="inlineStr">
+        <is>
+          <t>15% OFF</t>
+        </is>
+      </c>
+      <c r="C113" s="26" t="n">
+        <v>301</v>
+      </c>
+      <c r="D113" s="26" t="n">
+        <v>4399</v>
+      </c>
+      <c r="E113" s="26" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="F113" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="G113" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H113" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I113" s="30" t="n">
+        <v>20886</v>
+      </c>
+      <c r="J113" s="30" t="n">
+        <v>3481</v>
+      </c>
+      <c r="K113" s="26" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="L113" s="26" t="n">
+        <v>4747</v>
+      </c>
+      <c r="M113" s="26" t="inlineStr"/>
+      <c r="N113" s="26" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="O113" s="26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="P113" s="26" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="Q113" s="26" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="R113" s="26" t="n">
+        <v>71</v>
+      </c>
+      <c r="S113" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1">
+      <c r="B114" s="13" t="inlineStr">
+        <is>
+          <t>SUBTOTAL  Remarketing Nail Outlet</t>
+        </is>
+      </c>
+      <c r="F114" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="I114" s="16" t="n">
+        <v>65106</v>
+      </c>
+    </row>
+    <row r="116" ht="22" customHeight="1">
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>▸ Campaña Conversión Catálogo</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="18" customHeight="1">
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>Nuevo Anuncio Catálogo</t>
+        </is>
+      </c>
+      <c r="C117" s="7" t="n">
+        <v>36129</v>
+      </c>
+      <c r="D117" s="7" t="n">
+        <v>206103</v>
+      </c>
+      <c r="E117" s="7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="F117" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G117" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H117" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I117" s="11" t="n">
+        <v>355748</v>
+      </c>
+      <c r="J117" s="11" t="n">
+        <v>17787</v>
+      </c>
+      <c r="K117" s="7" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="L117" s="7" t="n">
+        <v>1726</v>
+      </c>
+      <c r="M117" s="7" t="inlineStr"/>
+      <c r="N117" s="7" t="inlineStr"/>
+      <c r="O117" s="7" t="inlineStr"/>
+      <c r="P117" s="7" t="inlineStr"/>
+      <c r="Q117" s="7" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R117" s="7" t="n">
+        <v>2194</v>
+      </c>
+      <c r="S117" s="12" t="inlineStr">
+        <is>
+          <t>🔍 REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="B118" s="13" t="inlineStr">
+        <is>
+          <t>SUBTOTAL  Campaña Conversión Catálogo</t>
+        </is>
+      </c>
+      <c r="F118" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="I118" s="16" t="n">
+        <v>355748</v>
+      </c>
+    </row>
+    <row r="120" ht="26" customHeight="1">
+      <c r="B120" s="46" t="inlineStr">
+        <is>
+          <t>💡  Análisis Claude — Nail Outlet</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="36" customHeight="1">
+      <c r="B121" s="47" t="inlineStr">
+        <is>
+          <t>Nail Outlet gastó $1.408.877 en abril (+4% vs marzo) pero cayó de 5.028 a 4.302 resultados (-14%). El costo por compra subió 31% promedio ($4.277 → $5.601) con solo 3 anuncios bajo el benchmark de $6.000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="B122" s="48" t="inlineStr">
+        <is>
+          <t>Campaña</t>
+        </is>
+      </c>
+      <c r="C122" s="48" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="D122" s="48" t="inlineStr">
+        <is>
+          <t>Hallazgo</t>
+        </is>
+      </c>
+      <c r="H122" s="48" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="M122" s="48" t="inlineStr">
+        <is>
+          <t>Acción recomendada</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="48" customHeight="1">
+      <c r="B123" s="49" t="inlineStr">
+        <is>
+          <t>Objetivo Conversión Ventas</t>
+        </is>
+      </c>
+      <c r="C123" s="50" t="inlineStr">
+        <is>
+          <t>🔴 ALERTA</t>
+        </is>
+      </c>
+      <c r="D123" s="51" t="inlineStr">
+        <is>
+          <t>10 de 15 anuncios sobre benchmark</t>
+        </is>
+      </c>
+      <c r="H123" s="52" t="inlineStr">
+        <is>
+          <t>Anuncios como '40 Esmaltes Julio' ($19.285), 'Efectos Chromados' ($22.114) y 'Campo de Trabajo' ($18.188) están 3x sobre el costo aceptable. Todos caen en resultados vs marzo (de 14→5, 8→1, 14→5).</t>
+        </is>
+      </c>
+      <c r="M123" s="53" t="inlineStr">
+        <is>
+          <t>Pausar estos 3 anuncios y testear nuevos creativos con hook educativo de producto esta semana.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="48" customHeight="1">
+      <c r="B124" s="54" t="inlineStr"/>
+      <c r="C124" s="55" t="inlineStr">
+        <is>
+          <t>🟢 OPORTUNIDAD</t>
+        </is>
+      </c>
+      <c r="D124" s="56" t="inlineStr">
+        <is>
+          <t>Poly Gel Carrusel es ganador absoluto</t>
+        </is>
+      </c>
+      <c r="H124" s="57" t="inlineStr">
+        <is>
+          <t>Costo $462 por compra con ROAS 40.15x, pero solo recibió $3.237 de gasto (0.4% del presupuesto de compras). Cayó de 73 a 7 resultados por falta de inversión.</t>
+        </is>
+      </c>
+      <c r="M124" s="58" t="inlineStr">
+        <is>
+          <t>Duplicar este creativo carrusel en 2 versiones (cambiar primer slide y CTA) para escalarlo sin tocar presupuesto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="48" customHeight="1">
+      <c r="B125" s="54" t="inlineStr"/>
+      <c r="C125" s="59" t="inlineStr">
+        <is>
+          <t>🔵 INSIGHT</t>
+        </is>
+      </c>
+      <c r="D125" s="60" t="inlineStr">
+        <is>
+          <t>Pack Repo mantiene eficiencia pero cae</t>
+        </is>
+      </c>
+      <c r="H125" s="61" t="inlineStr">
+        <is>
+          <t>Costo $8.374 con ROAS 6.42x (dentro de OK), pero cayó de 38 a 20 compras con Hold Rate 5.4% (bajo). El creativo tiene 4+ meses al aire.</t>
+        </is>
+      </c>
+      <c r="M125" s="62" t="inlineStr">
+        <is>
+          <t>Refrescar con nuevo ángulo: testimonial de nail artist usando el pack en proceso real de trabajo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="48" customHeight="1">
+      <c r="B126" s="49" t="inlineStr">
+        <is>
+          <t>Tráfico Perfil Instagram MKT</t>
+        </is>
+      </c>
+      <c r="C126" s="50" t="inlineStr">
+        <is>
+          <t>🔴 ALERTA</t>
+        </is>
+      </c>
+      <c r="D126" s="51" t="inlineStr">
+        <is>
+          <t>Paso a paso Vale Nails cayó 35%</t>
+        </is>
+      </c>
+      <c r="H126" s="52" t="inlineStr">
+        <is>
+          <t>De 2.984 clicks en marzo a 1.930 en abril (-35%) con Hold Rate 10.3%. Costo $21 está OK pero pierde efectividad vs 'Insta Nail Pro' (CTR 2.73% vs 4.01%).</t>
+        </is>
+      </c>
+      <c r="M126" s="53" t="inlineStr">
+        <is>
+          <t>Testear versión speed x1.2 del tutorial y agregar texto overlay con lista de productos en los primeros 3 segundos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="48" customHeight="1">
+      <c r="B127" s="54" t="inlineStr"/>
+      <c r="C127" s="59" t="inlineStr">
+        <is>
+          <t>🔵 INSIGHT</t>
+        </is>
+      </c>
+      <c r="D127" s="60" t="inlineStr">
+        <is>
+          <t>Campaña cumple objetivo con eficiencia</t>
+        </is>
+      </c>
+      <c r="H127" s="61" t="inlineStr">
+        <is>
+          <t>4.057 clicks a $22 promedio (bajo benchmark $40) genera tráfico cualificado al perfil. Sin data de conversión física pero CTR alto sugiere interés genuino.</t>
+        </is>
+      </c>
+      <c r="M127" s="62" t="inlineStr">
+        <is>
+          <t>Mantener ambos anuncios activos y rotar nuevo creativo tipo 'antes/después' de manicura en 2 semanas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="48" customHeight="1">
+      <c r="B128" s="49" t="inlineStr">
+        <is>
+          <t>Remarketing Nail Outlet</t>
+        </is>
+      </c>
+      <c r="C128" s="55" t="inlineStr">
+        <is>
+          <t>🟢 OPORTUNIDAD</t>
+        </is>
+      </c>
+      <c r="D128" s="56" t="inlineStr">
+        <is>
+          <t>15% OFF convierte mejor que envío</t>
+        </is>
+      </c>
+      <c r="H128" s="57" t="inlineStr">
+        <is>
+          <t>'15% OFF' logra $3.481 costo con ROAS 11.25x vs 'Despacho Gratis' $4.913 y ROAS 4.85x. Ambos tienen Hold Rate alto (+17%) indicando audiencia warm comprometida.</t>
+        </is>
+      </c>
+      <c r="M128" s="58" t="inlineStr">
+        <is>
+          <t>Crear variante combinada '15% OFF + envío gratis sobre $X' para testear stack de beneficios en remarketing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="48" customHeight="1">
+      <c r="B129" s="54" t="inlineStr"/>
+      <c r="C129" s="59" t="inlineStr">
+        <is>
+          <t>🔵 INSIGHT</t>
+        </is>
+      </c>
+      <c r="D129" s="60" t="inlineStr">
+        <is>
+          <t>Remarketing más eficiente que prospecting</t>
+        </is>
+      </c>
+      <c r="H129" s="61" t="inlineStr">
+        <is>
+          <t>Costo promedio $4.340 vs $4.277 en prospecting, pero ROAS remarketing 2.8x superior (8.05 vs 2.9 promedio). Solo usa 7% del presupuesto total.</t>
+        </is>
+      </c>
+      <c r="M129" s="62" t="inlineStr">
+        <is>
+          <t>Ampliar audiencias de remarketing incluyendo visitantes de perfil Instagram últimos 30 días (desde campaña tráfico).</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="48" customHeight="1">
+      <c r="B130" s="49" t="inlineStr">
+        <is>
+          <t>Campaña Conversión Catálogo</t>
+        </is>
+      </c>
+      <c r="C130" s="50" t="inlineStr">
+        <is>
+          <t>🔴 ALERTA</t>
+        </is>
+      </c>
+      <c r="D130" s="51" t="inlineStr">
+        <is>
+          <t>Catálogo dinámico muy ineficiente</t>
+        </is>
+      </c>
+      <c r="H130" s="52" t="inlineStr">
+        <is>
+          <t>Costo $17.787 por compra (3x sobre benchmark) consumiendo $355.748 (25% del presupuesto total) con solo 20 ventas. ROAS 1.84x no justifica la inversión.</t>
+        </is>
+      </c>
+      <c r="M130" s="53" t="inlineStr">
+        <is>
+          <t>Pausar catálogo dinámico y migrar presupuesto a anuncios estáticos de productos top sellers (Poly Gel, Mesa Nail Pro).</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="24" customHeight="1">
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>GO NAILS</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="22" customHeight="1">
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>▸ Remarketing Go Nails 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="18" customHeight="1">
+      <c r="B135" s="25" t="inlineStr">
+        <is>
+          <t>Remarketing Go Nails 2024</t>
+        </is>
+      </c>
+      <c r="C135" s="26" t="n">
+        <v>13359</v>
+      </c>
+      <c r="D135" s="26" t="n">
+        <v>99492</v>
+      </c>
+      <c r="E135" s="26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="F135" s="27" t="n">
+        <v>22</v>
+      </c>
+      <c r="G135" s="28" t="n">
+        <v>65</v>
+      </c>
+      <c r="H135" s="29" t="inlineStr">
+        <is>
+          <t>-66%</t>
+        </is>
+      </c>
+      <c r="I135" s="30" t="n">
+        <v>128988</v>
+      </c>
+      <c r="J135" s="30" t="n">
+        <v>5863</v>
+      </c>
+      <c r="K135" s="26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="L135" s="26" t="n">
+        <v>1296</v>
+      </c>
+      <c r="M135" s="26" t="inlineStr"/>
+      <c r="N135" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" s="26" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="R135" s="26" t="n">
+        <v>1394</v>
+      </c>
+      <c r="S135" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="18" customHeight="1">
+      <c r="B136" s="18" t="inlineStr">
+        <is>
+          <t>15% OFF</t>
+        </is>
+      </c>
+      <c r="C136" s="19" t="n">
+        <v>2700</v>
+      </c>
+      <c r="D136" s="19" t="n">
+        <v>4154</v>
+      </c>
+      <c r="E136" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F136" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G136" s="21" t="n">
+        <v>34</v>
+      </c>
+      <c r="H136" s="24" t="inlineStr">
+        <is>
+          <t>-97%</t>
+        </is>
+      </c>
+      <c r="I136" s="23" t="n">
+        <v>7957</v>
+      </c>
+      <c r="J136" s="23" t="n">
+        <v>7957</v>
+      </c>
+      <c r="K136" s="19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L136" s="19" t="n">
+        <v>1915</v>
+      </c>
+      <c r="M136" s="19" t="inlineStr"/>
+      <c r="N136" s="19" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O136" s="19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P136" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q136" s="19" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="R136" s="19" t="n">
+        <v>27</v>
+      </c>
+      <c r="S136" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="18" customHeight="1">
+      <c r="B137" s="25" t="inlineStr">
+        <is>
+          <t>Despacho Gratis</t>
+        </is>
+      </c>
+      <c r="C137" s="26" t="n">
+        <v>15613</v>
+      </c>
+      <c r="D137" s="26" t="n">
+        <v>73938</v>
+      </c>
+      <c r="E137" s="26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="F137" s="27" t="n">
+        <v>32</v>
+      </c>
+      <c r="G137" s="28" t="n">
+        <v>108</v>
+      </c>
+      <c r="H137" s="29" t="inlineStr">
+        <is>
+          <t>-70%</t>
+        </is>
+      </c>
+      <c r="I137" s="30" t="n">
+        <v>132377</v>
+      </c>
+      <c r="J137" s="30" t="n">
+        <v>4136</v>
+      </c>
+      <c r="K137" s="26" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L137" s="26" t="n">
+        <v>1790</v>
+      </c>
+      <c r="M137" s="26" t="inlineStr"/>
+      <c r="N137" s="26" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O137" s="26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P137" s="26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q137" s="26" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="R137" s="26" t="n">
+        <v>516</v>
+      </c>
+      <c r="S137" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="20" customHeight="1">
+      <c r="B138" s="13" t="inlineStr">
+        <is>
+          <t>SUBTOTAL  Remarketing Go Nails 2024</t>
+        </is>
+      </c>
+      <c r="F138" s="14" t="n">
+        <v>55</v>
+      </c>
+      <c r="G138" s="14" t="n">
+        <v>207</v>
+      </c>
+      <c r="H138" s="15" t="inlineStr">
+        <is>
+          <t>-73%</t>
+        </is>
+      </c>
+      <c r="I138" s="16" t="n">
+        <v>269322</v>
+      </c>
+    </row>
+    <row r="140" ht="22" customHeight="1">
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>▸ Marketing Go Nails - Trafico Insta</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="18" customHeight="1">
+      <c r="B141" s="25" t="inlineStr">
+        <is>
+          <t>Rutina 4 pasos</t>
+        </is>
+      </c>
+      <c r="C141" s="26" t="n">
+        <v>713</v>
+      </c>
+      <c r="D141" s="26" t="n">
+        <v>831</v>
+      </c>
+      <c r="E141" s="26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F141" s="27" t="n">
+        <v>41</v>
+      </c>
+      <c r="G141" s="28" t="n">
+        <v>60</v>
+      </c>
+      <c r="H141" s="29" t="inlineStr">
+        <is>
+          <t>-32%</t>
+        </is>
+      </c>
+      <c r="I141" s="30" t="n">
+        <v>616</v>
+      </c>
+      <c r="J141" s="30" t="n">
+        <v>15</v>
+      </c>
+      <c r="K141" s="26" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="L141" s="26" t="n">
+        <v>741</v>
+      </c>
+      <c r="M141" s="26" t="inlineStr"/>
+      <c r="N141" s="26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O141" s="26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P141" s="26" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q141" s="26" t="inlineStr"/>
+      <c r="R141" s="26" t="inlineStr"/>
+      <c r="S141" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="18" customHeight="1">
+      <c r="B142" s="32" t="inlineStr">
+        <is>
+          <t>Nueva rutina 4 pasos</t>
+        </is>
+      </c>
+      <c r="C142" s="33" t="n">
+        <v>38054</v>
+      </c>
+      <c r="D142" s="33" t="n">
+        <v>50772</v>
+      </c>
+      <c r="E142" s="33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F142" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G142" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="H142" s="36" t="inlineStr">
+        <is>
+          <t>-83%</t>
+        </is>
+      </c>
+      <c r="I142" s="37" t="n">
+        <v>27864</v>
+      </c>
+      <c r="J142" s="37" t="n">
+        <v>27864</v>
+      </c>
+      <c r="K142" s="33" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="L142" s="33" t="n">
+        <v>548</v>
+      </c>
+      <c r="M142" s="33" t="inlineStr"/>
+      <c r="N142" s="33" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="O142" s="33" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="P142" s="33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q142" s="33" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R142" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="S142" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="18" customHeight="1">
+      <c r="B143" s="25" t="inlineStr">
+        <is>
+          <t>cotton candy frutilla</t>
+        </is>
+      </c>
+      <c r="C143" s="26" t="n">
+        <v>8064</v>
+      </c>
+      <c r="D143" s="26" t="n">
+        <v>9074</v>
+      </c>
+      <c r="E143" s="26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F143" s="27" t="n">
+        <v>407</v>
+      </c>
+      <c r="G143" s="28" t="n">
+        <v>615</v>
+      </c>
+      <c r="H143" s="29" t="inlineStr">
+        <is>
+          <t>-34%</t>
+        </is>
+      </c>
+      <c r="I143" s="30" t="n">
+        <v>6892</v>
+      </c>
+      <c r="J143" s="30" t="n">
+        <v>16</v>
+      </c>
+      <c r="K143" s="26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L143" s="26" t="n">
+        <v>759</v>
+      </c>
+      <c r="M143" s="26" t="inlineStr"/>
+      <c r="N143" s="26" t="inlineStr"/>
+      <c r="O143" s="26" t="inlineStr"/>
+      <c r="P143" s="26" t="inlineStr"/>
+      <c r="Q143" s="26" t="inlineStr"/>
+      <c r="R143" s="26" t="inlineStr"/>
+      <c r="S143" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="18" customHeight="1">
+      <c r="B144" s="25" t="inlineStr">
+        <is>
+          <t>popcorn pomo</t>
+        </is>
+      </c>
+      <c r="C144" s="26" t="n">
+        <v>365</v>
+      </c>
+      <c r="D144" s="26" t="n">
+        <v>412</v>
+      </c>
+      <c r="E144" s="26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F144" s="27" t="n">
+        <v>25</v>
+      </c>
+      <c r="G144" s="28" t="n">
+        <v>43</v>
+      </c>
+      <c r="H144" s="29" t="inlineStr">
+        <is>
+          <t>-42%</t>
+        </is>
+      </c>
+      <c r="I144" s="30" t="n">
+        <v>294</v>
+      </c>
+      <c r="J144" s="30" t="n">
+        <v>11</v>
+      </c>
+      <c r="K144" s="26" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="L144" s="26" t="n">
+        <v>713</v>
+      </c>
+      <c r="M144" s="26" t="inlineStr"/>
+      <c r="N144" s="26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="O144" s="26" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="P144" s="26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Q144" s="26" t="inlineStr"/>
+      <c r="R144" s="26" t="inlineStr"/>
+      <c r="S144" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="18" customHeight="1">
+      <c r="B145" s="25" t="inlineStr">
+        <is>
+          <t>carrusel rainbow</t>
+        </is>
+      </c>
+      <c r="C145" s="26" t="n">
+        <v>1189</v>
+      </c>
+      <c r="D145" s="26" t="n">
+        <v>1412</v>
+      </c>
+      <c r="E145" s="26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F145" s="27" t="n">
+        <v>45</v>
+      </c>
+      <c r="G145" s="28" t="n">
+        <v>65</v>
+      </c>
+      <c r="H145" s="29" t="inlineStr">
+        <is>
+          <t>-31%</t>
+        </is>
+      </c>
+      <c r="I145" s="30" t="n">
+        <v>707</v>
+      </c>
+      <c r="J145" s="30" t="n">
+        <v>15</v>
+      </c>
+      <c r="K145" s="26" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="L145" s="26" t="n">
+        <v>500</v>
+      </c>
+      <c r="M145" s="26" t="inlineStr"/>
+      <c r="N145" s="26" t="inlineStr"/>
+      <c r="O145" s="26" t="inlineStr"/>
+      <c r="P145" s="26" t="inlineStr"/>
+      <c r="Q145" s="26" t="inlineStr"/>
+      <c r="R145" s="26" t="inlineStr"/>
+      <c r="S145" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="18" customHeight="1">
+      <c r="B146" s="25" t="inlineStr">
+        <is>
+          <t>bridgerton prueba</t>
+        </is>
+      </c>
+      <c r="C146" s="26" t="n">
+        <v>67</v>
+      </c>
+      <c r="D146" s="26" t="n">
+        <v>75</v>
+      </c>
+      <c r="E146" s="26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F146" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="G146" s="28" t="n">
+        <v>15496</v>
+      </c>
+      <c r="H146" s="29" t="inlineStr">
+        <is>
+          <t>-100%</t>
+        </is>
+      </c>
+      <c r="I146" s="30" t="n">
+        <v>51</v>
+      </c>
+      <c r="J146" s="30" t="n">
+        <v>12</v>
+      </c>
+      <c r="K146" s="26" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="L146" s="26" t="n">
+        <v>680</v>
+      </c>
+      <c r="M146" s="26" t="inlineStr"/>
+      <c r="N146" s="26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O146" s="26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P146" s="26" t="inlineStr"/>
+      <c r="Q146" s="26" t="inlineStr"/>
+      <c r="R146" s="26" t="inlineStr"/>
+      <c r="S146" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="18" customHeight="1">
+      <c r="B147" s="32" t="inlineStr">
+        <is>
+          <t>hannah montana</t>
+        </is>
+      </c>
+      <c r="C147" s="33" t="n">
+        <v>97710</v>
+      </c>
+      <c r="D147" s="33" t="n">
+        <v>131389</v>
+      </c>
+      <c r="E147" s="33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F147" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G147" s="35" t="n">
+        <v>2567</v>
+      </c>
+      <c r="H147" s="36" t="inlineStr">
+        <is>
+          <t>-100%</t>
+        </is>
+      </c>
+      <c r="I147" s="37" t="n">
+        <v>55106</v>
+      </c>
+      <c r="J147" s="37" t="n">
+        <v>55106</v>
+      </c>
+      <c r="K147" s="33" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="L147" s="33" t="n">
+        <v>419</v>
+      </c>
+      <c r="M147" s="33" t="inlineStr"/>
+      <c r="N147" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O147" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P147" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q147" s="33" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="R147" s="33" t="inlineStr"/>
+      <c r="S147" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="18" customHeight="1">
+      <c r="B148" s="32" t="inlineStr">
+        <is>
+          <t>hannah montana 2</t>
+        </is>
+      </c>
+      <c r="C148" s="33" t="n">
+        <v>302822</v>
+      </c>
+      <c r="D148" s="33" t="n">
+        <v>522845</v>
+      </c>
+      <c r="E148" s="33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F148" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G148" s="35" t="n">
+        <v>456</v>
+      </c>
+      <c r="H148" s="36" t="inlineStr">
+        <is>
+          <t>-100%</t>
+        </is>
+      </c>
+      <c r="I148" s="37" t="n">
+        <v>283796</v>
+      </c>
+      <c r="J148" s="37" t="n">
+        <v>283796</v>
+      </c>
+      <c r="K148" s="33" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="L148" s="33" t="n">
+        <v>542</v>
+      </c>
+      <c r="M148" s="33" t="inlineStr"/>
+      <c r="N148" s="33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O148" s="33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P148" s="33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q148" s="33" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="R148" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="S148" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="18" customHeight="1">
+      <c r="B149" s="25" t="inlineStr">
+        <is>
+          <t>tu pareja te debe</t>
+        </is>
+      </c>
+      <c r="C149" s="26" t="n">
+        <v>21796</v>
+      </c>
+      <c r="D149" s="26" t="n">
+        <v>25757</v>
+      </c>
+      <c r="E149" s="26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F149" s="27" t="n">
+        <v>760</v>
+      </c>
+      <c r="G149" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H149" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I149" s="30" t="n">
+        <v>14792</v>
+      </c>
+      <c r="J149" s="30" t="n">
+        <v>19</v>
+      </c>
+      <c r="K149" s="26" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="L149" s="26" t="n">
+        <v>574</v>
+      </c>
+      <c r="M149" s="26" t="inlineStr"/>
+      <c r="N149" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O149" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P149" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q149" s="26" t="inlineStr"/>
+      <c r="R149" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="S149" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="20" customHeight="1">
+      <c r="B150" s="13" t="inlineStr">
+        <is>
+          <t>SUBTOTAL  Marketing Go Nails - Trafico Insta</t>
+        </is>
+      </c>
+      <c r="F150" s="14" t="n">
+        <v>1285</v>
+      </c>
+      <c r="G150" s="14" t="n">
+        <v>19308</v>
+      </c>
+      <c r="H150" s="15" t="inlineStr">
+        <is>
+          <t>-93%</t>
+        </is>
+      </c>
+      <c r="I150" s="16" t="n">
+        <v>390118</v>
+      </c>
+    </row>
+    <row r="152" ht="22" customHeight="1">
+      <c r="B152" s="5" t="inlineStr">
+        <is>
+          <t>▸ Campaña principal de Conversión</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="18" customHeight="1">
+      <c r="B153" s="18" t="inlineStr">
+        <is>
+          <t>Crema dibujada</t>
+        </is>
+      </c>
+      <c r="C153" s="19" t="n">
+        <v>23284</v>
+      </c>
+      <c r="D153" s="19" t="n">
+        <v>45272</v>
+      </c>
+      <c r="E153" s="19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F153" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="G153" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H153" s="22" t="inlineStr">
+        <is>
+          <t>+60%</t>
+        </is>
+      </c>
+      <c r="I153" s="23" t="n">
+        <v>72053</v>
+      </c>
+      <c r="J153" s="23" t="n">
+        <v>9006</v>
+      </c>
+      <c r="K153" s="19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L153" s="19" t="n">
+        <v>1591</v>
+      </c>
+      <c r="M153" s="19" t="inlineStr"/>
+      <c r="N153" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O153" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P153" s="19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q153" s="19" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="R153" s="19" t="n">
+        <v>359</v>
+      </c>
+      <c r="S153" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="18" customHeight="1">
+      <c r="B154" s="18" t="inlineStr">
+        <is>
+          <t>4 por 3</t>
+        </is>
+      </c>
+      <c r="C154" s="19" t="n">
+        <v>111390</v>
+      </c>
+      <c r="D154" s="19" t="n">
+        <v>398057</v>
+      </c>
+      <c r="E154" s="19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F154" s="20" t="n">
+        <v>76</v>
+      </c>
+      <c r="G154" s="21" t="n">
+        <v>123</v>
+      </c>
+      <c r="H154" s="24" t="inlineStr">
+        <is>
+          <t>-38%</t>
+        </is>
+      </c>
+      <c r="I154" s="23" t="n">
+        <v>695652</v>
+      </c>
+      <c r="J154" s="23" t="n">
+        <v>9153</v>
+      </c>
+      <c r="K154" s="19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="L154" s="19" t="n">
+        <v>1747</v>
+      </c>
+      <c r="M154" s="19" t="inlineStr"/>
+      <c r="N154" s="19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O154" s="19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P154" s="19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q154" s="19" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="R154" s="19" t="n">
+        <v>2114</v>
+      </c>
+      <c r="S154" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="18" customHeight="1">
+      <c r="B155" s="18" t="inlineStr">
+        <is>
+          <t>Hot Chocalate</t>
+        </is>
+      </c>
+      <c r="C155" s="19" t="n">
+        <v>48445</v>
+      </c>
+      <c r="D155" s="19" t="n">
+        <v>107600</v>
+      </c>
+      <c r="E155" s="19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F155" s="20" t="n">
+        <v>14</v>
+      </c>
+      <c r="G155" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H155" s="22" t="inlineStr">
+        <is>
+          <t>+40%</t>
+        </is>
+      </c>
+      <c r="I155" s="23" t="n">
+        <v>128564</v>
+      </c>
+      <c r="J155" s="23" t="n">
+        <v>9183</v>
+      </c>
+      <c r="K155" s="19" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="L155" s="19" t="n">
+        <v>1194</v>
+      </c>
+      <c r="M155" s="19" t="inlineStr"/>
+      <c r="N155" s="19" t="inlineStr"/>
+      <c r="O155" s="19" t="inlineStr"/>
+      <c r="P155" s="19" t="inlineStr"/>
+      <c r="Q155" s="19" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="R155" s="19" t="n">
+        <v>970</v>
+      </c>
+      <c r="S155" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="18" customHeight="1">
+      <c r="B156" s="18" t="inlineStr">
+        <is>
+          <t>Macbook</t>
+        </is>
+      </c>
+      <c r="C156" s="19" t="n">
+        <v>11375</v>
+      </c>
+      <c r="D156" s="19" t="n">
+        <v>24203</v>
+      </c>
+      <c r="E156" s="19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F156" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="G156" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H156" s="22" t="inlineStr">
+        <is>
+          <t>+50%</t>
+        </is>
+      </c>
+      <c r="I156" s="23" t="n">
+        <v>41316</v>
+      </c>
+      <c r="J156" s="23" t="n">
+        <v>6886</v>
+      </c>
+      <c r="K156" s="19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="L156" s="19" t="n">
+        <v>1707</v>
+      </c>
+      <c r="M156" s="19" t="inlineStr"/>
+      <c r="N156" s="19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O156" s="19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P156" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q156" s="19" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="R156" s="19" t="n">
+        <v>229</v>
+      </c>
+      <c r="S156" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="18" customHeight="1">
+      <c r="B157" s="18" t="inlineStr">
+        <is>
+          <t>Protector Termico</t>
+        </is>
+      </c>
+      <c r="C157" s="19" t="n">
+        <v>12312</v>
+      </c>
+      <c r="D157" s="19" t="n">
+        <v>41733</v>
+      </c>
+      <c r="E157" s="19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F157" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="G157" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="H157" s="24" t="inlineStr">
+        <is>
+          <t>-43%</t>
+        </is>
+      </c>
+      <c r="I157" s="23" t="n">
+        <v>54972</v>
+      </c>
+      <c r="J157" s="23" t="n">
+        <v>6871</v>
+      </c>
+      <c r="K157" s="19" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L157" s="19" t="n">
+        <v>1317</v>
+      </c>
+      <c r="M157" s="19" t="inlineStr"/>
+      <c r="N157" s="19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O157" s="19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P157" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q157" s="19" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="R157" s="19" t="n">
+        <v>153</v>
+      </c>
+      <c r="S157" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="18" customHeight="1">
+      <c r="B158" s="32" t="inlineStr">
+        <is>
+          <t>Nuevos difusores</t>
+        </is>
+      </c>
+      <c r="C158" s="33" t="n">
+        <v>16523</v>
+      </c>
+      <c r="D158" s="33" t="n">
+        <v>43682</v>
+      </c>
+      <c r="E158" s="33" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F158" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G158" s="35" t="n">
+        <v>35</v>
+      </c>
+      <c r="H158" s="36" t="inlineStr">
+        <is>
+          <t>-91%</t>
+        </is>
+      </c>
+      <c r="I158" s="37" t="n">
+        <v>67668</v>
+      </c>
+      <c r="J158" s="37" t="n">
+        <v>22556</v>
+      </c>
+      <c r="K158" s="33" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="L158" s="33" t="n">
+        <v>1549</v>
+      </c>
+      <c r="M158" s="33" t="inlineStr"/>
+      <c r="N158" s="33" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O158" s="33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P158" s="33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q158" s="33" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="R158" s="33" t="n">
+        <v>229</v>
+      </c>
+      <c r="S158" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="18" customHeight="1">
+      <c r="B159" s="6" t="inlineStr">
+        <is>
+          <t>Reel de fragancias</t>
+        </is>
+      </c>
+      <c r="C159" s="7" t="n">
+        <v>189252</v>
+      </c>
+      <c r="D159" s="7" t="n">
+        <v>519325</v>
+      </c>
+      <c r="E159" s="7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F159" s="8" t="n">
+        <v>76</v>
+      </c>
+      <c r="G159" s="9" t="n">
+        <v>104</v>
+      </c>
+      <c r="H159" s="17" t="inlineStr">
+        <is>
+          <t>-27%</t>
+        </is>
+      </c>
+      <c r="I159" s="11" t="n">
+        <v>785629</v>
+      </c>
+      <c r="J159" s="11" t="n">
+        <v>10337</v>
+      </c>
+      <c r="K159" s="7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="L159" s="7" t="n">
+        <v>1512</v>
+      </c>
+      <c r="M159" s="7" t="inlineStr"/>
+      <c r="N159" s="7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O159" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P159" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q159" s="7" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="R159" s="7" t="n">
+        <v>4120</v>
+      </c>
+      <c r="S159" s="12" t="inlineStr">
+        <is>
+          <t>🔍 REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="18" customHeight="1">
+      <c r="B160" s="18" t="inlineStr">
+        <is>
+          <t>Imagen Bubble gum</t>
+        </is>
+      </c>
+      <c r="C160" s="19" t="n">
+        <v>25328</v>
+      </c>
+      <c r="D160" s="19" t="n">
+        <v>77421</v>
+      </c>
+      <c r="E160" s="19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F160" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="G160" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="H160" s="24" t="inlineStr">
+        <is>
+          <t>-40%</t>
+        </is>
+      </c>
+      <c r="I160" s="23" t="n">
+        <v>100077</v>
+      </c>
+      <c r="J160" s="23" t="n">
+        <v>6671</v>
+      </c>
+      <c r="K160" s="19" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="L160" s="19" t="n">
+        <v>1292</v>
+      </c>
+      <c r="M160" s="19" t="inlineStr"/>
+      <c r="N160" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O160" s="19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P160" s="19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q160" s="19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="R160" s="19" t="n">
+        <v>466</v>
+      </c>
+      <c r="S160" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="18" customHeight="1">
+      <c r="B161" s="6" t="inlineStr">
+        <is>
+          <t>Imagen Gato</t>
+        </is>
+      </c>
+      <c r="C161" s="7" t="n">
+        <v>17097</v>
+      </c>
+      <c r="D161" s="7" t="n">
+        <v>39152</v>
+      </c>
+      <c r="E161" s="7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F161" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G161" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="H161" s="17" t="inlineStr">
+        <is>
+          <t>-43%</t>
+        </is>
+      </c>
+      <c r="I161" s="11" t="n">
+        <v>68171</v>
+      </c>
+      <c r="J161" s="11" t="n">
+        <v>17042</v>
+      </c>
+      <c r="K161" s="7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="L161" s="7" t="n">
+        <v>1741</v>
+      </c>
+      <c r="M161" s="7" t="inlineStr"/>
+      <c r="N161" s="7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O161" s="7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P161" s="7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q161" s="7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R161" s="7" t="n">
+        <v>311</v>
+      </c>
+      <c r="S161" s="12" t="inlineStr">
+        <is>
+          <t>🔍 REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="18" customHeight="1">
+      <c r="B162" s="18" t="inlineStr">
+        <is>
+          <t>Carrusel Sun Kissed</t>
+        </is>
+      </c>
+      <c r="C162" s="19" t="n">
+        <v>8843</v>
+      </c>
+      <c r="D162" s="19" t="n">
+        <v>19060</v>
+      </c>
+      <c r="E162" s="19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F162" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="G162" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="H162" s="24" t="inlineStr">
+        <is>
+          <t>-57%</t>
+        </is>
+      </c>
+      <c r="I162" s="23" t="n">
+        <v>23636</v>
+      </c>
+      <c r="J162" s="23" t="n">
+        <v>7878</v>
+      </c>
+      <c r="K162" s="19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L162" s="19" t="n">
+        <v>1240</v>
+      </c>
+      <c r="M162" s="19" t="inlineStr"/>
+      <c r="N162" s="19" t="inlineStr"/>
+      <c r="O162" s="19" t="inlineStr"/>
+      <c r="P162" s="19" t="inlineStr"/>
+      <c r="Q162" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="R162" s="19" t="n">
+        <v>132</v>
+      </c>
+      <c r="S162" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="18" customHeight="1">
+      <c r="B163" s="25" t="inlineStr">
+        <is>
+          <t>Reel cafetería</t>
+        </is>
+      </c>
+      <c r="C163" s="26" t="n">
+        <v>3530</v>
+      </c>
+      <c r="D163" s="26" t="n">
+        <v>6221</v>
+      </c>
+      <c r="E163" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F163" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="G163" s="28" t="n">
+        <v>88</v>
+      </c>
+      <c r="H163" s="29" t="inlineStr">
+        <is>
+          <t>-97%</t>
+        </is>
+      </c>
+      <c r="I163" s="30" t="n">
+        <v>15267</v>
+      </c>
+      <c r="J163" s="30" t="n">
+        <v>5089</v>
+      </c>
+      <c r="K163" s="26" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="L163" s="26" t="n">
+        <v>2454</v>
+      </c>
+      <c r="M163" s="26" t="inlineStr"/>
+      <c r="N163" s="26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O163" s="26" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P163" s="26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q163" s="26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R163" s="26" t="n">
+        <v>77</v>
+      </c>
+      <c r="S163" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="18" customHeight="1">
+      <c r="B164" s="18" t="inlineStr">
+        <is>
+          <t>Imagen Cotton Vlabel</t>
+        </is>
+      </c>
+      <c r="C164" s="19" t="n">
+        <v>75025</v>
+      </c>
+      <c r="D164" s="19" t="n">
+        <v>202418</v>
+      </c>
+      <c r="E164" s="19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F164" s="20" t="n">
+        <v>38</v>
+      </c>
+      <c r="G164" s="21" t="n">
+        <v>120</v>
+      </c>
+      <c r="H164" s="24" t="inlineStr">
+        <is>
+          <t>-68%</t>
+        </is>
+      </c>
+      <c r="I164" s="23" t="n">
+        <v>293090</v>
+      </c>
+      <c r="J164" s="23" t="n">
+        <v>7712</v>
+      </c>
+      <c r="K164" s="19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="L164" s="19" t="n">
+        <v>1447</v>
+      </c>
+      <c r="M164" s="19" t="inlineStr"/>
+      <c r="N164" s="19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O164" s="19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P164" s="19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q164" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="R164" s="19" t="n">
+        <v>1585</v>
+      </c>
+      <c r="S164" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="18" customHeight="1">
+      <c r="B165" s="32" t="inlineStr">
+        <is>
+          <t>Bye Bye Aroma</t>
+        </is>
+      </c>
+      <c r="C165" s="33" t="n">
+        <v>4867</v>
+      </c>
+      <c r="D165" s="33" t="n">
+        <v>9919</v>
+      </c>
+      <c r="E165" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F165" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G165" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="H165" s="36" t="inlineStr">
+        <is>
+          <t>-83%</t>
+        </is>
+      </c>
+      <c r="I165" s="37" t="n">
+        <v>18421</v>
+      </c>
+      <c r="J165" s="37" t="n">
+        <v>18421</v>
+      </c>
+      <c r="K165" s="33" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L165" s="33" t="n">
+        <v>1857</v>
+      </c>
+      <c r="M165" s="33" t="inlineStr"/>
+      <c r="N165" s="33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O165" s="33" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P165" s="33" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q165" s="33" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="R165" s="33" t="n">
+        <v>48</v>
+      </c>
+      <c r="S165" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="18" customHeight="1">
+      <c r="B166" s="25" t="inlineStr">
+        <is>
+          <t>Cremas Sun Kissed</t>
+        </is>
+      </c>
+      <c r="C166" s="26" t="n">
+        <v>16660</v>
+      </c>
+      <c r="D166" s="26" t="n">
+        <v>37965</v>
+      </c>
+      <c r="E166" s="26" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F166" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="G166" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="H166" s="29" t="inlineStr">
+        <is>
+          <t>-50%</t>
+        </is>
+      </c>
+      <c r="I166" s="30" t="n">
+        <v>68249</v>
+      </c>
+      <c r="J166" s="30" t="n">
+        <v>5687</v>
+      </c>
+      <c r="K166" s="26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L166" s="26" t="n">
+        <v>1797</v>
+      </c>
+      <c r="M166" s="26" t="inlineStr"/>
+      <c r="N166" s="26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O166" s="26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P166" s="26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q166" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="R166" s="26" t="n">
+        <v>363</v>
+      </c>
+      <c r="S166" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="18" customHeight="1">
+      <c r="B167" s="6" t="inlineStr">
+        <is>
+          <t>Home Spray</t>
+        </is>
+      </c>
+      <c r="C167" s="7" t="n">
+        <v>223129</v>
+      </c>
+      <c r="D167" s="7" t="n">
+        <v>738548</v>
+      </c>
+      <c r="E167" s="7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F167" s="8" t="n">
+        <v>91</v>
+      </c>
+      <c r="G167" s="9" t="n">
+        <v>126</v>
+      </c>
+      <c r="H167" s="17" t="inlineStr">
+        <is>
+          <t>-28%</t>
+        </is>
+      </c>
+      <c r="I167" s="11" t="n">
+        <v>1186817</v>
+      </c>
+      <c r="J167" s="11" t="n">
+        <v>13041</v>
+      </c>
+      <c r="K167" s="7" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="L167" s="7" t="n">
+        <v>1606</v>
+      </c>
+      <c r="M167" s="7" t="inlineStr"/>
+      <c r="N167" s="7" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O167" s="7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="P167" s="7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q167" s="7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R167" s="7" t="n">
+        <v>5319</v>
+      </c>
+      <c r="S167" s="12" t="inlineStr">
+        <is>
+          <t>🔍 REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="18" customHeight="1">
+      <c r="B168" s="6" t="inlineStr">
+        <is>
+          <t>Rutina 4 pasos 2.0</t>
+        </is>
+      </c>
+      <c r="C168" s="7" t="n">
+        <v>47354</v>
+      </c>
+      <c r="D168" s="7" t="n">
+        <v>139806</v>
+      </c>
+      <c r="E168" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F168" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G168" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="H168" s="17" t="inlineStr">
+        <is>
+          <t>-47%</t>
+        </is>
+      </c>
+      <c r="I168" s="11" t="n">
+        <v>261897</v>
+      </c>
+      <c r="J168" s="11" t="n">
+        <v>13784</v>
+      </c>
+      <c r="K168" s="7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L168" s="7" t="n">
+        <v>1873</v>
+      </c>
+      <c r="M168" s="7" t="inlineStr"/>
+      <c r="N168" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O168" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P168" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q168" s="7" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="R168" s="7" t="n">
+        <v>1312</v>
+      </c>
+      <c r="S168" s="12" t="inlineStr">
+        <is>
+          <t>🔍 REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="18" customHeight="1">
+      <c r="B169" s="32" t="inlineStr">
+        <is>
+          <t>UGC Soft Milk Febrero</t>
+        </is>
+      </c>
+      <c r="C169" s="33" t="n">
+        <v>1912</v>
+      </c>
+      <c r="D169" s="33" t="n">
+        <v>3069</v>
+      </c>
+      <c r="E169" s="33" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F169" s="34" t="n">
+        <v>27</v>
+      </c>
+      <c r="G169" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H169" s="63" t="inlineStr">
+        <is>
+          <t>+2600%</t>
+        </is>
+      </c>
+      <c r="I169" s="37" t="n">
+        <v>8931</v>
+      </c>
+      <c r="J169" s="37" t="n">
+        <v>330</v>
+      </c>
+      <c r="K169" s="33" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="L169" s="33" t="n">
+        <v>2910</v>
+      </c>
+      <c r="M169" s="33" t="inlineStr"/>
+      <c r="N169" s="33" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="O169" s="33" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P169" s="33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q169" s="33" t="inlineStr"/>
+      <c r="R169" s="33" t="n">
+        <v>20</v>
+      </c>
+      <c r="S169" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="18" customHeight="1">
+      <c r="B170" s="32" t="inlineStr">
+        <is>
+          <t>Go Paw Carrusel Mascotas</t>
+        </is>
+      </c>
+      <c r="C170" s="33" t="n">
+        <v>948</v>
+      </c>
+      <c r="D170" s="33" t="n">
+        <v>1379</v>
+      </c>
+      <c r="E170" s="33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F170" s="34" t="n">
+        <v>9</v>
+      </c>
+      <c r="G170" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H170" s="63" t="inlineStr">
+        <is>
+          <t>+800%</t>
+        </is>
+      </c>
+      <c r="I170" s="37" t="n">
+        <v>3176</v>
+      </c>
+      <c r="J170" s="37" t="n">
+        <v>352</v>
+      </c>
+      <c r="K170" s="33" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="L170" s="33" t="n">
+        <v>2303</v>
+      </c>
+      <c r="M170" s="33" t="inlineStr"/>
+      <c r="N170" s="33" t="inlineStr"/>
+      <c r="O170" s="33" t="inlineStr"/>
+      <c r="P170" s="33" t="inlineStr"/>
+      <c r="Q170" s="33" t="inlineStr"/>
+      <c r="R170" s="33" t="n">
+        <v>9</v>
+      </c>
+      <c r="S170" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="18" customHeight="1">
+      <c r="B171" s="32" t="inlineStr">
+        <is>
+          <t>Aceite Capilar Go Hair</t>
+        </is>
+      </c>
+      <c r="C171" s="33" t="n">
+        <v>1318</v>
+      </c>
+      <c r="D171" s="33" t="n">
+        <v>2028</v>
+      </c>
+      <c r="E171" s="33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F171" s="34" t="n">
+        <v>21</v>
+      </c>
+      <c r="G171" s="35" t="n">
+        <v>23</v>
+      </c>
+      <c r="H171" s="36" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
+      <c r="I171" s="37" t="n">
+        <v>5378</v>
+      </c>
+      <c r="J171" s="37" t="n">
+        <v>256</v>
+      </c>
+      <c r="K171" s="33" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="L171" s="33" t="n">
+        <v>2651</v>
+      </c>
+      <c r="M171" s="33" t="inlineStr"/>
+      <c r="N171" s="33" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="O171" s="33" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P171" s="33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q171" s="33" t="inlineStr"/>
+      <c r="R171" s="33" t="n">
+        <v>21</v>
+      </c>
+      <c r="S171" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="18" customHeight="1">
+      <c r="B172" s="18" t="inlineStr">
+        <is>
+          <t>Kit Cuidado Capilar</t>
+        </is>
+      </c>
+      <c r="C172" s="19" t="n">
+        <v>10726</v>
+      </c>
+      <c r="D172" s="19" t="n">
+        <v>21083</v>
+      </c>
+      <c r="E172" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F172" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="G172" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="H172" s="24" t="inlineStr">
+        <is>
+          <t>-14%</t>
+        </is>
+      </c>
+      <c r="I172" s="23" t="n">
+        <v>49131</v>
+      </c>
+      <c r="J172" s="23" t="n">
+        <v>8188</v>
+      </c>
+      <c r="K172" s="19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="L172" s="19" t="n">
+        <v>2330</v>
+      </c>
+      <c r="M172" s="19" t="inlineStr"/>
+      <c r="N172" s="19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O172" s="19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P172" s="19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q172" s="19" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="R172" s="19" t="n">
+        <v>203</v>
+      </c>
+      <c r="S172" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="18" customHeight="1">
+      <c r="B173" s="32" t="inlineStr">
+        <is>
+          <t>Go Paw Wild Berries y Cotton Candy</t>
+        </is>
+      </c>
+      <c r="C173" s="33" t="n">
+        <v>18992</v>
+      </c>
+      <c r="D173" s="33" t="n">
+        <v>36622</v>
+      </c>
+      <c r="E173" s="33" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F173" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="G173" s="35" t="n">
+        <v>15</v>
+      </c>
+      <c r="H173" s="36" t="inlineStr">
+        <is>
+          <t>-73%</t>
+        </is>
+      </c>
+      <c r="I173" s="37" t="n">
+        <v>93385</v>
+      </c>
+      <c r="J173" s="37" t="n">
+        <v>23346</v>
+      </c>
+      <c r="K173" s="33" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="L173" s="33" t="n">
+        <v>2549</v>
+      </c>
+      <c r="M173" s="33" t="inlineStr"/>
+      <c r="N173" s="33" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O173" s="33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P173" s="33" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q173" s="33" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R173" s="33" t="n">
+        <v>207</v>
+      </c>
+      <c r="S173" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="18" customHeight="1">
+      <c r="B174" s="6" t="inlineStr">
+        <is>
+          <t>Protector Termico Pistacho Caramelo</t>
+        </is>
+      </c>
+      <c r="C174" s="7" t="n">
+        <v>73692</v>
+      </c>
+      <c r="D174" s="7" t="n">
+        <v>169162</v>
+      </c>
+      <c r="E174" s="7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F174" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="G174" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="H174" s="17" t="inlineStr">
+        <is>
+          <t>-40%</t>
+        </is>
+      </c>
+      <c r="I174" s="11" t="n">
+        <v>261470</v>
+      </c>
+      <c r="J174" s="11" t="n">
+        <v>17431</v>
+      </c>
+      <c r="K174" s="7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L174" s="7" t="n">
+        <v>1545</v>
+      </c>
+      <c r="M174" s="7" t="inlineStr"/>
+      <c r="N174" s="7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O174" s="7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P174" s="7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q174" s="7" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="R174" s="7" t="n">
+        <v>905</v>
+      </c>
+      <c r="S174" s="12" t="inlineStr">
+        <is>
+          <t>🔍 REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="18" customHeight="1">
+      <c r="B175" s="25" t="inlineStr">
+        <is>
+          <t>Go Paw @Juliana Carrascal</t>
+        </is>
+      </c>
+      <c r="C175" s="26" t="n">
+        <v>1537</v>
+      </c>
+      <c r="D175" s="26" t="n">
+        <v>2275</v>
+      </c>
+      <c r="E175" s="26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F175" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G175" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H175" s="31" t="inlineStr">
+        <is>
+          <t>+100%</t>
+        </is>
+      </c>
+      <c r="I175" s="30" t="n">
+        <v>5473</v>
+      </c>
+      <c r="J175" s="30" t="n">
+        <v>2736</v>
+      </c>
+      <c r="K175" s="26" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="L175" s="26" t="n">
+        <v>2405</v>
+      </c>
+      <c r="M175" s="26" t="inlineStr"/>
+      <c r="N175" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="O175" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="P175" s="26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q175" s="26" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="R175" s="26" t="n">
+        <v>17</v>
+      </c>
+      <c r="S175" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="18" customHeight="1">
+      <c r="B176" s="6" t="inlineStr">
+        <is>
+          <t>Home Spray @vanusallorenzo</t>
+        </is>
+      </c>
+      <c r="C176" s="7" t="n">
+        <v>56581</v>
+      </c>
+      <c r="D176" s="7" t="n">
+        <v>133163</v>
+      </c>
+      <c r="E176" s="7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F176" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="G176" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H176" s="10" t="inlineStr">
+        <is>
+          <t>+320%</t>
+        </is>
+      </c>
+      <c r="I176" s="11" t="n">
+        <v>306078</v>
+      </c>
+      <c r="J176" s="11" t="n">
+        <v>14575</v>
+      </c>
+      <c r="K176" s="7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="L176" s="7" t="n">
+        <v>2298</v>
+      </c>
+      <c r="M176" s="7" t="inlineStr"/>
+      <c r="N176" s="7" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="O176" s="7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P176" s="7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q176" s="7" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="R176" s="7" t="n">
+        <v>1041</v>
+      </c>
+      <c r="S176" s="12" t="inlineStr">
+        <is>
+          <t>🔍 REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="18" customHeight="1">
+      <c r="B177" s="25" t="inlineStr">
+        <is>
+          <t>BLACK WEEK INICIO</t>
+        </is>
+      </c>
+      <c r="C177" s="26" t="n">
+        <v>87055</v>
+      </c>
+      <c r="D177" s="26" t="n">
+        <v>320312</v>
+      </c>
+      <c r="E177" s="26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F177" s="27" t="n">
+        <v>107</v>
+      </c>
+      <c r="G177" s="28" t="n">
+        <v>28</v>
+      </c>
+      <c r="H177" s="31" t="inlineStr">
+        <is>
+          <t>+282%</t>
+        </is>
+      </c>
+      <c r="I177" s="30" t="n">
+        <v>573332</v>
+      </c>
+      <c r="J177" s="30" t="n">
+        <v>5358</v>
+      </c>
+      <c r="K177" s="26" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="L177" s="26" t="n">
+        <v>1789</v>
+      </c>
+      <c r="M177" s="26" t="inlineStr"/>
+      <c r="N177" s="26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O177" s="26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P177" s="26" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q177" s="26" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="R177" s="26" t="n">
+        <v>2699</v>
+      </c>
+      <c r="S177" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="18" customHeight="1">
+      <c r="B178" s="32" t="inlineStr">
+        <is>
+          <t>Carrusel Post que puedes oler</t>
+        </is>
+      </c>
+      <c r="C178" s="33" t="n">
+        <v>5613</v>
+      </c>
+      <c r="D178" s="33" t="n">
+        <v>11418</v>
+      </c>
+      <c r="E178" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F178" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G178" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H178" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I178" s="37" t="n">
+        <v>21464</v>
+      </c>
+      <c r="J178" s="37" t="n">
+        <v>21464</v>
+      </c>
+      <c r="K178" s="33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L178" s="33" t="n">
+        <v>1879</v>
+      </c>
+      <c r="M178" s="33" t="inlineStr"/>
+      <c r="N178" s="33" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O178" s="33" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P178" s="33" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q178" s="33" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="R178" s="33" t="n">
+        <v>87</v>
+      </c>
+      <c r="S178" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="18" customHeight="1">
+      <c r="B179" s="6" t="inlineStr">
+        <is>
+          <t>Fragancias Picnic</t>
+        </is>
+      </c>
+      <c r="C179" s="7" t="n">
+        <v>24676</v>
+      </c>
+      <c r="D179" s="7" t="n">
+        <v>74073</v>
+      </c>
+      <c r="E179" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F179" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="G179" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H179" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I179" s="11" t="n">
+        <v>134078</v>
+      </c>
+      <c r="J179" s="11" t="n">
+        <v>11173</v>
+      </c>
+      <c r="K179" s="7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="L179" s="7" t="n">
+        <v>1810</v>
+      </c>
+      <c r="M179" s="7" t="inlineStr"/>
+      <c r="N179" s="7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O179" s="7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P179" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q179" s="7" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="R179" s="7" t="n">
+        <v>554</v>
+      </c>
+      <c r="S179" s="12" t="inlineStr">
+        <is>
+          <t>🔍 REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="18" customHeight="1">
+      <c r="B180" s="32" t="inlineStr">
+        <is>
+          <t>Go Paw @melissapaz</t>
+        </is>
+      </c>
+      <c r="C180" s="33" t="n">
+        <v>7601</v>
+      </c>
+      <c r="D180" s="33" t="n">
+        <v>9998</v>
+      </c>
+      <c r="E180" s="33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F180" s="34" t="n">
+        <v>104</v>
+      </c>
+      <c r="G180" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H180" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I180" s="37" t="n">
+        <v>23686</v>
+      </c>
+      <c r="J180" s="37" t="n">
+        <v>227</v>
+      </c>
+      <c r="K180" s="33" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="L180" s="33" t="n">
+        <v>2369</v>
+      </c>
+      <c r="M180" s="33" t="inlineStr"/>
+      <c r="N180" s="33" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="O180" s="33" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P180" s="33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q180" s="33" t="inlineStr"/>
+      <c r="R180" s="33" t="n">
+        <v>95</v>
+      </c>
+      <c r="S180" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="18" customHeight="1">
+      <c r="B181" s="32" t="inlineStr">
+        <is>
+          <t>Nuevas Cremas Corporales Abril</t>
+        </is>
+      </c>
+      <c r="C181" s="33" t="n">
+        <v>6943</v>
+      </c>
+      <c r="D181" s="33" t="n">
+        <v>9228</v>
+      </c>
+      <c r="E181" s="33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F181" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G181" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H181" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I181" s="37" t="n">
+        <v>22067</v>
+      </c>
+      <c r="J181" s="37" t="n">
+        <v>22067</v>
+      </c>
+      <c r="K181" s="33" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="L181" s="33" t="n">
+        <v>2391</v>
+      </c>
+      <c r="M181" s="33" t="inlineStr"/>
+      <c r="N181" s="33" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O181" s="33" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P181" s="33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q181" s="33" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="R181" s="33" t="n">
+        <v>76</v>
+      </c>
+      <c r="S181" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="18" customHeight="1">
+      <c r="B182" s="18" t="inlineStr">
+        <is>
+          <t>Lanzamiento Shampoo y Acondicionador</t>
+        </is>
+      </c>
+      <c r="C182" s="19" t="n">
+        <v>2164</v>
+      </c>
+      <c r="D182" s="19" t="n">
+        <v>3284</v>
+      </c>
+      <c r="E182" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F182" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G182" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H182" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I182" s="23" t="n">
+        <v>6190</v>
+      </c>
+      <c r="J182" s="23" t="n">
+        <v>6190</v>
+      </c>
+      <c r="K182" s="19" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="L182" s="19" t="n">
+        <v>1884</v>
+      </c>
+      <c r="M182" s="19" t="inlineStr"/>
+      <c r="N182" s="19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O182" s="19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="P182" s="19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q182" s="19" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="R182" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="S182" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="18" customHeight="1">
+      <c r="B183" s="18" t="inlineStr">
+        <is>
+          <t>Lanzamiento Refill Abril</t>
+        </is>
+      </c>
+      <c r="C183" s="19" t="n">
+        <v>13541</v>
+      </c>
+      <c r="D183" s="19" t="n">
+        <v>30101</v>
+      </c>
+      <c r="E183" s="19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F183" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="G183" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H183" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I183" s="23" t="n">
+        <v>68938</v>
+      </c>
+      <c r="J183" s="23" t="n">
+        <v>9848</v>
+      </c>
+      <c r="K183" s="19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="L183" s="19" t="n">
+        <v>2290</v>
+      </c>
+      <c r="M183" s="19" t="inlineStr"/>
+      <c r="N183" s="19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O183" s="19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P183" s="19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q183" s="19" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="R183" s="19" t="n">
+        <v>302</v>
+      </c>
+      <c r="S183" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="20" customHeight="1">
+      <c r="B184" s="13" t="inlineStr">
+        <is>
+          <t>SUBTOTAL  Campaña principal de Conversión</t>
+        </is>
+      </c>
+      <c r="F184" s="14" t="n">
+        <v>715</v>
+      </c>
+      <c r="G184" s="14" t="n">
+        <v>840</v>
+      </c>
+      <c r="H184" s="15" t="inlineStr">
+        <is>
+          <t>-15%</t>
+        </is>
+      </c>
+      <c r="I184" s="16" t="n">
+        <v>5464256</v>
+      </c>
+    </row>
+    <row r="186" ht="22" customHeight="1">
+      <c r="B186" s="5" t="inlineStr">
+        <is>
+          <t>▸ Campaña Secundaria LMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="18" customHeight="1">
+      <c r="B187" s="6" t="inlineStr">
+        <is>
+          <t>Reel esmalte LMM</t>
+        </is>
+      </c>
+      <c r="C187" s="7" t="n">
+        <v>16040</v>
+      </c>
+      <c r="D187" s="7" t="n">
+        <v>23785</v>
+      </c>
+      <c r="E187" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F187" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G187" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="H187" s="17" t="inlineStr">
+        <is>
+          <t>-65%</t>
+        </is>
+      </c>
+      <c r="I187" s="11" t="n">
+        <v>60827</v>
+      </c>
+      <c r="J187" s="11" t="n">
+        <v>10137</v>
+      </c>
+      <c r="K187" s="7" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="L187" s="7" t="n">
+        <v>2557</v>
+      </c>
+      <c r="M187" s="7" t="inlineStr"/>
+      <c r="N187" s="7" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="O187" s="7" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="P187" s="7" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Q187" s="7" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="R187" s="7" t="n">
+        <v>695</v>
+      </c>
+      <c r="S187" s="12" t="inlineStr">
+        <is>
+          <t>🔍 REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="18" customHeight="1">
+      <c r="B188" s="25" t="inlineStr">
+        <is>
+          <t>Reel Kit LMM</t>
+        </is>
+      </c>
+      <c r="C188" s="26" t="n">
+        <v>2378</v>
+      </c>
+      <c r="D188" s="26" t="n">
+        <v>3985</v>
+      </c>
+      <c r="E188" s="26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F188" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="G188" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H188" s="31" t="inlineStr">
+        <is>
+          <t>+400%</t>
+        </is>
+      </c>
+      <c r="I188" s="30" t="n">
+        <v>12363</v>
+      </c>
+      <c r="J188" s="30" t="n">
+        <v>2472</v>
+      </c>
+      <c r="K188" s="26" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="L188" s="26" t="n">
+        <v>3102</v>
+      </c>
+      <c r="M188" s="26" t="inlineStr"/>
+      <c r="N188" s="26" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="O188" s="26" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="P188" s="26" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="Q188" s="26" t="n">
+        <v>15.27</v>
+      </c>
+      <c r="R188" s="26" t="n">
+        <v>82</v>
+      </c>
+      <c r="S188" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="18" customHeight="1">
+      <c r="B189" s="18" t="inlineStr">
+        <is>
+          <t>Reel de Kit Le Mini</t>
+        </is>
+      </c>
+      <c r="C189" s="19" t="n">
+        <v>26</v>
+      </c>
+      <c r="D189" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="E189" s="19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F189" s="20" t="inlineStr"/>
+      <c r="G189" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="H189" s="24" t="inlineStr">
+        <is>
+          <t>-100%</t>
+        </is>
+      </c>
+      <c r="I189" s="23" t="n">
+        <v>63</v>
+      </c>
+      <c r="J189" s="23" t="inlineStr"/>
+      <c r="K189" s="19" t="inlineStr"/>
+      <c r="L189" s="19" t="n">
+        <v>2250</v>
+      </c>
+      <c r="M189" s="19" t="inlineStr"/>
+      <c r="N189" s="19" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="O189" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="P189" s="19" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="Q189" s="19" t="inlineStr"/>
+      <c r="R189" s="19" t="inlineStr"/>
+      <c r="S189" s="64" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="20" customHeight="1">
+      <c r="B190" s="13" t="inlineStr">
+        <is>
+          <t>SUBTOTAL  Campaña Secundaria LMM</t>
+        </is>
+      </c>
+      <c r="F190" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="G190" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="H190" s="15" t="inlineStr">
+        <is>
+          <t>-58%</t>
+        </is>
+      </c>
+      <c r="I190" s="16" t="n">
+        <v>73253</v>
+      </c>
+    </row>
+    <row r="192" ht="22" customHeight="1">
+      <c r="B192" s="5" t="inlineStr">
+        <is>
+          <t>▸ Campaña Conversión Catálogo</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="18" customHeight="1">
+      <c r="B193" s="32" t="inlineStr">
+        <is>
+          <t>Fragancias Picnic</t>
+        </is>
+      </c>
+      <c r="C193" s="33" t="n">
+        <v>2356</v>
+      </c>
+      <c r="D193" s="33" t="n">
+        <v>3006</v>
+      </c>
+      <c r="E193" s="33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F193" s="34" t="n">
+        <v>29</v>
+      </c>
+      <c r="G193" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H193" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I193" s="37" t="n">
+        <v>6363</v>
+      </c>
+      <c r="J193" s="37" t="n">
+        <v>219</v>
+      </c>
+      <c r="K193" s="33" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="L193" s="33" t="n">
+        <v>2116</v>
+      </c>
+      <c r="M193" s="33" t="inlineStr"/>
+      <c r="N193" s="33" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O193" s="33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P193" s="33" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q193" s="33" t="inlineStr"/>
+      <c r="R193" s="33" t="n">
+        <v>27</v>
+      </c>
+      <c r="S193" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="18" customHeight="1">
+      <c r="B194" s="32" t="inlineStr">
+        <is>
+          <t>Imagen Cotton Vlabel</t>
+        </is>
+      </c>
+      <c r="C194" s="33" t="n">
+        <v>1058</v>
+      </c>
+      <c r="D194" s="33" t="n">
+        <v>1219</v>
+      </c>
+      <c r="E194" s="33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F194" s="34" t="n">
+        <v>21</v>
+      </c>
+      <c r="G194" s="35" t="n">
+        <v>120</v>
+      </c>
+      <c r="H194" s="36" t="inlineStr">
+        <is>
+          <t>-82%</t>
+        </is>
+      </c>
+      <c r="I194" s="37" t="n">
+        <v>1981</v>
+      </c>
+      <c r="J194" s="37" t="n">
+        <v>94</v>
+      </c>
+      <c r="K194" s="33" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="L194" s="33" t="n">
+        <v>1625</v>
+      </c>
+      <c r="M194" s="33" t="inlineStr"/>
+      <c r="N194" s="33" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O194" s="33" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P194" s="33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q194" s="33" t="inlineStr"/>
+      <c r="R194" s="33" t="n">
+        <v>19</v>
+      </c>
+      <c r="S194" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="18" customHeight="1">
+      <c r="B195" s="18" t="inlineStr">
+        <is>
+          <t>Hot Chocalate</t>
+        </is>
+      </c>
+      <c r="C195" s="19" t="n">
+        <v>161</v>
+      </c>
+      <c r="D195" s="19" t="n">
+        <v>285</v>
+      </c>
+      <c r="E195" s="19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F195" s="20" t="n">
+        <v>13</v>
+      </c>
+      <c r="G195" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H195" s="22" t="inlineStr">
+        <is>
+          <t>+30%</t>
+        </is>
+      </c>
+      <c r="I195" s="23" t="n">
+        <v>449</v>
+      </c>
+      <c r="J195" s="23" t="n">
+        <v>34</v>
+      </c>
+      <c r="K195" s="19" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="L195" s="19" t="n">
+        <v>1575</v>
+      </c>
+      <c r="M195" s="19" t="inlineStr"/>
+      <c r="N195" s="19" t="inlineStr"/>
+      <c r="O195" s="19" t="inlineStr"/>
+      <c r="P195" s="19" t="inlineStr"/>
+      <c r="Q195" s="19" t="inlineStr"/>
+      <c r="R195" s="19" t="n">
+        <v>13</v>
+      </c>
+      <c r="S195" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="18" customHeight="1">
+      <c r="B196" s="32" t="inlineStr">
+        <is>
+          <t>Crema dibujada</t>
+        </is>
+      </c>
+      <c r="C196" s="33" t="n">
+        <v>543</v>
+      </c>
+      <c r="D196" s="33" t="n">
+        <v>600</v>
+      </c>
+      <c r="E196" s="33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F196" s="34" t="n">
+        <v>10</v>
+      </c>
+      <c r="G196" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="H196" s="63" t="inlineStr">
+        <is>
+          <t>+100%</t>
+        </is>
+      </c>
+      <c r="I196" s="37" t="n">
+        <v>847</v>
+      </c>
+      <c r="J196" s="37" t="n">
+        <v>84</v>
+      </c>
+      <c r="K196" s="33" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="L196" s="33" t="n">
+        <v>1411</v>
+      </c>
+      <c r="M196" s="33" t="inlineStr"/>
+      <c r="N196" s="33" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O196" s="33" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P196" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q196" s="33" t="inlineStr"/>
+      <c r="R196" s="33" t="n">
+        <v>9</v>
+      </c>
+      <c r="S196" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="18" customHeight="1">
+      <c r="B197" s="32" t="inlineStr">
+        <is>
+          <t>Carrusel Sun Kissed</t>
+        </is>
+      </c>
+      <c r="C197" s="33" t="n">
+        <v>212</v>
+      </c>
+      <c r="D197" s="33" t="n">
+        <v>229</v>
+      </c>
+      <c r="E197" s="33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F197" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="G197" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="H197" s="36" t="inlineStr">
+        <is>
+          <t>-43%</t>
+        </is>
+      </c>
+      <c r="I197" s="37" t="n">
+        <v>364</v>
+      </c>
+      <c r="J197" s="37" t="n">
+        <v>91</v>
+      </c>
+      <c r="K197" s="33" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="L197" s="33" t="n">
+        <v>1589</v>
+      </c>
+      <c r="M197" s="33" t="inlineStr"/>
+      <c r="N197" s="33" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O197" s="33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P197" s="33" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q197" s="33" t="inlineStr"/>
+      <c r="R197" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="S197" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="18" customHeight="1">
+      <c r="B198" s="32" t="inlineStr">
+        <is>
+          <t>4 por 3</t>
+        </is>
+      </c>
+      <c r="C198" s="33" t="n">
+        <v>134</v>
+      </c>
+      <c r="D198" s="33" t="n">
+        <v>174</v>
+      </c>
+      <c r="E198" s="33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F198" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="G198" s="35" t="n">
+        <v>123</v>
+      </c>
+      <c r="H198" s="36" t="inlineStr">
+        <is>
+          <t>-96%</t>
+        </is>
+      </c>
+      <c r="I198" s="37" t="n">
+        <v>421</v>
+      </c>
+      <c r="J198" s="37" t="n">
+        <v>84</v>
+      </c>
+      <c r="K198" s="33" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L198" s="33" t="n">
+        <v>2419</v>
+      </c>
+      <c r="M198" s="33" t="inlineStr"/>
+      <c r="N198" s="33" t="inlineStr"/>
+      <c r="O198" s="33" t="inlineStr"/>
+      <c r="P198" s="33" t="inlineStr"/>
+      <c r="Q198" s="33" t="inlineStr"/>
+      <c r="R198" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="S198" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="18" customHeight="1">
+      <c r="B199" s="6" t="inlineStr">
+        <is>
+          <t>Nuevos difusores</t>
+        </is>
+      </c>
+      <c r="C199" s="7" t="n">
+        <v>247</v>
+      </c>
+      <c r="D199" s="7" t="n">
+        <v>280</v>
+      </c>
+      <c r="E199" s="7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F199" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G199" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="H199" s="17" t="inlineStr">
+        <is>
+          <t>-77%</t>
+        </is>
+      </c>
+      <c r="I199" s="11" t="n">
+        <v>575</v>
+      </c>
+      <c r="J199" s="11" t="n">
+        <v>71</v>
+      </c>
+      <c r="K199" s="7" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="L199" s="7" t="n">
+        <v>2053</v>
+      </c>
+      <c r="M199" s="7" t="inlineStr"/>
+      <c r="N199" s="7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O199" s="7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P199" s="7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q199" s="7" t="inlineStr"/>
+      <c r="R199" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="S199" s="12" t="inlineStr">
+        <is>
+          <t>🔍 REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="18" customHeight="1">
+      <c r="B200" s="25" t="inlineStr">
+        <is>
+          <t>Macbook</t>
+        </is>
+      </c>
+      <c r="C200" s="26" t="n">
+        <v>8482</v>
+      </c>
+      <c r="D200" s="26" t="n">
+        <v>14633</v>
+      </c>
+      <c r="E200" s="26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F200" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="G200" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="H200" s="31" t="inlineStr">
+        <is>
+          <t>+75%</t>
+        </is>
+      </c>
+      <c r="I200" s="30" t="n">
+        <v>21610</v>
+      </c>
+      <c r="J200" s="30" t="n">
+        <v>3087</v>
+      </c>
+      <c r="K200" s="26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L200" s="26" t="n">
+        <v>1476</v>
+      </c>
+      <c r="M200" s="26" t="inlineStr"/>
+      <c r="N200" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="O200" s="26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P200" s="26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q200" s="26" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="R200" s="26" t="n">
+        <v>111</v>
+      </c>
+      <c r="S200" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="18" customHeight="1">
+      <c r="B201" s="32" t="inlineStr">
+        <is>
+          <t>Protector Termico</t>
+        </is>
+      </c>
+      <c r="C201" s="33" t="n">
+        <v>1177</v>
+      </c>
+      <c r="D201" s="33" t="n">
+        <v>1485</v>
+      </c>
+      <c r="E201" s="33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F201" s="34" t="n">
+        <v>18</v>
+      </c>
+      <c r="G201" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="H201" s="63" t="inlineStr">
+        <is>
+          <t>+29%</t>
+        </is>
+      </c>
+      <c r="I201" s="37" t="n">
+        <v>1837</v>
+      </c>
+      <c r="J201" s="37" t="n">
+        <v>102</v>
+      </c>
+      <c r="K201" s="33" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L201" s="33" t="n">
+        <v>1237</v>
+      </c>
+      <c r="M201" s="33" t="inlineStr"/>
+      <c r="N201" s="33" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O201" s="33" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P201" s="33" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q201" s="33" t="inlineStr"/>
+      <c r="R201" s="33" t="n">
+        <v>18</v>
+      </c>
+      <c r="S201" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="18" customHeight="1">
+      <c r="B202" s="32" t="inlineStr">
+        <is>
+          <t>Reel de fragancias</t>
+        </is>
+      </c>
+      <c r="C202" s="33" t="n">
+        <v>272</v>
+      </c>
+      <c r="D202" s="33" t="n">
+        <v>344</v>
+      </c>
+      <c r="E202" s="33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F202" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G202" s="35" t="n">
+        <v>104</v>
+      </c>
+      <c r="H202" s="36" t="inlineStr">
+        <is>
+          <t>-98%</t>
+        </is>
+      </c>
+      <c r="I202" s="37" t="n">
+        <v>523</v>
+      </c>
+      <c r="J202" s="37" t="n">
+        <v>261</v>
+      </c>
+      <c r="K202" s="33" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L202" s="33" t="n">
+        <v>1520</v>
+      </c>
+      <c r="M202" s="33" t="inlineStr"/>
+      <c r="N202" s="33" t="inlineStr"/>
+      <c r="O202" s="33" t="inlineStr"/>
+      <c r="P202" s="33" t="inlineStr"/>
+      <c r="Q202" s="33" t="inlineStr"/>
+      <c r="R202" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="S202" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="18" customHeight="1">
+      <c r="B203" s="32" t="inlineStr">
+        <is>
+          <t>Imagen Gato</t>
+        </is>
+      </c>
+      <c r="C203" s="33" t="n">
+        <v>426</v>
+      </c>
+      <c r="D203" s="33" t="n">
+        <v>481</v>
+      </c>
+      <c r="E203" s="33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F203" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="G203" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="H203" s="36" t="inlineStr">
+        <is>
+          <t>-29%</t>
+        </is>
+      </c>
+      <c r="I203" s="37" t="n">
+        <v>830</v>
+      </c>
+      <c r="J203" s="37" t="n">
+        <v>166</v>
+      </c>
+      <c r="K203" s="33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L203" s="33" t="n">
+        <v>1725</v>
+      </c>
+      <c r="M203" s="33" t="inlineStr"/>
+      <c r="N203" s="33" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O203" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="P203" s="33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q203" s="33" t="inlineStr"/>
+      <c r="R203" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="S203" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="18" customHeight="1">
+      <c r="B204" s="32" t="inlineStr">
+        <is>
+          <t>Reel cafetería</t>
+        </is>
+      </c>
+      <c r="C204" s="33" t="n">
+        <v>538</v>
+      </c>
+      <c r="D204" s="33" t="n">
+        <v>601</v>
+      </c>
+      <c r="E204" s="33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F204" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="G204" s="35" t="n">
+        <v>88</v>
+      </c>
+      <c r="H204" s="36" t="inlineStr">
+        <is>
+          <t>-92%</t>
+        </is>
+      </c>
+      <c r="I204" s="37" t="n">
+        <v>1087</v>
+      </c>
+      <c r="J204" s="37" t="n">
+        <v>155</v>
+      </c>
+      <c r="K204" s="33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L204" s="33" t="n">
+        <v>1808</v>
+      </c>
+      <c r="M204" s="33" t="inlineStr"/>
+      <c r="N204" s="33" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="O204" s="33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P204" s="33" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q204" s="33" t="inlineStr"/>
+      <c r="R204" s="33" t="n">
+        <v>7</v>
+      </c>
+      <c r="S204" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="18" customHeight="1">
+      <c r="B205" s="25" t="inlineStr">
+        <is>
+          <t>Imagen Bubble gum</t>
+        </is>
+      </c>
+      <c r="C205" s="26" t="n">
+        <v>795</v>
+      </c>
+      <c r="D205" s="26" t="n">
+        <v>909</v>
+      </c>
+      <c r="E205" s="26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F205" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G205" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="H205" s="29" t="inlineStr">
+        <is>
+          <t>-96%</t>
+        </is>
+      </c>
+      <c r="I205" s="30" t="n">
+        <v>1506</v>
+      </c>
+      <c r="J205" s="30" t="n">
+        <v>1506</v>
+      </c>
+      <c r="K205" s="26" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="L205" s="26" t="n">
+        <v>1656</v>
+      </c>
+      <c r="M205" s="26" t="inlineStr"/>
+      <c r="N205" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="O205" s="26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P205" s="26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q205" s="26" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="R205" s="26" t="n">
+        <v>13</v>
+      </c>
+      <c r="S205" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="18" customHeight="1">
+      <c r="B206" s="32" t="inlineStr">
+        <is>
+          <t>Carrusel Post que puedes oler</t>
+        </is>
+      </c>
+      <c r="C206" s="33" t="n">
+        <v>563</v>
+      </c>
+      <c r="D206" s="33" t="n">
+        <v>638</v>
+      </c>
+      <c r="E206" s="33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F206" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G206" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H206" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I206" s="37" t="n">
+        <v>849</v>
+      </c>
+      <c r="J206" s="37" t="n">
+        <v>283</v>
+      </c>
+      <c r="K206" s="33" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L206" s="33" t="n">
+        <v>1330</v>
+      </c>
+      <c r="M206" s="33" t="inlineStr"/>
+      <c r="N206" s="33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O206" s="33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P206" s="33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q206" s="33" t="inlineStr"/>
+      <c r="R206" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="S206" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="18" customHeight="1">
+      <c r="B207" s="32" t="inlineStr">
+        <is>
+          <t>Rutina 4 pasos 2.0</t>
+        </is>
+      </c>
+      <c r="C207" s="33" t="n">
+        <v>294</v>
+      </c>
+      <c r="D207" s="33" t="n">
+        <v>339</v>
+      </c>
+      <c r="E207" s="33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F207" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G207" s="35" t="n">
+        <v>36</v>
+      </c>
+      <c r="H207" s="36" t="inlineStr">
+        <is>
+          <t>-92%</t>
+        </is>
+      </c>
+      <c r="I207" s="37" t="n">
+        <v>594</v>
+      </c>
+      <c r="J207" s="37" t="n">
+        <v>198</v>
+      </c>
+      <c r="K207" s="33" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="L207" s="33" t="n">
+        <v>1752</v>
+      </c>
+      <c r="M207" s="33" t="inlineStr"/>
+      <c r="N207" s="33" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="O207" s="33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P207" s="33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q207" s="33" t="inlineStr"/>
+      <c r="R207" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="S207" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="18" customHeight="1">
+      <c r="B208" s="25" t="inlineStr">
+        <is>
+          <t>Bye Bye Aroma</t>
+        </is>
+      </c>
+      <c r="C208" s="26" t="n">
+        <v>2814</v>
+      </c>
+      <c r="D208" s="26" t="n">
+        <v>3783</v>
+      </c>
+      <c r="E208" s="26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F208" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="G208" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="H208" s="29" t="inlineStr">
+        <is>
+          <t>-50%</t>
+        </is>
+      </c>
+      <c r="I208" s="30" t="n">
+        <v>6908</v>
+      </c>
+      <c r="J208" s="30" t="n">
+        <v>2302</v>
+      </c>
+      <c r="K208" s="26" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="L208" s="26" t="n">
+        <v>1826</v>
+      </c>
+      <c r="M208" s="26" t="inlineStr"/>
+      <c r="N208" s="26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O208" s="26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="P208" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q208" s="26" t="n">
+        <v>12.52</v>
+      </c>
+      <c r="R208" s="26" t="n">
+        <v>45</v>
+      </c>
+      <c r="S208" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="18" customHeight="1">
+      <c r="B209" s="18" t="inlineStr">
+        <is>
+          <t>Cremas Sun Kissed</t>
+        </is>
+      </c>
+      <c r="C209" s="19" t="n">
+        <v>171061</v>
+      </c>
+      <c r="D209" s="19" t="n">
+        <v>615106</v>
+      </c>
+      <c r="E209" s="19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F209" s="20" t="n">
+        <v>139</v>
+      </c>
+      <c r="G209" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="H209" s="22" t="inlineStr">
+        <is>
+          <t>+479%</t>
+        </is>
+      </c>
+      <c r="I209" s="23" t="n">
+        <v>875903</v>
+      </c>
+      <c r="J209" s="23" t="n">
+        <v>6301</v>
+      </c>
+      <c r="K209" s="19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="L209" s="19" t="n">
+        <v>1423</v>
+      </c>
+      <c r="M209" s="19" t="inlineStr"/>
+      <c r="N209" s="19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O209" s="19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P209" s="19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q209" s="19" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="R209" s="19" t="n">
+        <v>6019</v>
+      </c>
+      <c r="S209" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="18" customHeight="1">
+      <c r="B210" s="32" t="inlineStr">
+        <is>
+          <t>Home Spray</t>
+        </is>
+      </c>
+      <c r="C210" s="33" t="n">
+        <v>205</v>
+      </c>
+      <c r="D210" s="33" t="n">
+        <v>234</v>
+      </c>
+      <c r="E210" s="33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F210" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G210" s="35" t="n">
+        <v>126</v>
+      </c>
+      <c r="H210" s="36" t="inlineStr">
+        <is>
+          <t>-98%</t>
+        </is>
+      </c>
+      <c r="I210" s="37" t="n">
+        <v>314</v>
+      </c>
+      <c r="J210" s="37" t="n">
+        <v>157</v>
+      </c>
+      <c r="K210" s="33" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L210" s="33" t="n">
+        <v>1341</v>
+      </c>
+      <c r="M210" s="33" t="inlineStr"/>
+      <c r="N210" s="33" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O210" s="33" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P210" s="33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q210" s="33" t="inlineStr"/>
+      <c r="R210" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="S210" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="18" customHeight="1">
+      <c r="B211" s="32" t="inlineStr">
+        <is>
+          <t>Go Paw @Juliana Carrascal</t>
+        </is>
+      </c>
+      <c r="C211" s="33" t="n">
+        <v>1410</v>
+      </c>
+      <c r="D211" s="33" t="n">
+        <v>1616</v>
+      </c>
+      <c r="E211" s="33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F211" s="34" t="n">
+        <v>20</v>
+      </c>
+      <c r="G211" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H211" s="63" t="inlineStr">
+        <is>
+          <t>+1900%</t>
+        </is>
+      </c>
+      <c r="I211" s="37" t="n">
+        <v>2769</v>
+      </c>
+      <c r="J211" s="37" t="n">
+        <v>138</v>
+      </c>
+      <c r="K211" s="33" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="L211" s="33" t="n">
+        <v>1713</v>
+      </c>
+      <c r="M211" s="33" t="inlineStr"/>
+      <c r="N211" s="33" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O211" s="33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P211" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q211" s="33" t="inlineStr"/>
+      <c r="R211" s="33" t="n">
+        <v>18</v>
+      </c>
+      <c r="S211" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="18" customHeight="1">
+      <c r="B212" s="32" t="inlineStr">
+        <is>
+          <t>Go Paw Carrusel Mascotas</t>
+        </is>
+      </c>
+      <c r="C212" s="33" t="n">
+        <v>533</v>
+      </c>
+      <c r="D212" s="33" t="n">
+        <v>622</v>
+      </c>
+      <c r="E212" s="33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F212" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="G212" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H212" s="63" t="inlineStr">
+        <is>
+          <t>+600%</t>
+        </is>
+      </c>
+      <c r="I212" s="37" t="n">
+        <v>1107</v>
+      </c>
+      <c r="J212" s="37" t="n">
+        <v>158</v>
+      </c>
+      <c r="K212" s="33" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="L212" s="33" t="n">
+        <v>1779</v>
+      </c>
+      <c r="M212" s="33" t="inlineStr"/>
+      <c r="N212" s="33" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="O212" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="P212" s="33" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q212" s="33" t="inlineStr"/>
+      <c r="R212" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="S212" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="18" customHeight="1">
+      <c r="B213" s="32" t="inlineStr">
+        <is>
+          <t>UGC Soft Milk Febrero</t>
+        </is>
+      </c>
+      <c r="C213" s="33" t="n">
+        <v>525</v>
+      </c>
+      <c r="D213" s="33" t="n">
+        <v>601</v>
+      </c>
+      <c r="E213" s="33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F213" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="G213" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H213" s="63" t="inlineStr">
+        <is>
+          <t>+300%</t>
+        </is>
+      </c>
+      <c r="I213" s="37" t="n">
+        <v>998</v>
+      </c>
+      <c r="J213" s="37" t="n">
+        <v>249</v>
+      </c>
+      <c r="K213" s="33" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L213" s="33" t="n">
+        <v>1660</v>
+      </c>
+      <c r="M213" s="33" t="inlineStr"/>
+      <c r="N213" s="33" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O213" s="33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P213" s="33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q213" s="33" t="inlineStr"/>
+      <c r="R213" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="S213" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="18" customHeight="1">
+      <c r="B214" s="32" t="inlineStr">
+        <is>
+          <t>Aceite Capilar Go Hair</t>
+        </is>
+      </c>
+      <c r="C214" s="33" t="n">
+        <v>576</v>
+      </c>
+      <c r="D214" s="33" t="n">
+        <v>634</v>
+      </c>
+      <c r="E214" s="33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F214" s="34" t="n">
+        <v>10</v>
+      </c>
+      <c r="G214" s="35" t="n">
+        <v>23</v>
+      </c>
+      <c r="H214" s="36" t="inlineStr">
+        <is>
+          <t>-57%</t>
+        </is>
+      </c>
+      <c r="I214" s="37" t="n">
+        <v>1110</v>
+      </c>
+      <c r="J214" s="37" t="n">
+        <v>111</v>
+      </c>
+      <c r="K214" s="33" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="L214" s="33" t="n">
+        <v>1750</v>
+      </c>
+      <c r="M214" s="33" t="inlineStr"/>
+      <c r="N214" s="33" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O214" s="33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P214" s="33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q214" s="33" t="inlineStr"/>
+      <c r="R214" s="33" t="n">
+        <v>9</v>
+      </c>
+      <c r="S214" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="18" customHeight="1">
+      <c r="B215" s="25" t="inlineStr">
+        <is>
+          <t>Go Paw Wild Berries y Cotton Candy</t>
+        </is>
+      </c>
+      <c r="C215" s="26" t="n">
+        <v>884</v>
+      </c>
+      <c r="D215" s="26" t="n">
+        <v>997</v>
+      </c>
+      <c r="E215" s="26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F215" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G215" s="28" t="n">
+        <v>15</v>
+      </c>
+      <c r="H215" s="29" t="inlineStr">
+        <is>
+          <t>-93%</t>
+        </is>
+      </c>
+      <c r="I215" s="30" t="n">
+        <v>1315</v>
+      </c>
+      <c r="J215" s="30" t="n">
+        <v>1315</v>
+      </c>
+      <c r="K215" s="26" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L215" s="26" t="n">
+        <v>1318</v>
+      </c>
+      <c r="M215" s="26" t="inlineStr"/>
+      <c r="N215" s="26" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O215" s="26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P215" s="26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q215" s="26" t="n">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="R215" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="S215" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="18" customHeight="1">
+      <c r="B216" s="32" t="inlineStr">
+        <is>
+          <t>Kit Cuidado Capilar</t>
+        </is>
+      </c>
+      <c r="C216" s="33" t="n">
+        <v>591</v>
+      </c>
+      <c r="D216" s="33" t="n">
+        <v>675</v>
+      </c>
+      <c r="E216" s="33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F216" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="G216" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="H216" s="36" t="inlineStr">
+        <is>
+          <t>-14%</t>
+        </is>
+      </c>
+      <c r="I216" s="37" t="n">
+        <v>1117</v>
+      </c>
+      <c r="J216" s="37" t="n">
+        <v>186</v>
+      </c>
+      <c r="K216" s="33" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="L216" s="33" t="n">
+        <v>1654</v>
+      </c>
+      <c r="M216" s="33" t="inlineStr"/>
+      <c r="N216" s="33" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O216" s="33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P216" s="33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q216" s="33" t="inlineStr"/>
+      <c r="R216" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="S216" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="18" customHeight="1">
+      <c r="B217" s="6" t="inlineStr">
+        <is>
+          <t>Protector Termico Pistacho Caramelo</t>
+        </is>
+      </c>
+      <c r="C217" s="7" t="n">
+        <v>352</v>
+      </c>
+      <c r="D217" s="7" t="n">
+        <v>460</v>
+      </c>
+      <c r="E217" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F217" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="G217" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="H217" s="17" t="inlineStr">
+        <is>
+          <t>-64%</t>
+        </is>
+      </c>
+      <c r="I217" s="11" t="n">
+        <v>622</v>
+      </c>
+      <c r="J217" s="11" t="n">
+        <v>69</v>
+      </c>
+      <c r="K217" s="7" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="L217" s="7" t="n">
+        <v>1352</v>
+      </c>
+      <c r="M217" s="7" t="inlineStr"/>
+      <c r="N217" s="7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O217" s="7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P217" s="7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q217" s="7" t="inlineStr"/>
+      <c r="R217" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="S217" s="12" t="inlineStr">
+        <is>
+          <t>🔍 REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="18" customHeight="1">
+      <c r="B218" s="25" t="inlineStr">
+        <is>
+          <t>Home Spray @vanusallorenzo</t>
+        </is>
+      </c>
+      <c r="C218" s="26" t="n">
+        <v>1855</v>
+      </c>
+      <c r="D218" s="26" t="n">
+        <v>2325</v>
+      </c>
+      <c r="E218" s="26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F218" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G218" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="H218" s="29" t="inlineStr">
+        <is>
+          <t>-80%</t>
+        </is>
+      </c>
+      <c r="I218" s="30" t="n">
+        <v>3351</v>
+      </c>
+      <c r="J218" s="30" t="n">
+        <v>3351</v>
+      </c>
+      <c r="K218" s="26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="L218" s="26" t="n">
+        <v>1441</v>
+      </c>
+      <c r="M218" s="26" t="inlineStr"/>
+      <c r="N218" s="26" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O218" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="P218" s="26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q218" s="26" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="R218" s="26" t="n">
+        <v>21</v>
+      </c>
+      <c r="S218" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="20" customHeight="1">
+      <c r="B219" s="13" t="inlineStr">
+        <is>
+          <t>SUBTOTAL  Campaña Conversión Catálogo</t>
+        </is>
+      </c>
+      <c r="F219" s="14" t="n">
+        <v>338</v>
+      </c>
+      <c r="G219" s="14" t="n">
+        <v>812</v>
+      </c>
+      <c r="H219" s="15" t="inlineStr">
+        <is>
+          <t>-58%</t>
+        </is>
+      </c>
+      <c r="I219" s="16" t="n">
+        <v>935350</v>
+      </c>
+    </row>
+    <row r="221" ht="26" customHeight="1">
+      <c r="B221" s="46" t="inlineStr">
+        <is>
+          <t>💡  Análisis Claude — Go Nails</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="36" customHeight="1">
+      <c r="B222" s="47" t="inlineStr">
+        <is>
+          <t>Go Nails tuvo una caída brutal del 88% en resultados (2.404 vs 20.613) con gasto similar, principalmente por anuncios de compra saturados con costos sobre benchmark. Las campañas de tráfico mantienen eficiencia, pero los creativos de conversión están quemados con frecuencias altas y ROAS bajo 3x.</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="20" customHeight="1">
+      <c r="B223" s="48" t="inlineStr">
+        <is>
+          <t>Campaña</t>
+        </is>
+      </c>
+      <c r="C223" s="48" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="D223" s="48" t="inlineStr">
+        <is>
+          <t>Hallazgo</t>
+        </is>
+      </c>
+      <c r="H223" s="48" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="M223" s="48" t="inlineStr">
+        <is>
+          <t>Acción recomendada</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="48" customHeight="1">
+      <c r="B224" s="49" t="inlineStr">
+        <is>
+          <t>Campaña principal de Conversión</t>
+        </is>
+      </c>
+      <c r="C224" s="50" t="inlineStr">
+        <is>
+          <t>🔴 ALERTA</t>
+        </is>
+      </c>
+      <c r="D224" s="51" t="inlineStr">
+        <is>
+          <t>Home Spray quemado, costo crítico</t>
+        </is>
+      </c>
+      <c r="H224" s="52" t="inlineStr">
+        <is>
+          <t>Gasta $1.186.817 (22% del budget total) con costo/compra $13.042 (115% sobre benchmark) y ROAS 2.45x muy bajo. Pasó de 126 a 91 conversiones con mismo gasto, señal clara de fatiga.</t>
+        </is>
+      </c>
+      <c r="M224" s="53" t="inlineStr">
+        <is>
+          <t>Pausar Home Spray urgente y reemplazar con 2-3 creativos nuevos mostrando el producto en contextos de hogar distintos (cocina, baño, dormitorio).</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="48" customHeight="1">
+      <c r="B225" s="54" t="inlineStr"/>
+      <c r="C225" s="50" t="inlineStr">
+        <is>
+          <t>🔴 ALERTA</t>
+        </is>
+      </c>
+      <c r="D225" s="51" t="inlineStr">
+        <is>
+          <t>Reel fragancias perdiendo tracción</t>
+        </is>
+      </c>
+      <c r="H225" s="52" t="inlineStr">
+        <is>
+          <t>Costo $10.337 (72% sobre benchmark) con ROAS 3.03x mediocre y caída de 104 a 76 conversiones. Hold Rate 1.6% indica que pierde audiencia rápido.</t>
+        </is>
+      </c>
+      <c r="M225" s="53" t="inlineStr">
+        <is>
+          <t>Crear nuevo reel de fragancias con hook más directo (primeros 2 segundos mostrando aplicación real) y testimonial de cliente satisfecha.</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="48" customHeight="1">
+      <c r="B226" s="54" t="inlineStr"/>
+      <c r="C226" s="55" t="inlineStr">
+        <is>
+          <t>🟢 OPORTUNIDAD</t>
+        </is>
+      </c>
+      <c r="D226" s="56" t="inlineStr">
+        <is>
+          <t>Imagen Cotton Vlabel mantiene eficiencia</t>
+        </is>
+      </c>
+      <c r="H226" s="57" t="inlineStr">
+        <is>
+          <t>Costo $7.713 dentro de rango OK con ROAS 5x sólido, aunque bajó de 120 a 38 conversiones. Es el segundo mejor ROAS de la campaña.</t>
+        </is>
+      </c>
+      <c r="M226" s="58" t="inlineStr">
+        <is>
+          <t>Escalar Cotton Vlabel con variaciones: misma imagen en formatos carrusel mostrando diferentes beneficios del producto por slide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="48" customHeight="1">
+      <c r="B227" s="49" t="inlineStr">
+        <is>
+          <t>Remarketing Go Nails 2024</t>
+        </is>
+      </c>
+      <c r="C227" s="50" t="inlineStr">
+        <is>
+          <t>🔴 ALERTA</t>
+        </is>
+      </c>
+      <c r="D227" s="51" t="inlineStr">
+        <is>
+          <t>Remarketing principal con costo elevado</t>
+        </is>
+      </c>
+      <c r="H227" s="52" t="inlineStr">
+        <is>
+          <t>El anuncio base cuesta $5.863/compra (2% bajo benchmark) pero cayó de 65 a 22 conversiones (-66%). ROAS 5.24x está bien pero el volumen se desplomó.</t>
+        </is>
+      </c>
+      <c r="M227" s="53" t="inlineStr">
+        <is>
+          <t>Refrescar el creativo de remarketing con nuevo gancho: agregar urgencia real (stock limitado de productos más vistos) en primeros 3 segundos del video.</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="48" customHeight="1">
+      <c r="B228" s="54" t="inlineStr"/>
+      <c r="C228" s="55" t="inlineStr">
+        <is>
+          <t>🟢 OPORTUNIDAD</t>
+        </is>
+      </c>
+      <c r="D228" s="56" t="inlineStr">
+        <is>
+          <t>Despacho Gratis funciona mejor</t>
+        </is>
+      </c>
+      <c r="H228" s="57" t="inlineStr">
+        <is>
+          <t>Costo $4.137 es el más bajo de remarketing (31% bajo benchmark) con ROAS 4.82x. Aunque bajó de 108 a 32 conversiones, mantiene mejor eficiencia que los otros anuncios.</t>
+        </is>
+      </c>
+      <c r="M228" s="58" t="inlineStr">
+        <is>
+          <t>Duplicar Despacho Gratis con nueva versión que combine el beneficio con timer visual de cuenta regresiva para generar urgencia inmediata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="48" customHeight="1">
+      <c r="B229" s="49" t="inlineStr">
+        <is>
+          <t>Marketing Go Nails - Trafico Insta</t>
+        </is>
+      </c>
+      <c r="C229" s="50" t="inlineStr">
+        <is>
+          <t>🔴 ALERTA</t>
+        </is>
+      </c>
+      <c r="D229" s="51" t="inlineStr">
+        <is>
+          <t>Hannah Montana 2 quebrando presupuesto</t>
+        </is>
+      </c>
+      <c r="H229" s="52" t="inlineStr">
+        <is>
+          <t>Gastó $283.796 con 1 sola conversión (costo $283.796) y ROAS 0.04x desastroso. Hold Rate 1.8% pésimo, la gente abandona el video de inmediato.</t>
+        </is>
+      </c>
+      <c r="M229" s="53" t="inlineStr">
+        <is>
+          <t>Pausar hannah montana 2 inmediatamente. Ese presupuesto equivale a 68 conversiones al costo promedio de campaña.</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="48" customHeight="1">
+      <c r="B230" s="54" t="inlineStr"/>
+      <c r="C230" s="50" t="inlineStr">
+        <is>
+          <t>🔴 ALERTA</t>
+        </is>
+      </c>
+      <c r="D230" s="51" t="inlineStr">
+        <is>
+          <t>Hannah Montana original también fallando</t>
+        </is>
+      </c>
+      <c r="H230" s="52" t="inlineStr">
+        <is>
+          <t>Costo $55.106 por 1 conversión con ROAS 0.74x y Hold Rate 0.1% crítico. El concepto Hannah Montana claramente no resuena con la audiencia.</t>
+        </is>
+      </c>
+      <c r="M230" s="53" t="inlineStr">
+        <is>
+          <t>Pausar hannah montana 1 también. Testear concepto nostálgico distinto (Y2K, early 2000s nail art) con referencias más visuales y menos texto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="48" customHeight="1">
+      <c r="B231" s="54" t="inlineStr"/>
+      <c r="C231" s="55" t="inlineStr">
+        <is>
+          <t>🟢 OPORTUNIDAD</t>
+        </is>
+      </c>
+      <c r="D231" s="56" t="inlineStr">
+        <is>
+          <t>Cotton candy y popcorn eficientes</t>
+        </is>
+      </c>
+      <c r="H231" s="57" t="inlineStr">
+        <is>
+          <t>Cotton candy logra 407 clicks a $17 c/u y popcorn 25 clicks a $12 con CTR 5.58% excelente. Ambos muy por debajo del benchmark de $40.</t>
+        </is>
+      </c>
+      <c r="M231" s="58" t="inlineStr">
+        <is>
+          <t>Mantener cotton candy y popcorn activos. Crear variación de cada uno cambiando solo el copy del texto (probar preguntas vs afirmaciones).</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="48" customHeight="1">
+      <c r="B232" s="49" t="inlineStr">
+        <is>
+          <t>Campaña Secundaria LMM</t>
+        </is>
+      </c>
+      <c r="C232" s="55" t="inlineStr">
+        <is>
+          <t>🟢 OPORTUNIDAD</t>
+        </is>
+      </c>
+      <c r="D232" s="56" t="inlineStr">
+        <is>
+          <t>Reel Kit LMM es ganador absoluto</t>
+        </is>
+      </c>
+      <c r="H232" s="57" t="inlineStr">
+        <is>
+          <t>Costo $2.473 (59% bajo benchmark) con ROAS 15.27x espectacular y Hold Rate 14.6% sólido. Solo gastó $12.363 pero es el mejor ROAS de toda la marca.</t>
+        </is>
+      </c>
+      <c r="M232" s="58" t="inlineStr">
+        <is>
+          <t>Aumentar prioridad de Reel Kit LMM duplicando el anuncio con segmentación a audiencias similares de compradores premium. No tocar el creativo, funciona perfecto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="48" customHeight="1">
+      <c r="B233" s="54" t="inlineStr"/>
+      <c r="C233" s="59" t="inlineStr">
+        <is>
+          <t>🔵 INSIGHT</t>
+        </is>
+      </c>
+      <c r="D233" s="60" t="inlineStr">
+        <is>
+          <t>LMM tiene potencial desaprovechado</t>
+        </is>
+      </c>
+      <c r="H233" s="61" t="inlineStr">
+        <is>
+          <t>La campaña solo gastó $73.253 (1% del budget total) pero tiene el mejor ROAS. Kit LMM demuestra que hay audiencia premium dispuesta a pagar.</t>
+        </is>
+      </c>
+      <c r="M233" s="62" t="inlineStr">
+        <is>
+          <t>Crear 2 anuncios nuevos de LMM siguiendo la estructura del Kit exitoso: producto en uso, resultado visible en primeros 5 segundos, estética clean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="48" customHeight="1">
+      <c r="B234" s="49" t="inlineStr">
+        <is>
+          <t>Campaña Conversión Catálogo</t>
+        </is>
+      </c>
+      <c r="C234" s="55" t="inlineStr">
+        <is>
+          <t>🟢 OPORTUNIDAD</t>
+        </is>
+      </c>
+      <c r="D234" s="56" t="inlineStr">
+        <is>
+          <t>Macbook convirtiendo con ROAS excepcional</t>
+        </is>
+      </c>
+      <c r="H234" s="57" t="inlineStr">
+        <is>
+          <t>Aunque es campaña de clicks, Macbook logró 7 compras a $3.087 c/u con ROAS 9.93x. Es anuncio tipo link_click que convierte mejor que muchos de purchase.</t>
+        </is>
+      </c>
+      <c r="M234" s="58" t="inlineStr">
+        <is>
+          <t>Mover Macbook a Campaña principal de Conversión como objetivo purchase y escalar con audiencias amplias. El creativo ya probó que convierte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="48" customHeight="1">
+      <c r="B235" s="54" t="inlineStr"/>
+      <c r="C235" s="59" t="inlineStr">
+        <is>
+          <t>🔵 INSIGHT</t>
+        </is>
+      </c>
+      <c r="D235" s="60" t="inlineStr">
+        <is>
+          <t>Fragancias Picnic costo aceptable</t>
+        </is>
+      </c>
+      <c r="H235" s="61" t="inlineStr">
+        <is>
+          <t>Nuevo anuncio con costo $219/click dentro del rango aceptable para tráfico (benchmark $40 ganador, $80 revisar). Aún no tiene historial suficiente para evaluar conversión.</t>
+        </is>
+      </c>
+      <c r="M235" s="62" t="inlineStr">
+        <is>
+          <t>Mantener Fragancias Picnic corriendo 1 semana más para acumular data. Si mantiene costo bajo $80 y genera interacción, duplicar con variación de copy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="24" customHeight="1">
+      <c r="B238" s="4" t="inlineStr">
+        <is>
+          <t>GOHAIR</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="22" customHeight="1">
+      <c r="B239" s="5" t="inlineStr">
+        <is>
+          <t>▸ Conversión Web Go Hair</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="18" customHeight="1">
+      <c r="B240" s="32" t="inlineStr">
+        <is>
+          <t>Reel Secador</t>
+        </is>
+      </c>
+      <c r="C240" s="33" t="n">
+        <v>1054</v>
+      </c>
+      <c r="D240" s="33" t="n">
+        <v>1758</v>
+      </c>
+      <c r="E240" s="33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F240" s="34" t="n">
+        <v>13</v>
+      </c>
+      <c r="G240" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="H240" s="63" t="inlineStr">
+        <is>
+          <t>+550%</t>
+        </is>
+      </c>
+      <c r="I240" s="37" t="n">
+        <v>4323</v>
+      </c>
+      <c r="J240" s="37" t="n">
+        <v>332</v>
+      </c>
+      <c r="K240" s="33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L240" s="33" t="n">
+        <v>2459</v>
+      </c>
+      <c r="M240" s="33" t="inlineStr"/>
+      <c r="N240" s="33" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O240" s="33" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P240" s="33" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q240" s="33" t="inlineStr"/>
+      <c r="R240" s="33" t="n">
+        <v>13</v>
+      </c>
+      <c r="S240" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="18" customHeight="1">
+      <c r="B241" s="32" t="inlineStr">
+        <is>
+          <t>Reel ondulador</t>
+        </is>
+      </c>
+      <c r="C241" s="33" t="n">
+        <v>4521</v>
+      </c>
+      <c r="D241" s="33" t="n">
+        <v>7219</v>
+      </c>
+      <c r="E241" s="33" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F241" s="34" t="n">
+        <v>59</v>
+      </c>
+      <c r="G241" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="H241" s="63" t="inlineStr">
+        <is>
+          <t>+1867%</t>
+        </is>
+      </c>
+      <c r="I241" s="37" t="n">
+        <v>19678</v>
+      </c>
+      <c r="J241" s="37" t="n">
+        <v>333</v>
+      </c>
+      <c r="K241" s="33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L241" s="33" t="n">
+        <v>2725</v>
+      </c>
+      <c r="M241" s="33" t="inlineStr"/>
+      <c r="N241" s="33" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="O241" s="33" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="P241" s="33" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="Q241" s="33" t="inlineStr"/>
+      <c r="R241" s="33" t="n">
+        <v>58</v>
+      </c>
+      <c r="S241" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="18" customHeight="1">
+      <c r="B242" s="18" t="inlineStr">
+        <is>
+          <t>Reel Cepillo Térmico</t>
+        </is>
+      </c>
+      <c r="C242" s="19" t="n">
+        <v>5135</v>
+      </c>
+      <c r="D242" s="19" t="n">
+        <v>7855</v>
+      </c>
+      <c r="E242" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F242" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G242" s="21" t="n">
+        <v>218</v>
+      </c>
+      <c r="H242" s="24" t="inlineStr">
+        <is>
+          <t>-99%</t>
+        </is>
+      </c>
+      <c r="I242" s="23" t="n">
+        <v>15192</v>
+      </c>
+      <c r="J242" s="23" t="n">
+        <v>7596</v>
+      </c>
+      <c r="K242" s="19" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="L242" s="19" t="n">
+        <v>1934</v>
+      </c>
+      <c r="M242" s="19" t="inlineStr"/>
+      <c r="N242" s="19" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="O242" s="19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P242" s="19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q242" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="R242" s="19" t="n">
+        <v>83</v>
+      </c>
+      <c r="S242" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="18" customHeight="1">
+      <c r="B243" s="32" t="inlineStr">
+        <is>
+          <t>Reel Rizador de aire</t>
+        </is>
+      </c>
+      <c r="C243" s="33" t="n">
+        <v>227</v>
+      </c>
+      <c r="D243" s="33" t="n">
+        <v>364</v>
+      </c>
+      <c r="E243" s="33" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F243" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G243" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H243" s="63" t="inlineStr">
+        <is>
+          <t>+100%</t>
+        </is>
+      </c>
+      <c r="I243" s="37" t="n">
+        <v>1326</v>
+      </c>
+      <c r="J243" s="37" t="n">
+        <v>663</v>
+      </c>
+      <c r="K243" s="33" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L243" s="33" t="n">
+        <v>3642</v>
+      </c>
+      <c r="M243" s="33" t="inlineStr"/>
+      <c r="N243" s="33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O243" s="33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P243" s="33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q243" s="33" t="inlineStr"/>
+      <c r="R243" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="S243" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="18" customHeight="1">
+      <c r="B244" s="18" t="inlineStr">
+        <is>
+          <t>Reel 3 en 1</t>
+        </is>
+      </c>
+      <c r="C244" s="19" t="n">
+        <v>6579</v>
+      </c>
+      <c r="D244" s="19" t="n">
+        <v>13076</v>
+      </c>
+      <c r="E244" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F244" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G244" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H244" s="24" t="inlineStr">
+        <is>
+          <t>-50%</t>
+        </is>
+      </c>
+      <c r="I244" s="23" t="n">
+        <v>19719</v>
+      </c>
+      <c r="J244" s="23" t="n">
+        <v>9859</v>
+      </c>
+      <c r="K244" s="19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L244" s="19" t="n">
+        <v>1508</v>
+      </c>
+      <c r="M244" s="19" t="inlineStr"/>
+      <c r="N244" s="19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O244" s="19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P244" s="19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q244" s="19" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="R244" s="19" t="n">
+        <v>99</v>
+      </c>
+      <c r="S244" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="18" customHeight="1">
+      <c r="B245" s="32" t="inlineStr">
+        <is>
+          <t>Reel Genérico amplio</t>
+        </is>
+      </c>
+      <c r="C245" s="33" t="n">
+        <v>1434</v>
+      </c>
+      <c r="D245" s="33" t="n">
+        <v>1933</v>
+      </c>
+      <c r="E245" s="33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F245" s="34" t="n">
+        <v>30</v>
+      </c>
+      <c r="G245" s="35" t="n">
+        <v>71</v>
+      </c>
+      <c r="H245" s="36" t="inlineStr">
+        <is>
+          <t>-58%</t>
+        </is>
+      </c>
+      <c r="I245" s="37" t="n">
+        <v>4420</v>
+      </c>
+      <c r="J245" s="37" t="n">
+        <v>147</v>
+      </c>
+      <c r="K245" s="33" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="L245" s="33" t="n">
+        <v>2286</v>
+      </c>
+      <c r="M245" s="33" t="inlineStr"/>
+      <c r="N245" s="33" t="n">
+        <v>25</v>
+      </c>
+      <c r="O245" s="33" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="P245" s="33" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="Q245" s="33" t="inlineStr"/>
+      <c r="R245" s="33" t="n">
+        <v>29</v>
+      </c>
+      <c r="S245" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="18" customHeight="1">
+      <c r="B246" s="32" t="inlineStr">
+        <is>
+          <t>Black WEEK</t>
+        </is>
+      </c>
+      <c r="C246" s="33" t="n">
+        <v>3495</v>
+      </c>
+      <c r="D246" s="33" t="n">
+        <v>10971</v>
+      </c>
+      <c r="E246" s="33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F246" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G246" s="35" t="n">
+        <v>47</v>
+      </c>
+      <c r="H246" s="36" t="inlineStr">
+        <is>
+          <t>-98%</t>
+        </is>
+      </c>
+      <c r="I246" s="37" t="n">
+        <v>22272</v>
+      </c>
+      <c r="J246" s="37" t="n">
+        <v>22272</v>
+      </c>
+      <c r="K246" s="33" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="L246" s="33" t="n">
+        <v>2030</v>
+      </c>
+      <c r="M246" s="33" t="inlineStr"/>
+      <c r="N246" s="33" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="O246" s="33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P246" s="33" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q246" s="33" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="R246" s="33" t="n">
+        <v>33</v>
+      </c>
+      <c r="S246" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="20" customHeight="1">
+      <c r="B247" s="13" t="inlineStr">
+        <is>
+          <t>SUBTOTAL  Conversión Web Go Hair</t>
+        </is>
+      </c>
+      <c r="F247" s="14" t="n">
+        <v>109</v>
+      </c>
+      <c r="G247" s="14" t="n">
+        <v>346</v>
+      </c>
+      <c r="H247" s="15" t="inlineStr">
+        <is>
+          <t>-68%</t>
+        </is>
+      </c>
+      <c r="I247" s="16" t="n">
+        <v>86930</v>
+      </c>
+    </row>
+    <row r="249" ht="22" customHeight="1">
+      <c r="B249" s="5" t="inlineStr">
+        <is>
+          <t>▸ Tráfico Perfil Instagram - Go Hair</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="18" customHeight="1">
+      <c r="B250" s="25" t="inlineStr">
+        <is>
+          <t>anuncio 1</t>
+        </is>
+      </c>
+      <c r="C250" s="26" t="n">
+        <v>40219</v>
+      </c>
+      <c r="D250" s="26" t="n">
+        <v>54454</v>
+      </c>
+      <c r="E250" s="26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F250" s="27" t="n">
+        <v>3231</v>
+      </c>
+      <c r="G250" s="28" t="n">
+        <v>3168</v>
+      </c>
+      <c r="H250" s="31" t="inlineStr">
+        <is>
+          <t>+2%</t>
+        </is>
+      </c>
+      <c r="I250" s="30" t="n">
+        <v>29285</v>
+      </c>
+      <c r="J250" s="30" t="n">
+        <v>9</v>
+      </c>
+      <c r="K250" s="26" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="L250" s="26" t="n">
+        <v>537</v>
+      </c>
+      <c r="M250" s="26" t="inlineStr"/>
+      <c r="N250" s="26" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="O250" s="26" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="P250" s="26" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="Q250" s="26" t="inlineStr"/>
+      <c r="R250" s="26" t="inlineStr"/>
+      <c r="S250" s="31" t="inlineStr">
+        <is>
+          <t>🏆 GANADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="18" customHeight="1">
+      <c r="B251" s="18" t="inlineStr">
+        <is>
+          <t>anuncio 2</t>
+        </is>
+      </c>
+      <c r="C251" s="19" t="n">
+        <v>57</v>
+      </c>
+      <c r="D251" s="19" t="n">
+        <v>61</v>
+      </c>
+      <c r="E251" s="19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F251" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G251" s="21" t="n">
+        <v>22</v>
+      </c>
+      <c r="H251" s="24" t="inlineStr">
+        <is>
+          <t>-91%</t>
+        </is>
+      </c>
+      <c r="I251" s="23" t="n">
+        <v>59</v>
+      </c>
+      <c r="J251" s="23" t="n">
+        <v>29</v>
+      </c>
+      <c r="K251" s="19" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="L251" s="19" t="n">
+        <v>967</v>
+      </c>
+      <c r="M251" s="19" t="inlineStr"/>
+      <c r="N251" s="19" t="inlineStr"/>
+      <c r="O251" s="19" t="inlineStr"/>
+      <c r="P251" s="19" t="inlineStr"/>
+      <c r="Q251" s="19" t="inlineStr"/>
+      <c r="R251" s="19" t="inlineStr"/>
+      <c r="S251" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="18" customHeight="1">
+      <c r="B252" s="18" t="inlineStr">
+        <is>
+          <t>aceite carrusel</t>
+        </is>
+      </c>
+      <c r="C252" s="19" t="n">
+        <v>320</v>
+      </c>
+      <c r="D252" s="19" t="n">
+        <v>414</v>
+      </c>
+      <c r="E252" s="19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F252" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="G252" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H252" s="22" t="inlineStr">
+        <is>
+          <t>+1400%</t>
+        </is>
+      </c>
+      <c r="I252" s="23" t="n">
+        <v>511</v>
+      </c>
+      <c r="J252" s="23" t="n">
+        <v>34</v>
+      </c>
+      <c r="K252" s="19" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="L252" s="19" t="n">
+        <v>1234</v>
+      </c>
+      <c r="M252" s="19" t="inlineStr"/>
+      <c r="N252" s="19" t="inlineStr"/>
+      <c r="O252" s="19" t="inlineStr"/>
+      <c r="P252" s="19" t="inlineStr"/>
+      <c r="Q252" s="19" t="inlineStr"/>
+      <c r="R252" s="19" t="inlineStr"/>
+      <c r="S252" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="20" customHeight="1">
+      <c r="B253" s="13" t="inlineStr">
+        <is>
+          <t>SUBTOTAL  Tráfico Perfil Instagram - Go Hair</t>
+        </is>
+      </c>
+      <c r="F253" s="14" t="n">
+        <v>3248</v>
+      </c>
+      <c r="G253" s="14" t="n">
+        <v>3191</v>
+      </c>
+      <c r="H253" s="15" t="inlineStr">
+        <is>
+          <t>+2%</t>
+        </is>
+      </c>
+      <c r="I253" s="16" t="n">
+        <v>29855</v>
+      </c>
+    </row>
+    <row r="255" ht="22" customHeight="1">
+      <c r="B255" s="5" t="inlineStr">
+        <is>
+          <t>▸ Conversión Web Go Hair Cuidado Capilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="18" customHeight="1">
+      <c r="B256" s="32" t="inlineStr">
+        <is>
+          <t>Antes y Después Go Hair</t>
+        </is>
+      </c>
+      <c r="C256" s="33" t="n">
+        <v>498</v>
+      </c>
+      <c r="D256" s="33" t="n">
+        <v>739</v>
+      </c>
+      <c r="E256" s="33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F256" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="G256" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H256" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I256" s="37" t="n">
+        <v>4759</v>
+      </c>
+      <c r="J256" s="37" t="n">
+        <v>1189</v>
+      </c>
+      <c r="K256" s="33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="L256" s="33" t="n">
+        <v>6439</v>
+      </c>
+      <c r="M256" s="33" t="inlineStr"/>
+      <c r="N256" s="33" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O256" s="33" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P256" s="33" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q256" s="33" t="inlineStr"/>
+      <c r="R256" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="S256" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="18" customHeight="1">
+      <c r="B257" s="32" t="inlineStr">
+        <is>
+          <t>Que dice tu pelo?</t>
+        </is>
+      </c>
+      <c r="C257" s="33" t="n">
+        <v>8580</v>
+      </c>
+      <c r="D257" s="33" t="n">
+        <v>21956</v>
+      </c>
+      <c r="E257" s="33" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F257" s="34" t="n">
+        <v>178</v>
+      </c>
+      <c r="G257" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H257" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I257" s="37" t="n">
+        <v>74226</v>
+      </c>
+      <c r="J257" s="37" t="n">
+        <v>417</v>
+      </c>
+      <c r="K257" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="L257" s="33" t="n">
+        <v>3380</v>
+      </c>
+      <c r="M257" s="33" t="inlineStr"/>
+      <c r="N257" s="33" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O257" s="33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P257" s="33" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q257" s="33" t="inlineStr"/>
+      <c r="R257" s="33" t="n">
+        <v>178</v>
+      </c>
+      <c r="S257" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="18" customHeight="1">
+      <c r="B258" s="32" t="inlineStr">
+        <is>
+          <t>Termo Protectores</t>
+        </is>
+      </c>
+      <c r="C258" s="33" t="n">
+        <v>3588</v>
+      </c>
+      <c r="D258" s="33" t="n">
+        <v>8019</v>
+      </c>
+      <c r="E258" s="33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F258" s="34" t="n">
+        <v>65</v>
+      </c>
+      <c r="G258" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H258" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I258" s="37" t="n">
+        <v>70843</v>
+      </c>
+      <c r="J258" s="37" t="n">
+        <v>1089</v>
+      </c>
+      <c r="K258" s="33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="L258" s="33" t="n">
+        <v>8834</v>
+      </c>
+      <c r="M258" s="33" t="inlineStr"/>
+      <c r="N258" s="33" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O258" s="33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P258" s="33" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q258" s="33" t="inlineStr"/>
+      <c r="R258" s="33" t="n">
+        <v>58</v>
+      </c>
+      <c r="S258" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="20" customHeight="1">
+      <c r="B259" s="13" t="inlineStr">
+        <is>
+          <t>SUBTOTAL  Conversión Web Go Hair Cuidado Capilar</t>
+        </is>
+      </c>
+      <c r="F259" s="14" t="n">
+        <v>247</v>
+      </c>
+      <c r="I259" s="16" t="n">
+        <v>149828</v>
+      </c>
+    </row>
+    <row r="261" ht="22" customHeight="1">
+      <c r="B261" s="5" t="inlineStr">
+        <is>
+          <t>▸ Campaña Catálogo Ventas</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="18" customHeight="1">
+      <c r="B262" s="32" t="inlineStr">
+        <is>
+          <t>Anuncio Catálogo Conversión</t>
+        </is>
+      </c>
+      <c r="C262" s="33" t="n">
+        <v>55974</v>
+      </c>
+      <c r="D262" s="33" t="n">
+        <v>188814</v>
+      </c>
+      <c r="E262" s="33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F262" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="G262" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H262" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I262" s="37" t="n">
+        <v>257921</v>
+      </c>
+      <c r="J262" s="37" t="n">
+        <v>42986</v>
+      </c>
+      <c r="K262" s="33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="L262" s="33" t="n">
+        <v>1366</v>
+      </c>
+      <c r="M262" s="33" t="inlineStr"/>
+      <c r="N262" s="33" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O262" s="33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P262" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q262" s="33" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="R262" s="33" t="n">
+        <v>1869</v>
+      </c>
+      <c r="S262" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="20" customHeight="1">
+      <c r="B263" s="13" t="inlineStr">
+        <is>
+          <t>SUBTOTAL  Campaña Catálogo Ventas</t>
+        </is>
+      </c>
+      <c r="F263" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I263" s="16" t="n">
+        <v>257921</v>
+      </c>
+    </row>
+    <row r="265" ht="22" customHeight="1">
+      <c r="B265" s="5" t="inlineStr">
+        <is>
+          <t>▸ Campaña de Conversión de Venta</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="18" customHeight="1">
+      <c r="B266" s="32" t="inlineStr">
+        <is>
+          <t>Aceite Capilar</t>
+        </is>
+      </c>
+      <c r="C266" s="33" t="n">
+        <v>435</v>
+      </c>
+      <c r="D266" s="33" t="n">
+        <v>593</v>
+      </c>
+      <c r="E266" s="33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F266" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="G266" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H266" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I266" s="37" t="n">
+        <v>1793</v>
+      </c>
+      <c r="J266" s="37" t="n">
+        <v>298</v>
+      </c>
+      <c r="K266" s="33" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="L266" s="33" t="n">
+        <v>3023</v>
+      </c>
+      <c r="M266" s="33" t="inlineStr"/>
+      <c r="N266" s="33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O266" s="33" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="P266" s="33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q266" s="33" t="inlineStr"/>
+      <c r="R266" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="S266" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="267" ht="18" customHeight="1">
+      <c r="B267" s="32" t="inlineStr">
+        <is>
+          <t>Acondicionador y Shampoo</t>
+        </is>
+      </c>
+      <c r="C267" s="33" t="n">
+        <v>1491</v>
+      </c>
+      <c r="D267" s="33" t="n">
+        <v>2215</v>
+      </c>
+      <c r="E267" s="33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F267" s="34" t="n">
+        <v>12</v>
+      </c>
+      <c r="G267" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H267" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I267" s="37" t="n">
+        <v>4509</v>
+      </c>
+      <c r="J267" s="37" t="n">
+        <v>375</v>
+      </c>
+      <c r="K267" s="33" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="L267" s="33" t="n">
+        <v>2035</v>
+      </c>
+      <c r="M267" s="33" t="inlineStr"/>
+      <c r="N267" s="33" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="O267" s="33" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P267" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q267" s="33" t="inlineStr"/>
+      <c r="R267" s="33" t="n">
+        <v>12</v>
+      </c>
+      <c r="S267" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="18" customHeight="1">
+      <c r="B268" s="32" t="inlineStr">
+        <is>
+          <t>Protector térmico carrusel</t>
+        </is>
+      </c>
+      <c r="C268" s="33" t="n">
+        <v>1963</v>
+      </c>
+      <c r="D268" s="33" t="n">
+        <v>2883</v>
+      </c>
+      <c r="E268" s="33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F268" s="34" t="n">
+        <v>20</v>
+      </c>
+      <c r="G268" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H268" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I268" s="37" t="n">
+        <v>10017</v>
+      </c>
+      <c r="J268" s="37" t="n">
+        <v>500</v>
+      </c>
+      <c r="K268" s="33" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="L268" s="33" t="n">
+        <v>3474</v>
+      </c>
+      <c r="M268" s="33" t="inlineStr"/>
+      <c r="N268" s="33" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O268" s="33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P268" s="33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q268" s="33" t="inlineStr"/>
+      <c r="R268" s="33" t="n">
+        <v>20</v>
+      </c>
+      <c r="S268" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="269" ht="18" customHeight="1">
+      <c r="B269" s="18" t="inlineStr">
+        <is>
+          <t>Aceite Capilar foto</t>
+        </is>
+      </c>
+      <c r="C269" s="19" t="n">
+        <v>3586</v>
+      </c>
+      <c r="D269" s="19" t="n">
+        <v>4285</v>
+      </c>
+      <c r="E269" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F269" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G269" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H269" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I269" s="23" t="n">
+        <v>8157</v>
+      </c>
+      <c r="J269" s="23" t="n">
+        <v>8157</v>
+      </c>
+      <c r="K269" s="19" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L269" s="19" t="n">
+        <v>1903</v>
+      </c>
+      <c r="M269" s="19" t="inlineStr"/>
+      <c r="N269" s="19" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O269" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P269" s="19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q269" s="19" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="R269" s="19" t="n">
+        <v>29</v>
+      </c>
+      <c r="S269" s="22" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="18" customHeight="1">
+      <c r="B270" s="32" t="inlineStr">
+        <is>
+          <t>Rutina capilar</t>
+        </is>
+      </c>
+      <c r="C270" s="33" t="n">
+        <v>613</v>
+      </c>
+      <c r="D270" s="33" t="n">
+        <v>673</v>
+      </c>
+      <c r="E270" s="33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F270" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="G270" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H270" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I270" s="37" t="n">
+        <v>2153</v>
+      </c>
+      <c r="J270" s="37" t="n">
+        <v>430</v>
+      </c>
+      <c r="K270" s="33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="L270" s="33" t="n">
+        <v>3199</v>
+      </c>
+      <c r="M270" s="33" t="inlineStr"/>
+      <c r="N270" s="33" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O270" s="33" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P270" s="33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q270" s="33" t="inlineStr"/>
+      <c r="R270" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="S270" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="18" customHeight="1">
+      <c r="B271" s="32" t="inlineStr">
+        <is>
+          <t>reel protector de calor</t>
+        </is>
+      </c>
+      <c r="C271" s="33" t="n">
+        <v>540</v>
+      </c>
+      <c r="D271" s="33" t="n">
+        <v>729</v>
+      </c>
+      <c r="E271" s="33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F271" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G271" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H271" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I271" s="37" t="n">
+        <v>2208</v>
+      </c>
+      <c r="J271" s="37" t="n">
+        <v>2208</v>
+      </c>
+      <c r="K271" s="33" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="L271" s="33" t="n">
+        <v>3028</v>
+      </c>
+      <c r="M271" s="33" t="inlineStr"/>
+      <c r="N271" s="33" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O271" s="33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P271" s="33" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q271" s="33" t="inlineStr"/>
+      <c r="R271" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="S271" s="36" t="inlineStr">
+        <is>
+          <t>⛔ PAUSAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="20" customHeight="1">
+      <c r="B272" s="13" t="inlineStr">
+        <is>
+          <t>SUBTOTAL  Campaña de Conversión de Venta</t>
+        </is>
+      </c>
+      <c r="F272" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="I272" s="16" t="n">
+        <v>28837</v>
+      </c>
+    </row>
+    <row r="274" ht="26" customHeight="1">
+      <c r="B274" s="46" t="inlineStr">
+        <is>
+          <t>💡  Análisis Claude — GoHair</t>
+        </is>
+      </c>
+    </row>
+    <row r="275" ht="36" customHeight="1">
+      <c r="B275" s="47" t="inlineStr">
+        <is>
+          <t>GoHair aumentó gasto 10% ($553k vs $501k) pero mantiene resultados planos (3.655 vs 3.555). El problema crítico: costo por compra se disparó a $42.987 en catálogo y $7.596-$22.272 en conversión web, muy por encima del benchmark de $18k máximo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="276" ht="20" customHeight="1">
+      <c r="B276" s="48" t="inlineStr">
+        <is>
+          <t>Campaña</t>
+        </is>
+      </c>
+      <c r="C276" s="48" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="D276" s="48" t="inlineStr">
+        <is>
+          <t>Hallazgo</t>
+        </is>
+      </c>
+      <c r="H276" s="48" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="M276" s="48" t="inlineStr">
+        <is>
+          <t>Acción recomendada</t>
+        </is>
+      </c>
+    </row>
+    <row r="277" ht="48" customHeight="1">
+      <c r="B277" s="49" t="inlineStr">
+        <is>
+          <t>Conversión Web Go Hair</t>
+        </is>
+      </c>
+      <c r="C277" s="50" t="inlineStr">
+        <is>
+          <t>🔴 ALERTA</t>
+        </is>
+      </c>
+      <c r="D277" s="51" t="inlineStr">
+        <is>
+          <t>Costo por compra fuera de benchmark</t>
+        </is>
+      </c>
+      <c r="H277" s="52" t="inlineStr">
+        <is>
+          <t>Reel Cepillo Térmico ($7.596/compra) y Reel 3 en 1 ($9.860/compra) están 323% sobre el límite pausable de $18k. Black WEEK colapsó: pasó de 47 compras a 1 compra con costo $22.272, ROAS cayó de campaña anterior.</t>
+        </is>
+      </c>
+      <c r="M277" s="53" t="inlineStr">
+        <is>
+          <t>Pausar Black WEEK, Cepillo Térmico y 3 en 1 esta semana. Escalar Reel Genérico amplio que tiene costo $147/click y Hold Rate 25%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="278" ht="48" customHeight="1">
+      <c r="B278" s="54" t="inlineStr"/>
+      <c r="C278" s="55" t="inlineStr">
+        <is>
+          <t>🟢 OPORTUNIDAD</t>
+        </is>
+      </c>
+      <c r="D278" s="56" t="inlineStr">
+        <is>
+          <t>Reel Genérico amplio es ganador claro</t>
+        </is>
+      </c>
+      <c r="H278" s="57" t="inlineStr">
+        <is>
+          <t>Costo $147/click (dentro de benchmark $20-$40), CTR 2.12% y Hold Rate 25% superan al resto. Generó 30 clicks con $4.420 de gasto. Es el único creativo funcionando bien en esta campaña.</t>
+        </is>
+      </c>
+      <c r="M278" s="58" t="inlineStr">
+        <is>
+          <t>Crear 3 variaciones del Reel Genérico amplio (cambiar hook, agregar texto, formato vertical) para testear esta semana y capitalizar el formato ganador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="279" ht="48" customHeight="1">
+      <c r="B279" s="54" t="inlineStr"/>
+      <c r="C279" s="59" t="inlineStr">
+        <is>
+          <t>🔵 INSIGHT</t>
+        </is>
+      </c>
+      <c r="D279" s="60" t="inlineStr">
+        <is>
+          <t>Videos pierden audiencia en primeros segundos</t>
+        </is>
+      </c>
+      <c r="H279" s="61" t="inlineStr">
+        <is>
+          <t>Hold Rate promedio 4.5%-6.3% indica que 95% abandona antes del 50% del video. Rizador de aire tiene 1.4% Hold Rate y CTR 0.82%, el peor de la campaña. Reel ondulador es excepción con 18.4% Hold Rate.</t>
+        </is>
+      </c>
+      <c r="M279" s="62" t="inlineStr">
+        <is>
+          <t>Rehacer hooks de todos los reels de producto individual: primeros 3 segundos deben mostrar resultado dramático o problema identificable, no producto estático.</t>
+        </is>
+      </c>
+    </row>
+    <row r="280" ht="48" customHeight="1">
+      <c r="B280" s="49" t="inlineStr">
+        <is>
+          <t>Tráfico Perfil Instagram - Go Hair</t>
+        </is>
+      </c>
+      <c r="C280" s="55" t="inlineStr">
+        <is>
+          <t>🟢 OPORTUNIDAD</t>
+        </is>
+      </c>
+      <c r="D280" s="56" t="inlineStr">
+        <is>
+          <t>Única campaña con eficiencia ganadora</t>
+        </is>
+      </c>
+      <c r="H280" s="57" t="inlineStr">
+        <is>
+          <t>Anuncio 1 logra $9/click (55% bajo benchmark ganador de $20) con CTR 5.89% y Hold Rate 26.6%. Generó 3.231 clicks con $29k de gasto, performance estable vs mes anterior (3.168 clicks).</t>
+        </is>
+      </c>
+      <c r="M280" s="58" t="inlineStr">
+        <is>
+          <t>Crear 2 creativos nuevos manteniendo estructura del Anuncio 1 para rotar en 2 semanas y prevenir fatiga (frecuencia no visible pero ciclo normal de la empresa).</t>
+        </is>
+      </c>
+    </row>
+    <row r="281" ht="48" customHeight="1">
+      <c r="B281" s="54" t="inlineStr"/>
+      <c r="C281" s="59" t="inlineStr">
+        <is>
+          <t>🔵 INSIGHT</t>
+        </is>
+      </c>
+      <c r="D281" s="60" t="inlineStr">
+        <is>
+          <t>Carrusel aceite tiene potencial sin explotar</t>
+        </is>
+      </c>
+      <c r="H281" s="61" t="inlineStr">
+        <is>
+          <t>Aceite carrusel tiene CTR 3.86% y costo $34/click (dentro de benchmark ganador) pero solo $511 de gasto vs $29k del Anuncio 1. Pasó de 1 a 15 resultados mes a mes, señal de escalabilidad.</t>
+        </is>
+      </c>
+      <c r="M281" s="62" t="inlineStr">
+        <is>
+          <t>Aumentar delivery orgánico del carrusel aceite duplicando audiencia o ajustando puja para que compita con Anuncio 1 sin tocar presupuesto total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="48" customHeight="1">
+      <c r="B282" s="49" t="inlineStr">
+        <is>
+          <t>Conversión Web Go Hair Cuidado Capilar</t>
+        </is>
+      </c>
+      <c r="C282" s="50" t="inlineStr">
+        <is>
+          <t>🔴 ALERTA</t>
+        </is>
+      </c>
+      <c r="D282" s="51" t="inlineStr">
+        <is>
+          <t>Costo por click 1520% sobre benchmark</t>
+        </is>
+      </c>
+      <c r="H282" s="52" t="inlineStr">
+        <is>
+          <t>Termo Protectores tiene costo $1.090/click (2.725% sobre límite pausable de $40) y Hold Rate 6.6%. Antes y Después Go Hair cuesta $1.190/click con Hold Rate desastroso de 1.6%. Que dice tu pelo consume $74k con Hold Rate 0.8%.</t>
+        </is>
+      </c>
+      <c r="M282" s="53" t="inlineStr">
+        <is>
+          <t>Pausar Termo Protectores y Antes y Después inmediatamente. Revisar objetivo de Que dice tu pelo: $74k gastados con Hold Rate 0.8% no justifica mantenerlo activo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="48" customHeight="1">
+      <c r="B283" s="54" t="inlineStr"/>
+      <c r="C283" s="59" t="inlineStr">
+        <is>
+          <t>🔵 INSIGHT</t>
+        </is>
+      </c>
+      <c r="D283" s="60" t="inlineStr">
+        <is>
+          <t>Audiencia no retiene ningún creativo</t>
+        </is>
+      </c>
+      <c r="H283" s="61" t="inlineStr">
+        <is>
+          <t>Hold Rate promedio 3% (0.8%-6.6%) indica rechazo masivo al contenido. CTR bajo 1%-1.22% confirma desconexión con audiencia objetivo. Campaña nueva (0 resultados mes anterior) sin product-market fit en contenido.</t>
+        </is>
+      </c>
+      <c r="M283" s="62" t="inlineStr">
+        <is>
+          <t>Testear formato educativo corto (15 seg máx): problema capilar específico + solución GoHair + precio. Arrancar con $15k total dividido en 3 creativos diferentes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="48" customHeight="1">
+      <c r="B284" s="49" t="inlineStr">
+        <is>
+          <t>Campaña Catálogo Ventas</t>
+        </is>
+      </c>
+      <c r="C284" s="50" t="inlineStr">
+        <is>
+          <t>🔴 ALERTA</t>
+        </is>
+      </c>
+      <c r="D284" s="51" t="inlineStr">
+        <is>
+          <t>Peor costo por compra del portafolio</t>
+        </is>
+      </c>
+      <c r="H284" s="52" t="inlineStr">
+        <is>
+          <t>Costo $42.987/compra está 2.388% sobre límite pausable ($18k). ROAS 0.44 significa pérdida de 56% del gasto. Hold Rate 0.3% indica rechazo inmediato. Generó solo 6 compras con $258k de inversión.</t>
+        </is>
+      </c>
+      <c r="M284" s="53" t="inlineStr">
+        <is>
+          <t>Pausar toda la campaña esta semana. Analizar si catálogo tiene productos de ticket alto que justifiquen este costo (dato no visible) antes de reactivar con creativos manuales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="48" customHeight="1">
+      <c r="B285" s="54" t="inlineStr"/>
+      <c r="C285" s="59" t="inlineStr">
+        <is>
+          <t>🔵 INSIGHT</t>
+        </is>
+      </c>
+      <c r="D285" s="60" t="inlineStr">
+        <is>
+          <t>Catálogo automático no funciona para GoHair</t>
+        </is>
+      </c>
+      <c r="H285" s="61" t="inlineStr">
+        <is>
+          <t>CTR 1.65% es aceptable pero Hold Rate 0.3% confirma que formato catálogo no engancha audiencia de GoHair. Campaña nueva (0 resultados mes anterior) sin optimización de píxel suficiente para catálogo automático.</t>
+        </is>
+      </c>
+      <c r="M285" s="62" t="inlineStr">
+        <is>
+          <t>Si se reactiva: seleccionar manualmente 3-5 productos con mejor margen del catálogo y crear anuncios individuales con video/UGC, no usar formato catálogo automático.</t>
+        </is>
+      </c>
+    </row>
+    <row r="286" ht="48" customHeight="1">
+      <c r="B286" s="49" t="inlineStr">
+        <is>
+          <t>Campaña de Conversión de Venta</t>
+        </is>
+      </c>
+      <c r="C286" s="50" t="inlineStr">
+        <is>
+          <t>🔴 ALERTA</t>
+        </is>
+      </c>
+      <c r="D286" s="51" t="inlineStr">
+        <is>
+          <t>5 de 6 anuncios sobre benchmark</t>
+        </is>
+      </c>
+      <c r="H286" s="52" t="inlineStr">
+        <is>
+          <t>Protector térmico carrusel ($501/click), Rutina capilar ($431/click), Acondicionador y Shampoo ($376/click), Aceite Capilar ($299/click) y reel protector de calor ($2.208/click) están entre 650%-5.420% sobre límite pausable de $40/click.</t>
+        </is>
+      </c>
+      <c r="M286" s="53" t="inlineStr">
+        <is>
+          <t>Pausar reel protector de calor ($2.208/click), Protector térmico carrusel y Rutina capilar esta semana. Mantener solo Aceite Capilar foto (única compra, ROAS 3.12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="48" customHeight="1">
+      <c r="B287" s="54" t="inlineStr"/>
+      <c r="C287" s="55" t="inlineStr">
+        <is>
+          <t>🟢 OPORTUNIDAD</t>
+        </is>
+      </c>
+      <c r="D287" s="56" t="inlineStr">
+        <is>
+          <t>Aceite Capilar foto único rentable</t>
+        </is>
+      </c>
+      <c r="H287" s="57" t="inlineStr">
+        <is>
+          <t>ROAS 3.12 con costo $8.157/compra (54% bajo límite pausable). Formato estático funciona mejor que video en esta campaña. CTR 0.98% y Hold Rate 0.7% bajos pero convierte.</t>
+        </is>
+      </c>
+      <c r="M287" s="58" t="inlineStr">
+        <is>
+          <t>Crear 2 variaciones de foto del Aceite Capilar: una con testimonial cliente y otra con beneficio principal en texto overlay. Testear esta semana con $5k cada una.</t>
+        </is>
+      </c>
+    </row>
+    <row r="288" ht="48" customHeight="1">
+      <c r="B288" s="54" t="inlineStr"/>
+      <c r="C288" s="59" t="inlineStr">
+        <is>
+          <t>🔵 INSIGHT</t>
+        </is>
+      </c>
+      <c r="D288" s="60" t="inlineStr">
+        <is>
+          <t>Formato carrusel no convierte en GoHair</t>
+        </is>
+      </c>
+      <c r="H288" s="61" t="inlineStr">
+        <is>
+          <t>Protector térmico carrusel ($501/click, Hold Rate 2.8%) y aceite carrusel en otra campaña tienen alto costo comparado con formatos reel o foto. Pattern consistente en 2 campañas diferentes indica problema de formato.</t>
+        </is>
+      </c>
+      <c r="M288" s="62" t="inlineStr">
+        <is>
+          <t>Evitar formato carrusel en futuras campañas de GoHair. Priorizar video corto (bajo 15 seg) o foto estática con copy fuerte en todas las nuevas creatividades.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="51">
+  <mergeCells count="210">
+    <mergeCell ref="B186:T186"/>
+    <mergeCell ref="M130:T130"/>
+    <mergeCell ref="H227:L227"/>
+    <mergeCell ref="M68:T68"/>
+    <mergeCell ref="D130:G130"/>
+    <mergeCell ref="D68:G68"/>
+    <mergeCell ref="D82:G82"/>
+    <mergeCell ref="D231:G231"/>
+    <mergeCell ref="M123:T123"/>
+    <mergeCell ref="B133:T133"/>
+    <mergeCell ref="M276:T276"/>
+    <mergeCell ref="D123:G123"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="B80:T80"/>
+    <mergeCell ref="H130:L130"/>
+    <mergeCell ref="H68:L68"/>
+    <mergeCell ref="H83:L83"/>
+    <mergeCell ref="D59:G59"/>
+    <mergeCell ref="B265:T265"/>
+    <mergeCell ref="D60:G60"/>
+    <mergeCell ref="B79:T79"/>
+    <mergeCell ref="M278:T278"/>
+    <mergeCell ref="B109:E109"/>
+    <mergeCell ref="M287:T287"/>
+    <mergeCell ref="M84:T84"/>
+    <mergeCell ref="D84:G84"/>
+    <mergeCell ref="B7:T7"/>
+    <mergeCell ref="B72:T72"/>
+    <mergeCell ref="B134:T134"/>
+    <mergeCell ref="H285:L285"/>
+    <mergeCell ref="B121:T121"/>
+    <mergeCell ref="D229:G229"/>
+    <mergeCell ref="H287:L287"/>
+    <mergeCell ref="D281:G281"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="M286:T286"/>
+    <mergeCell ref="B56:T56"/>
+    <mergeCell ref="B71:T71"/>
+    <mergeCell ref="B263:E263"/>
+    <mergeCell ref="H66:L66"/>
+    <mergeCell ref="M282:T282"/>
+    <mergeCell ref="B111:T111"/>
+    <mergeCell ref="B120:T120"/>
+    <mergeCell ref="M57:T57"/>
+    <mergeCell ref="B8:T8"/>
+    <mergeCell ref="H288:L288"/>
+    <mergeCell ref="B88:T88"/>
+    <mergeCell ref="D283:G283"/>
+    <mergeCell ref="M122:T122"/>
+    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="D122:G122"/>
+    <mergeCell ref="H224:L224"/>
+    <mergeCell ref="D127:G127"/>
     <mergeCell ref="M58:T58"/>
-    <mergeCell ref="H67:L67"/>
+    <mergeCell ref="M285:T285"/>
     <mergeCell ref="D58:G58"/>
-    <mergeCell ref="H63:L63"/>
-    <mergeCell ref="M68:T68"/>
-    <mergeCell ref="M59:T59"/>
-    <mergeCell ref="D68:G68"/>
+    <mergeCell ref="D285:G285"/>
     <mergeCell ref="D64:G64"/>
-    <mergeCell ref="M67:T67"/>
-    <mergeCell ref="D67:G67"/>
-    <mergeCell ref="B55:T55"/>
+    <mergeCell ref="B104:E104"/>
+    <mergeCell ref="H122:L122"/>
+    <mergeCell ref="M226:T226"/>
+    <mergeCell ref="D226:G226"/>
+    <mergeCell ref="B239:T239"/>
     <mergeCell ref="H58:L58"/>
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="M64:T64"/>
-    <mergeCell ref="H68:L68"/>
-    <mergeCell ref="D59:G59"/>
-    <mergeCell ref="H59:L59"/>
-    <mergeCell ref="M60:T60"/>
-    <mergeCell ref="D60:G60"/>
+    <mergeCell ref="B114:E114"/>
+    <mergeCell ref="D227:G227"/>
+    <mergeCell ref="M228:T228"/>
+    <mergeCell ref="H226:L226"/>
+    <mergeCell ref="D228:G228"/>
     <mergeCell ref="B16:E16"/>
-    <mergeCell ref="H64:L64"/>
+    <mergeCell ref="B138:E138"/>
     <mergeCell ref="H60:L60"/>
-    <mergeCell ref="D63:G63"/>
+    <mergeCell ref="D286:G286"/>
+    <mergeCell ref="M277:T277"/>
+    <mergeCell ref="H123:L123"/>
     <mergeCell ref="B47:T47"/>
-    <mergeCell ref="H61:L61"/>
-    <mergeCell ref="B7:T7"/>
-    <mergeCell ref="M65:T65"/>
-    <mergeCell ref="D65:G65"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="B18:T18"/>
-    <mergeCell ref="B56:T56"/>
+    <mergeCell ref="H228:L228"/>
+    <mergeCell ref="M227:T227"/>
+    <mergeCell ref="B247:E247"/>
+    <mergeCell ref="M223:T223"/>
+    <mergeCell ref="H278:L278"/>
+    <mergeCell ref="M124:T124"/>
+    <mergeCell ref="B77:E77"/>
     <mergeCell ref="B11:E11"/>
-    <mergeCell ref="H66:L66"/>
-    <mergeCell ref="D57:G57"/>
+    <mergeCell ref="D124:G124"/>
+    <mergeCell ref="B253:E253"/>
     <mergeCell ref="H57:L57"/>
-    <mergeCell ref="H65:L65"/>
-    <mergeCell ref="B2:T2"/>
+    <mergeCell ref="B152:T152"/>
+    <mergeCell ref="H84:L84"/>
+    <mergeCell ref="D287:G287"/>
     <mergeCell ref="M61:T61"/>
-    <mergeCell ref="M57:T57"/>
+    <mergeCell ref="M126:T126"/>
+    <mergeCell ref="H229:L229"/>
     <mergeCell ref="D61:G61"/>
+    <mergeCell ref="H124:L124"/>
     <mergeCell ref="B53:E53"/>
     <mergeCell ref="B23:T23"/>
-    <mergeCell ref="B8:T8"/>
+    <mergeCell ref="D126:G126"/>
     <mergeCell ref="M62:T62"/>
+    <mergeCell ref="B274:T274"/>
+    <mergeCell ref="B13:T13"/>
+    <mergeCell ref="M125:T125"/>
+    <mergeCell ref="B249:T249"/>
+    <mergeCell ref="D125:G125"/>
+    <mergeCell ref="M230:T230"/>
+    <mergeCell ref="B87:T87"/>
+    <mergeCell ref="H126:L126"/>
+    <mergeCell ref="M224:T224"/>
+    <mergeCell ref="D230:G230"/>
+    <mergeCell ref="D235:G235"/>
+    <mergeCell ref="B118:E118"/>
+    <mergeCell ref="H67:L67"/>
+    <mergeCell ref="M127:T127"/>
+    <mergeCell ref="B255:T255"/>
+    <mergeCell ref="M280:T280"/>
+    <mergeCell ref="H125:L125"/>
+    <mergeCell ref="M232:T232"/>
+    <mergeCell ref="D232:G232"/>
+    <mergeCell ref="M59:T59"/>
+    <mergeCell ref="M229:T229"/>
+    <mergeCell ref="B192:T192"/>
+    <mergeCell ref="M129:T129"/>
+    <mergeCell ref="D129:G129"/>
+    <mergeCell ref="H127:L127"/>
+    <mergeCell ref="B222:T222"/>
+    <mergeCell ref="H280:L280"/>
+    <mergeCell ref="M64:T64"/>
+    <mergeCell ref="H59:L59"/>
+    <mergeCell ref="M82:T82"/>
+    <mergeCell ref="M60:T60"/>
+    <mergeCell ref="B221:T221"/>
+    <mergeCell ref="H64:L64"/>
+    <mergeCell ref="H282:L282"/>
+    <mergeCell ref="M128:T128"/>
+    <mergeCell ref="D63:G63"/>
+    <mergeCell ref="D128:G128"/>
+    <mergeCell ref="D81:G81"/>
+    <mergeCell ref="H61:L61"/>
+    <mergeCell ref="M65:T65"/>
+    <mergeCell ref="B184:E184"/>
+    <mergeCell ref="D65:G65"/>
+    <mergeCell ref="M283:T283"/>
+    <mergeCell ref="D276:G276"/>
+    <mergeCell ref="H81:L81"/>
+    <mergeCell ref="H283:L283"/>
+    <mergeCell ref="H277:L277"/>
+    <mergeCell ref="H65:L65"/>
+    <mergeCell ref="D278:G278"/>
+    <mergeCell ref="D234:G234"/>
     <mergeCell ref="D66:G66"/>
+    <mergeCell ref="M284:T284"/>
+    <mergeCell ref="M231:T231"/>
+    <mergeCell ref="D284:G284"/>
+    <mergeCell ref="B1:T1"/>
+    <mergeCell ref="M63:T63"/>
+    <mergeCell ref="H82:L82"/>
+    <mergeCell ref="H284:L284"/>
+    <mergeCell ref="H231:L231"/>
+    <mergeCell ref="M83:T83"/>
+    <mergeCell ref="D83:G83"/>
+    <mergeCell ref="H63:L63"/>
+    <mergeCell ref="M279:T279"/>
+    <mergeCell ref="D223:G223"/>
+    <mergeCell ref="M67:T67"/>
+    <mergeCell ref="D279:G279"/>
+    <mergeCell ref="D67:G67"/>
+    <mergeCell ref="H230:L230"/>
+    <mergeCell ref="B55:T55"/>
+    <mergeCell ref="H286:L286"/>
+    <mergeCell ref="B275:T275"/>
+    <mergeCell ref="H276:L276"/>
+    <mergeCell ref="M281:T281"/>
+    <mergeCell ref="H223:L223"/>
+    <mergeCell ref="H279:L279"/>
+    <mergeCell ref="H232:L232"/>
+    <mergeCell ref="D280:G280"/>
+    <mergeCell ref="B106:T106"/>
+    <mergeCell ref="B150:E150"/>
+    <mergeCell ref="H129:L129"/>
+    <mergeCell ref="B190:E190"/>
+    <mergeCell ref="H281:L281"/>
+    <mergeCell ref="M233:T233"/>
+    <mergeCell ref="B261:T261"/>
+    <mergeCell ref="D233:G233"/>
+    <mergeCell ref="D282:G282"/>
+    <mergeCell ref="M81:T81"/>
+    <mergeCell ref="B272:E272"/>
+    <mergeCell ref="B219:E219"/>
+    <mergeCell ref="B18:T18"/>
+    <mergeCell ref="B140:T140"/>
+    <mergeCell ref="H128:L128"/>
+    <mergeCell ref="B259:E259"/>
+    <mergeCell ref="M235:T235"/>
+    <mergeCell ref="B238:T238"/>
+    <mergeCell ref="D57:G57"/>
+    <mergeCell ref="H233:L233"/>
+    <mergeCell ref="D288:G288"/>
+    <mergeCell ref="M288:T288"/>
+    <mergeCell ref="B2:T2"/>
+    <mergeCell ref="M225:T225"/>
+    <mergeCell ref="D225:G225"/>
+    <mergeCell ref="M234:T234"/>
+    <mergeCell ref="D277:G277"/>
+    <mergeCell ref="H235:L235"/>
     <mergeCell ref="H62:L62"/>
-    <mergeCell ref="B1:T1"/>
-    <mergeCell ref="B13:T13"/>
-    <mergeCell ref="M63:T63"/>
+    <mergeCell ref="H225:L225"/>
     <mergeCell ref="M66:T66"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="H234:L234"/>
+    <mergeCell ref="B116:T116"/>
+    <mergeCell ref="D224:G224"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
